--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3210" uniqueCount="450">
   <si>
     <t>Group</t>
   </si>
@@ -1355,6 +1355,21 @@
   <si>
     <t>Darcy Hull</t>
   </si>
+  <si>
+    <t>Waringstown Women 1st XI v CSNI Women 1st XI, The Lawn - 19 July 2026</t>
+  </si>
+  <si>
+    <t>Anna Megarrell</t>
+  </si>
+  <si>
+    <t>Ellen Taylor Skilling</t>
+  </si>
+  <si>
+    <t>32*</t>
+  </si>
+  <si>
+    <t>Holywood Women 1st XI v Instonians Women 1st XI, Stormont - 19 July 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -2160,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1412"/>
+  <dimension ref="A1:T1456"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -84707,6 +84722,2575 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1413" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1413" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1413">
+        <v>1</v>
+      </c>
+      <c r="D1413">
+        <v>0</v>
+      </c>
+      <c r="E1413">
+        <v>0</v>
+      </c>
+      <c r="F1413">
+        <v>0</v>
+      </c>
+      <c r="I1413">
+        <v>0</v>
+      </c>
+      <c r="J1413">
+        <v>0</v>
+      </c>
+      <c r="L1413">
+        <v>0</v>
+      </c>
+      <c r="M1413">
+        <v>0</v>
+      </c>
+      <c r="N1413">
+        <v>0</v>
+      </c>
+      <c r="O1413">
+        <v>0</v>
+      </c>
+      <c r="P1413">
+        <v>0</v>
+      </c>
+      <c r="Q1413">
+        <v>0</v>
+      </c>
+      <c r="R1413">
+        <v>0</v>
+      </c>
+      <c r="S1413">
+        <v>0</v>
+      </c>
+      <c r="T1413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1414" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1414">
+        <v>1</v>
+      </c>
+      <c r="D1414">
+        <v>1</v>
+      </c>
+      <c r="E1414">
+        <v>0</v>
+      </c>
+      <c r="F1414">
+        <v>5</v>
+      </c>
+      <c r="G1414">
+        <v>5</v>
+      </c>
+      <c r="H1414">
+        <v>5</v>
+      </c>
+      <c r="I1414">
+        <v>0</v>
+      </c>
+      <c r="J1414">
+        <v>0</v>
+      </c>
+      <c r="K1414">
+        <v>15.15</v>
+      </c>
+      <c r="L1414">
+        <v>33</v>
+      </c>
+      <c r="M1414">
+        <v>28</v>
+      </c>
+      <c r="N1414">
+        <v>0</v>
+      </c>
+      <c r="O1414">
+        <v>0</v>
+      </c>
+      <c r="P1414">
+        <v>4.5</v>
+      </c>
+      <c r="Q1414">
+        <v>0</v>
+      </c>
+      <c r="R1414">
+        <v>0</v>
+      </c>
+      <c r="S1414">
+        <v>0</v>
+      </c>
+      <c r="T1414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1415" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1415">
+        <v>1</v>
+      </c>
+      <c r="D1415">
+        <v>0</v>
+      </c>
+      <c r="E1415">
+        <v>0</v>
+      </c>
+      <c r="F1415">
+        <v>0</v>
+      </c>
+      <c r="I1415">
+        <v>0</v>
+      </c>
+      <c r="J1415">
+        <v>0</v>
+      </c>
+      <c r="L1415">
+        <v>0</v>
+      </c>
+      <c r="M1415">
+        <v>0</v>
+      </c>
+      <c r="N1415">
+        <v>0</v>
+      </c>
+      <c r="O1415">
+        <v>0</v>
+      </c>
+      <c r="P1415">
+        <v>0</v>
+      </c>
+      <c r="Q1415">
+        <v>0</v>
+      </c>
+      <c r="R1415">
+        <v>0</v>
+      </c>
+      <c r="S1415">
+        <v>0</v>
+      </c>
+      <c r="T1415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1416" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1416">
+        <v>1</v>
+      </c>
+      <c r="D1416">
+        <v>1</v>
+      </c>
+      <c r="E1416">
+        <v>0</v>
+      </c>
+      <c r="F1416">
+        <v>2</v>
+      </c>
+      <c r="G1416">
+        <v>2</v>
+      </c>
+      <c r="H1416">
+        <v>2</v>
+      </c>
+      <c r="I1416">
+        <v>0</v>
+      </c>
+      <c r="J1416">
+        <v>0</v>
+      </c>
+      <c r="K1416">
+        <v>33.33</v>
+      </c>
+      <c r="L1416">
+        <v>6</v>
+      </c>
+      <c r="M1416">
+        <v>4</v>
+      </c>
+      <c r="N1416">
+        <v>0</v>
+      </c>
+      <c r="O1416">
+        <v>0</v>
+      </c>
+      <c r="P1416">
+        <v>1.79</v>
+      </c>
+      <c r="Q1416">
+        <v>0</v>
+      </c>
+      <c r="R1416">
+        <v>0</v>
+      </c>
+      <c r="S1416">
+        <v>0</v>
+      </c>
+      <c r="T1416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1417" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1417">
+        <v>1</v>
+      </c>
+      <c r="D1417">
+        <v>0</v>
+      </c>
+      <c r="E1417">
+        <v>0</v>
+      </c>
+      <c r="F1417">
+        <v>0</v>
+      </c>
+      <c r="I1417">
+        <v>0</v>
+      </c>
+      <c r="J1417">
+        <v>0</v>
+      </c>
+      <c r="L1417">
+        <v>0</v>
+      </c>
+      <c r="M1417">
+        <v>0</v>
+      </c>
+      <c r="N1417">
+        <v>0</v>
+      </c>
+      <c r="O1417">
+        <v>0</v>
+      </c>
+      <c r="P1417">
+        <v>0</v>
+      </c>
+      <c r="Q1417">
+        <v>0</v>
+      </c>
+      <c r="R1417">
+        <v>0</v>
+      </c>
+      <c r="S1417">
+        <v>0</v>
+      </c>
+      <c r="T1417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1418" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1418">
+        <v>1</v>
+      </c>
+      <c r="D1418">
+        <v>0</v>
+      </c>
+      <c r="E1418">
+        <v>0</v>
+      </c>
+      <c r="F1418">
+        <v>0</v>
+      </c>
+      <c r="I1418">
+        <v>0</v>
+      </c>
+      <c r="J1418">
+        <v>0</v>
+      </c>
+      <c r="L1418">
+        <v>0</v>
+      </c>
+      <c r="M1418">
+        <v>0</v>
+      </c>
+      <c r="N1418">
+        <v>0</v>
+      </c>
+      <c r="O1418">
+        <v>0</v>
+      </c>
+      <c r="P1418">
+        <v>0</v>
+      </c>
+      <c r="Q1418">
+        <v>0</v>
+      </c>
+      <c r="R1418">
+        <v>0</v>
+      </c>
+      <c r="S1418">
+        <v>0</v>
+      </c>
+      <c r="T1418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1419" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1419">
+        <v>1</v>
+      </c>
+      <c r="D1419">
+        <v>0</v>
+      </c>
+      <c r="E1419">
+        <v>0</v>
+      </c>
+      <c r="F1419">
+        <v>0</v>
+      </c>
+      <c r="I1419">
+        <v>0</v>
+      </c>
+      <c r="J1419">
+        <v>0</v>
+      </c>
+      <c r="L1419">
+        <v>0</v>
+      </c>
+      <c r="M1419">
+        <v>0</v>
+      </c>
+      <c r="N1419">
+        <v>0</v>
+      </c>
+      <c r="O1419">
+        <v>0</v>
+      </c>
+      <c r="P1419">
+        <v>0</v>
+      </c>
+      <c r="Q1419">
+        <v>0</v>
+      </c>
+      <c r="R1419">
+        <v>0</v>
+      </c>
+      <c r="S1419">
+        <v>0</v>
+      </c>
+      <c r="T1419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1420" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1420">
+        <v>1</v>
+      </c>
+      <c r="D1420">
+        <v>0</v>
+      </c>
+      <c r="E1420">
+        <v>0</v>
+      </c>
+      <c r="F1420">
+        <v>0</v>
+      </c>
+      <c r="I1420">
+        <v>0</v>
+      </c>
+      <c r="J1420">
+        <v>0</v>
+      </c>
+      <c r="L1420">
+        <v>0</v>
+      </c>
+      <c r="M1420">
+        <v>0</v>
+      </c>
+      <c r="N1420">
+        <v>0</v>
+      </c>
+      <c r="O1420">
+        <v>0</v>
+      </c>
+      <c r="P1420">
+        <v>0</v>
+      </c>
+      <c r="Q1420">
+        <v>0</v>
+      </c>
+      <c r="R1420">
+        <v>0</v>
+      </c>
+      <c r="S1420">
+        <v>0</v>
+      </c>
+      <c r="T1420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1421" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1421">
+        <v>1</v>
+      </c>
+      <c r="D1421">
+        <v>0</v>
+      </c>
+      <c r="E1421">
+        <v>0</v>
+      </c>
+      <c r="F1421">
+        <v>0</v>
+      </c>
+      <c r="I1421">
+        <v>0</v>
+      </c>
+      <c r="J1421">
+        <v>0</v>
+      </c>
+      <c r="L1421">
+        <v>0</v>
+      </c>
+      <c r="M1421">
+        <v>0</v>
+      </c>
+      <c r="N1421">
+        <v>0</v>
+      </c>
+      <c r="O1421">
+        <v>0</v>
+      </c>
+      <c r="P1421">
+        <v>0</v>
+      </c>
+      <c r="Q1421">
+        <v>0</v>
+      </c>
+      <c r="R1421">
+        <v>0</v>
+      </c>
+      <c r="S1421">
+        <v>0</v>
+      </c>
+      <c r="T1421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1422" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1422">
+        <v>1</v>
+      </c>
+      <c r="D1422">
+        <v>1</v>
+      </c>
+      <c r="E1422">
+        <v>0</v>
+      </c>
+      <c r="F1422">
+        <v>43</v>
+      </c>
+      <c r="G1422">
+        <v>43</v>
+      </c>
+      <c r="H1422">
+        <v>43</v>
+      </c>
+      <c r="I1422">
+        <v>0</v>
+      </c>
+      <c r="J1422">
+        <v>0</v>
+      </c>
+      <c r="K1422">
+        <v>102.38</v>
+      </c>
+      <c r="L1422">
+        <v>42</v>
+      </c>
+      <c r="M1422">
+        <v>22</v>
+      </c>
+      <c r="N1422">
+        <v>6</v>
+      </c>
+      <c r="O1422">
+        <v>0</v>
+      </c>
+      <c r="P1422">
+        <v>38.39</v>
+      </c>
+      <c r="Q1422">
+        <v>0</v>
+      </c>
+      <c r="R1422">
+        <v>0</v>
+      </c>
+      <c r="S1422">
+        <v>0</v>
+      </c>
+      <c r="T1422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1423" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1423">
+        <v>1</v>
+      </c>
+      <c r="D1423">
+        <v>0</v>
+      </c>
+      <c r="E1423">
+        <v>0</v>
+      </c>
+      <c r="F1423">
+        <v>0</v>
+      </c>
+      <c r="I1423">
+        <v>0</v>
+      </c>
+      <c r="J1423">
+        <v>0</v>
+      </c>
+      <c r="L1423">
+        <v>0</v>
+      </c>
+      <c r="M1423">
+        <v>0</v>
+      </c>
+      <c r="N1423">
+        <v>0</v>
+      </c>
+      <c r="O1423">
+        <v>0</v>
+      </c>
+      <c r="P1423">
+        <v>0</v>
+      </c>
+      <c r="Q1423">
+        <v>0</v>
+      </c>
+      <c r="R1423">
+        <v>0</v>
+      </c>
+      <c r="S1423">
+        <v>0</v>
+      </c>
+      <c r="T1423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1424" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1424">
+        <v>1</v>
+      </c>
+      <c r="D1424">
+        <v>1</v>
+      </c>
+      <c r="E1424">
+        <v>1</v>
+      </c>
+      <c r="F1424">
+        <v>29</v>
+      </c>
+      <c r="H1424" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1424">
+        <v>0</v>
+      </c>
+      <c r="J1424">
+        <v>0</v>
+      </c>
+      <c r="K1424">
+        <v>87.88</v>
+      </c>
+      <c r="L1424">
+        <v>33</v>
+      </c>
+      <c r="M1424">
+        <v>11</v>
+      </c>
+      <c r="N1424">
+        <v>1</v>
+      </c>
+      <c r="O1424">
+        <v>0</v>
+      </c>
+      <c r="P1424">
+        <v>26.13</v>
+      </c>
+      <c r="Q1424">
+        <v>0</v>
+      </c>
+      <c r="R1424">
+        <v>0</v>
+      </c>
+      <c r="S1424">
+        <v>0</v>
+      </c>
+      <c r="T1424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1425" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1425">
+        <v>1</v>
+      </c>
+      <c r="D1425">
+        <v>1</v>
+      </c>
+      <c r="E1425">
+        <v>1</v>
+      </c>
+      <c r="F1425">
+        <v>21</v>
+      </c>
+      <c r="H1425" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1425">
+        <v>0</v>
+      </c>
+      <c r="J1425">
+        <v>0</v>
+      </c>
+      <c r="K1425">
+        <v>116.67</v>
+      </c>
+      <c r="L1425">
+        <v>18</v>
+      </c>
+      <c r="M1425">
+        <v>6</v>
+      </c>
+      <c r="N1425">
+        <v>2</v>
+      </c>
+      <c r="O1425">
+        <v>0</v>
+      </c>
+      <c r="P1425">
+        <v>18.920000000000002</v>
+      </c>
+      <c r="Q1425">
+        <v>0</v>
+      </c>
+      <c r="R1425">
+        <v>0</v>
+      </c>
+      <c r="S1425">
+        <v>0</v>
+      </c>
+      <c r="T1425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1426" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1426">
+        <v>1</v>
+      </c>
+      <c r="D1426">
+        <v>0</v>
+      </c>
+      <c r="E1426">
+        <v>0</v>
+      </c>
+      <c r="F1426">
+        <v>0</v>
+      </c>
+      <c r="I1426">
+        <v>0</v>
+      </c>
+      <c r="J1426">
+        <v>0</v>
+      </c>
+      <c r="L1426">
+        <v>0</v>
+      </c>
+      <c r="M1426">
+        <v>0</v>
+      </c>
+      <c r="N1426">
+        <v>0</v>
+      </c>
+      <c r="O1426">
+        <v>0</v>
+      </c>
+      <c r="P1426">
+        <v>0</v>
+      </c>
+      <c r="Q1426">
+        <v>0</v>
+      </c>
+      <c r="R1426">
+        <v>0</v>
+      </c>
+      <c r="S1426">
+        <v>0</v>
+      </c>
+      <c r="T1426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1427" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1427">
+        <v>1</v>
+      </c>
+      <c r="D1427">
+        <v>0</v>
+      </c>
+      <c r="E1427">
+        <v>0</v>
+      </c>
+      <c r="F1427">
+        <v>0</v>
+      </c>
+      <c r="I1427">
+        <v>0</v>
+      </c>
+      <c r="J1427">
+        <v>0</v>
+      </c>
+      <c r="L1427">
+        <v>0</v>
+      </c>
+      <c r="M1427">
+        <v>0</v>
+      </c>
+      <c r="N1427">
+        <v>0</v>
+      </c>
+      <c r="O1427">
+        <v>0</v>
+      </c>
+      <c r="P1427">
+        <v>0</v>
+      </c>
+      <c r="Q1427">
+        <v>0</v>
+      </c>
+      <c r="R1427">
+        <v>0</v>
+      </c>
+      <c r="S1427">
+        <v>0</v>
+      </c>
+      <c r="T1427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1428" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1428">
+        <v>1</v>
+      </c>
+      <c r="D1428">
+        <v>1</v>
+      </c>
+      <c r="E1428">
+        <v>0</v>
+      </c>
+      <c r="F1428">
+        <v>11</v>
+      </c>
+      <c r="G1428">
+        <v>11</v>
+      </c>
+      <c r="H1428">
+        <v>11</v>
+      </c>
+      <c r="I1428">
+        <v>0</v>
+      </c>
+      <c r="J1428">
+        <v>0</v>
+      </c>
+      <c r="K1428">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="L1428">
+        <v>17</v>
+      </c>
+      <c r="M1428">
+        <v>10</v>
+      </c>
+      <c r="N1428">
+        <v>0</v>
+      </c>
+      <c r="O1428">
+        <v>0</v>
+      </c>
+      <c r="P1428">
+        <v>9.91</v>
+      </c>
+      <c r="Q1428">
+        <v>1</v>
+      </c>
+      <c r="R1428">
+        <v>0</v>
+      </c>
+      <c r="S1428">
+        <v>0</v>
+      </c>
+      <c r="T1428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1429" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1429">
+        <v>1</v>
+      </c>
+      <c r="D1429">
+        <v>0</v>
+      </c>
+      <c r="E1429">
+        <v>0</v>
+      </c>
+      <c r="F1429">
+        <v>0</v>
+      </c>
+      <c r="I1429">
+        <v>0</v>
+      </c>
+      <c r="J1429">
+        <v>0</v>
+      </c>
+      <c r="L1429">
+        <v>0</v>
+      </c>
+      <c r="M1429">
+        <v>0</v>
+      </c>
+      <c r="N1429">
+        <v>0</v>
+      </c>
+      <c r="O1429">
+        <v>0</v>
+      </c>
+      <c r="P1429">
+        <v>0</v>
+      </c>
+      <c r="Q1429">
+        <v>0</v>
+      </c>
+      <c r="R1429">
+        <v>0</v>
+      </c>
+      <c r="S1429">
+        <v>0</v>
+      </c>
+      <c r="T1429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1430" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>447</v>
+      </c>
+      <c r="C1430">
+        <v>1</v>
+      </c>
+      <c r="D1430">
+        <v>0</v>
+      </c>
+      <c r="E1430">
+        <v>0</v>
+      </c>
+      <c r="F1430">
+        <v>0</v>
+      </c>
+      <c r="I1430">
+        <v>0</v>
+      </c>
+      <c r="J1430">
+        <v>0</v>
+      </c>
+      <c r="L1430">
+        <v>0</v>
+      </c>
+      <c r="M1430">
+        <v>0</v>
+      </c>
+      <c r="N1430">
+        <v>0</v>
+      </c>
+      <c r="O1430">
+        <v>0</v>
+      </c>
+      <c r="P1430">
+        <v>0</v>
+      </c>
+      <c r="Q1430">
+        <v>0</v>
+      </c>
+      <c r="R1430">
+        <v>0</v>
+      </c>
+      <c r="S1430">
+        <v>0</v>
+      </c>
+      <c r="T1430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1431" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1431">
+        <v>1</v>
+      </c>
+      <c r="D1431">
+        <v>1</v>
+      </c>
+      <c r="E1431">
+        <v>0</v>
+      </c>
+      <c r="F1431">
+        <v>19</v>
+      </c>
+      <c r="G1431">
+        <v>19</v>
+      </c>
+      <c r="H1431">
+        <v>19</v>
+      </c>
+      <c r="I1431">
+        <v>0</v>
+      </c>
+      <c r="J1431">
+        <v>0</v>
+      </c>
+      <c r="K1431">
+        <v>90.48</v>
+      </c>
+      <c r="L1431">
+        <v>21</v>
+      </c>
+      <c r="M1431">
+        <v>13</v>
+      </c>
+      <c r="N1431">
+        <v>3</v>
+      </c>
+      <c r="O1431">
+        <v>0</v>
+      </c>
+      <c r="P1431">
+        <v>17.12</v>
+      </c>
+      <c r="Q1431">
+        <v>0</v>
+      </c>
+      <c r="R1431">
+        <v>0</v>
+      </c>
+      <c r="S1431">
+        <v>0</v>
+      </c>
+      <c r="T1431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1432" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1432">
+        <v>1</v>
+      </c>
+      <c r="D1432">
+        <v>1</v>
+      </c>
+      <c r="E1432">
+        <v>0</v>
+      </c>
+      <c r="F1432">
+        <v>13</v>
+      </c>
+      <c r="G1432">
+        <v>13</v>
+      </c>
+      <c r="H1432">
+        <v>13</v>
+      </c>
+      <c r="I1432">
+        <v>0</v>
+      </c>
+      <c r="J1432">
+        <v>0</v>
+      </c>
+      <c r="K1432">
+        <v>65</v>
+      </c>
+      <c r="L1432">
+        <v>20</v>
+      </c>
+      <c r="M1432">
+        <v>11</v>
+      </c>
+      <c r="N1432">
+        <v>1</v>
+      </c>
+      <c r="O1432">
+        <v>0</v>
+      </c>
+      <c r="P1432">
+        <v>11.61</v>
+      </c>
+      <c r="Q1432">
+        <v>0</v>
+      </c>
+      <c r="R1432">
+        <v>0</v>
+      </c>
+      <c r="S1432">
+        <v>0</v>
+      </c>
+      <c r="T1432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1433" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1433">
+        <v>1</v>
+      </c>
+      <c r="D1433">
+        <v>1</v>
+      </c>
+      <c r="E1433">
+        <v>1</v>
+      </c>
+      <c r="F1433">
+        <v>32</v>
+      </c>
+      <c r="H1433" t="s">
+        <v>448</v>
+      </c>
+      <c r="I1433">
+        <v>0</v>
+      </c>
+      <c r="J1433">
+        <v>0</v>
+      </c>
+      <c r="K1433">
+        <v>80</v>
+      </c>
+      <c r="L1433">
+        <v>40</v>
+      </c>
+      <c r="M1433">
+        <v>20</v>
+      </c>
+      <c r="N1433">
+        <v>3</v>
+      </c>
+      <c r="O1433">
+        <v>0</v>
+      </c>
+      <c r="P1433">
+        <v>28.57</v>
+      </c>
+      <c r="Q1433">
+        <v>0</v>
+      </c>
+      <c r="R1433">
+        <v>0</v>
+      </c>
+      <c r="S1433">
+        <v>0</v>
+      </c>
+      <c r="T1433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1434" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1434">
+        <v>1</v>
+      </c>
+      <c r="D1434">
+        <v>1</v>
+      </c>
+      <c r="E1434">
+        <v>1</v>
+      </c>
+      <c r="F1434">
+        <v>10</v>
+      </c>
+      <c r="H1434" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1434">
+        <v>0</v>
+      </c>
+      <c r="J1434">
+        <v>0</v>
+      </c>
+      <c r="K1434">
+        <v>111.11</v>
+      </c>
+      <c r="L1434">
+        <v>9</v>
+      </c>
+      <c r="M1434">
+        <v>3</v>
+      </c>
+      <c r="N1434">
+        <v>1</v>
+      </c>
+      <c r="O1434">
+        <v>0</v>
+      </c>
+      <c r="P1434">
+        <v>8.93</v>
+      </c>
+      <c r="Q1434">
+        <v>0</v>
+      </c>
+      <c r="R1434">
+        <v>0</v>
+      </c>
+      <c r="S1434">
+        <v>0</v>
+      </c>
+      <c r="T1434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1435" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1435">
+        <v>1</v>
+      </c>
+      <c r="D1435">
+        <v>1</v>
+      </c>
+      <c r="E1435">
+        <v>0</v>
+      </c>
+      <c r="F1435">
+        <v>0</v>
+      </c>
+      <c r="G1435">
+        <v>0</v>
+      </c>
+      <c r="H1435">
+        <v>0</v>
+      </c>
+      <c r="I1435">
+        <v>0</v>
+      </c>
+      <c r="J1435">
+        <v>0</v>
+      </c>
+      <c r="K1435">
+        <v>0</v>
+      </c>
+      <c r="L1435">
+        <v>5</v>
+      </c>
+      <c r="M1435">
+        <v>5</v>
+      </c>
+      <c r="N1435">
+        <v>0</v>
+      </c>
+      <c r="O1435">
+        <v>0</v>
+      </c>
+      <c r="P1435">
+        <v>0</v>
+      </c>
+      <c r="Q1435">
+        <v>0</v>
+      </c>
+      <c r="R1435">
+        <v>0</v>
+      </c>
+      <c r="S1435">
+        <v>0</v>
+      </c>
+      <c r="T1435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1436" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1436">
+        <v>1</v>
+      </c>
+      <c r="D1436">
+        <v>1</v>
+      </c>
+      <c r="E1436">
+        <v>0</v>
+      </c>
+      <c r="F1436">
+        <v>12</v>
+      </c>
+      <c r="G1436">
+        <v>12</v>
+      </c>
+      <c r="H1436">
+        <v>12</v>
+      </c>
+      <c r="I1436">
+        <v>0</v>
+      </c>
+      <c r="J1436">
+        <v>0</v>
+      </c>
+      <c r="K1436">
+        <v>60</v>
+      </c>
+      <c r="L1436">
+        <v>20</v>
+      </c>
+      <c r="M1436">
+        <v>14</v>
+      </c>
+      <c r="N1436">
+        <v>2</v>
+      </c>
+      <c r="O1436">
+        <v>0</v>
+      </c>
+      <c r="P1436">
+        <v>4.04</v>
+      </c>
+      <c r="Q1436">
+        <v>0</v>
+      </c>
+      <c r="R1436">
+        <v>0</v>
+      </c>
+      <c r="S1436">
+        <v>0</v>
+      </c>
+      <c r="T1436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1437" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1437">
+        <v>1</v>
+      </c>
+      <c r="D1437">
+        <v>0</v>
+      </c>
+      <c r="E1437">
+        <v>0</v>
+      </c>
+      <c r="F1437">
+        <v>0</v>
+      </c>
+      <c r="I1437">
+        <v>0</v>
+      </c>
+      <c r="J1437">
+        <v>0</v>
+      </c>
+      <c r="L1437">
+        <v>0</v>
+      </c>
+      <c r="M1437">
+        <v>0</v>
+      </c>
+      <c r="N1437">
+        <v>0</v>
+      </c>
+      <c r="O1437">
+        <v>0</v>
+      </c>
+      <c r="P1437">
+        <v>0</v>
+      </c>
+      <c r="Q1437">
+        <v>0</v>
+      </c>
+      <c r="R1437">
+        <v>0</v>
+      </c>
+      <c r="S1437">
+        <v>0</v>
+      </c>
+      <c r="T1437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1438" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1438">
+        <v>1</v>
+      </c>
+      <c r="D1438">
+        <v>1</v>
+      </c>
+      <c r="E1438">
+        <v>1</v>
+      </c>
+      <c r="F1438">
+        <v>1</v>
+      </c>
+      <c r="H1438" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1438">
+        <v>0</v>
+      </c>
+      <c r="J1438">
+        <v>0</v>
+      </c>
+      <c r="K1438">
+        <v>100</v>
+      </c>
+      <c r="L1438">
+        <v>1</v>
+      </c>
+      <c r="M1438">
+        <v>0</v>
+      </c>
+      <c r="N1438">
+        <v>0</v>
+      </c>
+      <c r="O1438">
+        <v>0</v>
+      </c>
+      <c r="P1438">
+        <v>0.34</v>
+      </c>
+      <c r="Q1438">
+        <v>0</v>
+      </c>
+      <c r="R1438">
+        <v>0</v>
+      </c>
+      <c r="S1438">
+        <v>0</v>
+      </c>
+      <c r="T1438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1439" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1439">
+        <v>1</v>
+      </c>
+      <c r="D1439">
+        <v>0</v>
+      </c>
+      <c r="E1439">
+        <v>0</v>
+      </c>
+      <c r="F1439">
+        <v>0</v>
+      </c>
+      <c r="I1439">
+        <v>0</v>
+      </c>
+      <c r="J1439">
+        <v>0</v>
+      </c>
+      <c r="L1439">
+        <v>0</v>
+      </c>
+      <c r="M1439">
+        <v>0</v>
+      </c>
+      <c r="N1439">
+        <v>0</v>
+      </c>
+      <c r="O1439">
+        <v>0</v>
+      </c>
+      <c r="P1439">
+        <v>0</v>
+      </c>
+      <c r="Q1439">
+        <v>3</v>
+      </c>
+      <c r="R1439">
+        <v>0</v>
+      </c>
+      <c r="S1439">
+        <v>0</v>
+      </c>
+      <c r="T1439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1440" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>295</v>
+      </c>
+      <c r="C1440">
+        <v>1</v>
+      </c>
+      <c r="D1440">
+        <v>1</v>
+      </c>
+      <c r="E1440">
+        <v>0</v>
+      </c>
+      <c r="F1440">
+        <v>17</v>
+      </c>
+      <c r="G1440">
+        <v>17</v>
+      </c>
+      <c r="H1440">
+        <v>17</v>
+      </c>
+      <c r="I1440">
+        <v>0</v>
+      </c>
+      <c r="J1440">
+        <v>0</v>
+      </c>
+      <c r="K1440">
+        <v>77.27</v>
+      </c>
+      <c r="L1440">
+        <v>22</v>
+      </c>
+      <c r="M1440">
+        <v>13</v>
+      </c>
+      <c r="N1440">
+        <v>1</v>
+      </c>
+      <c r="O1440">
+        <v>0</v>
+      </c>
+      <c r="P1440">
+        <v>32.08</v>
+      </c>
+      <c r="Q1440">
+        <v>0</v>
+      </c>
+      <c r="R1440">
+        <v>0</v>
+      </c>
+      <c r="S1440">
+        <v>0</v>
+      </c>
+      <c r="T1440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1441" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1441">
+        <v>1</v>
+      </c>
+      <c r="D1441">
+        <v>1</v>
+      </c>
+      <c r="E1441">
+        <v>1</v>
+      </c>
+      <c r="F1441">
+        <v>19</v>
+      </c>
+      <c r="H1441" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1441">
+        <v>0</v>
+      </c>
+      <c r="J1441">
+        <v>0</v>
+      </c>
+      <c r="K1441">
+        <v>90.48</v>
+      </c>
+      <c r="L1441">
+        <v>21</v>
+      </c>
+      <c r="M1441">
+        <v>11</v>
+      </c>
+      <c r="N1441">
+        <v>2</v>
+      </c>
+      <c r="O1441">
+        <v>0</v>
+      </c>
+      <c r="P1441">
+        <v>6.4</v>
+      </c>
+      <c r="Q1441">
+        <v>0</v>
+      </c>
+      <c r="R1441">
+        <v>0</v>
+      </c>
+      <c r="S1441">
+        <v>0</v>
+      </c>
+      <c r="T1441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1442" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1442">
+        <v>1</v>
+      </c>
+      <c r="D1442">
+        <v>1</v>
+      </c>
+      <c r="E1442">
+        <v>0</v>
+      </c>
+      <c r="F1442">
+        <v>0</v>
+      </c>
+      <c r="G1442">
+        <v>0</v>
+      </c>
+      <c r="H1442">
+        <v>0</v>
+      </c>
+      <c r="I1442">
+        <v>0</v>
+      </c>
+      <c r="J1442">
+        <v>0</v>
+      </c>
+      <c r="L1442">
+        <v>0</v>
+      </c>
+      <c r="M1442">
+        <v>0</v>
+      </c>
+      <c r="N1442">
+        <v>0</v>
+      </c>
+      <c r="O1442">
+        <v>0</v>
+      </c>
+      <c r="P1442">
+        <v>0</v>
+      </c>
+      <c r="Q1442">
+        <v>0</v>
+      </c>
+      <c r="R1442">
+        <v>0</v>
+      </c>
+      <c r="S1442">
+        <v>0</v>
+      </c>
+      <c r="T1442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1443" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1443">
+        <v>1</v>
+      </c>
+      <c r="D1443">
+        <v>1</v>
+      </c>
+      <c r="E1443">
+        <v>0</v>
+      </c>
+      <c r="F1443">
+        <v>117</v>
+      </c>
+      <c r="G1443">
+        <v>117</v>
+      </c>
+      <c r="H1443">
+        <v>117</v>
+      </c>
+      <c r="I1443">
+        <v>0</v>
+      </c>
+      <c r="J1443">
+        <v>1</v>
+      </c>
+      <c r="K1443">
+        <v>185.71</v>
+      </c>
+      <c r="L1443">
+        <v>63</v>
+      </c>
+      <c r="M1443">
+        <v>23</v>
+      </c>
+      <c r="N1443">
+        <v>18</v>
+      </c>
+      <c r="O1443">
+        <v>4</v>
+      </c>
+      <c r="P1443">
+        <v>39.39</v>
+      </c>
+      <c r="Q1443">
+        <v>0</v>
+      </c>
+      <c r="R1443">
+        <v>0</v>
+      </c>
+      <c r="S1443">
+        <v>0</v>
+      </c>
+      <c r="T1443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1444" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1444">
+        <v>1</v>
+      </c>
+      <c r="D1444">
+        <v>1</v>
+      </c>
+      <c r="E1444">
+        <v>1</v>
+      </c>
+      <c r="F1444">
+        <v>0</v>
+      </c>
+      <c r="H1444" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1444">
+        <v>0</v>
+      </c>
+      <c r="J1444">
+        <v>0</v>
+      </c>
+      <c r="K1444">
+        <v>0</v>
+      </c>
+      <c r="L1444">
+        <v>2</v>
+      </c>
+      <c r="M1444">
+        <v>2</v>
+      </c>
+      <c r="N1444">
+        <v>0</v>
+      </c>
+      <c r="O1444">
+        <v>0</v>
+      </c>
+      <c r="P1444">
+        <v>0</v>
+      </c>
+      <c r="Q1444">
+        <v>0</v>
+      </c>
+      <c r="R1444">
+        <v>1</v>
+      </c>
+      <c r="S1444">
+        <v>0</v>
+      </c>
+      <c r="T1444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1445" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1445">
+        <v>1</v>
+      </c>
+      <c r="D1445">
+        <v>0</v>
+      </c>
+      <c r="E1445">
+        <v>0</v>
+      </c>
+      <c r="F1445">
+        <v>0</v>
+      </c>
+      <c r="I1445">
+        <v>0</v>
+      </c>
+      <c r="J1445">
+        <v>0</v>
+      </c>
+      <c r="L1445">
+        <v>0</v>
+      </c>
+      <c r="M1445">
+        <v>0</v>
+      </c>
+      <c r="N1445">
+        <v>0</v>
+      </c>
+      <c r="O1445">
+        <v>0</v>
+      </c>
+      <c r="P1445">
+        <v>0</v>
+      </c>
+      <c r="Q1445">
+        <v>0</v>
+      </c>
+      <c r="R1445">
+        <v>0</v>
+      </c>
+      <c r="S1445">
+        <v>0</v>
+      </c>
+      <c r="T1445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1446" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1446">
+        <v>1</v>
+      </c>
+      <c r="D1446">
+        <v>1</v>
+      </c>
+      <c r="E1446">
+        <v>0</v>
+      </c>
+      <c r="F1446">
+        <v>86</v>
+      </c>
+      <c r="G1446">
+        <v>86</v>
+      </c>
+      <c r="H1446">
+        <v>86</v>
+      </c>
+      <c r="I1446">
+        <v>1</v>
+      </c>
+      <c r="J1446">
+        <v>0</v>
+      </c>
+      <c r="K1446">
+        <v>150.88</v>
+      </c>
+      <c r="L1446">
+        <v>57</v>
+      </c>
+      <c r="M1446">
+        <v>26</v>
+      </c>
+      <c r="N1446">
+        <v>13</v>
+      </c>
+      <c r="O1446">
+        <v>2</v>
+      </c>
+      <c r="P1446">
+        <v>28.96</v>
+      </c>
+      <c r="Q1446">
+        <v>1</v>
+      </c>
+      <c r="R1446">
+        <v>0</v>
+      </c>
+      <c r="S1446">
+        <v>0</v>
+      </c>
+      <c r="T1446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1447" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1447">
+        <v>1</v>
+      </c>
+      <c r="D1447">
+        <v>1</v>
+      </c>
+      <c r="E1447">
+        <v>0</v>
+      </c>
+      <c r="F1447">
+        <v>0</v>
+      </c>
+      <c r="G1447">
+        <v>0</v>
+      </c>
+      <c r="H1447">
+        <v>0</v>
+      </c>
+      <c r="I1447">
+        <v>0</v>
+      </c>
+      <c r="J1447">
+        <v>0</v>
+      </c>
+      <c r="K1447">
+        <v>0</v>
+      </c>
+      <c r="L1447">
+        <v>2</v>
+      </c>
+      <c r="M1447">
+        <v>2</v>
+      </c>
+      <c r="N1447">
+        <v>0</v>
+      </c>
+      <c r="O1447">
+        <v>0</v>
+      </c>
+      <c r="P1447">
+        <v>0</v>
+      </c>
+      <c r="Q1447">
+        <v>0</v>
+      </c>
+      <c r="R1447">
+        <v>0</v>
+      </c>
+      <c r="S1447">
+        <v>0</v>
+      </c>
+      <c r="T1447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1448" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1448">
+        <v>1</v>
+      </c>
+      <c r="D1448">
+        <v>1</v>
+      </c>
+      <c r="E1448">
+        <v>0</v>
+      </c>
+      <c r="F1448">
+        <v>4</v>
+      </c>
+      <c r="G1448">
+        <v>4</v>
+      </c>
+      <c r="H1448">
+        <v>4</v>
+      </c>
+      <c r="I1448">
+        <v>0</v>
+      </c>
+      <c r="J1448">
+        <v>0</v>
+      </c>
+      <c r="K1448">
+        <v>50</v>
+      </c>
+      <c r="L1448">
+        <v>8</v>
+      </c>
+      <c r="M1448">
+        <v>5</v>
+      </c>
+      <c r="N1448">
+        <v>0</v>
+      </c>
+      <c r="O1448">
+        <v>0</v>
+      </c>
+      <c r="P1448">
+        <v>1.35</v>
+      </c>
+      <c r="Q1448">
+        <v>0</v>
+      </c>
+      <c r="R1448">
+        <v>0</v>
+      </c>
+      <c r="S1448">
+        <v>0</v>
+      </c>
+      <c r="T1448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1449" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1449">
+        <v>1</v>
+      </c>
+      <c r="D1449">
+        <v>1</v>
+      </c>
+      <c r="E1449">
+        <v>0</v>
+      </c>
+      <c r="F1449">
+        <v>6</v>
+      </c>
+      <c r="G1449">
+        <v>6</v>
+      </c>
+      <c r="H1449">
+        <v>6</v>
+      </c>
+      <c r="I1449">
+        <v>0</v>
+      </c>
+      <c r="J1449">
+        <v>0</v>
+      </c>
+      <c r="K1449">
+        <v>54.55</v>
+      </c>
+      <c r="L1449">
+        <v>11</v>
+      </c>
+      <c r="M1449">
+        <v>6</v>
+      </c>
+      <c r="N1449">
+        <v>0</v>
+      </c>
+      <c r="O1449">
+        <v>0</v>
+      </c>
+      <c r="P1449">
+        <v>11.32</v>
+      </c>
+      <c r="Q1449">
+        <v>1</v>
+      </c>
+      <c r="R1449">
+        <v>0</v>
+      </c>
+      <c r="S1449">
+        <v>0</v>
+      </c>
+      <c r="T1449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1450" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1450">
+        <v>1</v>
+      </c>
+      <c r="D1450">
+        <v>1</v>
+      </c>
+      <c r="E1450">
+        <v>0</v>
+      </c>
+      <c r="F1450">
+        <v>4</v>
+      </c>
+      <c r="G1450">
+        <v>4</v>
+      </c>
+      <c r="H1450">
+        <v>4</v>
+      </c>
+      <c r="I1450">
+        <v>0</v>
+      </c>
+      <c r="J1450">
+        <v>0</v>
+      </c>
+      <c r="K1450">
+        <v>44.44</v>
+      </c>
+      <c r="L1450">
+        <v>9</v>
+      </c>
+      <c r="M1450">
+        <v>8</v>
+      </c>
+      <c r="N1450">
+        <v>1</v>
+      </c>
+      <c r="O1450">
+        <v>0</v>
+      </c>
+      <c r="P1450">
+        <v>7.55</v>
+      </c>
+      <c r="Q1450">
+        <v>0</v>
+      </c>
+      <c r="R1450">
+        <v>0</v>
+      </c>
+      <c r="S1450">
+        <v>0</v>
+      </c>
+      <c r="T1450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1451" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1451">
+        <v>1</v>
+      </c>
+      <c r="D1451">
+        <v>1</v>
+      </c>
+      <c r="E1451">
+        <v>0</v>
+      </c>
+      <c r="F1451">
+        <v>0</v>
+      </c>
+      <c r="G1451">
+        <v>0</v>
+      </c>
+      <c r="H1451">
+        <v>0</v>
+      </c>
+      <c r="I1451">
+        <v>0</v>
+      </c>
+      <c r="J1451">
+        <v>0</v>
+      </c>
+      <c r="K1451">
+        <v>0</v>
+      </c>
+      <c r="L1451">
+        <v>2</v>
+      </c>
+      <c r="M1451">
+        <v>2</v>
+      </c>
+      <c r="N1451">
+        <v>0</v>
+      </c>
+      <c r="O1451">
+        <v>0</v>
+      </c>
+      <c r="P1451">
+        <v>0</v>
+      </c>
+      <c r="Q1451">
+        <v>0</v>
+      </c>
+      <c r="R1451">
+        <v>0</v>
+      </c>
+      <c r="S1451">
+        <v>0</v>
+      </c>
+      <c r="T1451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1452" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1452">
+        <v>1</v>
+      </c>
+      <c r="D1452">
+        <v>1</v>
+      </c>
+      <c r="E1452">
+        <v>0</v>
+      </c>
+      <c r="F1452">
+        <v>9</v>
+      </c>
+      <c r="G1452">
+        <v>9</v>
+      </c>
+      <c r="H1452">
+        <v>9</v>
+      </c>
+      <c r="I1452">
+        <v>0</v>
+      </c>
+      <c r="J1452">
+        <v>0</v>
+      </c>
+      <c r="K1452">
+        <v>90</v>
+      </c>
+      <c r="L1452">
+        <v>10</v>
+      </c>
+      <c r="M1452">
+        <v>5</v>
+      </c>
+      <c r="N1452">
+        <v>1</v>
+      </c>
+      <c r="O1452">
+        <v>0</v>
+      </c>
+      <c r="P1452">
+        <v>3.03</v>
+      </c>
+      <c r="Q1452">
+        <v>0</v>
+      </c>
+      <c r="R1452">
+        <v>2</v>
+      </c>
+      <c r="S1452">
+        <v>0</v>
+      </c>
+      <c r="T1452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1453" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1453">
+        <v>1</v>
+      </c>
+      <c r="D1453">
+        <v>1</v>
+      </c>
+      <c r="E1453">
+        <v>0</v>
+      </c>
+      <c r="F1453">
+        <v>0</v>
+      </c>
+      <c r="G1453">
+        <v>0</v>
+      </c>
+      <c r="H1453">
+        <v>0</v>
+      </c>
+      <c r="I1453">
+        <v>0</v>
+      </c>
+      <c r="J1453">
+        <v>0</v>
+      </c>
+      <c r="K1453">
+        <v>0</v>
+      </c>
+      <c r="L1453">
+        <v>1</v>
+      </c>
+      <c r="M1453">
+        <v>1</v>
+      </c>
+      <c r="N1453">
+        <v>0</v>
+      </c>
+      <c r="O1453">
+        <v>0</v>
+      </c>
+      <c r="P1453">
+        <v>0</v>
+      </c>
+      <c r="Q1453">
+        <v>1</v>
+      </c>
+      <c r="R1453">
+        <v>0</v>
+      </c>
+      <c r="S1453">
+        <v>0</v>
+      </c>
+      <c r="T1453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1454" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1454">
+        <v>1</v>
+      </c>
+      <c r="D1454">
+        <v>1</v>
+      </c>
+      <c r="E1454">
+        <v>0</v>
+      </c>
+      <c r="F1454">
+        <v>1</v>
+      </c>
+      <c r="G1454">
+        <v>1</v>
+      </c>
+      <c r="H1454">
+        <v>1</v>
+      </c>
+      <c r="I1454">
+        <v>0</v>
+      </c>
+      <c r="J1454">
+        <v>0</v>
+      </c>
+      <c r="K1454">
+        <v>25</v>
+      </c>
+      <c r="L1454">
+        <v>4</v>
+      </c>
+      <c r="M1454">
+        <v>3</v>
+      </c>
+      <c r="N1454">
+        <v>0</v>
+      </c>
+      <c r="O1454">
+        <v>0</v>
+      </c>
+      <c r="P1454">
+        <v>1.89</v>
+      </c>
+      <c r="Q1454">
+        <v>0</v>
+      </c>
+      <c r="R1454">
+        <v>0</v>
+      </c>
+      <c r="S1454">
+        <v>0</v>
+      </c>
+      <c r="T1454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1455" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1455">
+        <v>1</v>
+      </c>
+      <c r="D1455">
+        <v>1</v>
+      </c>
+      <c r="E1455">
+        <v>0</v>
+      </c>
+      <c r="F1455">
+        <v>7</v>
+      </c>
+      <c r="G1455">
+        <v>7</v>
+      </c>
+      <c r="H1455">
+        <v>7</v>
+      </c>
+      <c r="I1455">
+        <v>0</v>
+      </c>
+      <c r="J1455">
+        <v>0</v>
+      </c>
+      <c r="K1455">
+        <v>58.33</v>
+      </c>
+      <c r="L1455">
+        <v>12</v>
+      </c>
+      <c r="M1455">
+        <v>9</v>
+      </c>
+      <c r="N1455">
+        <v>1</v>
+      </c>
+      <c r="O1455">
+        <v>0</v>
+      </c>
+      <c r="P1455">
+        <v>13.21</v>
+      </c>
+      <c r="Q1455">
+        <v>0</v>
+      </c>
+      <c r="R1455">
+        <v>0</v>
+      </c>
+      <c r="S1455">
+        <v>0</v>
+      </c>
+      <c r="T1455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1456" t="s">
+        <v>449</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1456">
+        <v>1</v>
+      </c>
+      <c r="D1456">
+        <v>1</v>
+      </c>
+      <c r="E1456">
+        <v>0</v>
+      </c>
+      <c r="F1456">
+        <v>6</v>
+      </c>
+      <c r="G1456">
+        <v>6</v>
+      </c>
+      <c r="H1456">
+        <v>6</v>
+      </c>
+      <c r="I1456">
+        <v>0</v>
+      </c>
+      <c r="J1456">
+        <v>0</v>
+      </c>
+      <c r="K1456">
+        <v>100</v>
+      </c>
+      <c r="L1456">
+        <v>6</v>
+      </c>
+      <c r="M1456">
+        <v>4</v>
+      </c>
+      <c r="N1456">
+        <v>1</v>
+      </c>
+      <c r="O1456">
+        <v>0</v>
+      </c>
+      <c r="P1456">
+        <v>11.32</v>
+      </c>
+      <c r="Q1456">
+        <v>0</v>
+      </c>
+      <c r="R1456">
+        <v>0</v>
+      </c>
+      <c r="S1456">
+        <v>0</v>
+      </c>
+      <c r="T1456">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3210" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="465">
   <si>
     <t>Group</t>
   </si>
@@ -1370,6 +1370,51 @@
   <si>
     <t>Holywood Women 1st XI v Instonians Women 1st XI, Stormont - 19 July 2026</t>
   </si>
+  <si>
+    <t>Dundrum Women 1st XI v Waringstown Women 2nd XI, The Meadow - 20 July 2026</t>
+  </si>
+  <si>
+    <t>Holywood Women 2nd XI v North Down Women 2nd XI, Seapark Oval - 20 July 2026</t>
+  </si>
+  <si>
+    <t>Skye Eggleton</t>
+  </si>
+  <si>
+    <t>Rosa Kirk</t>
+  </si>
+  <si>
+    <t>Instonians Women 2nd XI v CSNI Women 2nd XI, Shaw's Bridge - 20 July 2026</t>
+  </si>
+  <si>
+    <t>Karen Kennedy</t>
+  </si>
+  <si>
+    <t>Lisburn Women 3rd XI v Drumaness Superkings Women 1st XI, TBC - 20 July 2026</t>
+  </si>
+  <si>
+    <t>Amy Branks</t>
+  </si>
+  <si>
+    <t>Ava Templeton</t>
+  </si>
+  <si>
+    <t>Emma Cunningham</t>
+  </si>
+  <si>
+    <t>Georgie Kennedy</t>
+  </si>
+  <si>
+    <t>Lauren Duguid</t>
+  </si>
+  <si>
+    <t>Lyla Cubitt</t>
+  </si>
+  <si>
+    <t>Olivia Boyd</t>
+  </si>
+  <si>
+    <t>Olivia Cunningham</t>
+  </si>
 </sst>
 </file>
 
@@ -1852,8 +1897,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2175,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1456"/>
+  <dimension ref="A1:T1544"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -87291,6 +87337,5177 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1457" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1457" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1457">
+        <v>1</v>
+      </c>
+      <c r="D1457">
+        <v>1</v>
+      </c>
+      <c r="E1457">
+        <v>0</v>
+      </c>
+      <c r="F1457">
+        <v>6</v>
+      </c>
+      <c r="G1457">
+        <v>6</v>
+      </c>
+      <c r="H1457">
+        <v>6</v>
+      </c>
+      <c r="I1457">
+        <v>0</v>
+      </c>
+      <c r="J1457">
+        <v>0</v>
+      </c>
+      <c r="K1457">
+        <v>46.15</v>
+      </c>
+      <c r="L1457">
+        <v>13</v>
+      </c>
+      <c r="M1457">
+        <v>8</v>
+      </c>
+      <c r="N1457">
+        <v>0</v>
+      </c>
+      <c r="O1457">
+        <v>0</v>
+      </c>
+      <c r="P1457">
+        <v>6.52</v>
+      </c>
+      <c r="Q1457">
+        <v>0</v>
+      </c>
+      <c r="R1457">
+        <v>0</v>
+      </c>
+      <c r="S1457">
+        <v>0</v>
+      </c>
+      <c r="T1457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1458" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1458">
+        <v>1</v>
+      </c>
+      <c r="D1458">
+        <v>1</v>
+      </c>
+      <c r="E1458">
+        <v>0</v>
+      </c>
+      <c r="F1458">
+        <v>24</v>
+      </c>
+      <c r="G1458">
+        <v>24</v>
+      </c>
+      <c r="H1458">
+        <v>24</v>
+      </c>
+      <c r="I1458">
+        <v>0</v>
+      </c>
+      <c r="J1458">
+        <v>0</v>
+      </c>
+      <c r="K1458">
+        <v>58.54</v>
+      </c>
+      <c r="L1458">
+        <v>41</v>
+      </c>
+      <c r="M1458">
+        <v>23</v>
+      </c>
+      <c r="N1458">
+        <v>1</v>
+      </c>
+      <c r="O1458">
+        <v>0</v>
+      </c>
+      <c r="P1458">
+        <v>26.37</v>
+      </c>
+      <c r="Q1458">
+        <v>0</v>
+      </c>
+      <c r="R1458">
+        <v>0</v>
+      </c>
+      <c r="S1458">
+        <v>0</v>
+      </c>
+      <c r="T1458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1459" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1459" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C1459">
+        <v>1</v>
+      </c>
+      <c r="D1459">
+        <v>1</v>
+      </c>
+      <c r="E1459">
+        <v>0</v>
+      </c>
+      <c r="F1459">
+        <v>1</v>
+      </c>
+      <c r="G1459">
+        <v>1</v>
+      </c>
+      <c r="H1459">
+        <v>1</v>
+      </c>
+      <c r="I1459">
+        <v>0</v>
+      </c>
+      <c r="J1459">
+        <v>0</v>
+      </c>
+      <c r="K1459">
+        <v>9.09</v>
+      </c>
+      <c r="L1459">
+        <v>11</v>
+      </c>
+      <c r="M1459">
+        <v>10</v>
+      </c>
+      <c r="N1459">
+        <v>0</v>
+      </c>
+      <c r="O1459">
+        <v>0</v>
+      </c>
+      <c r="P1459">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q1459">
+        <v>0</v>
+      </c>
+      <c r="R1459">
+        <v>0</v>
+      </c>
+      <c r="S1459">
+        <v>0</v>
+      </c>
+      <c r="T1459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1460" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1460" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C1460">
+        <v>1</v>
+      </c>
+      <c r="D1460">
+        <v>1</v>
+      </c>
+      <c r="E1460">
+        <v>1</v>
+      </c>
+      <c r="F1460">
+        <v>5</v>
+      </c>
+      <c r="H1460" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1460">
+        <v>0</v>
+      </c>
+      <c r="J1460">
+        <v>0</v>
+      </c>
+      <c r="K1460">
+        <v>125</v>
+      </c>
+      <c r="L1460">
+        <v>4</v>
+      </c>
+      <c r="M1460">
+        <v>2</v>
+      </c>
+      <c r="N1460">
+        <v>1</v>
+      </c>
+      <c r="O1460">
+        <v>0</v>
+      </c>
+      <c r="P1460">
+        <v>5.49</v>
+      </c>
+      <c r="Q1460">
+        <v>0</v>
+      </c>
+      <c r="R1460">
+        <v>0</v>
+      </c>
+      <c r="S1460">
+        <v>0</v>
+      </c>
+      <c r="T1460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1461" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1461" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C1461">
+        <v>1</v>
+      </c>
+      <c r="D1461">
+        <v>1</v>
+      </c>
+      <c r="E1461">
+        <v>1</v>
+      </c>
+      <c r="F1461">
+        <v>4</v>
+      </c>
+      <c r="H1461" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1461">
+        <v>0</v>
+      </c>
+      <c r="J1461">
+        <v>0</v>
+      </c>
+      <c r="K1461">
+        <v>80</v>
+      </c>
+      <c r="L1461">
+        <v>5</v>
+      </c>
+      <c r="M1461">
+        <v>3</v>
+      </c>
+      <c r="N1461">
+        <v>0</v>
+      </c>
+      <c r="O1461">
+        <v>0</v>
+      </c>
+      <c r="P1461">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="Q1461">
+        <v>0</v>
+      </c>
+      <c r="R1461">
+        <v>0</v>
+      </c>
+      <c r="S1461">
+        <v>0</v>
+      </c>
+      <c r="T1461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1462" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1462" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1462">
+        <v>1</v>
+      </c>
+      <c r="D1462">
+        <v>1</v>
+      </c>
+      <c r="E1462">
+        <v>0</v>
+      </c>
+      <c r="F1462">
+        <v>2</v>
+      </c>
+      <c r="G1462">
+        <v>2</v>
+      </c>
+      <c r="H1462">
+        <v>2</v>
+      </c>
+      <c r="I1462">
+        <v>0</v>
+      </c>
+      <c r="J1462">
+        <v>0</v>
+      </c>
+      <c r="K1462">
+        <v>50</v>
+      </c>
+      <c r="L1462">
+        <v>4</v>
+      </c>
+      <c r="M1462">
+        <v>3</v>
+      </c>
+      <c r="N1462">
+        <v>0</v>
+      </c>
+      <c r="O1462">
+        <v>0</v>
+      </c>
+      <c r="P1462">
+        <v>2.17</v>
+      </c>
+      <c r="Q1462">
+        <v>0</v>
+      </c>
+      <c r="R1462">
+        <v>2</v>
+      </c>
+      <c r="S1462">
+        <v>0</v>
+      </c>
+      <c r="T1462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1463" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1463" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1463">
+        <v>1</v>
+      </c>
+      <c r="D1463">
+        <v>1</v>
+      </c>
+      <c r="E1463">
+        <v>0</v>
+      </c>
+      <c r="F1463">
+        <v>1</v>
+      </c>
+      <c r="G1463">
+        <v>1</v>
+      </c>
+      <c r="H1463">
+        <v>1</v>
+      </c>
+      <c r="I1463">
+        <v>0</v>
+      </c>
+      <c r="J1463">
+        <v>0</v>
+      </c>
+      <c r="K1463">
+        <v>14.29</v>
+      </c>
+      <c r="L1463">
+        <v>7</v>
+      </c>
+      <c r="M1463">
+        <v>6</v>
+      </c>
+      <c r="N1463">
+        <v>0</v>
+      </c>
+      <c r="O1463">
+        <v>0</v>
+      </c>
+      <c r="P1463">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q1463">
+        <v>0</v>
+      </c>
+      <c r="R1463">
+        <v>0</v>
+      </c>
+      <c r="S1463">
+        <v>0</v>
+      </c>
+      <c r="T1463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1464" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1464" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1464">
+        <v>1</v>
+      </c>
+      <c r="D1464">
+        <v>1</v>
+      </c>
+      <c r="E1464">
+        <v>0</v>
+      </c>
+      <c r="F1464">
+        <v>6</v>
+      </c>
+      <c r="G1464">
+        <v>6</v>
+      </c>
+      <c r="H1464">
+        <v>6</v>
+      </c>
+      <c r="I1464">
+        <v>0</v>
+      </c>
+      <c r="J1464">
+        <v>0</v>
+      </c>
+      <c r="K1464">
+        <v>120</v>
+      </c>
+      <c r="L1464">
+        <v>5</v>
+      </c>
+      <c r="M1464">
+        <v>1</v>
+      </c>
+      <c r="N1464">
+        <v>0</v>
+      </c>
+      <c r="O1464">
+        <v>0</v>
+      </c>
+      <c r="P1464">
+        <v>6.59</v>
+      </c>
+      <c r="Q1464">
+        <v>1</v>
+      </c>
+      <c r="R1464">
+        <v>0</v>
+      </c>
+      <c r="S1464">
+        <v>0</v>
+      </c>
+      <c r="T1464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1465" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1465" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1465">
+        <v>1</v>
+      </c>
+      <c r="D1465">
+        <v>1</v>
+      </c>
+      <c r="E1465">
+        <v>1</v>
+      </c>
+      <c r="F1465">
+        <v>35</v>
+      </c>
+      <c r="H1465" t="s">
+        <v>331</v>
+      </c>
+      <c r="I1465">
+        <v>0</v>
+      </c>
+      <c r="J1465">
+        <v>0</v>
+      </c>
+      <c r="K1465">
+        <v>102.94</v>
+      </c>
+      <c r="L1465">
+        <v>34</v>
+      </c>
+      <c r="M1465">
+        <v>14</v>
+      </c>
+      <c r="N1465">
+        <v>4</v>
+      </c>
+      <c r="O1465">
+        <v>0</v>
+      </c>
+      <c r="P1465">
+        <v>38.04</v>
+      </c>
+      <c r="Q1465">
+        <v>0</v>
+      </c>
+      <c r="R1465">
+        <v>0</v>
+      </c>
+      <c r="S1465">
+        <v>0</v>
+      </c>
+      <c r="T1465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1466" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1466" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1466">
+        <v>1</v>
+      </c>
+      <c r="D1466">
+        <v>1</v>
+      </c>
+      <c r="E1466">
+        <v>0</v>
+      </c>
+      <c r="F1466">
+        <v>3</v>
+      </c>
+      <c r="G1466">
+        <v>3</v>
+      </c>
+      <c r="H1466">
+        <v>3</v>
+      </c>
+      <c r="I1466">
+        <v>0</v>
+      </c>
+      <c r="J1466">
+        <v>0</v>
+      </c>
+      <c r="K1466">
+        <v>60</v>
+      </c>
+      <c r="L1466">
+        <v>5</v>
+      </c>
+      <c r="M1466">
+        <v>2</v>
+      </c>
+      <c r="N1466">
+        <v>0</v>
+      </c>
+      <c r="O1466">
+        <v>0</v>
+      </c>
+      <c r="P1466">
+        <v>3.26</v>
+      </c>
+      <c r="Q1466">
+        <v>1</v>
+      </c>
+      <c r="R1466">
+        <v>0</v>
+      </c>
+      <c r="S1466">
+        <v>0</v>
+      </c>
+      <c r="T1466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1467" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1467" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1467">
+        <v>1</v>
+      </c>
+      <c r="D1467">
+        <v>1</v>
+      </c>
+      <c r="E1467">
+        <v>0</v>
+      </c>
+      <c r="F1467">
+        <v>2</v>
+      </c>
+      <c r="G1467">
+        <v>2</v>
+      </c>
+      <c r="H1467">
+        <v>2</v>
+      </c>
+      <c r="I1467">
+        <v>0</v>
+      </c>
+      <c r="J1467">
+        <v>0</v>
+      </c>
+      <c r="K1467">
+        <v>50</v>
+      </c>
+      <c r="L1467">
+        <v>4</v>
+      </c>
+      <c r="M1467">
+        <v>2</v>
+      </c>
+      <c r="N1467">
+        <v>0</v>
+      </c>
+      <c r="O1467">
+        <v>0</v>
+      </c>
+      <c r="P1467">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q1467">
+        <v>0</v>
+      </c>
+      <c r="R1467">
+        <v>0</v>
+      </c>
+      <c r="S1467">
+        <v>0</v>
+      </c>
+      <c r="T1467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1468" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1468" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1468">
+        <v>1</v>
+      </c>
+      <c r="D1468">
+        <v>1</v>
+      </c>
+      <c r="E1468">
+        <v>0</v>
+      </c>
+      <c r="F1468">
+        <v>5</v>
+      </c>
+      <c r="G1468">
+        <v>5</v>
+      </c>
+      <c r="H1468">
+        <v>5</v>
+      </c>
+      <c r="I1468">
+        <v>0</v>
+      </c>
+      <c r="J1468">
+        <v>0</v>
+      </c>
+      <c r="K1468">
+        <v>166.67</v>
+      </c>
+      <c r="L1468">
+        <v>3</v>
+      </c>
+      <c r="M1468">
+        <v>1</v>
+      </c>
+      <c r="N1468">
+        <v>1</v>
+      </c>
+      <c r="O1468">
+        <v>0</v>
+      </c>
+      <c r="P1468">
+        <v>5.43</v>
+      </c>
+      <c r="Q1468">
+        <v>0</v>
+      </c>
+      <c r="R1468">
+        <v>0</v>
+      </c>
+      <c r="S1468">
+        <v>0</v>
+      </c>
+      <c r="T1468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1469" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1469" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1469">
+        <v>1</v>
+      </c>
+      <c r="D1469">
+        <v>0</v>
+      </c>
+      <c r="E1469">
+        <v>0</v>
+      </c>
+      <c r="F1469">
+        <v>0</v>
+      </c>
+      <c r="I1469">
+        <v>0</v>
+      </c>
+      <c r="J1469">
+        <v>0</v>
+      </c>
+      <c r="L1469">
+        <v>0</v>
+      </c>
+      <c r="M1469">
+        <v>0</v>
+      </c>
+      <c r="N1469">
+        <v>0</v>
+      </c>
+      <c r="O1469">
+        <v>0</v>
+      </c>
+      <c r="P1469">
+        <v>0</v>
+      </c>
+      <c r="Q1469">
+        <v>0</v>
+      </c>
+      <c r="R1469">
+        <v>0</v>
+      </c>
+      <c r="S1469">
+        <v>0</v>
+      </c>
+      <c r="T1469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1470" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1470" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1470">
+        <v>1</v>
+      </c>
+      <c r="D1470">
+        <v>0</v>
+      </c>
+      <c r="E1470">
+        <v>0</v>
+      </c>
+      <c r="F1470">
+        <v>0</v>
+      </c>
+      <c r="I1470">
+        <v>0</v>
+      </c>
+      <c r="J1470">
+        <v>0</v>
+      </c>
+      <c r="L1470">
+        <v>0</v>
+      </c>
+      <c r="M1470">
+        <v>0</v>
+      </c>
+      <c r="N1470">
+        <v>0</v>
+      </c>
+      <c r="O1470">
+        <v>0</v>
+      </c>
+      <c r="P1470">
+        <v>0</v>
+      </c>
+      <c r="Q1470">
+        <v>0</v>
+      </c>
+      <c r="R1470">
+        <v>0</v>
+      </c>
+      <c r="S1470">
+        <v>0</v>
+      </c>
+      <c r="T1470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1471" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1471" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1471">
+        <v>1</v>
+      </c>
+      <c r="D1471">
+        <v>1</v>
+      </c>
+      <c r="E1471">
+        <v>0</v>
+      </c>
+      <c r="F1471">
+        <v>1</v>
+      </c>
+      <c r="G1471">
+        <v>1</v>
+      </c>
+      <c r="H1471">
+        <v>1</v>
+      </c>
+      <c r="I1471">
+        <v>0</v>
+      </c>
+      <c r="J1471">
+        <v>0</v>
+      </c>
+      <c r="K1471">
+        <v>7.69</v>
+      </c>
+      <c r="L1471">
+        <v>13</v>
+      </c>
+      <c r="M1471">
+        <v>12</v>
+      </c>
+      <c r="N1471">
+        <v>0</v>
+      </c>
+      <c r="O1471">
+        <v>0</v>
+      </c>
+      <c r="P1471">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q1471">
+        <v>0</v>
+      </c>
+      <c r="R1471">
+        <v>0</v>
+      </c>
+      <c r="S1471">
+        <v>0</v>
+      </c>
+      <c r="T1471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1472" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1472" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1472">
+        <v>1</v>
+      </c>
+      <c r="D1472">
+        <v>1</v>
+      </c>
+      <c r="E1472">
+        <v>1</v>
+      </c>
+      <c r="F1472">
+        <v>0</v>
+      </c>
+      <c r="H1472" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1472">
+        <v>0</v>
+      </c>
+      <c r="J1472">
+        <v>0</v>
+      </c>
+      <c r="K1472">
+        <v>0</v>
+      </c>
+      <c r="L1472">
+        <v>1</v>
+      </c>
+      <c r="M1472">
+        <v>1</v>
+      </c>
+      <c r="N1472">
+        <v>0</v>
+      </c>
+      <c r="O1472">
+        <v>0</v>
+      </c>
+      <c r="P1472">
+        <v>0</v>
+      </c>
+      <c r="Q1472">
+        <v>0</v>
+      </c>
+      <c r="R1472">
+        <v>0</v>
+      </c>
+      <c r="S1472">
+        <v>0</v>
+      </c>
+      <c r="T1472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1473" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1473" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1473">
+        <v>1</v>
+      </c>
+      <c r="D1473">
+        <v>1</v>
+      </c>
+      <c r="E1473">
+        <v>0</v>
+      </c>
+      <c r="F1473">
+        <v>1</v>
+      </c>
+      <c r="G1473">
+        <v>1</v>
+      </c>
+      <c r="H1473">
+        <v>1</v>
+      </c>
+      <c r="I1473">
+        <v>0</v>
+      </c>
+      <c r="J1473">
+        <v>0</v>
+      </c>
+      <c r="K1473">
+        <v>33.33</v>
+      </c>
+      <c r="L1473">
+        <v>3</v>
+      </c>
+      <c r="M1473">
+        <v>2</v>
+      </c>
+      <c r="N1473">
+        <v>0</v>
+      </c>
+      <c r="O1473">
+        <v>0</v>
+      </c>
+      <c r="P1473">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q1473">
+        <v>0</v>
+      </c>
+      <c r="R1473">
+        <v>1</v>
+      </c>
+      <c r="S1473">
+        <v>0</v>
+      </c>
+      <c r="T1473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1474" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1474" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1474">
+        <v>1</v>
+      </c>
+      <c r="D1474">
+        <v>1</v>
+      </c>
+      <c r="E1474">
+        <v>0</v>
+      </c>
+      <c r="F1474">
+        <v>8</v>
+      </c>
+      <c r="G1474">
+        <v>8</v>
+      </c>
+      <c r="H1474">
+        <v>8</v>
+      </c>
+      <c r="I1474">
+        <v>0</v>
+      </c>
+      <c r="J1474">
+        <v>0</v>
+      </c>
+      <c r="K1474">
+        <v>32</v>
+      </c>
+      <c r="L1474">
+        <v>25</v>
+      </c>
+      <c r="M1474">
+        <v>17</v>
+      </c>
+      <c r="N1474">
+        <v>0</v>
+      </c>
+      <c r="O1474">
+        <v>0</v>
+      </c>
+      <c r="P1474">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q1474">
+        <v>0</v>
+      </c>
+      <c r="R1474">
+        <v>0</v>
+      </c>
+      <c r="S1474">
+        <v>0</v>
+      </c>
+      <c r="T1474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1475" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1475" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1475">
+        <v>1</v>
+      </c>
+      <c r="D1475">
+        <v>0</v>
+      </c>
+      <c r="E1475">
+        <v>0</v>
+      </c>
+      <c r="F1475">
+        <v>0</v>
+      </c>
+      <c r="I1475">
+        <v>0</v>
+      </c>
+      <c r="J1475">
+        <v>0</v>
+      </c>
+      <c r="L1475">
+        <v>0</v>
+      </c>
+      <c r="M1475">
+        <v>0</v>
+      </c>
+      <c r="N1475">
+        <v>0</v>
+      </c>
+      <c r="O1475">
+        <v>0</v>
+      </c>
+      <c r="P1475">
+        <v>0</v>
+      </c>
+      <c r="Q1475">
+        <v>0</v>
+      </c>
+      <c r="R1475">
+        <v>0</v>
+      </c>
+      <c r="S1475">
+        <v>0</v>
+      </c>
+      <c r="T1475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1476" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1476" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C1476">
+        <v>1</v>
+      </c>
+      <c r="D1476">
+        <v>1</v>
+      </c>
+      <c r="E1476">
+        <v>0</v>
+      </c>
+      <c r="F1476">
+        <v>3</v>
+      </c>
+      <c r="G1476">
+        <v>3</v>
+      </c>
+      <c r="H1476">
+        <v>3</v>
+      </c>
+      <c r="I1476">
+        <v>0</v>
+      </c>
+      <c r="J1476">
+        <v>0</v>
+      </c>
+      <c r="K1476">
+        <v>42.86</v>
+      </c>
+      <c r="L1476">
+        <v>7</v>
+      </c>
+      <c r="M1476">
+        <v>4</v>
+      </c>
+      <c r="N1476">
+        <v>0</v>
+      </c>
+      <c r="O1476">
+        <v>0</v>
+      </c>
+      <c r="P1476">
+        <v>3.26</v>
+      </c>
+      <c r="Q1476">
+        <v>0</v>
+      </c>
+      <c r="R1476">
+        <v>0</v>
+      </c>
+      <c r="S1476">
+        <v>0</v>
+      </c>
+      <c r="T1476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1477" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1477" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1477">
+        <v>1</v>
+      </c>
+      <c r="D1477">
+        <v>1</v>
+      </c>
+      <c r="E1477">
+        <v>0</v>
+      </c>
+      <c r="F1477">
+        <v>24</v>
+      </c>
+      <c r="G1477">
+        <v>24</v>
+      </c>
+      <c r="H1477">
+        <v>24</v>
+      </c>
+      <c r="I1477">
+        <v>0</v>
+      </c>
+      <c r="J1477">
+        <v>0</v>
+      </c>
+      <c r="K1477">
+        <v>48</v>
+      </c>
+      <c r="L1477">
+        <v>50</v>
+      </c>
+      <c r="M1477">
+        <v>37</v>
+      </c>
+      <c r="N1477">
+        <v>2</v>
+      </c>
+      <c r="O1477">
+        <v>0</v>
+      </c>
+      <c r="P1477">
+        <v>26.37</v>
+      </c>
+      <c r="Q1477">
+        <v>1</v>
+      </c>
+      <c r="R1477">
+        <v>0</v>
+      </c>
+      <c r="S1477">
+        <v>0</v>
+      </c>
+      <c r="T1477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1478" t="s">
+        <v>450</v>
+      </c>
+      <c r="B1478" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1478">
+        <v>1</v>
+      </c>
+      <c r="D1478">
+        <v>1</v>
+      </c>
+      <c r="E1478">
+        <v>0</v>
+      </c>
+      <c r="F1478">
+        <v>3</v>
+      </c>
+      <c r="G1478">
+        <v>3</v>
+      </c>
+      <c r="H1478">
+        <v>3</v>
+      </c>
+      <c r="I1478">
+        <v>0</v>
+      </c>
+      <c r="J1478">
+        <v>0</v>
+      </c>
+      <c r="K1478">
+        <v>30</v>
+      </c>
+      <c r="L1478">
+        <v>10</v>
+      </c>
+      <c r="M1478">
+        <v>7</v>
+      </c>
+      <c r="N1478">
+        <v>0</v>
+      </c>
+      <c r="O1478">
+        <v>0</v>
+      </c>
+      <c r="P1478">
+        <v>3.3</v>
+      </c>
+      <c r="Q1478">
+        <v>0</v>
+      </c>
+      <c r="R1478">
+        <v>0</v>
+      </c>
+      <c r="S1478">
+        <v>0</v>
+      </c>
+      <c r="T1478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1479" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1479">
+        <v>1</v>
+      </c>
+      <c r="D1479">
+        <v>1</v>
+      </c>
+      <c r="E1479">
+        <v>0</v>
+      </c>
+      <c r="F1479">
+        <v>0</v>
+      </c>
+      <c r="G1479">
+        <v>0</v>
+      </c>
+      <c r="H1479">
+        <v>0</v>
+      </c>
+      <c r="I1479">
+        <v>0</v>
+      </c>
+      <c r="J1479">
+        <v>0</v>
+      </c>
+      <c r="K1479">
+        <v>0</v>
+      </c>
+      <c r="L1479">
+        <v>2</v>
+      </c>
+      <c r="M1479">
+        <v>2</v>
+      </c>
+      <c r="N1479">
+        <v>0</v>
+      </c>
+      <c r="O1479">
+        <v>0</v>
+      </c>
+      <c r="P1479">
+        <v>0</v>
+      </c>
+      <c r="Q1479">
+        <v>0</v>
+      </c>
+      <c r="R1479">
+        <v>0</v>
+      </c>
+      <c r="S1479">
+        <v>0</v>
+      </c>
+      <c r="T1479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1480" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1480">
+        <v>1</v>
+      </c>
+      <c r="D1480">
+        <v>1</v>
+      </c>
+      <c r="E1480">
+        <v>1</v>
+      </c>
+      <c r="F1480">
+        <v>50</v>
+      </c>
+      <c r="H1480" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1480">
+        <v>1</v>
+      </c>
+      <c r="J1480">
+        <v>0</v>
+      </c>
+      <c r="K1480">
+        <v>161.29</v>
+      </c>
+      <c r="L1480">
+        <v>31</v>
+      </c>
+      <c r="M1480">
+        <v>10</v>
+      </c>
+      <c r="N1480">
+        <v>6</v>
+      </c>
+      <c r="O1480">
+        <v>0</v>
+      </c>
+      <c r="P1480">
+        <v>38.46</v>
+      </c>
+      <c r="Q1480">
+        <v>0</v>
+      </c>
+      <c r="R1480">
+        <v>0</v>
+      </c>
+      <c r="S1480">
+        <v>0</v>
+      </c>
+      <c r="T1480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1481" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1481">
+        <v>1</v>
+      </c>
+      <c r="D1481">
+        <v>0</v>
+      </c>
+      <c r="E1481">
+        <v>0</v>
+      </c>
+      <c r="F1481">
+        <v>0</v>
+      </c>
+      <c r="I1481">
+        <v>0</v>
+      </c>
+      <c r="J1481">
+        <v>0</v>
+      </c>
+      <c r="L1481">
+        <v>0</v>
+      </c>
+      <c r="M1481">
+        <v>0</v>
+      </c>
+      <c r="N1481">
+        <v>0</v>
+      </c>
+      <c r="O1481">
+        <v>0</v>
+      </c>
+      <c r="P1481">
+        <v>0</v>
+      </c>
+      <c r="Q1481">
+        <v>0</v>
+      </c>
+      <c r="R1481">
+        <v>0</v>
+      </c>
+      <c r="S1481">
+        <v>0</v>
+      </c>
+      <c r="T1481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1482" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1482">
+        <v>1</v>
+      </c>
+      <c r="D1482">
+        <v>1</v>
+      </c>
+      <c r="E1482">
+        <v>0</v>
+      </c>
+      <c r="F1482">
+        <v>27</v>
+      </c>
+      <c r="G1482">
+        <v>27</v>
+      </c>
+      <c r="H1482">
+        <v>27</v>
+      </c>
+      <c r="I1482">
+        <v>0</v>
+      </c>
+      <c r="J1482">
+        <v>0</v>
+      </c>
+      <c r="K1482">
+        <v>69.23</v>
+      </c>
+      <c r="L1482">
+        <v>39</v>
+      </c>
+      <c r="M1482">
+        <v>23</v>
+      </c>
+      <c r="N1482">
+        <v>3</v>
+      </c>
+      <c r="O1482">
+        <v>0</v>
+      </c>
+      <c r="P1482">
+        <v>22.31</v>
+      </c>
+      <c r="Q1482">
+        <v>0</v>
+      </c>
+      <c r="R1482">
+        <v>2</v>
+      </c>
+      <c r="S1482">
+        <v>0</v>
+      </c>
+      <c r="T1482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1483" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1483">
+        <v>1</v>
+      </c>
+      <c r="D1483">
+        <v>0</v>
+      </c>
+      <c r="E1483">
+        <v>0</v>
+      </c>
+      <c r="F1483">
+        <v>0</v>
+      </c>
+      <c r="I1483">
+        <v>0</v>
+      </c>
+      <c r="J1483">
+        <v>0</v>
+      </c>
+      <c r="L1483">
+        <v>0</v>
+      </c>
+      <c r="M1483">
+        <v>0</v>
+      </c>
+      <c r="N1483">
+        <v>0</v>
+      </c>
+      <c r="O1483">
+        <v>0</v>
+      </c>
+      <c r="P1483">
+        <v>0</v>
+      </c>
+      <c r="Q1483">
+        <v>0</v>
+      </c>
+      <c r="R1483">
+        <v>0</v>
+      </c>
+      <c r="S1483">
+        <v>0</v>
+      </c>
+      <c r="T1483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1484" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1484">
+        <v>1</v>
+      </c>
+      <c r="D1484">
+        <v>1</v>
+      </c>
+      <c r="E1484">
+        <v>0</v>
+      </c>
+      <c r="F1484">
+        <v>5</v>
+      </c>
+      <c r="G1484">
+        <v>5</v>
+      </c>
+      <c r="H1484">
+        <v>5</v>
+      </c>
+      <c r="I1484">
+        <v>0</v>
+      </c>
+      <c r="J1484">
+        <v>0</v>
+      </c>
+      <c r="K1484">
+        <v>38.46</v>
+      </c>
+      <c r="L1484">
+        <v>13</v>
+      </c>
+      <c r="M1484">
+        <v>8</v>
+      </c>
+      <c r="N1484">
+        <v>0</v>
+      </c>
+      <c r="O1484">
+        <v>0</v>
+      </c>
+      <c r="P1484">
+        <v>4.13</v>
+      </c>
+      <c r="Q1484">
+        <v>0</v>
+      </c>
+      <c r="R1484">
+        <v>0</v>
+      </c>
+      <c r="S1484">
+        <v>0</v>
+      </c>
+      <c r="T1484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1485" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>452</v>
+      </c>
+      <c r="C1485">
+        <v>1</v>
+      </c>
+      <c r="D1485">
+        <v>0</v>
+      </c>
+      <c r="E1485">
+        <v>0</v>
+      </c>
+      <c r="F1485">
+        <v>0</v>
+      </c>
+      <c r="I1485">
+        <v>0</v>
+      </c>
+      <c r="J1485">
+        <v>0</v>
+      </c>
+      <c r="L1485">
+        <v>0</v>
+      </c>
+      <c r="M1485">
+        <v>0</v>
+      </c>
+      <c r="N1485">
+        <v>0</v>
+      </c>
+      <c r="O1485">
+        <v>0</v>
+      </c>
+      <c r="P1485">
+        <v>0</v>
+      </c>
+      <c r="Q1485">
+        <v>0</v>
+      </c>
+      <c r="R1485">
+        <v>0</v>
+      </c>
+      <c r="S1485">
+        <v>0</v>
+      </c>
+      <c r="T1485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1486" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1486">
+        <v>1</v>
+      </c>
+      <c r="D1486">
+        <v>0</v>
+      </c>
+      <c r="E1486">
+        <v>0</v>
+      </c>
+      <c r="F1486">
+        <v>0</v>
+      </c>
+      <c r="I1486">
+        <v>0</v>
+      </c>
+      <c r="J1486">
+        <v>0</v>
+      </c>
+      <c r="L1486">
+        <v>0</v>
+      </c>
+      <c r="M1486">
+        <v>0</v>
+      </c>
+      <c r="N1486">
+        <v>0</v>
+      </c>
+      <c r="O1486">
+        <v>0</v>
+      </c>
+      <c r="P1486">
+        <v>0</v>
+      </c>
+      <c r="Q1486">
+        <v>0</v>
+      </c>
+      <c r="R1486">
+        <v>0</v>
+      </c>
+      <c r="S1486">
+        <v>0</v>
+      </c>
+      <c r="T1486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1487" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1487">
+        <v>1</v>
+      </c>
+      <c r="D1487">
+        <v>1</v>
+      </c>
+      <c r="E1487">
+        <v>0</v>
+      </c>
+      <c r="F1487">
+        <v>1</v>
+      </c>
+      <c r="G1487">
+        <v>1</v>
+      </c>
+      <c r="H1487">
+        <v>1</v>
+      </c>
+      <c r="I1487">
+        <v>0</v>
+      </c>
+      <c r="J1487">
+        <v>0</v>
+      </c>
+      <c r="K1487">
+        <v>25</v>
+      </c>
+      <c r="L1487">
+        <v>4</v>
+      </c>
+      <c r="M1487">
+        <v>3</v>
+      </c>
+      <c r="N1487">
+        <v>0</v>
+      </c>
+      <c r="O1487">
+        <v>0</v>
+      </c>
+      <c r="P1487">
+        <v>0.77</v>
+      </c>
+      <c r="Q1487">
+        <v>0</v>
+      </c>
+      <c r="R1487">
+        <v>0</v>
+      </c>
+      <c r="S1487">
+        <v>0</v>
+      </c>
+      <c r="T1487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1488" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1488">
+        <v>1</v>
+      </c>
+      <c r="D1488">
+        <v>1</v>
+      </c>
+      <c r="E1488">
+        <v>0</v>
+      </c>
+      <c r="F1488">
+        <v>41</v>
+      </c>
+      <c r="G1488">
+        <v>41</v>
+      </c>
+      <c r="H1488">
+        <v>41</v>
+      </c>
+      <c r="I1488">
+        <v>0</v>
+      </c>
+      <c r="J1488">
+        <v>0</v>
+      </c>
+      <c r="K1488">
+        <v>102.5</v>
+      </c>
+      <c r="L1488">
+        <v>40</v>
+      </c>
+      <c r="M1488">
+        <v>21</v>
+      </c>
+      <c r="N1488">
+        <v>6</v>
+      </c>
+      <c r="O1488">
+        <v>0</v>
+      </c>
+      <c r="P1488">
+        <v>33.880000000000003</v>
+      </c>
+      <c r="Q1488">
+        <v>0</v>
+      </c>
+      <c r="R1488">
+        <v>0</v>
+      </c>
+      <c r="S1488">
+        <v>0</v>
+      </c>
+      <c r="T1488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1489" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1489">
+        <v>1</v>
+      </c>
+      <c r="D1489">
+        <v>0</v>
+      </c>
+      <c r="E1489">
+        <v>0</v>
+      </c>
+      <c r="F1489">
+        <v>0</v>
+      </c>
+      <c r="I1489">
+        <v>0</v>
+      </c>
+      <c r="J1489">
+        <v>0</v>
+      </c>
+      <c r="L1489">
+        <v>0</v>
+      </c>
+      <c r="M1489">
+        <v>0</v>
+      </c>
+      <c r="N1489">
+        <v>0</v>
+      </c>
+      <c r="O1489">
+        <v>0</v>
+      </c>
+      <c r="P1489">
+        <v>0</v>
+      </c>
+      <c r="Q1489">
+        <v>0</v>
+      </c>
+      <c r="R1489">
+        <v>0</v>
+      </c>
+      <c r="S1489">
+        <v>0</v>
+      </c>
+      <c r="T1489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1490" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1490">
+        <v>1</v>
+      </c>
+      <c r="D1490">
+        <v>1</v>
+      </c>
+      <c r="E1490">
+        <v>0</v>
+      </c>
+      <c r="F1490">
+        <v>11</v>
+      </c>
+      <c r="G1490">
+        <v>11</v>
+      </c>
+      <c r="H1490">
+        <v>11</v>
+      </c>
+      <c r="I1490">
+        <v>0</v>
+      </c>
+      <c r="J1490">
+        <v>0</v>
+      </c>
+      <c r="K1490">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="L1490">
+        <v>17</v>
+      </c>
+      <c r="M1490">
+        <v>10</v>
+      </c>
+      <c r="N1490">
+        <v>0</v>
+      </c>
+      <c r="O1490">
+        <v>0</v>
+      </c>
+      <c r="P1490">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="Q1490">
+        <v>1</v>
+      </c>
+      <c r="R1490">
+        <v>0</v>
+      </c>
+      <c r="S1490">
+        <v>0</v>
+      </c>
+      <c r="T1490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1491" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1491">
+        <v>1</v>
+      </c>
+      <c r="D1491">
+        <v>1</v>
+      </c>
+      <c r="E1491">
+        <v>0</v>
+      </c>
+      <c r="F1491">
+        <v>20</v>
+      </c>
+      <c r="G1491">
+        <v>20</v>
+      </c>
+      <c r="H1491">
+        <v>20</v>
+      </c>
+      <c r="I1491">
+        <v>0</v>
+      </c>
+      <c r="J1491">
+        <v>0</v>
+      </c>
+      <c r="K1491">
+        <v>86.96</v>
+      </c>
+      <c r="L1491">
+        <v>23</v>
+      </c>
+      <c r="M1491">
+        <v>10</v>
+      </c>
+      <c r="N1491">
+        <v>2</v>
+      </c>
+      <c r="O1491">
+        <v>0</v>
+      </c>
+      <c r="P1491">
+        <v>15.38</v>
+      </c>
+      <c r="Q1491">
+        <v>0</v>
+      </c>
+      <c r="R1491">
+        <v>0</v>
+      </c>
+      <c r="S1491">
+        <v>0</v>
+      </c>
+      <c r="T1491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1492" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>453</v>
+      </c>
+      <c r="C1492">
+        <v>1</v>
+      </c>
+      <c r="D1492">
+        <v>0</v>
+      </c>
+      <c r="E1492">
+        <v>0</v>
+      </c>
+      <c r="F1492">
+        <v>0</v>
+      </c>
+      <c r="I1492">
+        <v>0</v>
+      </c>
+      <c r="J1492">
+        <v>0</v>
+      </c>
+      <c r="L1492">
+        <v>0</v>
+      </c>
+      <c r="M1492">
+        <v>0</v>
+      </c>
+      <c r="N1492">
+        <v>0</v>
+      </c>
+      <c r="O1492">
+        <v>0</v>
+      </c>
+      <c r="P1492">
+        <v>0</v>
+      </c>
+      <c r="Q1492">
+        <v>0</v>
+      </c>
+      <c r="R1492">
+        <v>0</v>
+      </c>
+      <c r="S1492">
+        <v>0</v>
+      </c>
+      <c r="T1492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1493" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1493">
+        <v>1</v>
+      </c>
+      <c r="D1493">
+        <v>1</v>
+      </c>
+      <c r="E1493">
+        <v>1</v>
+      </c>
+      <c r="F1493">
+        <v>8</v>
+      </c>
+      <c r="H1493" t="s">
+        <v>143</v>
+      </c>
+      <c r="I1493">
+        <v>0</v>
+      </c>
+      <c r="J1493">
+        <v>0</v>
+      </c>
+      <c r="K1493">
+        <v>88.89</v>
+      </c>
+      <c r="L1493">
+        <v>9</v>
+      </c>
+      <c r="M1493">
+        <v>4</v>
+      </c>
+      <c r="N1493">
+        <v>0</v>
+      </c>
+      <c r="O1493">
+        <v>0</v>
+      </c>
+      <c r="P1493">
+        <v>6.15</v>
+      </c>
+      <c r="Q1493">
+        <v>1</v>
+      </c>
+      <c r="R1493">
+        <v>0</v>
+      </c>
+      <c r="S1493">
+        <v>0</v>
+      </c>
+      <c r="T1493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1494" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1494">
+        <v>1</v>
+      </c>
+      <c r="D1494">
+        <v>0</v>
+      </c>
+      <c r="E1494">
+        <v>0</v>
+      </c>
+      <c r="F1494">
+        <v>0</v>
+      </c>
+      <c r="I1494">
+        <v>0</v>
+      </c>
+      <c r="J1494">
+        <v>0</v>
+      </c>
+      <c r="L1494">
+        <v>0</v>
+      </c>
+      <c r="M1494">
+        <v>0</v>
+      </c>
+      <c r="N1494">
+        <v>0</v>
+      </c>
+      <c r="O1494">
+        <v>0</v>
+      </c>
+      <c r="P1494">
+        <v>0</v>
+      </c>
+      <c r="Q1494">
+        <v>0</v>
+      </c>
+      <c r="R1494">
+        <v>0</v>
+      </c>
+      <c r="S1494">
+        <v>0</v>
+      </c>
+      <c r="T1494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1495" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>330</v>
+      </c>
+      <c r="C1495">
+        <v>1</v>
+      </c>
+      <c r="D1495">
+        <v>1</v>
+      </c>
+      <c r="E1495">
+        <v>1</v>
+      </c>
+      <c r="F1495">
+        <v>5</v>
+      </c>
+      <c r="H1495" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1495">
+        <v>0</v>
+      </c>
+      <c r="J1495">
+        <v>0</v>
+      </c>
+      <c r="K1495">
+        <v>26.32</v>
+      </c>
+      <c r="L1495">
+        <v>19</v>
+      </c>
+      <c r="M1495">
+        <v>14</v>
+      </c>
+      <c r="N1495">
+        <v>0</v>
+      </c>
+      <c r="O1495">
+        <v>0</v>
+      </c>
+      <c r="P1495">
+        <v>3.85</v>
+      </c>
+      <c r="Q1495">
+        <v>0</v>
+      </c>
+      <c r="R1495">
+        <v>0</v>
+      </c>
+      <c r="S1495">
+        <v>0</v>
+      </c>
+      <c r="T1495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1496" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1496">
+        <v>1</v>
+      </c>
+      <c r="D1496">
+        <v>1</v>
+      </c>
+      <c r="E1496">
+        <v>1</v>
+      </c>
+      <c r="F1496">
+        <v>9</v>
+      </c>
+      <c r="H1496" t="s">
+        <v>196</v>
+      </c>
+      <c r="I1496">
+        <v>0</v>
+      </c>
+      <c r="J1496">
+        <v>0</v>
+      </c>
+      <c r="K1496">
+        <v>128.57</v>
+      </c>
+      <c r="L1496">
+        <v>7</v>
+      </c>
+      <c r="M1496">
+        <v>3</v>
+      </c>
+      <c r="N1496">
+        <v>1</v>
+      </c>
+      <c r="O1496">
+        <v>0</v>
+      </c>
+      <c r="P1496">
+        <v>7.44</v>
+      </c>
+      <c r="Q1496">
+        <v>2</v>
+      </c>
+      <c r="R1496">
+        <v>0</v>
+      </c>
+      <c r="S1496">
+        <v>0</v>
+      </c>
+      <c r="T1496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1497" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1497">
+        <v>1</v>
+      </c>
+      <c r="D1497">
+        <v>1</v>
+      </c>
+      <c r="E1497">
+        <v>0</v>
+      </c>
+      <c r="F1497">
+        <v>11</v>
+      </c>
+      <c r="G1497">
+        <v>11</v>
+      </c>
+      <c r="H1497">
+        <v>11</v>
+      </c>
+      <c r="I1497">
+        <v>0</v>
+      </c>
+      <c r="J1497">
+        <v>0</v>
+      </c>
+      <c r="K1497">
+        <v>61.11</v>
+      </c>
+      <c r="L1497">
+        <v>18</v>
+      </c>
+      <c r="M1497">
+        <v>11</v>
+      </c>
+      <c r="N1497">
+        <v>1</v>
+      </c>
+      <c r="O1497">
+        <v>0</v>
+      </c>
+      <c r="P1497">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="Q1497">
+        <v>0</v>
+      </c>
+      <c r="R1497">
+        <v>0</v>
+      </c>
+      <c r="S1497">
+        <v>0</v>
+      </c>
+      <c r="T1497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1498" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1498">
+        <v>1</v>
+      </c>
+      <c r="D1498">
+        <v>0</v>
+      </c>
+      <c r="E1498">
+        <v>0</v>
+      </c>
+      <c r="F1498">
+        <v>0</v>
+      </c>
+      <c r="I1498">
+        <v>0</v>
+      </c>
+      <c r="J1498">
+        <v>0</v>
+      </c>
+      <c r="L1498">
+        <v>0</v>
+      </c>
+      <c r="M1498">
+        <v>0</v>
+      </c>
+      <c r="N1498">
+        <v>0</v>
+      </c>
+      <c r="O1498">
+        <v>0</v>
+      </c>
+      <c r="P1498">
+        <v>0</v>
+      </c>
+      <c r="Q1498">
+        <v>0</v>
+      </c>
+      <c r="R1498">
+        <v>0</v>
+      </c>
+      <c r="S1498">
+        <v>0</v>
+      </c>
+      <c r="T1498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1499" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1499">
+        <v>1</v>
+      </c>
+      <c r="D1499">
+        <v>1</v>
+      </c>
+      <c r="E1499">
+        <v>0</v>
+      </c>
+      <c r="F1499">
+        <v>0</v>
+      </c>
+      <c r="G1499">
+        <v>0</v>
+      </c>
+      <c r="H1499">
+        <v>0</v>
+      </c>
+      <c r="I1499">
+        <v>0</v>
+      </c>
+      <c r="J1499">
+        <v>0</v>
+      </c>
+      <c r="K1499">
+        <v>0</v>
+      </c>
+      <c r="L1499">
+        <v>4</v>
+      </c>
+      <c r="M1499">
+        <v>4</v>
+      </c>
+      <c r="N1499">
+        <v>0</v>
+      </c>
+      <c r="O1499">
+        <v>0</v>
+      </c>
+      <c r="P1499">
+        <v>0</v>
+      </c>
+      <c r="Q1499">
+        <v>0</v>
+      </c>
+      <c r="R1499">
+        <v>0</v>
+      </c>
+      <c r="S1499">
+        <v>0</v>
+      </c>
+      <c r="T1499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1500" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1500">
+        <v>1</v>
+      </c>
+      <c r="D1500">
+        <v>1</v>
+      </c>
+      <c r="E1500">
+        <v>1</v>
+      </c>
+      <c r="F1500">
+        <v>21</v>
+      </c>
+      <c r="H1500" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1500">
+        <v>0</v>
+      </c>
+      <c r="J1500">
+        <v>0</v>
+      </c>
+      <c r="K1500">
+        <v>123.53</v>
+      </c>
+      <c r="L1500">
+        <v>17</v>
+      </c>
+      <c r="M1500">
+        <v>7</v>
+      </c>
+      <c r="N1500">
+        <v>3</v>
+      </c>
+      <c r="O1500">
+        <v>0</v>
+      </c>
+      <c r="P1500">
+        <v>17.36</v>
+      </c>
+      <c r="Q1500">
+        <v>0</v>
+      </c>
+      <c r="R1500">
+        <v>0</v>
+      </c>
+      <c r="S1500">
+        <v>0</v>
+      </c>
+      <c r="T1500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1501" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1501" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1501">
+        <v>1</v>
+      </c>
+      <c r="D1501">
+        <v>1</v>
+      </c>
+      <c r="E1501">
+        <v>0</v>
+      </c>
+      <c r="F1501">
+        <v>36</v>
+      </c>
+      <c r="G1501">
+        <v>36</v>
+      </c>
+      <c r="H1501">
+        <v>36</v>
+      </c>
+      <c r="I1501">
+        <v>0</v>
+      </c>
+      <c r="J1501">
+        <v>0</v>
+      </c>
+      <c r="K1501">
+        <v>120</v>
+      </c>
+      <c r="L1501">
+        <v>30</v>
+      </c>
+      <c r="M1501">
+        <v>12</v>
+      </c>
+      <c r="N1501">
+        <v>6</v>
+      </c>
+      <c r="O1501">
+        <v>0</v>
+      </c>
+      <c r="P1501">
+        <v>26.47</v>
+      </c>
+      <c r="Q1501">
+        <v>0</v>
+      </c>
+      <c r="R1501">
+        <v>0</v>
+      </c>
+      <c r="S1501">
+        <v>0</v>
+      </c>
+      <c r="T1501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1502" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1502" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1502">
+        <v>1</v>
+      </c>
+      <c r="D1502">
+        <v>1</v>
+      </c>
+      <c r="E1502">
+        <v>0</v>
+      </c>
+      <c r="F1502">
+        <v>0</v>
+      </c>
+      <c r="G1502">
+        <v>0</v>
+      </c>
+      <c r="H1502">
+        <v>0</v>
+      </c>
+      <c r="I1502">
+        <v>0</v>
+      </c>
+      <c r="J1502">
+        <v>0</v>
+      </c>
+      <c r="K1502">
+        <v>0</v>
+      </c>
+      <c r="L1502">
+        <v>1</v>
+      </c>
+      <c r="M1502">
+        <v>1</v>
+      </c>
+      <c r="N1502">
+        <v>0</v>
+      </c>
+      <c r="O1502">
+        <v>0</v>
+      </c>
+      <c r="P1502">
+        <v>0</v>
+      </c>
+      <c r="Q1502">
+        <v>0</v>
+      </c>
+      <c r="R1502">
+        <v>0</v>
+      </c>
+      <c r="S1502">
+        <v>0</v>
+      </c>
+      <c r="T1502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1503" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1503" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1503">
+        <v>1</v>
+      </c>
+      <c r="D1503">
+        <v>1</v>
+      </c>
+      <c r="E1503">
+        <v>1</v>
+      </c>
+      <c r="F1503">
+        <v>7</v>
+      </c>
+      <c r="H1503" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1503">
+        <v>0</v>
+      </c>
+      <c r="J1503">
+        <v>0</v>
+      </c>
+      <c r="K1503">
+        <v>140</v>
+      </c>
+      <c r="L1503">
+        <v>5</v>
+      </c>
+      <c r="M1503">
+        <v>2</v>
+      </c>
+      <c r="N1503">
+        <v>1</v>
+      </c>
+      <c r="O1503">
+        <v>0</v>
+      </c>
+      <c r="P1503">
+        <v>5.15</v>
+      </c>
+      <c r="Q1503">
+        <v>1</v>
+      </c>
+      <c r="R1503">
+        <v>0</v>
+      </c>
+      <c r="S1503">
+        <v>0</v>
+      </c>
+      <c r="T1503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1504" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1504" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1504">
+        <v>1</v>
+      </c>
+      <c r="D1504">
+        <v>0</v>
+      </c>
+      <c r="E1504">
+        <v>0</v>
+      </c>
+      <c r="F1504">
+        <v>0</v>
+      </c>
+      <c r="I1504">
+        <v>0</v>
+      </c>
+      <c r="J1504">
+        <v>0</v>
+      </c>
+      <c r="L1504">
+        <v>0</v>
+      </c>
+      <c r="M1504">
+        <v>0</v>
+      </c>
+      <c r="N1504">
+        <v>0</v>
+      </c>
+      <c r="O1504">
+        <v>0</v>
+      </c>
+      <c r="P1504">
+        <v>0</v>
+      </c>
+      <c r="Q1504">
+        <v>1</v>
+      </c>
+      <c r="R1504">
+        <v>0</v>
+      </c>
+      <c r="S1504">
+        <v>0</v>
+      </c>
+      <c r="T1504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1505" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1505" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1505">
+        <v>1</v>
+      </c>
+      <c r="D1505">
+        <v>1</v>
+      </c>
+      <c r="E1505">
+        <v>0</v>
+      </c>
+      <c r="F1505">
+        <v>6</v>
+      </c>
+      <c r="G1505">
+        <v>6</v>
+      </c>
+      <c r="H1505">
+        <v>6</v>
+      </c>
+      <c r="I1505">
+        <v>0</v>
+      </c>
+      <c r="J1505">
+        <v>0</v>
+      </c>
+      <c r="K1505">
+        <v>46.15</v>
+      </c>
+      <c r="L1505">
+        <v>13</v>
+      </c>
+      <c r="M1505">
+        <v>8</v>
+      </c>
+      <c r="N1505">
+        <v>0</v>
+      </c>
+      <c r="O1505">
+        <v>0</v>
+      </c>
+      <c r="P1505">
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="Q1505">
+        <v>0</v>
+      </c>
+      <c r="R1505">
+        <v>0</v>
+      </c>
+      <c r="S1505">
+        <v>0</v>
+      </c>
+      <c r="T1505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1506" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1506" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1506">
+        <v>1</v>
+      </c>
+      <c r="D1506">
+        <v>0</v>
+      </c>
+      <c r="E1506">
+        <v>0</v>
+      </c>
+      <c r="F1506">
+        <v>0</v>
+      </c>
+      <c r="I1506">
+        <v>0</v>
+      </c>
+      <c r="J1506">
+        <v>0</v>
+      </c>
+      <c r="L1506">
+        <v>0</v>
+      </c>
+      <c r="M1506">
+        <v>0</v>
+      </c>
+      <c r="N1506">
+        <v>0</v>
+      </c>
+      <c r="O1506">
+        <v>0</v>
+      </c>
+      <c r="P1506">
+        <v>0</v>
+      </c>
+      <c r="Q1506">
+        <v>0</v>
+      </c>
+      <c r="R1506">
+        <v>0</v>
+      </c>
+      <c r="S1506">
+        <v>0</v>
+      </c>
+      <c r="T1506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1507" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1507" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1507">
+        <v>1</v>
+      </c>
+      <c r="D1507">
+        <v>1</v>
+      </c>
+      <c r="E1507">
+        <v>1</v>
+      </c>
+      <c r="F1507">
+        <v>37</v>
+      </c>
+      <c r="H1507" t="s">
+        <v>399</v>
+      </c>
+      <c r="I1507">
+        <v>0</v>
+      </c>
+      <c r="J1507">
+        <v>0</v>
+      </c>
+      <c r="K1507">
+        <v>97.37</v>
+      </c>
+      <c r="L1507">
+        <v>38</v>
+      </c>
+      <c r="M1507">
+        <v>19</v>
+      </c>
+      <c r="N1507">
+        <v>5</v>
+      </c>
+      <c r="O1507">
+        <v>0</v>
+      </c>
+      <c r="P1507">
+        <v>27.41</v>
+      </c>
+      <c r="Q1507">
+        <v>0</v>
+      </c>
+      <c r="R1507">
+        <v>0</v>
+      </c>
+      <c r="S1507">
+        <v>0</v>
+      </c>
+      <c r="T1507">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1508" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1508" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1508">
+        <v>1</v>
+      </c>
+      <c r="D1508">
+        <v>1</v>
+      </c>
+      <c r="E1508">
+        <v>0</v>
+      </c>
+      <c r="F1508">
+        <v>0</v>
+      </c>
+      <c r="G1508">
+        <v>0</v>
+      </c>
+      <c r="H1508">
+        <v>0</v>
+      </c>
+      <c r="I1508">
+        <v>0</v>
+      </c>
+      <c r="J1508">
+        <v>0</v>
+      </c>
+      <c r="K1508">
+        <v>0</v>
+      </c>
+      <c r="L1508">
+        <v>11</v>
+      </c>
+      <c r="M1508">
+        <v>11</v>
+      </c>
+      <c r="N1508">
+        <v>0</v>
+      </c>
+      <c r="O1508">
+        <v>0</v>
+      </c>
+      <c r="P1508">
+        <v>0</v>
+      </c>
+      <c r="Q1508">
+        <v>0</v>
+      </c>
+      <c r="R1508">
+        <v>0</v>
+      </c>
+      <c r="S1508">
+        <v>0</v>
+      </c>
+      <c r="T1508">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1509" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1509" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1509">
+        <v>1</v>
+      </c>
+      <c r="D1509">
+        <v>0</v>
+      </c>
+      <c r="E1509">
+        <v>0</v>
+      </c>
+      <c r="F1509">
+        <v>0</v>
+      </c>
+      <c r="I1509">
+        <v>0</v>
+      </c>
+      <c r="J1509">
+        <v>0</v>
+      </c>
+      <c r="L1509">
+        <v>0</v>
+      </c>
+      <c r="M1509">
+        <v>0</v>
+      </c>
+      <c r="N1509">
+        <v>0</v>
+      </c>
+      <c r="O1509">
+        <v>0</v>
+      </c>
+      <c r="P1509">
+        <v>0</v>
+      </c>
+      <c r="Q1509">
+        <v>1</v>
+      </c>
+      <c r="R1509">
+        <v>0</v>
+      </c>
+      <c r="S1509">
+        <v>0</v>
+      </c>
+      <c r="T1509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1510" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1510" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1510">
+        <v>1</v>
+      </c>
+      <c r="D1510">
+        <v>1</v>
+      </c>
+      <c r="E1510">
+        <v>0</v>
+      </c>
+      <c r="F1510">
+        <v>33</v>
+      </c>
+      <c r="G1510">
+        <v>33</v>
+      </c>
+      <c r="H1510">
+        <v>33</v>
+      </c>
+      <c r="I1510">
+        <v>0</v>
+      </c>
+      <c r="J1510">
+        <v>0</v>
+      </c>
+      <c r="K1510">
+        <v>157.13999999999999</v>
+      </c>
+      <c r="L1510">
+        <v>21</v>
+      </c>
+      <c r="M1510">
+        <v>7</v>
+      </c>
+      <c r="N1510">
+        <v>6</v>
+      </c>
+      <c r="O1510">
+        <v>0</v>
+      </c>
+      <c r="P1510">
+        <v>24.44</v>
+      </c>
+      <c r="Q1510">
+        <v>0</v>
+      </c>
+      <c r="R1510">
+        <v>0</v>
+      </c>
+      <c r="S1510">
+        <v>0</v>
+      </c>
+      <c r="T1510">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1511" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1511" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1511">
+        <v>1</v>
+      </c>
+      <c r="D1511">
+        <v>1</v>
+      </c>
+      <c r="E1511">
+        <v>0</v>
+      </c>
+      <c r="F1511">
+        <v>1</v>
+      </c>
+      <c r="G1511">
+        <v>1</v>
+      </c>
+      <c r="H1511">
+        <v>1</v>
+      </c>
+      <c r="I1511">
+        <v>0</v>
+      </c>
+      <c r="J1511">
+        <v>0</v>
+      </c>
+      <c r="K1511">
+        <v>14.29</v>
+      </c>
+      <c r="L1511">
+        <v>7</v>
+      </c>
+      <c r="M1511">
+        <v>6</v>
+      </c>
+      <c r="N1511">
+        <v>0</v>
+      </c>
+      <c r="O1511">
+        <v>0</v>
+      </c>
+      <c r="P1511">
+        <v>0.74</v>
+      </c>
+      <c r="Q1511">
+        <v>0</v>
+      </c>
+      <c r="R1511">
+        <v>0</v>
+      </c>
+      <c r="S1511">
+        <v>0</v>
+      </c>
+      <c r="T1511">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1512" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1512" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1512">
+        <v>1</v>
+      </c>
+      <c r="D1512">
+        <v>0</v>
+      </c>
+      <c r="E1512">
+        <v>0</v>
+      </c>
+      <c r="F1512">
+        <v>0</v>
+      </c>
+      <c r="I1512">
+        <v>0</v>
+      </c>
+      <c r="J1512">
+        <v>0</v>
+      </c>
+      <c r="L1512">
+        <v>0</v>
+      </c>
+      <c r="M1512">
+        <v>0</v>
+      </c>
+      <c r="N1512">
+        <v>0</v>
+      </c>
+      <c r="O1512">
+        <v>0</v>
+      </c>
+      <c r="P1512">
+        <v>0</v>
+      </c>
+      <c r="Q1512">
+        <v>0</v>
+      </c>
+      <c r="R1512">
+        <v>0</v>
+      </c>
+      <c r="S1512">
+        <v>0</v>
+      </c>
+      <c r="T1512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1513" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1513" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C1513">
+        <v>1</v>
+      </c>
+      <c r="D1513">
+        <v>0</v>
+      </c>
+      <c r="E1513">
+        <v>0</v>
+      </c>
+      <c r="F1513">
+        <v>0</v>
+      </c>
+      <c r="I1513">
+        <v>0</v>
+      </c>
+      <c r="J1513">
+        <v>0</v>
+      </c>
+      <c r="L1513">
+        <v>0</v>
+      </c>
+      <c r="M1513">
+        <v>0</v>
+      </c>
+      <c r="N1513">
+        <v>0</v>
+      </c>
+      <c r="O1513">
+        <v>0</v>
+      </c>
+      <c r="P1513">
+        <v>0</v>
+      </c>
+      <c r="Q1513">
+        <v>0</v>
+      </c>
+      <c r="R1513">
+        <v>0</v>
+      </c>
+      <c r="S1513">
+        <v>0</v>
+      </c>
+      <c r="T1513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1514" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1514" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1514">
+        <v>1</v>
+      </c>
+      <c r="D1514">
+        <v>0</v>
+      </c>
+      <c r="E1514">
+        <v>0</v>
+      </c>
+      <c r="F1514">
+        <v>0</v>
+      </c>
+      <c r="I1514">
+        <v>0</v>
+      </c>
+      <c r="J1514">
+        <v>0</v>
+      </c>
+      <c r="L1514">
+        <v>0</v>
+      </c>
+      <c r="M1514">
+        <v>0</v>
+      </c>
+      <c r="N1514">
+        <v>0</v>
+      </c>
+      <c r="O1514">
+        <v>0</v>
+      </c>
+      <c r="P1514">
+        <v>0</v>
+      </c>
+      <c r="Q1514">
+        <v>0</v>
+      </c>
+      <c r="R1514">
+        <v>0</v>
+      </c>
+      <c r="S1514">
+        <v>0</v>
+      </c>
+      <c r="T1514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1515" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1515" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1515">
+        <v>1</v>
+      </c>
+      <c r="D1515">
+        <v>1</v>
+      </c>
+      <c r="E1515">
+        <v>1</v>
+      </c>
+      <c r="F1515">
+        <v>24</v>
+      </c>
+      <c r="H1515" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1515">
+        <v>0</v>
+      </c>
+      <c r="J1515">
+        <v>0</v>
+      </c>
+      <c r="K1515">
+        <v>200</v>
+      </c>
+      <c r="L1515">
+        <v>12</v>
+      </c>
+      <c r="M1515">
+        <v>3</v>
+      </c>
+      <c r="N1515">
+        <v>5</v>
+      </c>
+      <c r="O1515">
+        <v>0</v>
+      </c>
+      <c r="P1515">
+        <v>17.78</v>
+      </c>
+      <c r="Q1515">
+        <v>0</v>
+      </c>
+      <c r="R1515">
+        <v>0</v>
+      </c>
+      <c r="S1515">
+        <v>0</v>
+      </c>
+      <c r="T1515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1516" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1516" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1516">
+        <v>1</v>
+      </c>
+      <c r="D1516">
+        <v>0</v>
+      </c>
+      <c r="E1516">
+        <v>0</v>
+      </c>
+      <c r="F1516">
+        <v>0</v>
+      </c>
+      <c r="I1516">
+        <v>0</v>
+      </c>
+      <c r="J1516">
+        <v>0</v>
+      </c>
+      <c r="L1516">
+        <v>0</v>
+      </c>
+      <c r="M1516">
+        <v>0</v>
+      </c>
+      <c r="N1516">
+        <v>0</v>
+      </c>
+      <c r="O1516">
+        <v>0</v>
+      </c>
+      <c r="P1516">
+        <v>0</v>
+      </c>
+      <c r="Q1516">
+        <v>0</v>
+      </c>
+      <c r="R1516">
+        <v>0</v>
+      </c>
+      <c r="S1516">
+        <v>0</v>
+      </c>
+      <c r="T1516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1517" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1517" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1517">
+        <v>1</v>
+      </c>
+      <c r="D1517">
+        <v>1</v>
+      </c>
+      <c r="E1517">
+        <v>1</v>
+      </c>
+      <c r="F1517">
+        <v>50</v>
+      </c>
+      <c r="H1517" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1517">
+        <v>1</v>
+      </c>
+      <c r="J1517">
+        <v>0</v>
+      </c>
+      <c r="K1517">
+        <v>161.29</v>
+      </c>
+      <c r="L1517">
+        <v>31</v>
+      </c>
+      <c r="M1517">
+        <v>7</v>
+      </c>
+      <c r="N1517">
+        <v>8</v>
+      </c>
+      <c r="O1517">
+        <v>0</v>
+      </c>
+      <c r="P1517">
+        <v>36.76</v>
+      </c>
+      <c r="Q1517">
+        <v>0</v>
+      </c>
+      <c r="R1517">
+        <v>0</v>
+      </c>
+      <c r="S1517">
+        <v>0</v>
+      </c>
+      <c r="T1517">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1518" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1518" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1518">
+        <v>1</v>
+      </c>
+      <c r="D1518">
+        <v>1</v>
+      </c>
+      <c r="E1518">
+        <v>1</v>
+      </c>
+      <c r="F1518">
+        <v>1</v>
+      </c>
+      <c r="H1518" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1518">
+        <v>0</v>
+      </c>
+      <c r="J1518">
+        <v>0</v>
+      </c>
+      <c r="K1518">
+        <v>100</v>
+      </c>
+      <c r="L1518">
+        <v>1</v>
+      </c>
+      <c r="M1518">
+        <v>0</v>
+      </c>
+      <c r="N1518">
+        <v>0</v>
+      </c>
+      <c r="O1518">
+        <v>0</v>
+      </c>
+      <c r="P1518">
+        <v>0.74</v>
+      </c>
+      <c r="Q1518">
+        <v>0</v>
+      </c>
+      <c r="R1518">
+        <v>0</v>
+      </c>
+      <c r="S1518">
+        <v>0</v>
+      </c>
+      <c r="T1518">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1519" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1519" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1519">
+        <v>1</v>
+      </c>
+      <c r="D1519">
+        <v>1</v>
+      </c>
+      <c r="E1519">
+        <v>0</v>
+      </c>
+      <c r="F1519">
+        <v>10</v>
+      </c>
+      <c r="G1519">
+        <v>10</v>
+      </c>
+      <c r="H1519">
+        <v>10</v>
+      </c>
+      <c r="I1519">
+        <v>0</v>
+      </c>
+      <c r="J1519">
+        <v>0</v>
+      </c>
+      <c r="K1519">
+        <v>90.91</v>
+      </c>
+      <c r="L1519">
+        <v>11</v>
+      </c>
+      <c r="M1519">
+        <v>4</v>
+      </c>
+      <c r="N1519">
+        <v>1</v>
+      </c>
+      <c r="O1519">
+        <v>0</v>
+      </c>
+      <c r="P1519">
+        <v>7.41</v>
+      </c>
+      <c r="Q1519">
+        <v>0</v>
+      </c>
+      <c r="R1519">
+        <v>0</v>
+      </c>
+      <c r="S1519">
+        <v>0</v>
+      </c>
+      <c r="T1519">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1520" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1520" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="C1520">
+        <v>1</v>
+      </c>
+      <c r="D1520">
+        <v>0</v>
+      </c>
+      <c r="E1520">
+        <v>0</v>
+      </c>
+      <c r="F1520">
+        <v>0</v>
+      </c>
+      <c r="I1520">
+        <v>0</v>
+      </c>
+      <c r="J1520">
+        <v>0</v>
+      </c>
+      <c r="L1520">
+        <v>0</v>
+      </c>
+      <c r="M1520">
+        <v>0</v>
+      </c>
+      <c r="N1520">
+        <v>0</v>
+      </c>
+      <c r="O1520">
+        <v>0</v>
+      </c>
+      <c r="P1520">
+        <v>0</v>
+      </c>
+      <c r="Q1520">
+        <v>0</v>
+      </c>
+      <c r="R1520">
+        <v>0</v>
+      </c>
+      <c r="S1520">
+        <v>0</v>
+      </c>
+      <c r="T1520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1521" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1521" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1521">
+        <v>1</v>
+      </c>
+      <c r="D1521">
+        <v>1</v>
+      </c>
+      <c r="E1521">
+        <v>0</v>
+      </c>
+      <c r="F1521">
+        <v>2</v>
+      </c>
+      <c r="G1521">
+        <v>2</v>
+      </c>
+      <c r="H1521">
+        <v>2</v>
+      </c>
+      <c r="I1521">
+        <v>0</v>
+      </c>
+      <c r="J1521">
+        <v>0</v>
+      </c>
+      <c r="K1521">
+        <v>25</v>
+      </c>
+      <c r="L1521">
+        <v>8</v>
+      </c>
+      <c r="M1521">
+        <v>6</v>
+      </c>
+      <c r="N1521">
+        <v>0</v>
+      </c>
+      <c r="O1521">
+        <v>0</v>
+      </c>
+      <c r="P1521">
+        <v>1.48</v>
+      </c>
+      <c r="Q1521">
+        <v>0</v>
+      </c>
+      <c r="R1521">
+        <v>0</v>
+      </c>
+      <c r="S1521">
+        <v>0</v>
+      </c>
+      <c r="T1521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1522" t="s">
+        <v>454</v>
+      </c>
+      <c r="B1522" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1522">
+        <v>1</v>
+      </c>
+      <c r="D1522">
+        <v>1</v>
+      </c>
+      <c r="E1522">
+        <v>0</v>
+      </c>
+      <c r="F1522">
+        <v>31</v>
+      </c>
+      <c r="G1522">
+        <v>31</v>
+      </c>
+      <c r="H1522">
+        <v>31</v>
+      </c>
+      <c r="I1522">
+        <v>0</v>
+      </c>
+      <c r="J1522">
+        <v>0</v>
+      </c>
+      <c r="K1522">
+        <v>68.89</v>
+      </c>
+      <c r="L1522">
+        <v>45</v>
+      </c>
+      <c r="M1522">
+        <v>20</v>
+      </c>
+      <c r="N1522">
+        <v>1</v>
+      </c>
+      <c r="O1522">
+        <v>0</v>
+      </c>
+      <c r="P1522">
+        <v>22.79</v>
+      </c>
+      <c r="Q1522">
+        <v>0</v>
+      </c>
+      <c r="R1522">
+        <v>0</v>
+      </c>
+      <c r="S1522">
+        <v>0</v>
+      </c>
+      <c r="T1522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1523" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1523" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C1523">
+        <v>1</v>
+      </c>
+      <c r="D1523">
+        <v>1</v>
+      </c>
+      <c r="E1523">
+        <v>0</v>
+      </c>
+      <c r="F1523">
+        <v>13</v>
+      </c>
+      <c r="G1523">
+        <v>13</v>
+      </c>
+      <c r="H1523">
+        <v>13</v>
+      </c>
+      <c r="I1523">
+        <v>0</v>
+      </c>
+      <c r="J1523">
+        <v>0</v>
+      </c>
+      <c r="K1523">
+        <v>43.33</v>
+      </c>
+      <c r="L1523">
+        <v>30</v>
+      </c>
+      <c r="M1523">
+        <v>23</v>
+      </c>
+      <c r="N1523">
+        <v>2</v>
+      </c>
+      <c r="O1523">
+        <v>0</v>
+      </c>
+      <c r="P1523">
+        <v>12.87</v>
+      </c>
+      <c r="Q1523">
+        <v>0</v>
+      </c>
+      <c r="R1523">
+        <v>0</v>
+      </c>
+      <c r="S1523">
+        <v>0</v>
+      </c>
+      <c r="T1523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1524" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1524" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C1524">
+        <v>1</v>
+      </c>
+      <c r="D1524">
+        <v>0</v>
+      </c>
+      <c r="E1524">
+        <v>0</v>
+      </c>
+      <c r="F1524">
+        <v>0</v>
+      </c>
+      <c r="I1524">
+        <v>0</v>
+      </c>
+      <c r="J1524">
+        <v>0</v>
+      </c>
+      <c r="L1524">
+        <v>0</v>
+      </c>
+      <c r="M1524">
+        <v>0</v>
+      </c>
+      <c r="N1524">
+        <v>0</v>
+      </c>
+      <c r="O1524">
+        <v>0</v>
+      </c>
+      <c r="P1524">
+        <v>0</v>
+      </c>
+      <c r="Q1524">
+        <v>0</v>
+      </c>
+      <c r="R1524">
+        <v>0</v>
+      </c>
+      <c r="S1524">
+        <v>0</v>
+      </c>
+      <c r="T1524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1525" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1525" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1525">
+        <v>1</v>
+      </c>
+      <c r="D1525">
+        <v>0</v>
+      </c>
+      <c r="E1525">
+        <v>0</v>
+      </c>
+      <c r="F1525">
+        <v>0</v>
+      </c>
+      <c r="I1525">
+        <v>0</v>
+      </c>
+      <c r="J1525">
+        <v>0</v>
+      </c>
+      <c r="L1525">
+        <v>0</v>
+      </c>
+      <c r="M1525">
+        <v>0</v>
+      </c>
+      <c r="N1525">
+        <v>0</v>
+      </c>
+      <c r="O1525">
+        <v>0</v>
+      </c>
+      <c r="P1525">
+        <v>0</v>
+      </c>
+      <c r="Q1525">
+        <v>0</v>
+      </c>
+      <c r="R1525">
+        <v>0</v>
+      </c>
+      <c r="S1525">
+        <v>0</v>
+      </c>
+      <c r="T1525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1526" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1526" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1526">
+        <v>1</v>
+      </c>
+      <c r="D1526">
+        <v>1</v>
+      </c>
+      <c r="E1526">
+        <v>0</v>
+      </c>
+      <c r="F1526">
+        <v>0</v>
+      </c>
+      <c r="G1526">
+        <v>0</v>
+      </c>
+      <c r="H1526">
+        <v>0</v>
+      </c>
+      <c r="I1526">
+        <v>0</v>
+      </c>
+      <c r="J1526">
+        <v>0</v>
+      </c>
+      <c r="K1526">
+        <v>0</v>
+      </c>
+      <c r="L1526">
+        <v>6</v>
+      </c>
+      <c r="M1526">
+        <v>6</v>
+      </c>
+      <c r="N1526">
+        <v>0</v>
+      </c>
+      <c r="O1526">
+        <v>0</v>
+      </c>
+      <c r="P1526">
+        <v>0</v>
+      </c>
+      <c r="Q1526">
+        <v>0</v>
+      </c>
+      <c r="R1526">
+        <v>0</v>
+      </c>
+      <c r="S1526">
+        <v>0</v>
+      </c>
+      <c r="T1526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1527" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1527" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C1527">
+        <v>1</v>
+      </c>
+      <c r="D1527">
+        <v>1</v>
+      </c>
+      <c r="E1527">
+        <v>0</v>
+      </c>
+      <c r="F1527">
+        <v>29</v>
+      </c>
+      <c r="G1527">
+        <v>29</v>
+      </c>
+      <c r="H1527">
+        <v>29</v>
+      </c>
+      <c r="I1527">
+        <v>0</v>
+      </c>
+      <c r="J1527">
+        <v>0</v>
+      </c>
+      <c r="K1527">
+        <v>78.38</v>
+      </c>
+      <c r="L1527">
+        <v>37</v>
+      </c>
+      <c r="M1527">
+        <v>20</v>
+      </c>
+      <c r="N1527">
+        <v>4</v>
+      </c>
+      <c r="O1527">
+        <v>0</v>
+      </c>
+      <c r="P1527">
+        <v>28.71</v>
+      </c>
+      <c r="Q1527">
+        <v>0</v>
+      </c>
+      <c r="R1527">
+        <v>0</v>
+      </c>
+      <c r="S1527">
+        <v>0</v>
+      </c>
+      <c r="T1527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1528" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1528" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1528">
+        <v>1</v>
+      </c>
+      <c r="D1528">
+        <v>1</v>
+      </c>
+      <c r="E1528">
+        <v>0</v>
+      </c>
+      <c r="F1528">
+        <v>1</v>
+      </c>
+      <c r="G1528">
+        <v>1</v>
+      </c>
+      <c r="H1528">
+        <v>1</v>
+      </c>
+      <c r="I1528">
+        <v>0</v>
+      </c>
+      <c r="J1528">
+        <v>0</v>
+      </c>
+      <c r="K1528">
+        <v>20</v>
+      </c>
+      <c r="L1528">
+        <v>5</v>
+      </c>
+      <c r="M1528">
+        <v>4</v>
+      </c>
+      <c r="N1528">
+        <v>0</v>
+      </c>
+      <c r="O1528">
+        <v>0</v>
+      </c>
+      <c r="P1528">
+        <v>0.99</v>
+      </c>
+      <c r="Q1528">
+        <v>0</v>
+      </c>
+      <c r="R1528">
+        <v>0</v>
+      </c>
+      <c r="S1528">
+        <v>0</v>
+      </c>
+      <c r="T1528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1529" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1529" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C1529">
+        <v>1</v>
+      </c>
+      <c r="D1529">
+        <v>1</v>
+      </c>
+      <c r="E1529">
+        <v>0</v>
+      </c>
+      <c r="F1529">
+        <v>7</v>
+      </c>
+      <c r="G1529">
+        <v>7</v>
+      </c>
+      <c r="H1529">
+        <v>7</v>
+      </c>
+      <c r="I1529">
+        <v>0</v>
+      </c>
+      <c r="J1529">
+        <v>0</v>
+      </c>
+      <c r="K1529">
+        <v>63.64</v>
+      </c>
+      <c r="L1529">
+        <v>11</v>
+      </c>
+      <c r="M1529">
+        <v>7</v>
+      </c>
+      <c r="N1529">
+        <v>1</v>
+      </c>
+      <c r="O1529">
+        <v>0</v>
+      </c>
+      <c r="P1529">
+        <v>6.86</v>
+      </c>
+      <c r="Q1529">
+        <v>0</v>
+      </c>
+      <c r="R1529">
+        <v>0</v>
+      </c>
+      <c r="S1529">
+        <v>0</v>
+      </c>
+      <c r="T1529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1530" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1530" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1530">
+        <v>1</v>
+      </c>
+      <c r="D1530">
+        <v>1</v>
+      </c>
+      <c r="E1530">
+        <v>0</v>
+      </c>
+      <c r="F1530">
+        <v>2</v>
+      </c>
+      <c r="G1530">
+        <v>2</v>
+      </c>
+      <c r="H1530">
+        <v>2</v>
+      </c>
+      <c r="I1530">
+        <v>0</v>
+      </c>
+      <c r="J1530">
+        <v>0</v>
+      </c>
+      <c r="K1530">
+        <v>14.29</v>
+      </c>
+      <c r="L1530">
+        <v>14</v>
+      </c>
+      <c r="M1530">
+        <v>12</v>
+      </c>
+      <c r="N1530">
+        <v>0</v>
+      </c>
+      <c r="O1530">
+        <v>0</v>
+      </c>
+      <c r="P1530">
+        <v>1.98</v>
+      </c>
+      <c r="Q1530">
+        <v>0</v>
+      </c>
+      <c r="R1530">
+        <v>0</v>
+      </c>
+      <c r="S1530">
+        <v>0</v>
+      </c>
+      <c r="T1530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1531" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1531" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C1531">
+        <v>1</v>
+      </c>
+      <c r="D1531">
+        <v>1</v>
+      </c>
+      <c r="E1531">
+        <v>0</v>
+      </c>
+      <c r="F1531">
+        <v>0</v>
+      </c>
+      <c r="G1531">
+        <v>0</v>
+      </c>
+      <c r="H1531">
+        <v>0</v>
+      </c>
+      <c r="I1531">
+        <v>0</v>
+      </c>
+      <c r="J1531">
+        <v>0</v>
+      </c>
+      <c r="K1531">
+        <v>0</v>
+      </c>
+      <c r="L1531">
+        <v>1</v>
+      </c>
+      <c r="M1531">
+        <v>1</v>
+      </c>
+      <c r="N1531">
+        <v>0</v>
+      </c>
+      <c r="O1531">
+        <v>0</v>
+      </c>
+      <c r="P1531">
+        <v>0</v>
+      </c>
+      <c r="Q1531">
+        <v>0</v>
+      </c>
+      <c r="R1531">
+        <v>0</v>
+      </c>
+      <c r="S1531">
+        <v>0</v>
+      </c>
+      <c r="T1531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1532" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1532" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1532">
+        <v>1</v>
+      </c>
+      <c r="D1532">
+        <v>1</v>
+      </c>
+      <c r="E1532">
+        <v>1</v>
+      </c>
+      <c r="F1532">
+        <v>0</v>
+      </c>
+      <c r="H1532" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1532">
+        <v>0</v>
+      </c>
+      <c r="J1532">
+        <v>0</v>
+      </c>
+      <c r="K1532">
+        <v>0</v>
+      </c>
+      <c r="L1532">
+        <v>3</v>
+      </c>
+      <c r="M1532">
+        <v>3</v>
+      </c>
+      <c r="N1532">
+        <v>0</v>
+      </c>
+      <c r="O1532">
+        <v>0</v>
+      </c>
+      <c r="P1532">
+        <v>0</v>
+      </c>
+      <c r="Q1532">
+        <v>0</v>
+      </c>
+      <c r="R1532">
+        <v>0</v>
+      </c>
+      <c r="S1532">
+        <v>0</v>
+      </c>
+      <c r="T1532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1533" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1533" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C1533">
+        <v>1</v>
+      </c>
+      <c r="D1533">
+        <v>1</v>
+      </c>
+      <c r="E1533">
+        <v>1</v>
+      </c>
+      <c r="F1533">
+        <v>0</v>
+      </c>
+      <c r="H1533" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1533">
+        <v>0</v>
+      </c>
+      <c r="J1533">
+        <v>0</v>
+      </c>
+      <c r="K1533">
+        <v>0</v>
+      </c>
+      <c r="L1533">
+        <v>2</v>
+      </c>
+      <c r="M1533">
+        <v>2</v>
+      </c>
+      <c r="N1533">
+        <v>0</v>
+      </c>
+      <c r="O1533">
+        <v>0</v>
+      </c>
+      <c r="P1533">
+        <v>0</v>
+      </c>
+      <c r="Q1533">
+        <v>0</v>
+      </c>
+      <c r="R1533">
+        <v>0</v>
+      </c>
+      <c r="S1533">
+        <v>0</v>
+      </c>
+      <c r="T1533">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1534" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1534" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1534">
+        <v>1</v>
+      </c>
+      <c r="D1534">
+        <v>1</v>
+      </c>
+      <c r="E1534">
+        <v>0</v>
+      </c>
+      <c r="F1534">
+        <v>22</v>
+      </c>
+      <c r="G1534">
+        <v>22</v>
+      </c>
+      <c r="H1534">
+        <v>22</v>
+      </c>
+      <c r="I1534">
+        <v>0</v>
+      </c>
+      <c r="J1534">
+        <v>0</v>
+      </c>
+      <c r="K1534">
+        <v>81.48</v>
+      </c>
+      <c r="L1534">
+        <v>27</v>
+      </c>
+      <c r="M1534">
+        <v>15</v>
+      </c>
+      <c r="N1534">
+        <v>3</v>
+      </c>
+      <c r="O1534">
+        <v>0</v>
+      </c>
+      <c r="P1534">
+        <v>21.57</v>
+      </c>
+      <c r="Q1534">
+        <v>0</v>
+      </c>
+      <c r="R1534">
+        <v>0</v>
+      </c>
+      <c r="S1534">
+        <v>0</v>
+      </c>
+      <c r="T1534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1535" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1535" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1535">
+        <v>1</v>
+      </c>
+      <c r="D1535">
+        <v>1</v>
+      </c>
+      <c r="E1535">
+        <v>1</v>
+      </c>
+      <c r="F1535">
+        <v>12</v>
+      </c>
+      <c r="H1535" t="s">
+        <v>266</v>
+      </c>
+      <c r="I1535">
+        <v>0</v>
+      </c>
+      <c r="J1535">
+        <v>0</v>
+      </c>
+      <c r="K1535">
+        <v>48</v>
+      </c>
+      <c r="L1535">
+        <v>25</v>
+      </c>
+      <c r="M1535">
+        <v>16</v>
+      </c>
+      <c r="N1535">
+        <v>1</v>
+      </c>
+      <c r="O1535">
+        <v>0</v>
+      </c>
+      <c r="P1535">
+        <v>11.76</v>
+      </c>
+      <c r="Q1535">
+        <v>0</v>
+      </c>
+      <c r="R1535">
+        <v>0</v>
+      </c>
+      <c r="S1535">
+        <v>0</v>
+      </c>
+      <c r="T1535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1536" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1536" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1536">
+        <v>1</v>
+      </c>
+      <c r="D1536">
+        <v>1</v>
+      </c>
+      <c r="E1536">
+        <v>0</v>
+      </c>
+      <c r="F1536">
+        <v>4</v>
+      </c>
+      <c r="G1536">
+        <v>4</v>
+      </c>
+      <c r="H1536">
+        <v>4</v>
+      </c>
+      <c r="I1536">
+        <v>0</v>
+      </c>
+      <c r="J1536">
+        <v>0</v>
+      </c>
+      <c r="K1536">
+        <v>80</v>
+      </c>
+      <c r="L1536">
+        <v>5</v>
+      </c>
+      <c r="M1536">
+        <v>4</v>
+      </c>
+      <c r="N1536">
+        <v>1</v>
+      </c>
+      <c r="O1536">
+        <v>0</v>
+      </c>
+      <c r="P1536">
+        <v>3.96</v>
+      </c>
+      <c r="Q1536">
+        <v>0</v>
+      </c>
+      <c r="R1536">
+        <v>0</v>
+      </c>
+      <c r="S1536">
+        <v>0</v>
+      </c>
+      <c r="T1536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1537" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1537" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C1537">
+        <v>1</v>
+      </c>
+      <c r="D1537">
+        <v>0</v>
+      </c>
+      <c r="E1537">
+        <v>0</v>
+      </c>
+      <c r="F1537">
+        <v>0</v>
+      </c>
+      <c r="I1537">
+        <v>0</v>
+      </c>
+      <c r="J1537">
+        <v>0</v>
+      </c>
+      <c r="L1537">
+        <v>0</v>
+      </c>
+      <c r="M1537">
+        <v>0</v>
+      </c>
+      <c r="N1537">
+        <v>0</v>
+      </c>
+      <c r="O1537">
+        <v>0</v>
+      </c>
+      <c r="P1537">
+        <v>0</v>
+      </c>
+      <c r="Q1537">
+        <v>0</v>
+      </c>
+      <c r="R1537">
+        <v>0</v>
+      </c>
+      <c r="S1537">
+        <v>0</v>
+      </c>
+      <c r="T1537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1538" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1538" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C1538">
+        <v>1</v>
+      </c>
+      <c r="D1538">
+        <v>0</v>
+      </c>
+      <c r="E1538">
+        <v>0</v>
+      </c>
+      <c r="F1538">
+        <v>0</v>
+      </c>
+      <c r="I1538">
+        <v>0</v>
+      </c>
+      <c r="J1538">
+        <v>0</v>
+      </c>
+      <c r="L1538">
+        <v>0</v>
+      </c>
+      <c r="M1538">
+        <v>0</v>
+      </c>
+      <c r="N1538">
+        <v>0</v>
+      </c>
+      <c r="O1538">
+        <v>0</v>
+      </c>
+      <c r="P1538">
+        <v>0</v>
+      </c>
+      <c r="Q1538">
+        <v>0</v>
+      </c>
+      <c r="R1538">
+        <v>0</v>
+      </c>
+      <c r="S1538">
+        <v>0</v>
+      </c>
+      <c r="T1538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1539" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1539" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1539">
+        <v>1</v>
+      </c>
+      <c r="D1539">
+        <v>1</v>
+      </c>
+      <c r="E1539">
+        <v>1</v>
+      </c>
+      <c r="F1539">
+        <v>2</v>
+      </c>
+      <c r="H1539" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1539">
+        <v>0</v>
+      </c>
+      <c r="J1539">
+        <v>0</v>
+      </c>
+      <c r="K1539">
+        <v>33.33</v>
+      </c>
+      <c r="L1539">
+        <v>6</v>
+      </c>
+      <c r="M1539">
+        <v>4</v>
+      </c>
+      <c r="N1539">
+        <v>0</v>
+      </c>
+      <c r="O1539">
+        <v>0</v>
+      </c>
+      <c r="P1539">
+        <v>1.98</v>
+      </c>
+      <c r="Q1539">
+        <v>0</v>
+      </c>
+      <c r="R1539">
+        <v>0</v>
+      </c>
+      <c r="S1539">
+        <v>0</v>
+      </c>
+      <c r="T1539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1540" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1540" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1540">
+        <v>1</v>
+      </c>
+      <c r="D1540">
+        <v>1</v>
+      </c>
+      <c r="E1540">
+        <v>0</v>
+      </c>
+      <c r="F1540">
+        <v>1</v>
+      </c>
+      <c r="G1540">
+        <v>1</v>
+      </c>
+      <c r="H1540">
+        <v>1</v>
+      </c>
+      <c r="I1540">
+        <v>0</v>
+      </c>
+      <c r="J1540">
+        <v>0</v>
+      </c>
+      <c r="K1540">
+        <v>50</v>
+      </c>
+      <c r="L1540">
+        <v>2</v>
+      </c>
+      <c r="M1540">
+        <v>1</v>
+      </c>
+      <c r="N1540">
+        <v>0</v>
+      </c>
+      <c r="O1540">
+        <v>0</v>
+      </c>
+      <c r="P1540">
+        <v>0.98</v>
+      </c>
+      <c r="Q1540">
+        <v>0</v>
+      </c>
+      <c r="R1540">
+        <v>0</v>
+      </c>
+      <c r="S1540">
+        <v>0</v>
+      </c>
+      <c r="T1540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1541" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1541" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1541">
+        <v>1</v>
+      </c>
+      <c r="D1541">
+        <v>0</v>
+      </c>
+      <c r="E1541">
+        <v>0</v>
+      </c>
+      <c r="F1541">
+        <v>0</v>
+      </c>
+      <c r="I1541">
+        <v>0</v>
+      </c>
+      <c r="J1541">
+        <v>0</v>
+      </c>
+      <c r="L1541">
+        <v>0</v>
+      </c>
+      <c r="M1541">
+        <v>0</v>
+      </c>
+      <c r="N1541">
+        <v>0</v>
+      </c>
+      <c r="O1541">
+        <v>0</v>
+      </c>
+      <c r="P1541">
+        <v>0</v>
+      </c>
+      <c r="Q1541">
+        <v>0</v>
+      </c>
+      <c r="R1541">
+        <v>0</v>
+      </c>
+      <c r="S1541">
+        <v>0</v>
+      </c>
+      <c r="T1541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1542" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1542" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1542">
+        <v>1</v>
+      </c>
+      <c r="D1542">
+        <v>1</v>
+      </c>
+      <c r="E1542">
+        <v>1</v>
+      </c>
+      <c r="F1542">
+        <v>3</v>
+      </c>
+      <c r="H1542" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1542">
+        <v>0</v>
+      </c>
+      <c r="J1542">
+        <v>0</v>
+      </c>
+      <c r="K1542">
+        <v>23.08</v>
+      </c>
+      <c r="L1542">
+        <v>13</v>
+      </c>
+      <c r="M1542">
+        <v>10</v>
+      </c>
+      <c r="N1542">
+        <v>0</v>
+      </c>
+      <c r="O1542">
+        <v>0</v>
+      </c>
+      <c r="P1542">
+        <v>2.97</v>
+      </c>
+      <c r="Q1542">
+        <v>0</v>
+      </c>
+      <c r="R1542">
+        <v>0</v>
+      </c>
+      <c r="S1542">
+        <v>0</v>
+      </c>
+      <c r="T1542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1543" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1543" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1543">
+        <v>1</v>
+      </c>
+      <c r="D1543">
+        <v>0</v>
+      </c>
+      <c r="E1543">
+        <v>0</v>
+      </c>
+      <c r="F1543">
+        <v>0</v>
+      </c>
+      <c r="I1543">
+        <v>0</v>
+      </c>
+      <c r="J1543">
+        <v>0</v>
+      </c>
+      <c r="L1543">
+        <v>0</v>
+      </c>
+      <c r="M1543">
+        <v>0</v>
+      </c>
+      <c r="N1543">
+        <v>0</v>
+      </c>
+      <c r="O1543">
+        <v>0</v>
+      </c>
+      <c r="P1543">
+        <v>0</v>
+      </c>
+      <c r="Q1543">
+        <v>0</v>
+      </c>
+      <c r="R1543">
+        <v>2</v>
+      </c>
+      <c r="S1543">
+        <v>0</v>
+      </c>
+      <c r="T1543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1544" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1544" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1544">
+        <v>1</v>
+      </c>
+      <c r="D1544">
+        <v>1</v>
+      </c>
+      <c r="E1544">
+        <v>1</v>
+      </c>
+      <c r="F1544">
+        <v>26</v>
+      </c>
+      <c r="H1544" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1544">
+        <v>0</v>
+      </c>
+      <c r="J1544">
+        <v>0</v>
+      </c>
+      <c r="K1544">
+        <v>78.790000000000006</v>
+      </c>
+      <c r="L1544">
+        <v>33</v>
+      </c>
+      <c r="M1544">
+        <v>19</v>
+      </c>
+      <c r="N1544">
+        <v>4</v>
+      </c>
+      <c r="O1544">
+        <v>0</v>
+      </c>
+      <c r="P1544">
+        <v>25.49</v>
+      </c>
+      <c r="Q1544">
+        <v>0</v>
+      </c>
+      <c r="R1544">
+        <v>0</v>
+      </c>
+      <c r="S1544">
+        <v>0</v>
+      </c>
+      <c r="T1544">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3406" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3454" uniqueCount="466">
   <si>
     <t>Group</t>
   </si>
@@ -1415,6 +1415,9 @@
   <si>
     <t>Olivia Cunningham</t>
   </si>
+  <si>
+    <t>Lisburn Women 1st XI v North Down Women 1st XI, Wallace Park - 21 July 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -2221,7 +2224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1544"/>
+  <dimension ref="A1:T1566"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -92508,6 +92511,1250 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1545" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1545" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1545">
+        <v>1</v>
+      </c>
+      <c r="D1545">
+        <v>0</v>
+      </c>
+      <c r="E1545">
+        <v>0</v>
+      </c>
+      <c r="F1545">
+        <v>0</v>
+      </c>
+      <c r="I1545">
+        <v>0</v>
+      </c>
+      <c r="J1545">
+        <v>0</v>
+      </c>
+      <c r="L1545">
+        <v>0</v>
+      </c>
+      <c r="M1545">
+        <v>0</v>
+      </c>
+      <c r="N1545">
+        <v>0</v>
+      </c>
+      <c r="O1545">
+        <v>0</v>
+      </c>
+      <c r="P1545">
+        <v>0</v>
+      </c>
+      <c r="Q1545">
+        <v>0</v>
+      </c>
+      <c r="R1545">
+        <v>0</v>
+      </c>
+      <c r="S1545">
+        <v>0</v>
+      </c>
+      <c r="T1545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1546" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1546">
+        <v>1</v>
+      </c>
+      <c r="D1546">
+        <v>0</v>
+      </c>
+      <c r="E1546">
+        <v>0</v>
+      </c>
+      <c r="F1546">
+        <v>0</v>
+      </c>
+      <c r="I1546">
+        <v>0</v>
+      </c>
+      <c r="J1546">
+        <v>0</v>
+      </c>
+      <c r="L1546">
+        <v>0</v>
+      </c>
+      <c r="M1546">
+        <v>0</v>
+      </c>
+      <c r="N1546">
+        <v>0</v>
+      </c>
+      <c r="O1546">
+        <v>0</v>
+      </c>
+      <c r="P1546">
+        <v>0</v>
+      </c>
+      <c r="Q1546">
+        <v>0</v>
+      </c>
+      <c r="R1546">
+        <v>0</v>
+      </c>
+      <c r="S1546">
+        <v>0</v>
+      </c>
+      <c r="T1546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1547" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1547">
+        <v>1</v>
+      </c>
+      <c r="D1547">
+        <v>0</v>
+      </c>
+      <c r="E1547">
+        <v>0</v>
+      </c>
+      <c r="F1547">
+        <v>0</v>
+      </c>
+      <c r="I1547">
+        <v>0</v>
+      </c>
+      <c r="J1547">
+        <v>0</v>
+      </c>
+      <c r="L1547">
+        <v>0</v>
+      </c>
+      <c r="M1547">
+        <v>0</v>
+      </c>
+      <c r="N1547">
+        <v>0</v>
+      </c>
+      <c r="O1547">
+        <v>0</v>
+      </c>
+      <c r="P1547">
+        <v>0</v>
+      </c>
+      <c r="Q1547">
+        <v>0</v>
+      </c>
+      <c r="R1547">
+        <v>0</v>
+      </c>
+      <c r="S1547">
+        <v>0</v>
+      </c>
+      <c r="T1547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1548" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1548">
+        <v>1</v>
+      </c>
+      <c r="D1548">
+        <v>1</v>
+      </c>
+      <c r="E1548">
+        <v>1</v>
+      </c>
+      <c r="F1548">
+        <v>24</v>
+      </c>
+      <c r="H1548" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1548">
+        <v>0</v>
+      </c>
+      <c r="J1548">
+        <v>0</v>
+      </c>
+      <c r="K1548">
+        <v>88.89</v>
+      </c>
+      <c r="L1548">
+        <v>27</v>
+      </c>
+      <c r="M1548">
+        <v>11</v>
+      </c>
+      <c r="N1548">
+        <v>2</v>
+      </c>
+      <c r="O1548">
+        <v>0</v>
+      </c>
+      <c r="P1548">
+        <v>21.43</v>
+      </c>
+      <c r="Q1548">
+        <v>0</v>
+      </c>
+      <c r="R1548">
+        <v>0</v>
+      </c>
+      <c r="S1548">
+        <v>0</v>
+      </c>
+      <c r="T1548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1549" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>435</v>
+      </c>
+      <c r="C1549">
+        <v>1</v>
+      </c>
+      <c r="D1549">
+        <v>1</v>
+      </c>
+      <c r="E1549">
+        <v>1</v>
+      </c>
+      <c r="F1549">
+        <v>6</v>
+      </c>
+      <c r="H1549" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1549">
+        <v>0</v>
+      </c>
+      <c r="J1549">
+        <v>0</v>
+      </c>
+      <c r="K1549">
+        <v>40</v>
+      </c>
+      <c r="L1549">
+        <v>15</v>
+      </c>
+      <c r="M1549">
+        <v>10</v>
+      </c>
+      <c r="N1549">
+        <v>0</v>
+      </c>
+      <c r="O1549">
+        <v>0</v>
+      </c>
+      <c r="P1549">
+        <v>5.36</v>
+      </c>
+      <c r="Q1549">
+        <v>0</v>
+      </c>
+      <c r="R1549">
+        <v>0</v>
+      </c>
+      <c r="S1549">
+        <v>0</v>
+      </c>
+      <c r="T1549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1550" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1550">
+        <v>1</v>
+      </c>
+      <c r="D1550">
+        <v>0</v>
+      </c>
+      <c r="E1550">
+        <v>0</v>
+      </c>
+      <c r="F1550">
+        <v>0</v>
+      </c>
+      <c r="I1550">
+        <v>0</v>
+      </c>
+      <c r="J1550">
+        <v>0</v>
+      </c>
+      <c r="L1550">
+        <v>0</v>
+      </c>
+      <c r="M1550">
+        <v>0</v>
+      </c>
+      <c r="N1550">
+        <v>0</v>
+      </c>
+      <c r="O1550">
+        <v>0</v>
+      </c>
+      <c r="P1550">
+        <v>0</v>
+      </c>
+      <c r="Q1550">
+        <v>0</v>
+      </c>
+      <c r="R1550">
+        <v>0</v>
+      </c>
+      <c r="S1550">
+        <v>0</v>
+      </c>
+      <c r="T1550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1551" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1551">
+        <v>1</v>
+      </c>
+      <c r="D1551">
+        <v>1</v>
+      </c>
+      <c r="E1551">
+        <v>1</v>
+      </c>
+      <c r="F1551">
+        <v>66</v>
+      </c>
+      <c r="H1551" t="s">
+        <v>442</v>
+      </c>
+      <c r="I1551">
+        <v>1</v>
+      </c>
+      <c r="J1551">
+        <v>0</v>
+      </c>
+      <c r="K1551">
+        <v>140.43</v>
+      </c>
+      <c r="L1551">
+        <v>47</v>
+      </c>
+      <c r="M1551">
+        <v>16</v>
+      </c>
+      <c r="N1551">
+        <v>9</v>
+      </c>
+      <c r="O1551">
+        <v>0</v>
+      </c>
+      <c r="P1551">
+        <v>58.41</v>
+      </c>
+      <c r="Q1551">
+        <v>0</v>
+      </c>
+      <c r="R1551">
+        <v>0</v>
+      </c>
+      <c r="S1551">
+        <v>0</v>
+      </c>
+      <c r="T1551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1552" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1552">
+        <v>1</v>
+      </c>
+      <c r="D1552">
+        <v>1</v>
+      </c>
+      <c r="E1552">
+        <v>0</v>
+      </c>
+      <c r="F1552">
+        <v>0</v>
+      </c>
+      <c r="G1552">
+        <v>0</v>
+      </c>
+      <c r="H1552">
+        <v>0</v>
+      </c>
+      <c r="I1552">
+        <v>0</v>
+      </c>
+      <c r="J1552">
+        <v>0</v>
+      </c>
+      <c r="K1552">
+        <v>0</v>
+      </c>
+      <c r="L1552">
+        <v>1</v>
+      </c>
+      <c r="M1552">
+        <v>1</v>
+      </c>
+      <c r="N1552">
+        <v>0</v>
+      </c>
+      <c r="O1552">
+        <v>0</v>
+      </c>
+      <c r="P1552">
+        <v>0</v>
+      </c>
+      <c r="Q1552">
+        <v>0</v>
+      </c>
+      <c r="R1552">
+        <v>0</v>
+      </c>
+      <c r="S1552">
+        <v>0</v>
+      </c>
+      <c r="T1552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1553" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1553">
+        <v>1</v>
+      </c>
+      <c r="D1553">
+        <v>0</v>
+      </c>
+      <c r="E1553">
+        <v>0</v>
+      </c>
+      <c r="F1553">
+        <v>0</v>
+      </c>
+      <c r="I1553">
+        <v>0</v>
+      </c>
+      <c r="J1553">
+        <v>0</v>
+      </c>
+      <c r="L1553">
+        <v>0</v>
+      </c>
+      <c r="M1553">
+        <v>0</v>
+      </c>
+      <c r="N1553">
+        <v>0</v>
+      </c>
+      <c r="O1553">
+        <v>0</v>
+      </c>
+      <c r="P1553">
+        <v>0</v>
+      </c>
+      <c r="Q1553">
+        <v>0</v>
+      </c>
+      <c r="R1553">
+        <v>0</v>
+      </c>
+      <c r="S1553">
+        <v>0</v>
+      </c>
+      <c r="T1553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1554" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1554">
+        <v>1</v>
+      </c>
+      <c r="D1554">
+        <v>0</v>
+      </c>
+      <c r="E1554">
+        <v>0</v>
+      </c>
+      <c r="F1554">
+        <v>0</v>
+      </c>
+      <c r="I1554">
+        <v>0</v>
+      </c>
+      <c r="J1554">
+        <v>0</v>
+      </c>
+      <c r="L1554">
+        <v>0</v>
+      </c>
+      <c r="M1554">
+        <v>0</v>
+      </c>
+      <c r="N1554">
+        <v>0</v>
+      </c>
+      <c r="O1554">
+        <v>0</v>
+      </c>
+      <c r="P1554">
+        <v>0</v>
+      </c>
+      <c r="Q1554">
+        <v>0</v>
+      </c>
+      <c r="R1554">
+        <v>0</v>
+      </c>
+      <c r="S1554">
+        <v>0</v>
+      </c>
+      <c r="T1554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1555" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1555">
+        <v>1</v>
+      </c>
+      <c r="D1555">
+        <v>1</v>
+      </c>
+      <c r="E1555">
+        <v>0</v>
+      </c>
+      <c r="F1555">
+        <v>12</v>
+      </c>
+      <c r="G1555">
+        <v>12</v>
+      </c>
+      <c r="H1555">
+        <v>12</v>
+      </c>
+      <c r="I1555">
+        <v>0</v>
+      </c>
+      <c r="J1555">
+        <v>0</v>
+      </c>
+      <c r="K1555">
+        <v>52.17</v>
+      </c>
+      <c r="L1555">
+        <v>23</v>
+      </c>
+      <c r="M1555">
+        <v>14</v>
+      </c>
+      <c r="N1555">
+        <v>1</v>
+      </c>
+      <c r="O1555">
+        <v>0</v>
+      </c>
+      <c r="P1555">
+        <v>10.71</v>
+      </c>
+      <c r="Q1555">
+        <v>0</v>
+      </c>
+      <c r="R1555">
+        <v>0</v>
+      </c>
+      <c r="S1555">
+        <v>0</v>
+      </c>
+      <c r="T1555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1556" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1556">
+        <v>1</v>
+      </c>
+      <c r="D1556">
+        <v>1</v>
+      </c>
+      <c r="E1556">
+        <v>0</v>
+      </c>
+      <c r="F1556">
+        <v>9</v>
+      </c>
+      <c r="G1556">
+        <v>9</v>
+      </c>
+      <c r="H1556">
+        <v>9</v>
+      </c>
+      <c r="I1556">
+        <v>0</v>
+      </c>
+      <c r="J1556">
+        <v>0</v>
+      </c>
+      <c r="K1556">
+        <v>81.819999999999993</v>
+      </c>
+      <c r="L1556">
+        <v>11</v>
+      </c>
+      <c r="M1556">
+        <v>6</v>
+      </c>
+      <c r="N1556">
+        <v>1</v>
+      </c>
+      <c r="O1556">
+        <v>0</v>
+      </c>
+      <c r="P1556">
+        <v>8.0399999999999991</v>
+      </c>
+      <c r="Q1556">
+        <v>0</v>
+      </c>
+      <c r="R1556">
+        <v>0</v>
+      </c>
+      <c r="S1556">
+        <v>0</v>
+      </c>
+      <c r="T1556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1557" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1557">
+        <v>1</v>
+      </c>
+      <c r="D1557">
+        <v>1</v>
+      </c>
+      <c r="E1557">
+        <v>0</v>
+      </c>
+      <c r="F1557">
+        <v>3</v>
+      </c>
+      <c r="G1557">
+        <v>3</v>
+      </c>
+      <c r="H1557">
+        <v>3</v>
+      </c>
+      <c r="I1557">
+        <v>0</v>
+      </c>
+      <c r="J1557">
+        <v>0</v>
+      </c>
+      <c r="K1557">
+        <v>33.33</v>
+      </c>
+      <c r="L1557">
+        <v>9</v>
+      </c>
+      <c r="M1557">
+        <v>6</v>
+      </c>
+      <c r="N1557">
+        <v>0</v>
+      </c>
+      <c r="O1557">
+        <v>0</v>
+      </c>
+      <c r="P1557">
+        <v>2.68</v>
+      </c>
+      <c r="Q1557">
+        <v>0</v>
+      </c>
+      <c r="R1557">
+        <v>0</v>
+      </c>
+      <c r="S1557">
+        <v>0</v>
+      </c>
+      <c r="T1557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1558" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>322</v>
+      </c>
+      <c r="C1558">
+        <v>1</v>
+      </c>
+      <c r="D1558">
+        <v>0</v>
+      </c>
+      <c r="E1558">
+        <v>0</v>
+      </c>
+      <c r="F1558">
+        <v>0</v>
+      </c>
+      <c r="I1558">
+        <v>0</v>
+      </c>
+      <c r="J1558">
+        <v>0</v>
+      </c>
+      <c r="L1558">
+        <v>0</v>
+      </c>
+      <c r="M1558">
+        <v>0</v>
+      </c>
+      <c r="N1558">
+        <v>0</v>
+      </c>
+      <c r="O1558">
+        <v>0</v>
+      </c>
+      <c r="P1558">
+        <v>0</v>
+      </c>
+      <c r="Q1558">
+        <v>0</v>
+      </c>
+      <c r="R1558">
+        <v>0</v>
+      </c>
+      <c r="S1558">
+        <v>0</v>
+      </c>
+      <c r="T1558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1559" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1559">
+        <v>1</v>
+      </c>
+      <c r="D1559">
+        <v>0</v>
+      </c>
+      <c r="E1559">
+        <v>0</v>
+      </c>
+      <c r="F1559">
+        <v>0</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+      <c r="J1559">
+        <v>0</v>
+      </c>
+      <c r="L1559">
+        <v>0</v>
+      </c>
+      <c r="M1559">
+        <v>0</v>
+      </c>
+      <c r="N1559">
+        <v>0</v>
+      </c>
+      <c r="O1559">
+        <v>0</v>
+      </c>
+      <c r="P1559">
+        <v>0</v>
+      </c>
+      <c r="Q1559">
+        <v>0</v>
+      </c>
+      <c r="R1559">
+        <v>0</v>
+      </c>
+      <c r="S1559">
+        <v>0</v>
+      </c>
+      <c r="T1559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1560" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1560">
+        <v>1</v>
+      </c>
+      <c r="D1560">
+        <v>0</v>
+      </c>
+      <c r="E1560">
+        <v>0</v>
+      </c>
+      <c r="F1560">
+        <v>0</v>
+      </c>
+      <c r="I1560">
+        <v>0</v>
+      </c>
+      <c r="J1560">
+        <v>0</v>
+      </c>
+      <c r="L1560">
+        <v>0</v>
+      </c>
+      <c r="M1560">
+        <v>0</v>
+      </c>
+      <c r="N1560">
+        <v>0</v>
+      </c>
+      <c r="O1560">
+        <v>0</v>
+      </c>
+      <c r="P1560">
+        <v>0</v>
+      </c>
+      <c r="Q1560">
+        <v>0</v>
+      </c>
+      <c r="R1560">
+        <v>0</v>
+      </c>
+      <c r="S1560">
+        <v>0</v>
+      </c>
+      <c r="T1560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1561" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1561">
+        <v>1</v>
+      </c>
+      <c r="D1561">
+        <v>0</v>
+      </c>
+      <c r="E1561">
+        <v>0</v>
+      </c>
+      <c r="F1561">
+        <v>0</v>
+      </c>
+      <c r="I1561">
+        <v>0</v>
+      </c>
+      <c r="J1561">
+        <v>0</v>
+      </c>
+      <c r="L1561">
+        <v>0</v>
+      </c>
+      <c r="M1561">
+        <v>0</v>
+      </c>
+      <c r="N1561">
+        <v>0</v>
+      </c>
+      <c r="O1561">
+        <v>0</v>
+      </c>
+      <c r="P1561">
+        <v>0</v>
+      </c>
+      <c r="Q1561">
+        <v>0</v>
+      </c>
+      <c r="R1561">
+        <v>0</v>
+      </c>
+      <c r="S1561">
+        <v>0</v>
+      </c>
+      <c r="T1561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1562" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1562">
+        <v>1</v>
+      </c>
+      <c r="D1562">
+        <v>1</v>
+      </c>
+      <c r="E1562">
+        <v>0</v>
+      </c>
+      <c r="F1562">
+        <v>4</v>
+      </c>
+      <c r="G1562">
+        <v>4</v>
+      </c>
+      <c r="H1562">
+        <v>4</v>
+      </c>
+      <c r="I1562">
+        <v>0</v>
+      </c>
+      <c r="J1562">
+        <v>0</v>
+      </c>
+      <c r="K1562">
+        <v>50</v>
+      </c>
+      <c r="L1562">
+        <v>8</v>
+      </c>
+      <c r="M1562">
+        <v>4</v>
+      </c>
+      <c r="N1562">
+        <v>0</v>
+      </c>
+      <c r="O1562">
+        <v>0</v>
+      </c>
+      <c r="P1562">
+        <v>3.57</v>
+      </c>
+      <c r="Q1562">
+        <v>0</v>
+      </c>
+      <c r="R1562">
+        <v>0</v>
+      </c>
+      <c r="S1562">
+        <v>0</v>
+      </c>
+      <c r="T1562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1563" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1563">
+        <v>1</v>
+      </c>
+      <c r="D1563">
+        <v>0</v>
+      </c>
+      <c r="E1563">
+        <v>0</v>
+      </c>
+      <c r="F1563">
+        <v>0</v>
+      </c>
+      <c r="I1563">
+        <v>0</v>
+      </c>
+      <c r="J1563">
+        <v>0</v>
+      </c>
+      <c r="L1563">
+        <v>0</v>
+      </c>
+      <c r="M1563">
+        <v>0</v>
+      </c>
+      <c r="N1563">
+        <v>0</v>
+      </c>
+      <c r="O1563">
+        <v>0</v>
+      </c>
+      <c r="P1563">
+        <v>0</v>
+      </c>
+      <c r="Q1563">
+        <v>0</v>
+      </c>
+      <c r="R1563">
+        <v>0</v>
+      </c>
+      <c r="S1563">
+        <v>0</v>
+      </c>
+      <c r="T1563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1564" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1564">
+        <v>1</v>
+      </c>
+      <c r="D1564">
+        <v>0</v>
+      </c>
+      <c r="E1564">
+        <v>0</v>
+      </c>
+      <c r="F1564">
+        <v>0</v>
+      </c>
+      <c r="I1564">
+        <v>0</v>
+      </c>
+      <c r="J1564">
+        <v>0</v>
+      </c>
+      <c r="L1564">
+        <v>0</v>
+      </c>
+      <c r="M1564">
+        <v>0</v>
+      </c>
+      <c r="N1564">
+        <v>0</v>
+      </c>
+      <c r="O1564">
+        <v>0</v>
+      </c>
+      <c r="P1564">
+        <v>0</v>
+      </c>
+      <c r="Q1564">
+        <v>0</v>
+      </c>
+      <c r="R1564">
+        <v>0</v>
+      </c>
+      <c r="S1564">
+        <v>0</v>
+      </c>
+      <c r="T1564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1565" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1565">
+        <v>1</v>
+      </c>
+      <c r="D1565">
+        <v>1</v>
+      </c>
+      <c r="E1565">
+        <v>0</v>
+      </c>
+      <c r="F1565">
+        <v>26</v>
+      </c>
+      <c r="G1565">
+        <v>26</v>
+      </c>
+      <c r="H1565">
+        <v>26</v>
+      </c>
+      <c r="I1565">
+        <v>0</v>
+      </c>
+      <c r="J1565">
+        <v>0</v>
+      </c>
+      <c r="K1565">
+        <v>92.86</v>
+      </c>
+      <c r="L1565">
+        <v>28</v>
+      </c>
+      <c r="M1565">
+        <v>14</v>
+      </c>
+      <c r="N1565">
+        <v>3</v>
+      </c>
+      <c r="O1565">
+        <v>0</v>
+      </c>
+      <c r="P1565">
+        <v>23.21</v>
+      </c>
+      <c r="Q1565">
+        <v>0</v>
+      </c>
+      <c r="R1565">
+        <v>0</v>
+      </c>
+      <c r="S1565">
+        <v>0</v>
+      </c>
+      <c r="T1565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>465</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1566">
+        <v>1</v>
+      </c>
+      <c r="D1566">
+        <v>1</v>
+      </c>
+      <c r="E1566">
+        <v>1</v>
+      </c>
+      <c r="F1566">
+        <v>39</v>
+      </c>
+      <c r="H1566" t="s">
+        <v>367</v>
+      </c>
+      <c r="I1566">
+        <v>0</v>
+      </c>
+      <c r="J1566">
+        <v>0</v>
+      </c>
+      <c r="K1566">
+        <v>125.81</v>
+      </c>
+      <c r="L1566">
+        <v>31</v>
+      </c>
+      <c r="M1566">
+        <v>10</v>
+      </c>
+      <c r="N1566">
+        <v>3</v>
+      </c>
+      <c r="O1566">
+        <v>0</v>
+      </c>
+      <c r="P1566">
+        <v>34.51</v>
+      </c>
+      <c r="Q1566">
+        <v>0</v>
+      </c>
+      <c r="R1566">
+        <v>0</v>
+      </c>
+      <c r="S1566">
+        <v>0</v>
+      </c>
+      <c r="T1566">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3452" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3499" uniqueCount="462">
   <si>
     <t>Group</t>
   </si>
@@ -1400,6 +1400,12 @@
   <si>
     <t>Molly Sawyer</t>
   </si>
+  <si>
+    <t>CSNI Women 1st XI v Muckamore Women 1st XI, Stormont - 24 July 2026</t>
+  </si>
+  <si>
+    <t>36*</t>
+  </si>
 </sst>
 </file>
 
@@ -2206,7 +2212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1565"/>
+  <dimension ref="A1:T1587"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -93684,6 +93690,1343 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1566" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1566" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1566">
+        <v>1</v>
+      </c>
+      <c r="D1566">
+        <v>1</v>
+      </c>
+      <c r="E1566">
+        <v>0</v>
+      </c>
+      <c r="F1566">
+        <v>8</v>
+      </c>
+      <c r="G1566">
+        <v>8</v>
+      </c>
+      <c r="H1566">
+        <v>8</v>
+      </c>
+      <c r="I1566">
+        <v>0</v>
+      </c>
+      <c r="J1566">
+        <v>0</v>
+      </c>
+      <c r="K1566">
+        <v>57.14</v>
+      </c>
+      <c r="L1566">
+        <v>14</v>
+      </c>
+      <c r="M1566">
+        <v>9</v>
+      </c>
+      <c r="N1566">
+        <v>1</v>
+      </c>
+      <c r="O1566">
+        <v>0</v>
+      </c>
+      <c r="P1566">
+        <v>5.16</v>
+      </c>
+      <c r="Q1566">
+        <v>0</v>
+      </c>
+      <c r="R1566">
+        <v>0</v>
+      </c>
+      <c r="S1566">
+        <v>0</v>
+      </c>
+      <c r="T1566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1567" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1567">
+        <v>1</v>
+      </c>
+      <c r="D1567">
+        <v>1</v>
+      </c>
+      <c r="E1567">
+        <v>0</v>
+      </c>
+      <c r="F1567">
+        <v>37</v>
+      </c>
+      <c r="G1567">
+        <v>37</v>
+      </c>
+      <c r="H1567">
+        <v>37</v>
+      </c>
+      <c r="I1567">
+        <v>0</v>
+      </c>
+      <c r="J1567">
+        <v>0</v>
+      </c>
+      <c r="K1567">
+        <v>86.05</v>
+      </c>
+      <c r="L1567">
+        <v>43</v>
+      </c>
+      <c r="M1567">
+        <v>17</v>
+      </c>
+      <c r="N1567">
+        <v>3</v>
+      </c>
+      <c r="O1567">
+        <v>0</v>
+      </c>
+      <c r="P1567">
+        <v>23.87</v>
+      </c>
+      <c r="Q1567">
+        <v>0</v>
+      </c>
+      <c r="R1567">
+        <v>0</v>
+      </c>
+      <c r="S1567">
+        <v>0</v>
+      </c>
+      <c r="T1567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1568" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1568">
+        <v>1</v>
+      </c>
+      <c r="D1568">
+        <v>1</v>
+      </c>
+      <c r="E1568">
+        <v>1</v>
+      </c>
+      <c r="F1568">
+        <v>36</v>
+      </c>
+      <c r="H1568" t="s">
+        <v>461</v>
+      </c>
+      <c r="I1568">
+        <v>0</v>
+      </c>
+      <c r="J1568">
+        <v>0</v>
+      </c>
+      <c r="K1568">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1568">
+        <v>27</v>
+      </c>
+      <c r="M1568">
+        <v>10</v>
+      </c>
+      <c r="N1568">
+        <v>5</v>
+      </c>
+      <c r="O1568">
+        <v>0</v>
+      </c>
+      <c r="P1568">
+        <v>23.23</v>
+      </c>
+      <c r="Q1568">
+        <v>0</v>
+      </c>
+      <c r="R1568">
+        <v>0</v>
+      </c>
+      <c r="S1568">
+        <v>0</v>
+      </c>
+      <c r="T1568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1569" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1569">
+        <v>1</v>
+      </c>
+      <c r="D1569">
+        <v>1</v>
+      </c>
+      <c r="E1569">
+        <v>0</v>
+      </c>
+      <c r="F1569">
+        <v>11</v>
+      </c>
+      <c r="G1569">
+        <v>11</v>
+      </c>
+      <c r="H1569">
+        <v>11</v>
+      </c>
+      <c r="I1569">
+        <v>0</v>
+      </c>
+      <c r="J1569">
+        <v>0</v>
+      </c>
+      <c r="K1569">
+        <v>157.13999999999999</v>
+      </c>
+      <c r="L1569">
+        <v>7</v>
+      </c>
+      <c r="M1569">
+        <v>2</v>
+      </c>
+      <c r="N1569">
+        <v>2</v>
+      </c>
+      <c r="O1569">
+        <v>0</v>
+      </c>
+      <c r="P1569">
+        <v>7.1</v>
+      </c>
+      <c r="Q1569">
+        <v>0</v>
+      </c>
+      <c r="R1569">
+        <v>0</v>
+      </c>
+      <c r="S1569">
+        <v>0</v>
+      </c>
+      <c r="T1569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1570" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1570">
+        <v>1</v>
+      </c>
+      <c r="D1570">
+        <v>0</v>
+      </c>
+      <c r="E1570">
+        <v>0</v>
+      </c>
+      <c r="F1570">
+        <v>0</v>
+      </c>
+      <c r="I1570">
+        <v>0</v>
+      </c>
+      <c r="J1570">
+        <v>0</v>
+      </c>
+      <c r="L1570">
+        <v>0</v>
+      </c>
+      <c r="M1570">
+        <v>0</v>
+      </c>
+      <c r="N1570">
+        <v>0</v>
+      </c>
+      <c r="O1570">
+        <v>0</v>
+      </c>
+      <c r="P1570">
+        <v>0</v>
+      </c>
+      <c r="Q1570">
+        <v>0</v>
+      </c>
+      <c r="R1570">
+        <v>0</v>
+      </c>
+      <c r="S1570">
+        <v>0</v>
+      </c>
+      <c r="T1570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1571" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1571">
+        <v>1</v>
+      </c>
+      <c r="D1571">
+        <v>1</v>
+      </c>
+      <c r="E1571">
+        <v>0</v>
+      </c>
+      <c r="F1571">
+        <v>2</v>
+      </c>
+      <c r="G1571">
+        <v>2</v>
+      </c>
+      <c r="H1571">
+        <v>2</v>
+      </c>
+      <c r="I1571">
+        <v>0</v>
+      </c>
+      <c r="J1571">
+        <v>0</v>
+      </c>
+      <c r="K1571">
+        <v>40</v>
+      </c>
+      <c r="L1571">
+        <v>5</v>
+      </c>
+      <c r="M1571">
+        <v>4</v>
+      </c>
+      <c r="N1571">
+        <v>0</v>
+      </c>
+      <c r="O1571">
+        <v>0</v>
+      </c>
+      <c r="P1571">
+        <v>2.17</v>
+      </c>
+      <c r="Q1571">
+        <v>0</v>
+      </c>
+      <c r="R1571">
+        <v>0</v>
+      </c>
+      <c r="S1571">
+        <v>0</v>
+      </c>
+      <c r="T1571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1572" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1572">
+        <v>1</v>
+      </c>
+      <c r="D1572">
+        <v>1</v>
+      </c>
+      <c r="E1572">
+        <v>0</v>
+      </c>
+      <c r="F1572">
+        <v>15</v>
+      </c>
+      <c r="G1572">
+        <v>15</v>
+      </c>
+      <c r="H1572">
+        <v>15</v>
+      </c>
+      <c r="I1572">
+        <v>0</v>
+      </c>
+      <c r="J1572">
+        <v>0</v>
+      </c>
+      <c r="K1572">
+        <v>41.67</v>
+      </c>
+      <c r="L1572">
+        <v>36</v>
+      </c>
+      <c r="M1572">
+        <v>27</v>
+      </c>
+      <c r="N1572">
+        <v>2</v>
+      </c>
+      <c r="O1572">
+        <v>0</v>
+      </c>
+      <c r="P1572">
+        <v>16.3</v>
+      </c>
+      <c r="Q1572">
+        <v>0</v>
+      </c>
+      <c r="R1572">
+        <v>1</v>
+      </c>
+      <c r="S1572">
+        <v>1</v>
+      </c>
+      <c r="T1572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1573" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1573">
+        <v>1</v>
+      </c>
+      <c r="D1573">
+        <v>1</v>
+      </c>
+      <c r="E1573">
+        <v>0</v>
+      </c>
+      <c r="F1573">
+        <v>0</v>
+      </c>
+      <c r="G1573">
+        <v>0</v>
+      </c>
+      <c r="H1573">
+        <v>0</v>
+      </c>
+      <c r="I1573">
+        <v>0</v>
+      </c>
+      <c r="J1573">
+        <v>0</v>
+      </c>
+      <c r="K1573">
+        <v>0</v>
+      </c>
+      <c r="L1573">
+        <v>4</v>
+      </c>
+      <c r="M1573">
+        <v>4</v>
+      </c>
+      <c r="N1573">
+        <v>0</v>
+      </c>
+      <c r="O1573">
+        <v>0</v>
+      </c>
+      <c r="P1573">
+        <v>0</v>
+      </c>
+      <c r="Q1573">
+        <v>0</v>
+      </c>
+      <c r="R1573">
+        <v>0</v>
+      </c>
+      <c r="S1573">
+        <v>0</v>
+      </c>
+      <c r="T1573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1574" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>259</v>
+      </c>
+      <c r="C1574">
+        <v>1</v>
+      </c>
+      <c r="D1574">
+        <v>1</v>
+      </c>
+      <c r="E1574">
+        <v>0</v>
+      </c>
+      <c r="F1574">
+        <v>13</v>
+      </c>
+      <c r="G1574">
+        <v>13</v>
+      </c>
+      <c r="H1574">
+        <v>13</v>
+      </c>
+      <c r="I1574">
+        <v>0</v>
+      </c>
+      <c r="J1574">
+        <v>0</v>
+      </c>
+      <c r="K1574">
+        <v>100</v>
+      </c>
+      <c r="L1574">
+        <v>13</v>
+      </c>
+      <c r="M1574">
+        <v>8</v>
+      </c>
+      <c r="N1574">
+        <v>2</v>
+      </c>
+      <c r="O1574">
+        <v>0</v>
+      </c>
+      <c r="P1574">
+        <v>14.13</v>
+      </c>
+      <c r="Q1574">
+        <v>0</v>
+      </c>
+      <c r="R1574">
+        <v>0</v>
+      </c>
+      <c r="S1574">
+        <v>0</v>
+      </c>
+      <c r="T1574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1575" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1575">
+        <v>1</v>
+      </c>
+      <c r="D1575">
+        <v>1</v>
+      </c>
+      <c r="E1575">
+        <v>0</v>
+      </c>
+      <c r="F1575">
+        <v>2</v>
+      </c>
+      <c r="G1575">
+        <v>2</v>
+      </c>
+      <c r="H1575">
+        <v>2</v>
+      </c>
+      <c r="I1575">
+        <v>0</v>
+      </c>
+      <c r="J1575">
+        <v>0</v>
+      </c>
+      <c r="K1575">
+        <v>33.33</v>
+      </c>
+      <c r="L1575">
+        <v>6</v>
+      </c>
+      <c r="M1575">
+        <v>4</v>
+      </c>
+      <c r="N1575">
+        <v>0</v>
+      </c>
+      <c r="O1575">
+        <v>0</v>
+      </c>
+      <c r="P1575">
+        <v>2.17</v>
+      </c>
+      <c r="Q1575">
+        <v>0</v>
+      </c>
+      <c r="R1575">
+        <v>0</v>
+      </c>
+      <c r="S1575">
+        <v>0</v>
+      </c>
+      <c r="T1575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1576" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1576">
+        <v>1</v>
+      </c>
+      <c r="D1576">
+        <v>1</v>
+      </c>
+      <c r="E1576">
+        <v>0</v>
+      </c>
+      <c r="F1576">
+        <v>1</v>
+      </c>
+      <c r="G1576">
+        <v>1</v>
+      </c>
+      <c r="H1576">
+        <v>1</v>
+      </c>
+      <c r="I1576">
+        <v>0</v>
+      </c>
+      <c r="J1576">
+        <v>0</v>
+      </c>
+      <c r="K1576">
+        <v>20</v>
+      </c>
+      <c r="L1576">
+        <v>5</v>
+      </c>
+      <c r="M1576">
+        <v>4</v>
+      </c>
+      <c r="N1576">
+        <v>0</v>
+      </c>
+      <c r="O1576">
+        <v>0</v>
+      </c>
+      <c r="P1576">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q1576">
+        <v>0</v>
+      </c>
+      <c r="R1576">
+        <v>0</v>
+      </c>
+      <c r="S1576">
+        <v>0</v>
+      </c>
+      <c r="T1576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1577" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1577">
+        <v>1</v>
+      </c>
+      <c r="D1577">
+        <v>0</v>
+      </c>
+      <c r="E1577">
+        <v>0</v>
+      </c>
+      <c r="F1577">
+        <v>0</v>
+      </c>
+      <c r="I1577">
+        <v>0</v>
+      </c>
+      <c r="J1577">
+        <v>0</v>
+      </c>
+      <c r="L1577">
+        <v>0</v>
+      </c>
+      <c r="M1577">
+        <v>0</v>
+      </c>
+      <c r="N1577">
+        <v>0</v>
+      </c>
+      <c r="O1577">
+        <v>0</v>
+      </c>
+      <c r="P1577">
+        <v>0</v>
+      </c>
+      <c r="Q1577">
+        <v>0</v>
+      </c>
+      <c r="R1577">
+        <v>0</v>
+      </c>
+      <c r="S1577">
+        <v>0</v>
+      </c>
+      <c r="T1577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1578" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1578">
+        <v>1</v>
+      </c>
+      <c r="D1578">
+        <v>1</v>
+      </c>
+      <c r="E1578">
+        <v>0</v>
+      </c>
+      <c r="F1578">
+        <v>0</v>
+      </c>
+      <c r="G1578">
+        <v>0</v>
+      </c>
+      <c r="H1578">
+        <v>0</v>
+      </c>
+      <c r="I1578">
+        <v>0</v>
+      </c>
+      <c r="J1578">
+        <v>0</v>
+      </c>
+      <c r="K1578">
+        <v>0</v>
+      </c>
+      <c r="L1578">
+        <v>1</v>
+      </c>
+      <c r="M1578">
+        <v>1</v>
+      </c>
+      <c r="N1578">
+        <v>0</v>
+      </c>
+      <c r="O1578">
+        <v>0</v>
+      </c>
+      <c r="P1578">
+        <v>0</v>
+      </c>
+      <c r="Q1578">
+        <v>1</v>
+      </c>
+      <c r="R1578">
+        <v>0</v>
+      </c>
+      <c r="S1578">
+        <v>0</v>
+      </c>
+      <c r="T1578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1579" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1579">
+        <v>1</v>
+      </c>
+      <c r="D1579">
+        <v>1</v>
+      </c>
+      <c r="E1579">
+        <v>0</v>
+      </c>
+      <c r="F1579">
+        <v>7</v>
+      </c>
+      <c r="G1579">
+        <v>7</v>
+      </c>
+      <c r="H1579">
+        <v>7</v>
+      </c>
+      <c r="I1579">
+        <v>0</v>
+      </c>
+      <c r="J1579">
+        <v>0</v>
+      </c>
+      <c r="K1579">
+        <v>63.64</v>
+      </c>
+      <c r="L1579">
+        <v>11</v>
+      </c>
+      <c r="M1579">
+        <v>7</v>
+      </c>
+      <c r="N1579">
+        <v>1</v>
+      </c>
+      <c r="O1579">
+        <v>0</v>
+      </c>
+      <c r="P1579">
+        <v>7.61</v>
+      </c>
+      <c r="Q1579">
+        <v>1</v>
+      </c>
+      <c r="R1579">
+        <v>0</v>
+      </c>
+      <c r="S1579">
+        <v>0</v>
+      </c>
+      <c r="T1579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1580" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1580">
+        <v>1</v>
+      </c>
+      <c r="D1580">
+        <v>1</v>
+      </c>
+      <c r="E1580">
+        <v>0</v>
+      </c>
+      <c r="F1580">
+        <v>0</v>
+      </c>
+      <c r="G1580">
+        <v>0</v>
+      </c>
+      <c r="H1580">
+        <v>0</v>
+      </c>
+      <c r="I1580">
+        <v>0</v>
+      </c>
+      <c r="J1580">
+        <v>0</v>
+      </c>
+      <c r="K1580">
+        <v>0</v>
+      </c>
+      <c r="L1580">
+        <v>3</v>
+      </c>
+      <c r="M1580">
+        <v>3</v>
+      </c>
+      <c r="N1580">
+        <v>0</v>
+      </c>
+      <c r="O1580">
+        <v>0</v>
+      </c>
+      <c r="P1580">
+        <v>0</v>
+      </c>
+      <c r="Q1580">
+        <v>1</v>
+      </c>
+      <c r="R1580">
+        <v>0</v>
+      </c>
+      <c r="S1580">
+        <v>0</v>
+      </c>
+      <c r="T1580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1581" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1581">
+        <v>1</v>
+      </c>
+      <c r="D1581">
+        <v>1</v>
+      </c>
+      <c r="E1581">
+        <v>0</v>
+      </c>
+      <c r="F1581">
+        <v>25</v>
+      </c>
+      <c r="G1581">
+        <v>25</v>
+      </c>
+      <c r="H1581">
+        <v>25</v>
+      </c>
+      <c r="I1581">
+        <v>0</v>
+      </c>
+      <c r="J1581">
+        <v>0</v>
+      </c>
+      <c r="K1581">
+        <v>113.64</v>
+      </c>
+      <c r="L1581">
+        <v>22</v>
+      </c>
+      <c r="M1581">
+        <v>12</v>
+      </c>
+      <c r="N1581">
+        <v>5</v>
+      </c>
+      <c r="O1581">
+        <v>0</v>
+      </c>
+      <c r="P1581">
+        <v>27.17</v>
+      </c>
+      <c r="Q1581">
+        <v>0</v>
+      </c>
+      <c r="R1581">
+        <v>0</v>
+      </c>
+      <c r="S1581">
+        <v>0</v>
+      </c>
+      <c r="T1581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1582" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1582">
+        <v>1</v>
+      </c>
+      <c r="D1582">
+        <v>1</v>
+      </c>
+      <c r="E1582">
+        <v>1</v>
+      </c>
+      <c r="F1582">
+        <v>1</v>
+      </c>
+      <c r="H1582" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1582">
+        <v>0</v>
+      </c>
+      <c r="J1582">
+        <v>0</v>
+      </c>
+      <c r="K1582">
+        <v>100</v>
+      </c>
+      <c r="L1582">
+        <v>1</v>
+      </c>
+      <c r="M1582">
+        <v>0</v>
+      </c>
+      <c r="N1582">
+        <v>0</v>
+      </c>
+      <c r="O1582">
+        <v>0</v>
+      </c>
+      <c r="P1582">
+        <v>0.65</v>
+      </c>
+      <c r="Q1582">
+        <v>0</v>
+      </c>
+      <c r="R1582">
+        <v>0</v>
+      </c>
+      <c r="S1582">
+        <v>0</v>
+      </c>
+      <c r="T1582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1583" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1583">
+        <v>1</v>
+      </c>
+      <c r="D1583">
+        <v>1</v>
+      </c>
+      <c r="E1583">
+        <v>1</v>
+      </c>
+      <c r="F1583">
+        <v>0</v>
+      </c>
+      <c r="H1583" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1583">
+        <v>0</v>
+      </c>
+      <c r="J1583">
+        <v>0</v>
+      </c>
+      <c r="K1583">
+        <v>0</v>
+      </c>
+      <c r="L1583">
+        <v>1</v>
+      </c>
+      <c r="M1583">
+        <v>1</v>
+      </c>
+      <c r="N1583">
+        <v>0</v>
+      </c>
+      <c r="O1583">
+        <v>0</v>
+      </c>
+      <c r="P1583">
+        <v>0</v>
+      </c>
+      <c r="Q1583">
+        <v>0</v>
+      </c>
+      <c r="R1583">
+        <v>0</v>
+      </c>
+      <c r="S1583">
+        <v>0</v>
+      </c>
+      <c r="T1583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1584" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1584">
+        <v>1</v>
+      </c>
+      <c r="D1584">
+        <v>1</v>
+      </c>
+      <c r="E1584">
+        <v>0</v>
+      </c>
+      <c r="F1584">
+        <v>1</v>
+      </c>
+      <c r="G1584">
+        <v>1</v>
+      </c>
+      <c r="H1584">
+        <v>1</v>
+      </c>
+      <c r="I1584">
+        <v>0</v>
+      </c>
+      <c r="J1584">
+        <v>0</v>
+      </c>
+      <c r="K1584">
+        <v>25</v>
+      </c>
+      <c r="L1584">
+        <v>4</v>
+      </c>
+      <c r="M1584">
+        <v>3</v>
+      </c>
+      <c r="N1584">
+        <v>0</v>
+      </c>
+      <c r="O1584">
+        <v>0</v>
+      </c>
+      <c r="P1584">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="Q1584">
+        <v>0</v>
+      </c>
+      <c r="R1584">
+        <v>0</v>
+      </c>
+      <c r="S1584">
+        <v>0</v>
+      </c>
+      <c r="T1584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1585" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1585">
+        <v>1</v>
+      </c>
+      <c r="D1585">
+        <v>1</v>
+      </c>
+      <c r="E1585">
+        <v>0</v>
+      </c>
+      <c r="F1585">
+        <v>1</v>
+      </c>
+      <c r="G1585">
+        <v>1</v>
+      </c>
+      <c r="H1585">
+        <v>1</v>
+      </c>
+      <c r="I1585">
+        <v>0</v>
+      </c>
+      <c r="J1585">
+        <v>0</v>
+      </c>
+      <c r="K1585">
+        <v>20</v>
+      </c>
+      <c r="L1585">
+        <v>5</v>
+      </c>
+      <c r="M1585">
+        <v>4</v>
+      </c>
+      <c r="N1585">
+        <v>0</v>
+      </c>
+      <c r="O1585">
+        <v>0</v>
+      </c>
+      <c r="P1585">
+        <v>0.65</v>
+      </c>
+      <c r="Q1585">
+        <v>0</v>
+      </c>
+      <c r="R1585">
+        <v>1</v>
+      </c>
+      <c r="S1585">
+        <v>0</v>
+      </c>
+      <c r="T1585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1586" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1586">
+        <v>1</v>
+      </c>
+      <c r="D1586">
+        <v>1</v>
+      </c>
+      <c r="E1586">
+        <v>0</v>
+      </c>
+      <c r="F1586">
+        <v>9</v>
+      </c>
+      <c r="G1586">
+        <v>9</v>
+      </c>
+      <c r="H1586">
+        <v>9</v>
+      </c>
+      <c r="I1586">
+        <v>0</v>
+      </c>
+      <c r="J1586">
+        <v>0</v>
+      </c>
+      <c r="K1586">
+        <v>90</v>
+      </c>
+      <c r="L1586">
+        <v>10</v>
+      </c>
+      <c r="M1586">
+        <v>7</v>
+      </c>
+      <c r="N1586">
+        <v>2</v>
+      </c>
+      <c r="O1586">
+        <v>0</v>
+      </c>
+      <c r="P1586">
+        <v>5.81</v>
+      </c>
+      <c r="Q1586">
+        <v>1</v>
+      </c>
+      <c r="R1586">
+        <v>0</v>
+      </c>
+      <c r="S1586">
+        <v>0</v>
+      </c>
+      <c r="T1586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1587" t="s">
+        <v>460</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1587">
+        <v>1</v>
+      </c>
+      <c r="D1587">
+        <v>1</v>
+      </c>
+      <c r="E1587">
+        <v>0</v>
+      </c>
+      <c r="F1587">
+        <v>11</v>
+      </c>
+      <c r="G1587">
+        <v>11</v>
+      </c>
+      <c r="H1587">
+        <v>11</v>
+      </c>
+      <c r="I1587">
+        <v>0</v>
+      </c>
+      <c r="J1587">
+        <v>0</v>
+      </c>
+      <c r="K1587">
+        <v>110</v>
+      </c>
+      <c r="L1587">
+        <v>10</v>
+      </c>
+      <c r="M1587">
+        <v>2</v>
+      </c>
+      <c r="N1587">
+        <v>1</v>
+      </c>
+      <c r="O1587">
+        <v>0</v>
+      </c>
+      <c r="P1587">
+        <v>7.1</v>
+      </c>
+      <c r="Q1587">
+        <v>0</v>
+      </c>
+      <c r="R1587">
+        <v>0</v>
+      </c>
+      <c r="S1587">
+        <v>0</v>
+      </c>
+      <c r="T1587">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ncuireland-my.sharepoint.com/personal/wylie_mckinty_ncucricket_org/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_A02CE93B0792204CEBDC6FA3FD0A8DAE4B23CD75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15856276-A04F-4C49-A893-F3A0ADB26A98}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_A02CE93B0792204CEBDC6FA3FD0A8DAE4B23CD75" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A60CCF52-42B9-46D8-B210-4CD598DF9289}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1339,9 +1339,6 @@
     <t>Anna Megarrell</t>
   </si>
   <si>
-    <t>Ellen Taylor Skilling</t>
-  </si>
-  <si>
     <t>32*</t>
   </si>
   <si>
@@ -1430,6 +1427,9 @@
   </si>
   <si>
     <t>Charvisri Geddam</t>
+  </si>
+  <si>
+    <t>Ellen Skilling</t>
   </si>
 </sst>
 </file>
@@ -1973,6 +1973,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -28336,7 +28340,7 @@
         <v>236</v>
       </c>
       <c r="B445" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C445">
         <v>1</v>
@@ -28832,7 +28836,7 @@
         <v>236</v>
       </c>
       <c r="B453" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C453">
         <v>1</v>
@@ -85684,7 +85688,7 @@
         <v>437</v>
       </c>
       <c r="B1429" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="C1429">
         <v>1</v>
@@ -85876,7 +85880,7 @@
         <v>32</v>
       </c>
       <c r="H1432" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="I1432">
         <v>0</v>
@@ -85976,7 +85980,7 @@
     </row>
     <row r="1434" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1434" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1434" t="s">
         <v>72</v>
@@ -86038,7 +86042,7 @@
     </row>
     <row r="1435" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1435" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1435" t="s">
         <v>74</v>
@@ -86100,7 +86104,7 @@
     </row>
     <row r="1436" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1436" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1436" t="s">
         <v>76</v>
@@ -86153,7 +86157,7 @@
     </row>
     <row r="1437" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1437" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1437" t="s">
         <v>23</v>
@@ -86212,7 +86216,7 @@
     </row>
     <row r="1438" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1438" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1438" t="s">
         <v>118</v>
@@ -86265,7 +86269,7 @@
     </row>
     <row r="1439" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1439" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1439" t="s">
         <v>292</v>
@@ -86327,7 +86331,7 @@
     </row>
     <row r="1440" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1440" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1440" t="s">
         <v>34</v>
@@ -86386,7 +86390,7 @@
     </row>
     <row r="1441" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1441" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1441" t="s">
         <v>315</v>
@@ -86445,7 +86449,7 @@
     </row>
     <row r="1442" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1442" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1442" t="s">
         <v>80</v>
@@ -86507,7 +86511,7 @@
     </row>
     <row r="1443" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1443" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1443" t="s">
         <v>57</v>
@@ -86566,7 +86570,7 @@
     </row>
     <row r="1444" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1444" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1444" t="s">
         <v>39</v>
@@ -86619,7 +86623,7 @@
     </row>
     <row r="1445" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1445" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1445" t="s">
         <v>81</v>
@@ -86681,7 +86685,7 @@
     </row>
     <row r="1446" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1446" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1446" t="s">
         <v>293</v>
@@ -86743,7 +86747,7 @@
     </row>
     <row r="1447" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1447" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1447" t="s">
         <v>213</v>
@@ -86805,7 +86809,7 @@
     </row>
     <row r="1448" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1448" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1448" t="s">
         <v>60</v>
@@ -86867,7 +86871,7 @@
     </row>
     <row r="1449" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1449" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1449" t="s">
         <v>145</v>
@@ -86929,7 +86933,7 @@
     </row>
     <row r="1450" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1450" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1450" t="s">
         <v>138</v>
@@ -86991,7 +86995,7 @@
     </row>
     <row r="1451" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1451" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1451" t="s">
         <v>86</v>
@@ -87053,7 +87057,7 @@
     </row>
     <row r="1452" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1452" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1452" t="s">
         <v>67</v>
@@ -87115,7 +87119,7 @@
     </row>
     <row r="1453" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1453" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1453" t="s">
         <v>209</v>
@@ -87177,7 +87181,7 @@
     </row>
     <row r="1454" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1454" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1454" t="s">
         <v>70</v>
@@ -87239,7 +87243,7 @@
     </row>
     <row r="1455" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1455" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B1455" t="s">
         <v>294</v>
@@ -87301,7 +87305,7 @@
     </row>
     <row r="1456" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1456" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1456" t="s">
         <v>306</v>
@@ -87363,7 +87367,7 @@
     </row>
     <row r="1457" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1457" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1457" t="s">
         <v>438</v>
@@ -87425,7 +87429,7 @@
     </row>
     <row r="1458" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1458" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1458" t="s">
         <v>417</v>
@@ -87487,7 +87491,7 @@
     </row>
     <row r="1459" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1459" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1459" t="s">
         <v>205</v>
@@ -87546,7 +87550,7 @@
     </row>
     <row r="1460" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1460" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1460" t="s">
         <v>200</v>
@@ -87605,7 +87609,7 @@
     </row>
     <row r="1461" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1461" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1461" t="s">
         <v>110</v>
@@ -87667,7 +87671,7 @@
     </row>
     <row r="1462" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1462" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1462" t="s">
         <v>112</v>
@@ -87729,7 +87733,7 @@
     </row>
     <row r="1463" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1463" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1463" t="s">
         <v>203</v>
@@ -87791,7 +87795,7 @@
     </row>
     <row r="1464" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1464" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1464" t="s">
         <v>307</v>
@@ -87850,7 +87854,7 @@
     </row>
     <row r="1465" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1465" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1465" t="s">
         <v>114</v>
@@ -87912,7 +87916,7 @@
     </row>
     <row r="1466" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1466" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1466" t="s">
         <v>90</v>
@@ -87974,7 +87978,7 @@
     </row>
     <row r="1467" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1467" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1467" t="s">
         <v>106</v>
@@ -88036,7 +88040,7 @@
     </row>
     <row r="1468" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1468" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1468" t="s">
         <v>233</v>
@@ -88089,7 +88093,7 @@
     </row>
     <row r="1469" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1469" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1469" t="s">
         <v>88</v>
@@ -88142,7 +88146,7 @@
     </row>
     <row r="1470" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1470" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1470" t="s">
         <v>104</v>
@@ -88204,7 +88208,7 @@
     </row>
     <row r="1471" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1471" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1471" t="s">
         <v>305</v>
@@ -88263,7 +88267,7 @@
     </row>
     <row r="1472" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1472" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1472" t="s">
         <v>141</v>
@@ -88325,7 +88329,7 @@
     </row>
     <row r="1473" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1473" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1473" t="s">
         <v>111</v>
@@ -88387,7 +88391,7 @@
     </row>
     <row r="1474" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1474" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1474" t="s">
         <v>198</v>
@@ -88440,7 +88444,7 @@
     </row>
     <row r="1475" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1475" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1475" t="s">
         <v>194</v>
@@ -88502,7 +88506,7 @@
     </row>
     <row r="1476" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1476" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1476" t="s">
         <v>89</v>
@@ -88564,7 +88568,7 @@
     </row>
     <row r="1477" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1477" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B1477" t="s">
         <v>199</v>
@@ -88626,7 +88630,7 @@
     </row>
     <row r="1478" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1478" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1478" t="s">
         <v>76</v>
@@ -88688,7 +88692,7 @@
     </row>
     <row r="1479" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1479" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1479" t="s">
         <v>23</v>
@@ -88747,7 +88751,7 @@
     </row>
     <row r="1480" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1480" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1480" t="s">
         <v>25</v>
@@ -88800,7 +88804,7 @@
     </row>
     <row r="1481" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1481" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1481" t="s">
         <v>78</v>
@@ -88862,7 +88866,7 @@
     </row>
     <row r="1482" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1482" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1482" t="s">
         <v>350</v>
@@ -88915,7 +88919,7 @@
     </row>
     <row r="1483" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1483" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1483" t="s">
         <v>26</v>
@@ -88977,10 +88981,10 @@
     </row>
     <row r="1484" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1484" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1484" t="s">
         <v>443</v>
-      </c>
-      <c r="B1484" t="s">
-        <v>444</v>
       </c>
       <c r="C1484">
         <v>1</v>
@@ -89030,7 +89034,7 @@
     </row>
     <row r="1485" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1485" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1485" t="s">
         <v>27</v>
@@ -89083,7 +89087,7 @@
     </row>
     <row r="1486" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1486" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1486" t="s">
         <v>29</v>
@@ -89145,7 +89149,7 @@
     </row>
     <row r="1487" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1487" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1487" t="s">
         <v>30</v>
@@ -89207,7 +89211,7 @@
     </row>
     <row r="1488" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1488" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1488" t="s">
         <v>33</v>
@@ -89260,7 +89264,7 @@
     </row>
     <row r="1489" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1489" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1489" t="s">
         <v>34</v>
@@ -89322,7 +89326,7 @@
     </row>
     <row r="1490" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1490" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1490" t="s">
         <v>37</v>
@@ -89384,10 +89388,10 @@
     </row>
     <row r="1491" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1491" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1491" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C1491">
         <v>1</v>
@@ -89437,7 +89441,7 @@
     </row>
     <row r="1492" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1492" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1492" t="s">
         <v>39</v>
@@ -89496,7 +89500,7 @@
     </row>
     <row r="1493" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1493" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1493" t="s">
         <v>44</v>
@@ -89549,7 +89553,7 @@
     </row>
     <row r="1494" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1494" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1494" t="s">
         <v>327</v>
@@ -89608,7 +89612,7 @@
     </row>
     <row r="1495" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1495" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1495" t="s">
         <v>46</v>
@@ -89667,7 +89671,7 @@
     </row>
     <row r="1496" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1496" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1496" t="s">
         <v>85</v>
@@ -89729,7 +89733,7 @@
     </row>
     <row r="1497" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1497" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1497" t="s">
         <v>47</v>
@@ -89782,7 +89786,7 @@
     </row>
     <row r="1498" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1498" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1498" t="s">
         <v>422</v>
@@ -89844,7 +89848,7 @@
     </row>
     <row r="1499" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1499" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B1499" t="s">
         <v>113</v>
@@ -89903,7 +89907,7 @@
     </row>
     <row r="1500" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1500" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1500" t="s">
         <v>315</v>
@@ -89965,7 +89969,7 @@
     </row>
     <row r="1501" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1501" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1501" t="s">
         <v>215</v>
@@ -90027,7 +90031,7 @@
     </row>
     <row r="1502" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1502" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1502" t="s">
         <v>57</v>
@@ -90086,7 +90090,7 @@
     </row>
     <row r="1503" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1503" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1503" t="s">
         <v>316</v>
@@ -90139,7 +90143,7 @@
     </row>
     <row r="1504" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1504" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1504" t="s">
         <v>401</v>
@@ -90201,7 +90205,7 @@
     </row>
     <row r="1505" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1505" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1505" t="s">
         <v>64</v>
@@ -90254,7 +90258,7 @@
     </row>
     <row r="1506" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1506" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1506" t="s">
         <v>55</v>
@@ -90313,7 +90317,7 @@
     </row>
     <row r="1507" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1507" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1507" t="s">
         <v>175</v>
@@ -90375,7 +90379,7 @@
     </row>
     <row r="1508" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1508" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1508" t="s">
         <v>270</v>
@@ -90428,7 +90432,7 @@
     </row>
     <row r="1509" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1509" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1509" t="s">
         <v>52</v>
@@ -90490,7 +90494,7 @@
     </row>
     <row r="1510" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1510" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1510" t="s">
         <v>51</v>
@@ -90552,7 +90556,7 @@
     </row>
     <row r="1511" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1511" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1511" t="s">
         <v>133</v>
@@ -90605,10 +90609,10 @@
     </row>
     <row r="1512" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1512" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1512" t="s">
         <v>446</v>
-      </c>
-      <c r="B1512" t="s">
-        <v>447</v>
       </c>
       <c r="C1512">
         <v>1</v>
@@ -90658,7 +90662,7 @@
     </row>
     <row r="1513" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1513" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1513" t="s">
         <v>138</v>
@@ -90711,7 +90715,7 @@
     </row>
     <row r="1514" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1514" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1514" t="s">
         <v>69</v>
@@ -90770,7 +90774,7 @@
     </row>
     <row r="1515" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1515" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1515" t="s">
         <v>146</v>
@@ -90823,7 +90827,7 @@
     </row>
     <row r="1516" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1516" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1516" t="s">
         <v>209</v>
@@ -90882,7 +90886,7 @@
     </row>
     <row r="1517" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1517" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1517" t="s">
         <v>167</v>
@@ -90941,7 +90945,7 @@
     </row>
     <row r="1518" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1518" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1518" t="s">
         <v>172</v>
@@ -91003,7 +91007,7 @@
     </row>
     <row r="1519" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1519" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1519" t="s">
         <v>432</v>
@@ -91056,7 +91060,7 @@
     </row>
     <row r="1520" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1520" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1520" t="s">
         <v>159</v>
@@ -91118,7 +91122,7 @@
     </row>
     <row r="1521" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1521" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B1521" t="s">
         <v>67</v>
@@ -91180,7 +91184,7 @@
     </row>
     <row r="1522" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1522" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1522" t="s">
         <v>244</v>
@@ -91242,10 +91246,10 @@
     </row>
     <row r="1523" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1523" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1523" t="s">
         <v>448</v>
-      </c>
-      <c r="B1523" t="s">
-        <v>449</v>
       </c>
       <c r="C1523">
         <v>1</v>
@@ -91295,10 +91299,10 @@
     </row>
     <row r="1524" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1524" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1524" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C1524">
         <v>1</v>
@@ -91348,7 +91352,7 @@
     </row>
     <row r="1525" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1525" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1525" t="s">
         <v>342</v>
@@ -91410,10 +91414,10 @@
     </row>
     <row r="1526" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1526" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1526" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C1526">
         <v>1</v>
@@ -91472,7 +91476,7 @@
     </row>
     <row r="1527" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1527" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1527" t="s">
         <v>250</v>
@@ -91534,10 +91538,10 @@
     </row>
     <row r="1528" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1528" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1528" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C1528">
         <v>1</v>
@@ -91596,7 +91600,7 @@
     </row>
     <row r="1529" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1529" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1529" t="s">
         <v>239</v>
@@ -91658,7 +91662,7 @@
     </row>
     <row r="1530" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1530" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1530" t="s">
         <v>240</v>
@@ -91720,7 +91724,7 @@
     </row>
     <row r="1531" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1531" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1531" t="s">
         <v>245</v>
@@ -91779,10 +91783,10 @@
     </row>
     <row r="1532" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1532" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1532" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C1532">
         <v>1</v>
@@ -91838,7 +91842,7 @@
     </row>
     <row r="1533" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1533" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1533" t="s">
         <v>313</v>
@@ -91900,7 +91904,7 @@
     </row>
     <row r="1534" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1534" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1534" t="s">
         <v>375</v>
@@ -91959,7 +91963,7 @@
     </row>
     <row r="1535" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1535" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1535" t="s">
         <v>321</v>
@@ -92021,10 +92025,10 @@
     </row>
     <row r="1536" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1536" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1536" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C1536">
         <v>1</v>
@@ -92074,7 +92078,7 @@
     </row>
     <row r="1537" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1537" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1537" t="s">
         <v>252</v>
@@ -92127,7 +92131,7 @@
     </row>
     <row r="1538" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1538" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1538" t="s">
         <v>344</v>
@@ -92186,10 +92190,10 @@
     </row>
     <row r="1539" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1539" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1539" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C1539">
         <v>1</v>
@@ -92248,10 +92252,10 @@
     </row>
     <row r="1540" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1540" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1540" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C1540">
         <v>1</v>
@@ -92301,7 +92305,7 @@
     </row>
     <row r="1541" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1541" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1541" t="s">
         <v>336</v>
@@ -92360,7 +92364,7 @@
     </row>
     <row r="1542" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1542" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1542" t="s">
         <v>358</v>
@@ -92413,7 +92417,7 @@
     </row>
     <row r="1543" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1543" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B1543" t="s">
         <v>155</v>
@@ -92472,7 +92476,7 @@
     </row>
     <row r="1544" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1544" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1544" t="s">
         <v>262</v>
@@ -92525,7 +92529,7 @@
     </row>
     <row r="1545" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1545" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1545" t="s">
         <v>24</v>
@@ -92578,7 +92582,7 @@
     </row>
     <row r="1546" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1546" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1546" t="s">
         <v>25</v>
@@ -92631,7 +92635,7 @@
     </row>
     <row r="1547" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1547" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1547" t="s">
         <v>78</v>
@@ -92690,7 +92694,7 @@
     </row>
     <row r="1548" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1548" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1548" t="s">
         <v>427</v>
@@ -92749,7 +92753,7 @@
     </row>
     <row r="1549" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1549" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1549" t="s">
         <v>405</v>
@@ -92802,7 +92806,7 @@
     </row>
     <row r="1550" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1550" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1550" t="s">
         <v>93</v>
@@ -92861,7 +92865,7 @@
     </row>
     <row r="1551" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1551" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1551" t="s">
         <v>31</v>
@@ -92923,7 +92927,7 @@
     </row>
     <row r="1552" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1552" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1552" t="s">
         <v>297</v>
@@ -92976,7 +92980,7 @@
     </row>
     <row r="1553" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1553" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1553" t="s">
         <v>98</v>
@@ -93029,7 +93033,7 @@
     </row>
     <row r="1554" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1554" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1554" t="s">
         <v>32</v>
@@ -93091,7 +93095,7 @@
     </row>
     <row r="1555" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1555" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1555" t="s">
         <v>386</v>
@@ -93153,7 +93157,7 @@
     </row>
     <row r="1556" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1556" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1556" t="s">
         <v>82</v>
@@ -93215,7 +93219,7 @@
     </row>
     <row r="1557" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1557" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1557" t="s">
         <v>319</v>
@@ -93268,7 +93272,7 @@
     </row>
     <row r="1558" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1558" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1558" t="s">
         <v>302</v>
@@ -93321,7 +93325,7 @@
     </row>
     <row r="1559" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1559" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1559" t="s">
         <v>303</v>
@@ -93374,7 +93378,7 @@
     </row>
     <row r="1560" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1560" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1560" t="s">
         <v>99</v>
@@ -93427,7 +93431,7 @@
     </row>
     <row r="1561" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1561" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1561" t="s">
         <v>46</v>
@@ -93489,7 +93493,7 @@
     </row>
     <row r="1562" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1562" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1562" t="s">
         <v>422</v>
@@ -93542,7 +93546,7 @@
     </row>
     <row r="1563" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1563" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1563" t="s">
         <v>304</v>
@@ -93595,7 +93599,7 @@
     </row>
     <row r="1564" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1564" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1564" t="s">
         <v>113</v>
@@ -93657,7 +93661,7 @@
     </row>
     <row r="1565" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1565" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B1565" t="s">
         <v>102</v>
@@ -93716,7 +93720,7 @@
     </row>
     <row r="1566" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1566" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1566" t="s">
         <v>291</v>
@@ -93778,7 +93782,7 @@
     </row>
     <row r="1567" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1567" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1567" t="s">
         <v>49</v>
@@ -93840,7 +93844,7 @@
     </row>
     <row r="1568" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1568" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1568" t="s">
         <v>52</v>
@@ -93858,7 +93862,7 @@
         <v>36</v>
       </c>
       <c r="H1568" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I1568">
         <v>0</v>
@@ -93899,7 +93903,7 @@
     </row>
     <row r="1569" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1569" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1569" t="s">
         <v>401</v>
@@ -93961,7 +93965,7 @@
     </row>
     <row r="1570" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1570" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1570" t="s">
         <v>54</v>
@@ -94014,7 +94018,7 @@
     </row>
     <row r="1571" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1571" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1571" t="s">
         <v>258</v>
@@ -94076,7 +94080,7 @@
     </row>
     <row r="1572" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1572" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1572" t="s">
         <v>120</v>
@@ -94138,7 +94142,7 @@
     </row>
     <row r="1573" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1573" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1573" t="s">
         <v>55</v>
@@ -94200,7 +94204,7 @@
     </row>
     <row r="1574" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1574" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1574" t="s">
         <v>259</v>
@@ -94262,7 +94266,7 @@
     </row>
     <row r="1575" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1575" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1575" t="s">
         <v>309</v>
@@ -94324,7 +94328,7 @@
     </row>
     <row r="1576" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1576" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1576" t="s">
         <v>121</v>
@@ -94386,7 +94390,7 @@
     </row>
     <row r="1577" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1577" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1577" t="s">
         <v>208</v>
@@ -94439,7 +94443,7 @@
     </row>
     <row r="1578" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1578" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1578" t="s">
         <v>59</v>
@@ -94501,7 +94505,7 @@
     </row>
     <row r="1579" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1579" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1579" t="s">
         <v>151</v>
@@ -94563,7 +94567,7 @@
     </row>
     <row r="1580" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1580" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1580" t="s">
         <v>152</v>
@@ -94625,7 +94629,7 @@
     </row>
     <row r="1581" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1581" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1581" t="s">
         <v>154</v>
@@ -94687,10 +94691,10 @@
     </row>
     <row r="1582" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1582" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1582" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="C1582">
         <v>1</v>
@@ -94746,7 +94750,7 @@
     </row>
     <row r="1583" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1583" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1583" t="s">
         <v>125</v>
@@ -94805,7 +94809,7 @@
     </row>
     <row r="1584" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1584" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1584" t="s">
         <v>126</v>
@@ -94867,7 +94871,7 @@
     </row>
     <row r="1585" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1585" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1585" t="s">
         <v>66</v>
@@ -94929,7 +94933,7 @@
     </row>
     <row r="1586" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1586" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1586" t="s">
         <v>69</v>
@@ -94991,7 +94995,7 @@
     </row>
     <row r="1587" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1587" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B1587" t="s">
         <v>270</v>
@@ -95053,10 +95057,10 @@
     </row>
     <row r="1588" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1588" t="s">
+        <v>461</v>
+      </c>
+      <c r="B1588" t="s">
         <v>462</v>
-      </c>
-      <c r="B1588" t="s">
-        <v>463</v>
       </c>
       <c r="C1588">
         <v>1</v>
@@ -95106,7 +95110,7 @@
     </row>
     <row r="1589" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1589" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1589" t="s">
         <v>22</v>
@@ -95159,7 +95163,7 @@
     </row>
     <row r="1590" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1590" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1590" t="s">
         <v>257</v>
@@ -95212,7 +95216,7 @@
     </row>
     <row r="1591" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1591" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1591" t="s">
         <v>33</v>
@@ -95265,7 +95269,7 @@
     </row>
     <row r="1592" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1592" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1592" t="s">
         <v>34</v>
@@ -95283,7 +95287,7 @@
         <v>63</v>
       </c>
       <c r="H1592" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I1592">
         <v>1</v>
@@ -95324,7 +95328,7 @@
     </row>
     <row r="1593" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1593" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1593" t="s">
         <v>36</v>
@@ -95377,7 +95381,7 @@
     </row>
     <row r="1594" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1594" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1594" t="s">
         <v>37</v>
@@ -95430,7 +95434,7 @@
     </row>
     <row r="1595" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1595" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1595" t="s">
         <v>315</v>
@@ -95492,7 +95496,7 @@
     </row>
     <row r="1596" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1596" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1596" t="s">
         <v>80</v>
@@ -95554,7 +95558,7 @@
     </row>
     <row r="1597" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1597" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1597" t="s">
         <v>57</v>
@@ -95616,7 +95620,7 @@
     </row>
     <row r="1598" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1598" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1598" t="s">
         <v>39</v>
@@ -95669,7 +95673,7 @@
     </row>
     <row r="1599" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1599" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1599" t="s">
         <v>81</v>
@@ -95687,7 +95691,7 @@
         <v>87</v>
       </c>
       <c r="H1599" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I1599">
         <v>1</v>
@@ -95728,7 +95732,7 @@
     </row>
     <row r="1600" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1600" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1600" t="s">
         <v>293</v>
@@ -95790,7 +95794,7 @@
     </row>
     <row r="1601" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1601" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1601" t="s">
         <v>60</v>
@@ -95852,7 +95856,7 @@
     </row>
     <row r="1602" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1602" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1602" t="s">
         <v>64</v>
@@ -95908,7 +95912,7 @@
     </row>
     <row r="1603" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1603" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1603" t="s">
         <v>402</v>
@@ -95970,7 +95974,7 @@
     </row>
     <row r="1604" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1604" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1604" t="s">
         <v>85</v>
@@ -96023,7 +96027,7 @@
     </row>
     <row r="1605" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1605" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1605" t="s">
         <v>138</v>
@@ -96085,7 +96089,7 @@
     </row>
     <row r="1606" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1606" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1606" t="s">
         <v>67</v>
@@ -96147,7 +96151,7 @@
     </row>
     <row r="1607" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1607" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1607" t="s">
         <v>209</v>
@@ -96209,7 +96213,7 @@
     </row>
     <row r="1608" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1608" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1608" t="s">
         <v>70</v>
@@ -96271,7 +96275,7 @@
     </row>
     <row r="1609" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1609" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1609" t="s">
         <v>294</v>
@@ -96333,7 +96337,7 @@
     </row>
     <row r="1610" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1610" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1610" t="s">
         <v>291</v>
@@ -96395,7 +96399,7 @@
     </row>
     <row r="1611" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1611" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1611" t="s">
         <v>49</v>
@@ -96457,7 +96461,7 @@
     </row>
     <row r="1612" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1612" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1612" t="s">
         <v>52</v>
@@ -96519,7 +96523,7 @@
     </row>
     <row r="1613" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1613" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1613" t="s">
         <v>159</v>
@@ -96572,7 +96576,7 @@
     </row>
     <row r="1614" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1614" t="s">
         <v>148</v>
@@ -96634,7 +96638,7 @@
     </row>
     <row r="1615" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1615" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1615" t="s">
         <v>54</v>
@@ -96693,7 +96697,7 @@
     </row>
     <row r="1616" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1616" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1616" t="s">
         <v>258</v>
@@ -96755,7 +96759,7 @@
     </row>
     <row r="1617" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1617" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1617" t="s">
         <v>120</v>
@@ -96814,7 +96818,7 @@
     </row>
     <row r="1618" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1618" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1618" t="s">
         <v>259</v>
@@ -96867,7 +96871,7 @@
     </row>
     <row r="1619" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1619" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1619" t="s">
         <v>309</v>
@@ -96929,7 +96933,7 @@
     </row>
     <row r="1620" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1620" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1620" t="s">
         <v>121</v>
@@ -96982,7 +96986,7 @@
     </row>
     <row r="1621" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1621" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1621" t="s">
         <v>59</v>
@@ -97044,7 +97048,7 @@
     </row>
     <row r="1622" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1622" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1622" t="s">
         <v>151</v>
@@ -97097,7 +97101,7 @@
     </row>
     <row r="1623" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1623" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1623" t="s">
         <v>152</v>
@@ -97156,7 +97160,7 @@
     </row>
     <row r="1624" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1624" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1624" t="s">
         <v>154</v>
@@ -97218,10 +97222,10 @@
     </row>
     <row r="1625" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1625" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1625" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="C1625">
         <v>1</v>
@@ -97280,7 +97284,7 @@
     </row>
     <row r="1626" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1626" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1626" t="s">
         <v>125</v>
@@ -97333,7 +97337,7 @@
     </row>
     <row r="1627" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1627" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1627" t="s">
         <v>126</v>
@@ -97386,7 +97390,7 @@
     </row>
     <row r="1628" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1628" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1628" t="s">
         <v>175</v>
@@ -97439,7 +97443,7 @@
     </row>
     <row r="1629" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1629" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1629" t="s">
         <v>176</v>
@@ -97501,7 +97505,7 @@
     </row>
     <row r="1630" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1630" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1630" t="s">
         <v>66</v>
@@ -97563,7 +97567,7 @@
     </row>
     <row r="1631" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1631" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B1631" t="s">
         <v>270</v>
@@ -97625,7 +97629,7 @@
     </row>
     <row r="1632" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1632" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1632" t="s">
         <v>312</v>
@@ -97678,7 +97682,7 @@
     </row>
     <row r="1633" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1633" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1633" t="s">
         <v>348</v>
@@ -97740,7 +97744,7 @@
     </row>
     <row r="1634" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1634" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1634" t="s">
         <v>24</v>
@@ -97802,7 +97806,7 @@
     </row>
     <row r="1635" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1635" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1635" t="s">
         <v>25</v>
@@ -97864,10 +97868,10 @@
     </row>
     <row r="1636" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1636" t="s">
+        <v>466</v>
+      </c>
+      <c r="B1636" t="s">
         <v>467</v>
-      </c>
-      <c r="B1636" t="s">
-        <v>468</v>
       </c>
       <c r="C1636">
         <v>1</v>
@@ -97917,7 +97921,7 @@
     </row>
     <row r="1637" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1637" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1637" t="s">
         <v>427</v>
@@ -97979,10 +97983,10 @@
     </row>
     <row r="1638" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1638" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1638" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C1638">
         <v>1</v>
@@ -98032,7 +98036,7 @@
     </row>
     <row r="1639" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1639" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1639" t="s">
         <v>314</v>
@@ -98091,7 +98095,7 @@
     </row>
     <row r="1640" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1640" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1640" t="s">
         <v>98</v>
@@ -98150,7 +98154,7 @@
     </row>
     <row r="1641" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1641" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1641" t="s">
         <v>32</v>
@@ -98212,7 +98216,7 @@
     </row>
     <row r="1642" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1642" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1642" t="s">
         <v>386</v>
@@ -98274,7 +98278,7 @@
     </row>
     <row r="1643" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1643" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1643" t="s">
         <v>360</v>
@@ -98327,7 +98331,7 @@
     </row>
     <row r="1644" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1644" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1644" t="s">
         <v>82</v>
@@ -98389,7 +98393,7 @@
     </row>
     <row r="1645" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1645" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1645" t="s">
         <v>319</v>
@@ -98451,7 +98455,7 @@
     </row>
     <row r="1646" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1646" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1646" t="s">
         <v>44</v>
@@ -98510,7 +98514,7 @@
     </row>
     <row r="1647" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1647" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1647" t="s">
         <v>99</v>
@@ -98572,7 +98576,7 @@
     </row>
     <row r="1648" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1648" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1648" t="s">
         <v>155</v>
@@ -98625,7 +98629,7 @@
     </row>
     <row r="1649" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1649" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1649" t="s">
         <v>46</v>
@@ -98687,7 +98691,7 @@
     </row>
     <row r="1650" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1650" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1650" t="s">
         <v>47</v>
@@ -98749,7 +98753,7 @@
     </row>
     <row r="1651" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1651" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1651" t="s">
         <v>422</v>
@@ -98811,7 +98815,7 @@
     </row>
     <row r="1652" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1652" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1652" t="s">
         <v>304</v>
@@ -98873,7 +98877,7 @@
     </row>
     <row r="1653" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1653" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B1653" t="s">
         <v>101</v>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3640" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="477">
   <si>
     <t>Group</t>
   </si>
@@ -1433,6 +1433,24 @@
   <si>
     <t>Charvisri Geddam</t>
   </si>
+  <si>
+    <t>Dundrum Women 1st XI v Instonians Women 2nd XI, The Meadow - 27 July 2026</t>
+  </si>
+  <si>
+    <t>Suzanne Lunny</t>
+  </si>
+  <si>
+    <t>Bangor Women 1st XI v Holywood Women 2nd XI, Upritchard Park - 27 July 2026</t>
+  </si>
+  <si>
+    <t>Erin Knight</t>
+  </si>
+  <si>
+    <t>Waringstown Women 2nd XI v CSNI Women 2nd XI, The Lawn - 27 July 2026</t>
+  </si>
+  <si>
+    <t>Ellen McKane</t>
+  </si>
 </sst>
 </file>
 
@@ -2239,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1653"/>
+  <dimension ref="A1:T1716"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -98927,6 +98945,3771 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1654" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1654" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1654">
+        <v>1</v>
+      </c>
+      <c r="D1654">
+        <v>0</v>
+      </c>
+      <c r="E1654">
+        <v>0</v>
+      </c>
+      <c r="F1654">
+        <v>0</v>
+      </c>
+      <c r="I1654">
+        <v>0</v>
+      </c>
+      <c r="J1654">
+        <v>0</v>
+      </c>
+      <c r="L1654">
+        <v>0</v>
+      </c>
+      <c r="M1654">
+        <v>0</v>
+      </c>
+      <c r="N1654">
+        <v>0</v>
+      </c>
+      <c r="O1654">
+        <v>0</v>
+      </c>
+      <c r="P1654">
+        <v>0</v>
+      </c>
+      <c r="Q1654">
+        <v>0</v>
+      </c>
+      <c r="R1654">
+        <v>0</v>
+      </c>
+      <c r="S1654">
+        <v>0</v>
+      </c>
+      <c r="T1654">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1655" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1655">
+        <v>1</v>
+      </c>
+      <c r="D1655">
+        <v>1</v>
+      </c>
+      <c r="E1655">
+        <v>1</v>
+      </c>
+      <c r="F1655">
+        <v>1</v>
+      </c>
+      <c r="H1655" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1655">
+        <v>0</v>
+      </c>
+      <c r="J1655">
+        <v>0</v>
+      </c>
+      <c r="K1655">
+        <v>100</v>
+      </c>
+      <c r="L1655">
+        <v>1</v>
+      </c>
+      <c r="M1655">
+        <v>0</v>
+      </c>
+      <c r="N1655">
+        <v>0</v>
+      </c>
+      <c r="O1655">
+        <v>0</v>
+      </c>
+      <c r="P1655">
+        <v>0.85</v>
+      </c>
+      <c r="Q1655">
+        <v>0</v>
+      </c>
+      <c r="R1655">
+        <v>0</v>
+      </c>
+      <c r="S1655">
+        <v>0</v>
+      </c>
+      <c r="T1655">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1656" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1656">
+        <v>1</v>
+      </c>
+      <c r="D1656">
+        <v>0</v>
+      </c>
+      <c r="E1656">
+        <v>0</v>
+      </c>
+      <c r="F1656">
+        <v>0</v>
+      </c>
+      <c r="I1656">
+        <v>0</v>
+      </c>
+      <c r="J1656">
+        <v>0</v>
+      </c>
+      <c r="L1656">
+        <v>0</v>
+      </c>
+      <c r="M1656">
+        <v>0</v>
+      </c>
+      <c r="N1656">
+        <v>0</v>
+      </c>
+      <c r="O1656">
+        <v>0</v>
+      </c>
+      <c r="P1656">
+        <v>0</v>
+      </c>
+      <c r="Q1656">
+        <v>0</v>
+      </c>
+      <c r="R1656">
+        <v>0</v>
+      </c>
+      <c r="S1656">
+        <v>0</v>
+      </c>
+      <c r="T1656">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1657" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1657">
+        <v>1</v>
+      </c>
+      <c r="D1657">
+        <v>1</v>
+      </c>
+      <c r="E1657">
+        <v>0</v>
+      </c>
+      <c r="F1657">
+        <v>2</v>
+      </c>
+      <c r="G1657">
+        <v>2</v>
+      </c>
+      <c r="H1657">
+        <v>2</v>
+      </c>
+      <c r="I1657">
+        <v>0</v>
+      </c>
+      <c r="J1657">
+        <v>0</v>
+      </c>
+      <c r="K1657">
+        <v>18.18</v>
+      </c>
+      <c r="L1657">
+        <v>11</v>
+      </c>
+      <c r="M1657">
+        <v>9</v>
+      </c>
+      <c r="N1657">
+        <v>0</v>
+      </c>
+      <c r="O1657">
+        <v>0</v>
+      </c>
+      <c r="P1657">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q1657">
+        <v>0</v>
+      </c>
+      <c r="R1657">
+        <v>0</v>
+      </c>
+      <c r="S1657">
+        <v>0</v>
+      </c>
+      <c r="T1657">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1658" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1658">
+        <v>1</v>
+      </c>
+      <c r="D1658">
+        <v>1</v>
+      </c>
+      <c r="E1658">
+        <v>0</v>
+      </c>
+      <c r="F1658">
+        <v>2</v>
+      </c>
+      <c r="G1658">
+        <v>2</v>
+      </c>
+      <c r="H1658">
+        <v>2</v>
+      </c>
+      <c r="I1658">
+        <v>0</v>
+      </c>
+      <c r="J1658">
+        <v>0</v>
+      </c>
+      <c r="K1658">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="L1658">
+        <v>12</v>
+      </c>
+      <c r="M1658">
+        <v>10</v>
+      </c>
+      <c r="N1658">
+        <v>0</v>
+      </c>
+      <c r="O1658">
+        <v>0</v>
+      </c>
+      <c r="P1658">
+        <v>1.71</v>
+      </c>
+      <c r="Q1658">
+        <v>1</v>
+      </c>
+      <c r="R1658">
+        <v>0</v>
+      </c>
+      <c r="S1658">
+        <v>0</v>
+      </c>
+      <c r="T1658">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1659" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1659">
+        <v>1</v>
+      </c>
+      <c r="D1659">
+        <v>0</v>
+      </c>
+      <c r="E1659">
+        <v>0</v>
+      </c>
+      <c r="F1659">
+        <v>0</v>
+      </c>
+      <c r="I1659">
+        <v>0</v>
+      </c>
+      <c r="J1659">
+        <v>0</v>
+      </c>
+      <c r="L1659">
+        <v>0</v>
+      </c>
+      <c r="M1659">
+        <v>0</v>
+      </c>
+      <c r="N1659">
+        <v>0</v>
+      </c>
+      <c r="O1659">
+        <v>0</v>
+      </c>
+      <c r="P1659">
+        <v>0</v>
+      </c>
+      <c r="Q1659">
+        <v>0</v>
+      </c>
+      <c r="R1659">
+        <v>0</v>
+      </c>
+      <c r="S1659">
+        <v>0</v>
+      </c>
+      <c r="T1659">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1660" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>436</v>
+      </c>
+      <c r="C1660">
+        <v>1</v>
+      </c>
+      <c r="D1660">
+        <v>1</v>
+      </c>
+      <c r="E1660">
+        <v>1</v>
+      </c>
+      <c r="F1660">
+        <v>50</v>
+      </c>
+      <c r="H1660" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1660">
+        <v>1</v>
+      </c>
+      <c r="J1660">
+        <v>0</v>
+      </c>
+      <c r="K1660">
+        <v>98.04</v>
+      </c>
+      <c r="L1660">
+        <v>51</v>
+      </c>
+      <c r="M1660">
+        <v>23</v>
+      </c>
+      <c r="N1660">
+        <v>6</v>
+      </c>
+      <c r="O1660">
+        <v>0</v>
+      </c>
+      <c r="P1660">
+        <v>42.74</v>
+      </c>
+      <c r="Q1660">
+        <v>0</v>
+      </c>
+      <c r="R1660">
+        <v>0</v>
+      </c>
+      <c r="S1660">
+        <v>0</v>
+      </c>
+      <c r="T1660">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1661" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1661">
+        <v>1</v>
+      </c>
+      <c r="D1661">
+        <v>1</v>
+      </c>
+      <c r="E1661">
+        <v>0</v>
+      </c>
+      <c r="F1661">
+        <v>0</v>
+      </c>
+      <c r="G1661">
+        <v>0</v>
+      </c>
+      <c r="H1661">
+        <v>0</v>
+      </c>
+      <c r="I1661">
+        <v>0</v>
+      </c>
+      <c r="J1661">
+        <v>0</v>
+      </c>
+      <c r="K1661">
+        <v>0</v>
+      </c>
+      <c r="L1661">
+        <v>1</v>
+      </c>
+      <c r="M1661">
+        <v>1</v>
+      </c>
+      <c r="N1661">
+        <v>0</v>
+      </c>
+      <c r="O1661">
+        <v>0</v>
+      </c>
+      <c r="P1661">
+        <v>0</v>
+      </c>
+      <c r="Q1661">
+        <v>0</v>
+      </c>
+      <c r="R1661">
+        <v>0</v>
+      </c>
+      <c r="S1661">
+        <v>0</v>
+      </c>
+      <c r="T1661">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1662" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>433</v>
+      </c>
+      <c r="C1662">
+        <v>1</v>
+      </c>
+      <c r="D1662">
+        <v>1</v>
+      </c>
+      <c r="E1662">
+        <v>1</v>
+      </c>
+      <c r="F1662">
+        <v>5</v>
+      </c>
+      <c r="H1662" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1662">
+        <v>0</v>
+      </c>
+      <c r="J1662">
+        <v>0</v>
+      </c>
+      <c r="K1662">
+        <v>38.46</v>
+      </c>
+      <c r="L1662">
+        <v>13</v>
+      </c>
+      <c r="M1662">
+        <v>9</v>
+      </c>
+      <c r="N1662">
+        <v>0</v>
+      </c>
+      <c r="O1662">
+        <v>0</v>
+      </c>
+      <c r="P1662">
+        <v>6.17</v>
+      </c>
+      <c r="Q1662">
+        <v>0</v>
+      </c>
+      <c r="R1662">
+        <v>0</v>
+      </c>
+      <c r="S1662">
+        <v>0</v>
+      </c>
+      <c r="T1662">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1663" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1663">
+        <v>1</v>
+      </c>
+      <c r="D1663">
+        <v>1</v>
+      </c>
+      <c r="E1663">
+        <v>0</v>
+      </c>
+      <c r="F1663">
+        <v>21</v>
+      </c>
+      <c r="G1663">
+        <v>21</v>
+      </c>
+      <c r="H1663">
+        <v>21</v>
+      </c>
+      <c r="I1663">
+        <v>0</v>
+      </c>
+      <c r="J1663">
+        <v>0</v>
+      </c>
+      <c r="K1663">
+        <v>53.85</v>
+      </c>
+      <c r="L1663">
+        <v>39</v>
+      </c>
+      <c r="M1663">
+        <v>23</v>
+      </c>
+      <c r="N1663">
+        <v>1</v>
+      </c>
+      <c r="O1663">
+        <v>0</v>
+      </c>
+      <c r="P1663">
+        <v>25.93</v>
+      </c>
+      <c r="Q1663">
+        <v>0</v>
+      </c>
+      <c r="R1663">
+        <v>0</v>
+      </c>
+      <c r="S1663">
+        <v>0</v>
+      </c>
+      <c r="T1663">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1664" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>472</v>
+      </c>
+      <c r="C1664">
+        <v>1</v>
+      </c>
+      <c r="D1664">
+        <v>1</v>
+      </c>
+      <c r="E1664">
+        <v>0</v>
+      </c>
+      <c r="F1664">
+        <v>1</v>
+      </c>
+      <c r="G1664">
+        <v>1</v>
+      </c>
+      <c r="H1664">
+        <v>1</v>
+      </c>
+      <c r="I1664">
+        <v>0</v>
+      </c>
+      <c r="J1664">
+        <v>0</v>
+      </c>
+      <c r="K1664">
+        <v>33.33</v>
+      </c>
+      <c r="L1664">
+        <v>3</v>
+      </c>
+      <c r="M1664">
+        <v>2</v>
+      </c>
+      <c r="N1664">
+        <v>0</v>
+      </c>
+      <c r="O1664">
+        <v>0</v>
+      </c>
+      <c r="P1664">
+        <v>1.23</v>
+      </c>
+      <c r="Q1664">
+        <v>0</v>
+      </c>
+      <c r="R1664">
+        <v>0</v>
+      </c>
+      <c r="S1664">
+        <v>0</v>
+      </c>
+      <c r="T1664">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1665" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1665">
+        <v>1</v>
+      </c>
+      <c r="D1665">
+        <v>1</v>
+      </c>
+      <c r="E1665">
+        <v>0</v>
+      </c>
+      <c r="F1665">
+        <v>1</v>
+      </c>
+      <c r="G1665">
+        <v>1</v>
+      </c>
+      <c r="H1665">
+        <v>1</v>
+      </c>
+      <c r="I1665">
+        <v>0</v>
+      </c>
+      <c r="J1665">
+        <v>0</v>
+      </c>
+      <c r="K1665">
+        <v>20</v>
+      </c>
+      <c r="L1665">
+        <v>5</v>
+      </c>
+      <c r="M1665">
+        <v>4</v>
+      </c>
+      <c r="N1665">
+        <v>0</v>
+      </c>
+      <c r="O1665">
+        <v>0</v>
+      </c>
+      <c r="P1665">
+        <v>1.23</v>
+      </c>
+      <c r="Q1665">
+        <v>0</v>
+      </c>
+      <c r="R1665">
+        <v>0</v>
+      </c>
+      <c r="S1665">
+        <v>0</v>
+      </c>
+      <c r="T1665">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1666" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1666">
+        <v>1</v>
+      </c>
+      <c r="D1666">
+        <v>1</v>
+      </c>
+      <c r="E1666">
+        <v>1</v>
+      </c>
+      <c r="F1666">
+        <v>24</v>
+      </c>
+      <c r="H1666" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1666">
+        <v>0</v>
+      </c>
+      <c r="J1666">
+        <v>0</v>
+      </c>
+      <c r="K1666">
+        <v>92.31</v>
+      </c>
+      <c r="L1666">
+        <v>26</v>
+      </c>
+      <c r="M1666">
+        <v>12</v>
+      </c>
+      <c r="N1666">
+        <v>3</v>
+      </c>
+      <c r="O1666">
+        <v>0</v>
+      </c>
+      <c r="P1666">
+        <v>20.51</v>
+      </c>
+      <c r="Q1666">
+        <v>0</v>
+      </c>
+      <c r="R1666">
+        <v>0</v>
+      </c>
+      <c r="S1666">
+        <v>0</v>
+      </c>
+      <c r="T1666">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1667" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1667">
+        <v>1</v>
+      </c>
+      <c r="D1667">
+        <v>1</v>
+      </c>
+      <c r="E1667">
+        <v>1</v>
+      </c>
+      <c r="F1667">
+        <v>2</v>
+      </c>
+      <c r="H1667" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1667">
+        <v>0</v>
+      </c>
+      <c r="J1667">
+        <v>0</v>
+      </c>
+      <c r="K1667">
+        <v>40</v>
+      </c>
+      <c r="L1667">
+        <v>5</v>
+      </c>
+      <c r="M1667">
+        <v>3</v>
+      </c>
+      <c r="N1667">
+        <v>0</v>
+      </c>
+      <c r="O1667">
+        <v>0</v>
+      </c>
+      <c r="P1667">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q1667">
+        <v>0</v>
+      </c>
+      <c r="R1667">
+        <v>0</v>
+      </c>
+      <c r="S1667">
+        <v>0</v>
+      </c>
+      <c r="T1667">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1668" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1668">
+        <v>1</v>
+      </c>
+      <c r="D1668">
+        <v>1</v>
+      </c>
+      <c r="E1668">
+        <v>0</v>
+      </c>
+      <c r="F1668">
+        <v>2</v>
+      </c>
+      <c r="G1668">
+        <v>2</v>
+      </c>
+      <c r="H1668">
+        <v>2</v>
+      </c>
+      <c r="I1668">
+        <v>0</v>
+      </c>
+      <c r="J1668">
+        <v>0</v>
+      </c>
+      <c r="K1668">
+        <v>40</v>
+      </c>
+      <c r="L1668">
+        <v>5</v>
+      </c>
+      <c r="M1668">
+        <v>3</v>
+      </c>
+      <c r="N1668">
+        <v>0</v>
+      </c>
+      <c r="O1668">
+        <v>0</v>
+      </c>
+      <c r="P1668">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q1668">
+        <v>0</v>
+      </c>
+      <c r="R1668">
+        <v>0</v>
+      </c>
+      <c r="S1668">
+        <v>0</v>
+      </c>
+      <c r="T1668">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1669" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1669">
+        <v>1</v>
+      </c>
+      <c r="D1669">
+        <v>0</v>
+      </c>
+      <c r="E1669">
+        <v>0</v>
+      </c>
+      <c r="F1669">
+        <v>0</v>
+      </c>
+      <c r="I1669">
+        <v>0</v>
+      </c>
+      <c r="J1669">
+        <v>0</v>
+      </c>
+      <c r="L1669">
+        <v>0</v>
+      </c>
+      <c r="M1669">
+        <v>0</v>
+      </c>
+      <c r="N1669">
+        <v>0</v>
+      </c>
+      <c r="O1669">
+        <v>0</v>
+      </c>
+      <c r="P1669">
+        <v>0</v>
+      </c>
+      <c r="Q1669">
+        <v>0</v>
+      </c>
+      <c r="R1669">
+        <v>0</v>
+      </c>
+      <c r="S1669">
+        <v>0</v>
+      </c>
+      <c r="T1669">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1670" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1670">
+        <v>1</v>
+      </c>
+      <c r="D1670">
+        <v>1</v>
+      </c>
+      <c r="E1670">
+        <v>0</v>
+      </c>
+      <c r="F1670">
+        <v>4</v>
+      </c>
+      <c r="G1670">
+        <v>4</v>
+      </c>
+      <c r="H1670">
+        <v>4</v>
+      </c>
+      <c r="I1670">
+        <v>0</v>
+      </c>
+      <c r="J1670">
+        <v>0</v>
+      </c>
+      <c r="K1670">
+        <v>28.57</v>
+      </c>
+      <c r="L1670">
+        <v>14</v>
+      </c>
+      <c r="M1670">
+        <v>11</v>
+      </c>
+      <c r="N1670">
+        <v>0</v>
+      </c>
+      <c r="O1670">
+        <v>0</v>
+      </c>
+      <c r="P1670">
+        <v>3.42</v>
+      </c>
+      <c r="Q1670">
+        <v>0</v>
+      </c>
+      <c r="R1670">
+        <v>1</v>
+      </c>
+      <c r="S1670">
+        <v>0</v>
+      </c>
+      <c r="T1670">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1671" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1671">
+        <v>1</v>
+      </c>
+      <c r="D1671">
+        <v>1</v>
+      </c>
+      <c r="E1671">
+        <v>0</v>
+      </c>
+      <c r="F1671">
+        <v>8</v>
+      </c>
+      <c r="G1671">
+        <v>8</v>
+      </c>
+      <c r="H1671">
+        <v>8</v>
+      </c>
+      <c r="I1671">
+        <v>0</v>
+      </c>
+      <c r="J1671">
+        <v>0</v>
+      </c>
+      <c r="K1671">
+        <v>47.06</v>
+      </c>
+      <c r="L1671">
+        <v>17</v>
+      </c>
+      <c r="M1671">
+        <v>9</v>
+      </c>
+      <c r="N1671">
+        <v>0</v>
+      </c>
+      <c r="O1671">
+        <v>0</v>
+      </c>
+      <c r="P1671">
+        <v>6.84</v>
+      </c>
+      <c r="Q1671">
+        <v>0</v>
+      </c>
+      <c r="R1671">
+        <v>0</v>
+      </c>
+      <c r="S1671">
+        <v>0</v>
+      </c>
+      <c r="T1671">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1672" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1672">
+        <v>1</v>
+      </c>
+      <c r="D1672">
+        <v>1</v>
+      </c>
+      <c r="E1672">
+        <v>0</v>
+      </c>
+      <c r="F1672">
+        <v>2</v>
+      </c>
+      <c r="G1672">
+        <v>2</v>
+      </c>
+      <c r="H1672">
+        <v>2</v>
+      </c>
+      <c r="I1672">
+        <v>0</v>
+      </c>
+      <c r="J1672">
+        <v>0</v>
+      </c>
+      <c r="K1672">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="L1672">
+        <v>12</v>
+      </c>
+      <c r="M1672">
+        <v>10</v>
+      </c>
+      <c r="N1672">
+        <v>0</v>
+      </c>
+      <c r="O1672">
+        <v>0</v>
+      </c>
+      <c r="P1672">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="Q1672">
+        <v>0</v>
+      </c>
+      <c r="R1672">
+        <v>0</v>
+      </c>
+      <c r="S1672">
+        <v>0</v>
+      </c>
+      <c r="T1672">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1673" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1673">
+        <v>1</v>
+      </c>
+      <c r="D1673">
+        <v>0</v>
+      </c>
+      <c r="E1673">
+        <v>0</v>
+      </c>
+      <c r="F1673">
+        <v>0</v>
+      </c>
+      <c r="I1673">
+        <v>0</v>
+      </c>
+      <c r="J1673">
+        <v>0</v>
+      </c>
+      <c r="L1673">
+        <v>0</v>
+      </c>
+      <c r="M1673">
+        <v>0</v>
+      </c>
+      <c r="N1673">
+        <v>0</v>
+      </c>
+      <c r="O1673">
+        <v>0</v>
+      </c>
+      <c r="P1673">
+        <v>0</v>
+      </c>
+      <c r="Q1673">
+        <v>1</v>
+      </c>
+      <c r="R1673">
+        <v>0</v>
+      </c>
+      <c r="S1673">
+        <v>0</v>
+      </c>
+      <c r="T1673">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1674" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1674">
+        <v>1</v>
+      </c>
+      <c r="D1674">
+        <v>1</v>
+      </c>
+      <c r="E1674">
+        <v>0</v>
+      </c>
+      <c r="F1674">
+        <v>13</v>
+      </c>
+      <c r="G1674">
+        <v>13</v>
+      </c>
+      <c r="H1674">
+        <v>13</v>
+      </c>
+      <c r="I1674">
+        <v>0</v>
+      </c>
+      <c r="J1674">
+        <v>0</v>
+      </c>
+      <c r="K1674">
+        <v>46.43</v>
+      </c>
+      <c r="L1674">
+        <v>28</v>
+      </c>
+      <c r="M1674">
+        <v>18</v>
+      </c>
+      <c r="N1674">
+        <v>1</v>
+      </c>
+      <c r="O1674">
+        <v>0</v>
+      </c>
+      <c r="P1674">
+        <v>16.05</v>
+      </c>
+      <c r="Q1674">
+        <v>0</v>
+      </c>
+      <c r="R1674">
+        <v>0</v>
+      </c>
+      <c r="S1674">
+        <v>0</v>
+      </c>
+      <c r="T1674">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1675" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1675">
+        <v>1</v>
+      </c>
+      <c r="D1675">
+        <v>1</v>
+      </c>
+      <c r="E1675">
+        <v>0</v>
+      </c>
+      <c r="F1675">
+        <v>0</v>
+      </c>
+      <c r="G1675">
+        <v>0</v>
+      </c>
+      <c r="H1675">
+        <v>0</v>
+      </c>
+      <c r="I1675">
+        <v>0</v>
+      </c>
+      <c r="J1675">
+        <v>0</v>
+      </c>
+      <c r="K1675">
+        <v>0</v>
+      </c>
+      <c r="L1675">
+        <v>2</v>
+      </c>
+      <c r="M1675">
+        <v>2</v>
+      </c>
+      <c r="N1675">
+        <v>0</v>
+      </c>
+      <c r="O1675">
+        <v>0</v>
+      </c>
+      <c r="P1675">
+        <v>0</v>
+      </c>
+      <c r="Q1675">
+        <v>0</v>
+      </c>
+      <c r="R1675">
+        <v>0</v>
+      </c>
+      <c r="S1675">
+        <v>0</v>
+      </c>
+      <c r="T1675">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1676" t="s">
+        <v>471</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1676">
+        <v>1</v>
+      </c>
+      <c r="D1676">
+        <v>1</v>
+      </c>
+      <c r="E1676">
+        <v>0</v>
+      </c>
+      <c r="F1676">
+        <v>0</v>
+      </c>
+      <c r="G1676">
+        <v>0</v>
+      </c>
+      <c r="H1676">
+        <v>0</v>
+      </c>
+      <c r="I1676">
+        <v>0</v>
+      </c>
+      <c r="J1676">
+        <v>0</v>
+      </c>
+      <c r="K1676">
+        <v>0</v>
+      </c>
+      <c r="L1676">
+        <v>2</v>
+      </c>
+      <c r="M1676">
+        <v>2</v>
+      </c>
+      <c r="N1676">
+        <v>0</v>
+      </c>
+      <c r="O1676">
+        <v>0</v>
+      </c>
+      <c r="P1676">
+        <v>0</v>
+      </c>
+      <c r="Q1676">
+        <v>0</v>
+      </c>
+      <c r="R1676">
+        <v>0</v>
+      </c>
+      <c r="S1676">
+        <v>0</v>
+      </c>
+      <c r="T1676">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1677" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1677">
+        <v>1</v>
+      </c>
+      <c r="D1677">
+        <v>0</v>
+      </c>
+      <c r="E1677">
+        <v>0</v>
+      </c>
+      <c r="F1677">
+        <v>0</v>
+      </c>
+      <c r="I1677">
+        <v>0</v>
+      </c>
+      <c r="J1677">
+        <v>0</v>
+      </c>
+      <c r="L1677">
+        <v>0</v>
+      </c>
+      <c r="M1677">
+        <v>0</v>
+      </c>
+      <c r="N1677">
+        <v>0</v>
+      </c>
+      <c r="O1677">
+        <v>0</v>
+      </c>
+      <c r="P1677">
+        <v>0</v>
+      </c>
+      <c r="Q1677">
+        <v>0</v>
+      </c>
+      <c r="R1677">
+        <v>0</v>
+      </c>
+      <c r="S1677">
+        <v>0</v>
+      </c>
+      <c r="T1677">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1678" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1678">
+        <v>1</v>
+      </c>
+      <c r="D1678">
+        <v>1</v>
+      </c>
+      <c r="E1678">
+        <v>1</v>
+      </c>
+      <c r="F1678">
+        <v>13</v>
+      </c>
+      <c r="H1678" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1678">
+        <v>0</v>
+      </c>
+      <c r="J1678">
+        <v>0</v>
+      </c>
+      <c r="K1678">
+        <v>86.67</v>
+      </c>
+      <c r="L1678">
+        <v>15</v>
+      </c>
+      <c r="M1678">
+        <v>6</v>
+      </c>
+      <c r="N1678">
+        <v>1</v>
+      </c>
+      <c r="O1678">
+        <v>0</v>
+      </c>
+      <c r="P1678">
+        <v>7.18</v>
+      </c>
+      <c r="Q1678">
+        <v>0</v>
+      </c>
+      <c r="R1678">
+        <v>0</v>
+      </c>
+      <c r="S1678">
+        <v>0</v>
+      </c>
+      <c r="T1678">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1679" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1679">
+        <v>1</v>
+      </c>
+      <c r="D1679">
+        <v>1</v>
+      </c>
+      <c r="E1679">
+        <v>1</v>
+      </c>
+      <c r="F1679">
+        <v>1</v>
+      </c>
+      <c r="H1679" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1679">
+        <v>0</v>
+      </c>
+      <c r="J1679">
+        <v>0</v>
+      </c>
+      <c r="K1679">
+        <v>25</v>
+      </c>
+      <c r="L1679">
+        <v>4</v>
+      </c>
+      <c r="M1679">
+        <v>3</v>
+      </c>
+      <c r="N1679">
+        <v>0</v>
+      </c>
+      <c r="O1679">
+        <v>0</v>
+      </c>
+      <c r="P1679">
+        <v>0.98</v>
+      </c>
+      <c r="Q1679">
+        <v>0</v>
+      </c>
+      <c r="R1679">
+        <v>0</v>
+      </c>
+      <c r="S1679">
+        <v>0</v>
+      </c>
+      <c r="T1679">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1680" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1680">
+        <v>1</v>
+      </c>
+      <c r="D1680">
+        <v>1</v>
+      </c>
+      <c r="E1680">
+        <v>1</v>
+      </c>
+      <c r="F1680">
+        <v>39</v>
+      </c>
+      <c r="H1680" t="s">
+        <v>363</v>
+      </c>
+      <c r="I1680">
+        <v>0</v>
+      </c>
+      <c r="J1680">
+        <v>0</v>
+      </c>
+      <c r="K1680">
+        <v>105.41</v>
+      </c>
+      <c r="L1680">
+        <v>37</v>
+      </c>
+      <c r="M1680">
+        <v>15</v>
+      </c>
+      <c r="N1680">
+        <v>5</v>
+      </c>
+      <c r="O1680">
+        <v>0</v>
+      </c>
+      <c r="P1680">
+        <v>21.55</v>
+      </c>
+      <c r="Q1680">
+        <v>0</v>
+      </c>
+      <c r="R1680">
+        <v>1</v>
+      </c>
+      <c r="S1680">
+        <v>0</v>
+      </c>
+      <c r="T1680">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1681" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1681">
+        <v>1</v>
+      </c>
+      <c r="D1681">
+        <v>0</v>
+      </c>
+      <c r="E1681">
+        <v>0</v>
+      </c>
+      <c r="F1681">
+        <v>0</v>
+      </c>
+      <c r="I1681">
+        <v>0</v>
+      </c>
+      <c r="J1681">
+        <v>0</v>
+      </c>
+      <c r="L1681">
+        <v>0</v>
+      </c>
+      <c r="M1681">
+        <v>0</v>
+      </c>
+      <c r="N1681">
+        <v>0</v>
+      </c>
+      <c r="O1681">
+        <v>0</v>
+      </c>
+      <c r="P1681">
+        <v>0</v>
+      </c>
+      <c r="Q1681">
+        <v>0</v>
+      </c>
+      <c r="R1681">
+        <v>0</v>
+      </c>
+      <c r="S1681">
+        <v>0</v>
+      </c>
+      <c r="T1681">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1682" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1682">
+        <v>1</v>
+      </c>
+      <c r="D1682">
+        <v>1</v>
+      </c>
+      <c r="E1682">
+        <v>0</v>
+      </c>
+      <c r="F1682">
+        <v>1</v>
+      </c>
+      <c r="G1682">
+        <v>1</v>
+      </c>
+      <c r="H1682">
+        <v>1</v>
+      </c>
+      <c r="I1682">
+        <v>0</v>
+      </c>
+      <c r="J1682">
+        <v>0</v>
+      </c>
+      <c r="K1682">
+        <v>33.33</v>
+      </c>
+      <c r="L1682">
+        <v>3</v>
+      </c>
+      <c r="M1682">
+        <v>2</v>
+      </c>
+      <c r="N1682">
+        <v>0</v>
+      </c>
+      <c r="O1682">
+        <v>0</v>
+      </c>
+      <c r="P1682">
+        <v>0.98</v>
+      </c>
+      <c r="Q1682">
+        <v>0</v>
+      </c>
+      <c r="R1682">
+        <v>0</v>
+      </c>
+      <c r="S1682">
+        <v>0</v>
+      </c>
+      <c r="T1682">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1683" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1683">
+        <v>1</v>
+      </c>
+      <c r="D1683">
+        <v>1</v>
+      </c>
+      <c r="E1683">
+        <v>0</v>
+      </c>
+      <c r="F1683">
+        <v>3</v>
+      </c>
+      <c r="G1683">
+        <v>3</v>
+      </c>
+      <c r="H1683">
+        <v>3</v>
+      </c>
+      <c r="I1683">
+        <v>0</v>
+      </c>
+      <c r="J1683">
+        <v>0</v>
+      </c>
+      <c r="K1683">
+        <v>42.86</v>
+      </c>
+      <c r="L1683">
+        <v>7</v>
+      </c>
+      <c r="M1683">
+        <v>4</v>
+      </c>
+      <c r="N1683">
+        <v>0</v>
+      </c>
+      <c r="O1683">
+        <v>0</v>
+      </c>
+      <c r="P1683">
+        <v>2.94</v>
+      </c>
+      <c r="Q1683">
+        <v>0</v>
+      </c>
+      <c r="R1683">
+        <v>0</v>
+      </c>
+      <c r="S1683">
+        <v>0</v>
+      </c>
+      <c r="T1683">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1684" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1684">
+        <v>1</v>
+      </c>
+      <c r="D1684">
+        <v>0</v>
+      </c>
+      <c r="E1684">
+        <v>0</v>
+      </c>
+      <c r="F1684">
+        <v>0</v>
+      </c>
+      <c r="I1684">
+        <v>0</v>
+      </c>
+      <c r="J1684">
+        <v>0</v>
+      </c>
+      <c r="L1684">
+        <v>0</v>
+      </c>
+      <c r="M1684">
+        <v>0</v>
+      </c>
+      <c r="N1684">
+        <v>0</v>
+      </c>
+      <c r="O1684">
+        <v>0</v>
+      </c>
+      <c r="P1684">
+        <v>0</v>
+      </c>
+      <c r="Q1684">
+        <v>0</v>
+      </c>
+      <c r="R1684">
+        <v>0</v>
+      </c>
+      <c r="S1684">
+        <v>0</v>
+      </c>
+      <c r="T1684">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1685" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>416</v>
+      </c>
+      <c r="C1685">
+        <v>1</v>
+      </c>
+      <c r="D1685">
+        <v>1</v>
+      </c>
+      <c r="E1685">
+        <v>0</v>
+      </c>
+      <c r="F1685">
+        <v>0</v>
+      </c>
+      <c r="G1685">
+        <v>0</v>
+      </c>
+      <c r="H1685">
+        <v>0</v>
+      </c>
+      <c r="I1685">
+        <v>0</v>
+      </c>
+      <c r="J1685">
+        <v>0</v>
+      </c>
+      <c r="K1685">
+        <v>0</v>
+      </c>
+      <c r="L1685">
+        <v>1</v>
+      </c>
+      <c r="M1685">
+        <v>1</v>
+      </c>
+      <c r="N1685">
+        <v>0</v>
+      </c>
+      <c r="O1685">
+        <v>0</v>
+      </c>
+      <c r="P1685">
+        <v>0</v>
+      </c>
+      <c r="Q1685">
+        <v>0</v>
+      </c>
+      <c r="R1685">
+        <v>0</v>
+      </c>
+      <c r="S1685">
+        <v>0</v>
+      </c>
+      <c r="T1685">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1686" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1686">
+        <v>1</v>
+      </c>
+      <c r="D1686">
+        <v>1</v>
+      </c>
+      <c r="E1686">
+        <v>1</v>
+      </c>
+      <c r="F1686">
+        <v>50</v>
+      </c>
+      <c r="H1686" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1686">
+        <v>1</v>
+      </c>
+      <c r="J1686">
+        <v>0</v>
+      </c>
+      <c r="K1686">
+        <v>138.88999999999999</v>
+      </c>
+      <c r="L1686">
+        <v>36</v>
+      </c>
+      <c r="M1686">
+        <v>5</v>
+      </c>
+      <c r="N1686">
+        <v>4</v>
+      </c>
+      <c r="O1686">
+        <v>0</v>
+      </c>
+      <c r="P1686">
+        <v>27.62</v>
+      </c>
+      <c r="Q1686">
+        <v>2</v>
+      </c>
+      <c r="R1686">
+        <v>0</v>
+      </c>
+      <c r="S1686">
+        <v>0</v>
+      </c>
+      <c r="T1686">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1687" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1687">
+        <v>1</v>
+      </c>
+      <c r="D1687">
+        <v>1</v>
+      </c>
+      <c r="E1687">
+        <v>0</v>
+      </c>
+      <c r="F1687">
+        <v>15</v>
+      </c>
+      <c r="G1687">
+        <v>15</v>
+      </c>
+      <c r="H1687">
+        <v>15</v>
+      </c>
+      <c r="I1687">
+        <v>0</v>
+      </c>
+      <c r="J1687">
+        <v>0</v>
+      </c>
+      <c r="K1687">
+        <v>136.36000000000001</v>
+      </c>
+      <c r="L1687">
+        <v>11</v>
+      </c>
+      <c r="M1687">
+        <v>5</v>
+      </c>
+      <c r="N1687">
+        <v>3</v>
+      </c>
+      <c r="O1687">
+        <v>0</v>
+      </c>
+      <c r="P1687">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="Q1687">
+        <v>0</v>
+      </c>
+      <c r="R1687">
+        <v>0</v>
+      </c>
+      <c r="S1687">
+        <v>0</v>
+      </c>
+      <c r="T1687">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1688" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>474</v>
+      </c>
+      <c r="C1688">
+        <v>1</v>
+      </c>
+      <c r="D1688">
+        <v>1</v>
+      </c>
+      <c r="E1688">
+        <v>0</v>
+      </c>
+      <c r="F1688">
+        <v>11</v>
+      </c>
+      <c r="G1688">
+        <v>11</v>
+      </c>
+      <c r="H1688">
+        <v>11</v>
+      </c>
+      <c r="I1688">
+        <v>0</v>
+      </c>
+      <c r="J1688">
+        <v>0</v>
+      </c>
+      <c r="K1688">
+        <v>157.13999999999999</v>
+      </c>
+      <c r="L1688">
+        <v>7</v>
+      </c>
+      <c r="M1688">
+        <v>2</v>
+      </c>
+      <c r="N1688">
+        <v>1</v>
+      </c>
+      <c r="O1688">
+        <v>0</v>
+      </c>
+      <c r="P1688">
+        <v>6.08</v>
+      </c>
+      <c r="Q1688">
+        <v>0</v>
+      </c>
+      <c r="R1688">
+        <v>0</v>
+      </c>
+      <c r="S1688">
+        <v>0</v>
+      </c>
+      <c r="T1688">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1689" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1689">
+        <v>1</v>
+      </c>
+      <c r="D1689">
+        <v>0</v>
+      </c>
+      <c r="E1689">
+        <v>0</v>
+      </c>
+      <c r="F1689">
+        <v>0</v>
+      </c>
+      <c r="I1689">
+        <v>0</v>
+      </c>
+      <c r="J1689">
+        <v>0</v>
+      </c>
+      <c r="L1689">
+        <v>0</v>
+      </c>
+      <c r="M1689">
+        <v>0</v>
+      </c>
+      <c r="N1689">
+        <v>0</v>
+      </c>
+      <c r="O1689">
+        <v>0</v>
+      </c>
+      <c r="P1689">
+        <v>0</v>
+      </c>
+      <c r="Q1689">
+        <v>1</v>
+      </c>
+      <c r="R1689">
+        <v>0</v>
+      </c>
+      <c r="S1689">
+        <v>0</v>
+      </c>
+      <c r="T1689">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1690" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1690">
+        <v>1</v>
+      </c>
+      <c r="D1690">
+        <v>1</v>
+      </c>
+      <c r="E1690">
+        <v>0</v>
+      </c>
+      <c r="F1690">
+        <v>48</v>
+      </c>
+      <c r="G1690">
+        <v>48</v>
+      </c>
+      <c r="H1690">
+        <v>48</v>
+      </c>
+      <c r="I1690">
+        <v>0</v>
+      </c>
+      <c r="J1690">
+        <v>0</v>
+      </c>
+      <c r="K1690">
+        <v>94.12</v>
+      </c>
+      <c r="L1690">
+        <v>51</v>
+      </c>
+      <c r="M1690">
+        <v>29</v>
+      </c>
+      <c r="N1690">
+        <v>8</v>
+      </c>
+      <c r="O1690">
+        <v>0</v>
+      </c>
+      <c r="P1690">
+        <v>47.06</v>
+      </c>
+      <c r="Q1690">
+        <v>0</v>
+      </c>
+      <c r="R1690">
+        <v>0</v>
+      </c>
+      <c r="S1690">
+        <v>0</v>
+      </c>
+      <c r="T1690">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1691" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1691">
+        <v>1</v>
+      </c>
+      <c r="D1691">
+        <v>1</v>
+      </c>
+      <c r="E1691">
+        <v>0</v>
+      </c>
+      <c r="F1691">
+        <v>24</v>
+      </c>
+      <c r="G1691">
+        <v>24</v>
+      </c>
+      <c r="H1691">
+        <v>24</v>
+      </c>
+      <c r="I1691">
+        <v>0</v>
+      </c>
+      <c r="J1691">
+        <v>0</v>
+      </c>
+      <c r="K1691">
+        <v>141.18</v>
+      </c>
+      <c r="L1691">
+        <v>17</v>
+      </c>
+      <c r="M1691">
+        <v>5</v>
+      </c>
+      <c r="N1691">
+        <v>3</v>
+      </c>
+      <c r="O1691">
+        <v>0</v>
+      </c>
+      <c r="P1691">
+        <v>13.26</v>
+      </c>
+      <c r="Q1691">
+        <v>0</v>
+      </c>
+      <c r="R1691">
+        <v>0</v>
+      </c>
+      <c r="S1691">
+        <v>0</v>
+      </c>
+      <c r="T1691">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1692" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1692">
+        <v>1</v>
+      </c>
+      <c r="D1692">
+        <v>1</v>
+      </c>
+      <c r="E1692">
+        <v>0</v>
+      </c>
+      <c r="F1692">
+        <v>7</v>
+      </c>
+      <c r="G1692">
+        <v>7</v>
+      </c>
+      <c r="H1692">
+        <v>7</v>
+      </c>
+      <c r="I1692">
+        <v>0</v>
+      </c>
+      <c r="J1692">
+        <v>0</v>
+      </c>
+      <c r="K1692">
+        <v>77.78</v>
+      </c>
+      <c r="L1692">
+        <v>9</v>
+      </c>
+      <c r="M1692">
+        <v>5</v>
+      </c>
+      <c r="N1692">
+        <v>1</v>
+      </c>
+      <c r="O1692">
+        <v>0</v>
+      </c>
+      <c r="P1692">
+        <v>6.86</v>
+      </c>
+      <c r="Q1692">
+        <v>1</v>
+      </c>
+      <c r="R1692">
+        <v>0</v>
+      </c>
+      <c r="S1692">
+        <v>0</v>
+      </c>
+      <c r="T1692">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1693" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1693">
+        <v>1</v>
+      </c>
+      <c r="D1693">
+        <v>1</v>
+      </c>
+      <c r="E1693">
+        <v>0</v>
+      </c>
+      <c r="F1693">
+        <v>0</v>
+      </c>
+      <c r="G1693">
+        <v>0</v>
+      </c>
+      <c r="H1693">
+        <v>0</v>
+      </c>
+      <c r="I1693">
+        <v>0</v>
+      </c>
+      <c r="J1693">
+        <v>0</v>
+      </c>
+      <c r="K1693">
+        <v>0</v>
+      </c>
+      <c r="L1693">
+        <v>3</v>
+      </c>
+      <c r="M1693">
+        <v>3</v>
+      </c>
+      <c r="N1693">
+        <v>0</v>
+      </c>
+      <c r="O1693">
+        <v>0</v>
+      </c>
+      <c r="P1693">
+        <v>0</v>
+      </c>
+      <c r="Q1693">
+        <v>0</v>
+      </c>
+      <c r="R1693">
+        <v>0</v>
+      </c>
+      <c r="S1693">
+        <v>0</v>
+      </c>
+      <c r="T1693">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1694" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1694">
+        <v>1</v>
+      </c>
+      <c r="D1694">
+        <v>1</v>
+      </c>
+      <c r="E1694">
+        <v>1</v>
+      </c>
+      <c r="F1694">
+        <v>1</v>
+      </c>
+      <c r="H1694" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1694">
+        <v>0</v>
+      </c>
+      <c r="J1694">
+        <v>0</v>
+      </c>
+      <c r="K1694">
+        <v>33.33</v>
+      </c>
+      <c r="L1694">
+        <v>3</v>
+      </c>
+      <c r="M1694">
+        <v>2</v>
+      </c>
+      <c r="N1694">
+        <v>0</v>
+      </c>
+      <c r="O1694">
+        <v>0</v>
+      </c>
+      <c r="P1694">
+        <v>0.98</v>
+      </c>
+      <c r="Q1694">
+        <v>0</v>
+      </c>
+      <c r="R1694">
+        <v>0</v>
+      </c>
+      <c r="S1694">
+        <v>0</v>
+      </c>
+      <c r="T1694">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1695" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>228</v>
+      </c>
+      <c r="C1695">
+        <v>1</v>
+      </c>
+      <c r="D1695">
+        <v>1</v>
+      </c>
+      <c r="E1695">
+        <v>0</v>
+      </c>
+      <c r="F1695">
+        <v>3</v>
+      </c>
+      <c r="G1695">
+        <v>3</v>
+      </c>
+      <c r="H1695">
+        <v>3</v>
+      </c>
+      <c r="I1695">
+        <v>0</v>
+      </c>
+      <c r="J1695">
+        <v>0</v>
+      </c>
+      <c r="K1695">
+        <v>23.08</v>
+      </c>
+      <c r="L1695">
+        <v>13</v>
+      </c>
+      <c r="M1695">
+        <v>11</v>
+      </c>
+      <c r="N1695">
+        <v>0</v>
+      </c>
+      <c r="O1695">
+        <v>0</v>
+      </c>
+      <c r="P1695">
+        <v>2.94</v>
+      </c>
+      <c r="Q1695">
+        <v>0</v>
+      </c>
+      <c r="R1695">
+        <v>0</v>
+      </c>
+      <c r="S1695">
+        <v>0</v>
+      </c>
+      <c r="T1695">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1696" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1696">
+        <v>1</v>
+      </c>
+      <c r="D1696">
+        <v>1</v>
+      </c>
+      <c r="E1696">
+        <v>0</v>
+      </c>
+      <c r="F1696">
+        <v>7</v>
+      </c>
+      <c r="G1696">
+        <v>7</v>
+      </c>
+      <c r="H1696">
+        <v>7</v>
+      </c>
+      <c r="I1696">
+        <v>0</v>
+      </c>
+      <c r="J1696">
+        <v>0</v>
+      </c>
+      <c r="K1696">
+        <v>43.75</v>
+      </c>
+      <c r="L1696">
+        <v>16</v>
+      </c>
+      <c r="M1696">
+        <v>12</v>
+      </c>
+      <c r="N1696">
+        <v>1</v>
+      </c>
+      <c r="O1696">
+        <v>0</v>
+      </c>
+      <c r="P1696">
+        <v>6.86</v>
+      </c>
+      <c r="Q1696">
+        <v>0</v>
+      </c>
+      <c r="R1696">
+        <v>0</v>
+      </c>
+      <c r="S1696">
+        <v>0</v>
+      </c>
+      <c r="T1696">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1697" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1697">
+        <v>1</v>
+      </c>
+      <c r="D1697">
+        <v>1</v>
+      </c>
+      <c r="E1697">
+        <v>0</v>
+      </c>
+      <c r="F1697">
+        <v>17</v>
+      </c>
+      <c r="G1697">
+        <v>17</v>
+      </c>
+      <c r="H1697">
+        <v>17</v>
+      </c>
+      <c r="I1697">
+        <v>0</v>
+      </c>
+      <c r="J1697">
+        <v>0</v>
+      </c>
+      <c r="K1697">
+        <v>130.77000000000001</v>
+      </c>
+      <c r="L1697">
+        <v>13</v>
+      </c>
+      <c r="M1697">
+        <v>5</v>
+      </c>
+      <c r="N1697">
+        <v>3</v>
+      </c>
+      <c r="O1697">
+        <v>0</v>
+      </c>
+      <c r="P1697">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="Q1697">
+        <v>1</v>
+      </c>
+      <c r="R1697">
+        <v>0</v>
+      </c>
+      <c r="S1697">
+        <v>0</v>
+      </c>
+      <c r="T1697">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1698" t="s">
+        <v>473</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1698">
+        <v>1</v>
+      </c>
+      <c r="D1698">
+        <v>0</v>
+      </c>
+      <c r="E1698">
+        <v>0</v>
+      </c>
+      <c r="F1698">
+        <v>0</v>
+      </c>
+      <c r="I1698">
+        <v>0</v>
+      </c>
+      <c r="J1698">
+        <v>0</v>
+      </c>
+      <c r="L1698">
+        <v>0</v>
+      </c>
+      <c r="M1698">
+        <v>0</v>
+      </c>
+      <c r="N1698">
+        <v>0</v>
+      </c>
+      <c r="O1698">
+        <v>0</v>
+      </c>
+      <c r="P1698">
+        <v>0</v>
+      </c>
+      <c r="Q1698">
+        <v>0</v>
+      </c>
+      <c r="R1698">
+        <v>0</v>
+      </c>
+      <c r="S1698">
+        <v>0</v>
+      </c>
+      <c r="T1698">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1699" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1699">
+        <v>1</v>
+      </c>
+      <c r="D1699">
+        <v>1</v>
+      </c>
+      <c r="E1699">
+        <v>0</v>
+      </c>
+      <c r="F1699">
+        <v>4</v>
+      </c>
+      <c r="G1699">
+        <v>4</v>
+      </c>
+      <c r="H1699">
+        <v>4</v>
+      </c>
+      <c r="I1699">
+        <v>0</v>
+      </c>
+      <c r="J1699">
+        <v>0</v>
+      </c>
+      <c r="K1699">
+        <v>57.14</v>
+      </c>
+      <c r="L1699">
+        <v>7</v>
+      </c>
+      <c r="M1699">
+        <v>6</v>
+      </c>
+      <c r="N1699">
+        <v>1</v>
+      </c>
+      <c r="O1699">
+        <v>0</v>
+      </c>
+      <c r="P1699">
+        <v>4.76</v>
+      </c>
+      <c r="Q1699">
+        <v>0</v>
+      </c>
+      <c r="R1699">
+        <v>0</v>
+      </c>
+      <c r="S1699">
+        <v>0</v>
+      </c>
+      <c r="T1699">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1700" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1700">
+        <v>1</v>
+      </c>
+      <c r="D1700">
+        <v>1</v>
+      </c>
+      <c r="E1700">
+        <v>0</v>
+      </c>
+      <c r="F1700">
+        <v>6</v>
+      </c>
+      <c r="G1700">
+        <v>6</v>
+      </c>
+      <c r="H1700">
+        <v>6</v>
+      </c>
+      <c r="I1700">
+        <v>0</v>
+      </c>
+      <c r="J1700">
+        <v>0</v>
+      </c>
+      <c r="K1700">
+        <v>42.86</v>
+      </c>
+      <c r="L1700">
+        <v>14</v>
+      </c>
+      <c r="M1700">
+        <v>10</v>
+      </c>
+      <c r="N1700">
+        <v>0</v>
+      </c>
+      <c r="O1700">
+        <v>0</v>
+      </c>
+      <c r="P1700">
+        <v>7.14</v>
+      </c>
+      <c r="Q1700">
+        <v>0</v>
+      </c>
+      <c r="R1700">
+        <v>0</v>
+      </c>
+      <c r="S1700">
+        <v>0</v>
+      </c>
+      <c r="T1700">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1701" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1701">
+        <v>1</v>
+      </c>
+      <c r="D1701">
+        <v>1</v>
+      </c>
+      <c r="E1701">
+        <v>0</v>
+      </c>
+      <c r="F1701">
+        <v>13</v>
+      </c>
+      <c r="G1701">
+        <v>13</v>
+      </c>
+      <c r="H1701">
+        <v>13</v>
+      </c>
+      <c r="I1701">
+        <v>0</v>
+      </c>
+      <c r="J1701">
+        <v>0</v>
+      </c>
+      <c r="K1701">
+        <v>76.47</v>
+      </c>
+      <c r="L1701">
+        <v>17</v>
+      </c>
+      <c r="M1701">
+        <v>10</v>
+      </c>
+      <c r="N1701">
+        <v>1</v>
+      </c>
+      <c r="O1701">
+        <v>0</v>
+      </c>
+      <c r="P1701">
+        <v>15.48</v>
+      </c>
+      <c r="Q1701">
+        <v>0</v>
+      </c>
+      <c r="R1701">
+        <v>0</v>
+      </c>
+      <c r="S1701">
+        <v>0</v>
+      </c>
+      <c r="T1701">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1702" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1702">
+        <v>1</v>
+      </c>
+      <c r="D1702">
+        <v>1</v>
+      </c>
+      <c r="E1702">
+        <v>1</v>
+      </c>
+      <c r="F1702">
+        <v>7</v>
+      </c>
+      <c r="H1702" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1702">
+        <v>0</v>
+      </c>
+      <c r="J1702">
+        <v>0</v>
+      </c>
+      <c r="K1702">
+        <v>77.78</v>
+      </c>
+      <c r="L1702">
+        <v>9</v>
+      </c>
+      <c r="M1702">
+        <v>5</v>
+      </c>
+      <c r="N1702">
+        <v>1</v>
+      </c>
+      <c r="O1702">
+        <v>0</v>
+      </c>
+      <c r="P1702">
+        <v>7.53</v>
+      </c>
+      <c r="Q1702">
+        <v>1</v>
+      </c>
+      <c r="R1702">
+        <v>0</v>
+      </c>
+      <c r="S1702">
+        <v>0</v>
+      </c>
+      <c r="T1702">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1703" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1703">
+        <v>1</v>
+      </c>
+      <c r="D1703">
+        <v>1</v>
+      </c>
+      <c r="E1703">
+        <v>0</v>
+      </c>
+      <c r="F1703">
+        <v>8</v>
+      </c>
+      <c r="G1703">
+        <v>8</v>
+      </c>
+      <c r="H1703">
+        <v>8</v>
+      </c>
+      <c r="I1703">
+        <v>0</v>
+      </c>
+      <c r="J1703">
+        <v>0</v>
+      </c>
+      <c r="K1703">
+        <v>266.67</v>
+      </c>
+      <c r="L1703">
+        <v>3</v>
+      </c>
+      <c r="M1703">
+        <v>1</v>
+      </c>
+      <c r="N1703">
+        <v>2</v>
+      </c>
+      <c r="O1703">
+        <v>0</v>
+      </c>
+      <c r="P1703">
+        <v>8.6</v>
+      </c>
+      <c r="Q1703">
+        <v>0</v>
+      </c>
+      <c r="R1703">
+        <v>0</v>
+      </c>
+      <c r="S1703">
+        <v>0</v>
+      </c>
+      <c r="T1703">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1704" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>199</v>
+      </c>
+      <c r="C1704">
+        <v>1</v>
+      </c>
+      <c r="D1704">
+        <v>1</v>
+      </c>
+      <c r="E1704">
+        <v>0</v>
+      </c>
+      <c r="F1704">
+        <v>0</v>
+      </c>
+      <c r="G1704">
+        <v>0</v>
+      </c>
+      <c r="H1704">
+        <v>0</v>
+      </c>
+      <c r="I1704">
+        <v>0</v>
+      </c>
+      <c r="J1704">
+        <v>0</v>
+      </c>
+      <c r="K1704">
+        <v>0</v>
+      </c>
+      <c r="L1704">
+        <v>5</v>
+      </c>
+      <c r="M1704">
+        <v>5</v>
+      </c>
+      <c r="N1704">
+        <v>0</v>
+      </c>
+      <c r="O1704">
+        <v>0</v>
+      </c>
+      <c r="P1704">
+        <v>0</v>
+      </c>
+      <c r="Q1704">
+        <v>0</v>
+      </c>
+      <c r="R1704">
+        <v>0</v>
+      </c>
+      <c r="S1704">
+        <v>0</v>
+      </c>
+      <c r="T1704">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1705" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1705">
+        <v>1</v>
+      </c>
+      <c r="D1705">
+        <v>1</v>
+      </c>
+      <c r="E1705">
+        <v>0</v>
+      </c>
+      <c r="F1705">
+        <v>14</v>
+      </c>
+      <c r="G1705">
+        <v>14</v>
+      </c>
+      <c r="H1705">
+        <v>14</v>
+      </c>
+      <c r="I1705">
+        <v>0</v>
+      </c>
+      <c r="J1705">
+        <v>0</v>
+      </c>
+      <c r="K1705">
+        <v>48.28</v>
+      </c>
+      <c r="L1705">
+        <v>29</v>
+      </c>
+      <c r="M1705">
+        <v>19</v>
+      </c>
+      <c r="N1705">
+        <v>1</v>
+      </c>
+      <c r="O1705">
+        <v>0</v>
+      </c>
+      <c r="P1705">
+        <v>15.05</v>
+      </c>
+      <c r="Q1705">
+        <v>0</v>
+      </c>
+      <c r="R1705">
+        <v>0</v>
+      </c>
+      <c r="S1705">
+        <v>0</v>
+      </c>
+      <c r="T1705">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1706" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>476</v>
+      </c>
+      <c r="C1706">
+        <v>1</v>
+      </c>
+      <c r="D1706">
+        <v>0</v>
+      </c>
+      <c r="E1706">
+        <v>0</v>
+      </c>
+      <c r="F1706">
+        <v>0</v>
+      </c>
+      <c r="I1706">
+        <v>0</v>
+      </c>
+      <c r="J1706">
+        <v>0</v>
+      </c>
+      <c r="L1706">
+        <v>0</v>
+      </c>
+      <c r="M1706">
+        <v>0</v>
+      </c>
+      <c r="N1706">
+        <v>0</v>
+      </c>
+      <c r="O1706">
+        <v>0</v>
+      </c>
+      <c r="P1706">
+        <v>0</v>
+      </c>
+      <c r="Q1706">
+        <v>0</v>
+      </c>
+      <c r="R1706">
+        <v>0</v>
+      </c>
+      <c r="S1706">
+        <v>0</v>
+      </c>
+      <c r="T1706">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1707" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1707">
+        <v>1</v>
+      </c>
+      <c r="D1707">
+        <v>1</v>
+      </c>
+      <c r="E1707">
+        <v>1</v>
+      </c>
+      <c r="F1707">
+        <v>0</v>
+      </c>
+      <c r="H1707" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1707">
+        <v>0</v>
+      </c>
+      <c r="J1707">
+        <v>0</v>
+      </c>
+      <c r="K1707">
+        <v>0</v>
+      </c>
+      <c r="L1707">
+        <v>1</v>
+      </c>
+      <c r="M1707">
+        <v>1</v>
+      </c>
+      <c r="N1707">
+        <v>0</v>
+      </c>
+      <c r="O1707">
+        <v>0</v>
+      </c>
+      <c r="P1707">
+        <v>0</v>
+      </c>
+      <c r="Q1707">
+        <v>0</v>
+      </c>
+      <c r="R1707">
+        <v>0</v>
+      </c>
+      <c r="S1707">
+        <v>0</v>
+      </c>
+      <c r="T1707">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1708" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>438</v>
+      </c>
+      <c r="C1708">
+        <v>1</v>
+      </c>
+      <c r="D1708">
+        <v>1</v>
+      </c>
+      <c r="E1708">
+        <v>0</v>
+      </c>
+      <c r="F1708">
+        <v>19</v>
+      </c>
+      <c r="G1708">
+        <v>19</v>
+      </c>
+      <c r="H1708">
+        <v>19</v>
+      </c>
+      <c r="I1708">
+        <v>0</v>
+      </c>
+      <c r="J1708">
+        <v>0</v>
+      </c>
+      <c r="K1708">
+        <v>35.85</v>
+      </c>
+      <c r="L1708">
+        <v>53</v>
+      </c>
+      <c r="M1708">
+        <v>41</v>
+      </c>
+      <c r="N1708">
+        <v>1</v>
+      </c>
+      <c r="O1708">
+        <v>0</v>
+      </c>
+      <c r="P1708">
+        <v>22.62</v>
+      </c>
+      <c r="Q1708">
+        <v>1</v>
+      </c>
+      <c r="R1708">
+        <v>0</v>
+      </c>
+      <c r="S1708">
+        <v>0</v>
+      </c>
+      <c r="T1708">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1709" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1709">
+        <v>1</v>
+      </c>
+      <c r="D1709">
+        <v>1</v>
+      </c>
+      <c r="E1709">
+        <v>0</v>
+      </c>
+      <c r="F1709">
+        <v>9</v>
+      </c>
+      <c r="G1709">
+        <v>9</v>
+      </c>
+      <c r="H1709">
+        <v>9</v>
+      </c>
+      <c r="I1709">
+        <v>0</v>
+      </c>
+      <c r="J1709">
+        <v>0</v>
+      </c>
+      <c r="K1709">
+        <v>75</v>
+      </c>
+      <c r="L1709">
+        <v>12</v>
+      </c>
+      <c r="M1709">
+        <v>7</v>
+      </c>
+      <c r="N1709">
+        <v>1</v>
+      </c>
+      <c r="O1709">
+        <v>0</v>
+      </c>
+      <c r="P1709">
+        <v>9.68</v>
+      </c>
+      <c r="Q1709">
+        <v>0</v>
+      </c>
+      <c r="R1709">
+        <v>0</v>
+      </c>
+      <c r="S1709">
+        <v>0</v>
+      </c>
+      <c r="T1709">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1710" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1710">
+        <v>1</v>
+      </c>
+      <c r="D1710">
+        <v>1</v>
+      </c>
+      <c r="E1710">
+        <v>1</v>
+      </c>
+      <c r="F1710">
+        <v>0</v>
+      </c>
+      <c r="H1710" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1710">
+        <v>0</v>
+      </c>
+      <c r="J1710">
+        <v>0</v>
+      </c>
+      <c r="K1710">
+        <v>0</v>
+      </c>
+      <c r="L1710">
+        <v>4</v>
+      </c>
+      <c r="M1710">
+        <v>4</v>
+      </c>
+      <c r="N1710">
+        <v>0</v>
+      </c>
+      <c r="O1710">
+        <v>0</v>
+      </c>
+      <c r="P1710">
+        <v>0</v>
+      </c>
+      <c r="Q1710">
+        <v>0</v>
+      </c>
+      <c r="R1710">
+        <v>0</v>
+      </c>
+      <c r="S1710">
+        <v>0</v>
+      </c>
+      <c r="T1710">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1711" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1711">
+        <v>1</v>
+      </c>
+      <c r="D1711">
+        <v>1</v>
+      </c>
+      <c r="E1711">
+        <v>0</v>
+      </c>
+      <c r="F1711">
+        <v>9</v>
+      </c>
+      <c r="G1711">
+        <v>9</v>
+      </c>
+      <c r="H1711">
+        <v>9</v>
+      </c>
+      <c r="I1711">
+        <v>0</v>
+      </c>
+      <c r="J1711">
+        <v>0</v>
+      </c>
+      <c r="K1711">
+        <v>50</v>
+      </c>
+      <c r="L1711">
+        <v>18</v>
+      </c>
+      <c r="M1711">
+        <v>13</v>
+      </c>
+      <c r="N1711">
+        <v>1</v>
+      </c>
+      <c r="O1711">
+        <v>0</v>
+      </c>
+      <c r="P1711">
+        <v>9.68</v>
+      </c>
+      <c r="Q1711">
+        <v>0</v>
+      </c>
+      <c r="R1711">
+        <v>0</v>
+      </c>
+      <c r="S1711">
+        <v>0</v>
+      </c>
+      <c r="T1711">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1712" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1712">
+        <v>1</v>
+      </c>
+      <c r="D1712">
+        <v>1</v>
+      </c>
+      <c r="E1712">
+        <v>0</v>
+      </c>
+      <c r="F1712">
+        <v>9</v>
+      </c>
+      <c r="G1712">
+        <v>9</v>
+      </c>
+      <c r="H1712">
+        <v>9</v>
+      </c>
+      <c r="I1712">
+        <v>0</v>
+      </c>
+      <c r="J1712">
+        <v>0</v>
+      </c>
+      <c r="K1712">
+        <v>69.23</v>
+      </c>
+      <c r="L1712">
+        <v>13</v>
+      </c>
+      <c r="M1712">
+        <v>8</v>
+      </c>
+      <c r="N1712">
+        <v>1</v>
+      </c>
+      <c r="O1712">
+        <v>0</v>
+      </c>
+      <c r="P1712">
+        <v>10.71</v>
+      </c>
+      <c r="Q1712">
+        <v>0</v>
+      </c>
+      <c r="R1712">
+        <v>0</v>
+      </c>
+      <c r="S1712">
+        <v>0</v>
+      </c>
+      <c r="T1712">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1713" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1713">
+        <v>1</v>
+      </c>
+      <c r="D1713">
+        <v>1</v>
+      </c>
+      <c r="E1713">
+        <v>0</v>
+      </c>
+      <c r="F1713">
+        <v>2</v>
+      </c>
+      <c r="G1713">
+        <v>2</v>
+      </c>
+      <c r="H1713">
+        <v>2</v>
+      </c>
+      <c r="I1713">
+        <v>0</v>
+      </c>
+      <c r="J1713">
+        <v>0</v>
+      </c>
+      <c r="K1713">
+        <v>20</v>
+      </c>
+      <c r="L1713">
+        <v>10</v>
+      </c>
+      <c r="M1713">
+        <v>8</v>
+      </c>
+      <c r="N1713">
+        <v>0</v>
+      </c>
+      <c r="O1713">
+        <v>0</v>
+      </c>
+      <c r="P1713">
+        <v>2.38</v>
+      </c>
+      <c r="Q1713">
+        <v>0</v>
+      </c>
+      <c r="R1713">
+        <v>0</v>
+      </c>
+      <c r="S1713">
+        <v>0</v>
+      </c>
+      <c r="T1713">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1714" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>439</v>
+      </c>
+      <c r="C1714">
+        <v>1</v>
+      </c>
+      <c r="D1714">
+        <v>1</v>
+      </c>
+      <c r="E1714">
+        <v>0</v>
+      </c>
+      <c r="F1714">
+        <v>30</v>
+      </c>
+      <c r="G1714">
+        <v>30</v>
+      </c>
+      <c r="H1714">
+        <v>30</v>
+      </c>
+      <c r="I1714">
+        <v>0</v>
+      </c>
+      <c r="J1714">
+        <v>0</v>
+      </c>
+      <c r="K1714">
+        <v>62.5</v>
+      </c>
+      <c r="L1714">
+        <v>48</v>
+      </c>
+      <c r="M1714">
+        <v>32</v>
+      </c>
+      <c r="N1714">
+        <v>4</v>
+      </c>
+      <c r="O1714">
+        <v>0</v>
+      </c>
+      <c r="P1714">
+        <v>32.26</v>
+      </c>
+      <c r="Q1714">
+        <v>0</v>
+      </c>
+      <c r="R1714">
+        <v>0</v>
+      </c>
+      <c r="S1714">
+        <v>0</v>
+      </c>
+      <c r="T1714">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1715" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1715">
+        <v>1</v>
+      </c>
+      <c r="D1715">
+        <v>1</v>
+      </c>
+      <c r="E1715">
+        <v>0</v>
+      </c>
+      <c r="F1715">
+        <v>1</v>
+      </c>
+      <c r="G1715">
+        <v>1</v>
+      </c>
+      <c r="H1715">
+        <v>1</v>
+      </c>
+      <c r="I1715">
+        <v>0</v>
+      </c>
+      <c r="J1715">
+        <v>0</v>
+      </c>
+      <c r="K1715">
+        <v>20</v>
+      </c>
+      <c r="L1715">
+        <v>5</v>
+      </c>
+      <c r="M1715">
+        <v>4</v>
+      </c>
+      <c r="N1715">
+        <v>0</v>
+      </c>
+      <c r="O1715">
+        <v>0</v>
+      </c>
+      <c r="P1715">
+        <v>1.08</v>
+      </c>
+      <c r="Q1715">
+        <v>0</v>
+      </c>
+      <c r="R1715">
+        <v>0</v>
+      </c>
+      <c r="S1715">
+        <v>0</v>
+      </c>
+      <c r="T1715">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1716" t="s">
+        <v>475</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1716">
+        <v>1</v>
+      </c>
+      <c r="D1716">
+        <v>1</v>
+      </c>
+      <c r="E1716">
+        <v>1</v>
+      </c>
+      <c r="F1716">
+        <v>0</v>
+      </c>
+      <c r="H1716" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1716">
+        <v>0</v>
+      </c>
+      <c r="J1716">
+        <v>0</v>
+      </c>
+      <c r="K1716">
+        <v>0</v>
+      </c>
+      <c r="L1716">
+        <v>1</v>
+      </c>
+      <c r="M1716">
+        <v>1</v>
+      </c>
+      <c r="N1716">
+        <v>0</v>
+      </c>
+      <c r="O1716">
+        <v>0</v>
+      </c>
+      <c r="P1716">
+        <v>0</v>
+      </c>
+      <c r="Q1716">
+        <v>1</v>
+      </c>
+      <c r="R1716">
+        <v>0</v>
+      </c>
+      <c r="S1716">
+        <v>0</v>
+      </c>
+      <c r="T1716">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="482">
   <si>
     <t>Group</t>
   </si>
@@ -1451,6 +1451,21 @@
   <si>
     <t>Ellen McKane</t>
   </si>
+  <si>
+    <t>Lisburn Women 2nd XI v Bangor Women 2nd XI, TBC - 29 July 2026</t>
+  </si>
+  <si>
+    <t>Charlotte Shivers</t>
+  </si>
+  <si>
+    <t>Ella Mosgrove</t>
+  </si>
+  <si>
+    <t>Cate Hirst</t>
+  </si>
+  <si>
+    <t>Danielle Heron</t>
+  </si>
 </sst>
 </file>
 
@@ -2257,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1716"/>
+  <dimension ref="A1:T1737"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -102710,6 +102725,1233 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1717" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1717" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1717">
+        <v>1</v>
+      </c>
+      <c r="D1717">
+        <v>0</v>
+      </c>
+      <c r="E1717">
+        <v>0</v>
+      </c>
+      <c r="F1717">
+        <v>0</v>
+      </c>
+      <c r="I1717">
+        <v>0</v>
+      </c>
+      <c r="J1717">
+        <v>0</v>
+      </c>
+      <c r="L1717">
+        <v>0</v>
+      </c>
+      <c r="M1717">
+        <v>0</v>
+      </c>
+      <c r="N1717">
+        <v>0</v>
+      </c>
+      <c r="O1717">
+        <v>0</v>
+      </c>
+      <c r="P1717">
+        <v>0</v>
+      </c>
+      <c r="Q1717">
+        <v>0</v>
+      </c>
+      <c r="R1717">
+        <v>0</v>
+      </c>
+      <c r="S1717">
+        <v>0</v>
+      </c>
+      <c r="T1717">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1718" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1718">
+        <v>1</v>
+      </c>
+      <c r="D1718">
+        <v>0</v>
+      </c>
+      <c r="E1718">
+        <v>0</v>
+      </c>
+      <c r="F1718">
+        <v>0</v>
+      </c>
+      <c r="I1718">
+        <v>0</v>
+      </c>
+      <c r="J1718">
+        <v>0</v>
+      </c>
+      <c r="L1718">
+        <v>0</v>
+      </c>
+      <c r="M1718">
+        <v>0</v>
+      </c>
+      <c r="N1718">
+        <v>0</v>
+      </c>
+      <c r="O1718">
+        <v>0</v>
+      </c>
+      <c r="P1718">
+        <v>0</v>
+      </c>
+      <c r="Q1718">
+        <v>0</v>
+      </c>
+      <c r="R1718">
+        <v>0</v>
+      </c>
+      <c r="S1718">
+        <v>0</v>
+      </c>
+      <c r="T1718">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1719" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1719">
+        <v>1</v>
+      </c>
+      <c r="D1719">
+        <v>1</v>
+      </c>
+      <c r="E1719">
+        <v>0</v>
+      </c>
+      <c r="F1719">
+        <v>4</v>
+      </c>
+      <c r="G1719">
+        <v>4</v>
+      </c>
+      <c r="H1719">
+        <v>4</v>
+      </c>
+      <c r="I1719">
+        <v>0</v>
+      </c>
+      <c r="J1719">
+        <v>0</v>
+      </c>
+      <c r="K1719">
+        <v>21.05</v>
+      </c>
+      <c r="L1719">
+        <v>19</v>
+      </c>
+      <c r="M1719">
+        <v>16</v>
+      </c>
+      <c r="N1719">
+        <v>0</v>
+      </c>
+      <c r="O1719">
+        <v>0</v>
+      </c>
+      <c r="P1719">
+        <v>5.63</v>
+      </c>
+      <c r="Q1719">
+        <v>0</v>
+      </c>
+      <c r="R1719">
+        <v>0</v>
+      </c>
+      <c r="S1719">
+        <v>0</v>
+      </c>
+      <c r="T1719">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1720" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1720">
+        <v>1</v>
+      </c>
+      <c r="D1720">
+        <v>0</v>
+      </c>
+      <c r="E1720">
+        <v>0</v>
+      </c>
+      <c r="F1720">
+        <v>0</v>
+      </c>
+      <c r="I1720">
+        <v>0</v>
+      </c>
+      <c r="J1720">
+        <v>0</v>
+      </c>
+      <c r="L1720">
+        <v>0</v>
+      </c>
+      <c r="M1720">
+        <v>0</v>
+      </c>
+      <c r="N1720">
+        <v>0</v>
+      </c>
+      <c r="O1720">
+        <v>0</v>
+      </c>
+      <c r="P1720">
+        <v>0</v>
+      </c>
+      <c r="Q1720">
+        <v>0</v>
+      </c>
+      <c r="R1720">
+        <v>0</v>
+      </c>
+      <c r="S1720">
+        <v>0</v>
+      </c>
+      <c r="T1720">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1721" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1721">
+        <v>1</v>
+      </c>
+      <c r="D1721">
+        <v>0</v>
+      </c>
+      <c r="E1721">
+        <v>0</v>
+      </c>
+      <c r="F1721">
+        <v>0</v>
+      </c>
+      <c r="I1721">
+        <v>0</v>
+      </c>
+      <c r="J1721">
+        <v>0</v>
+      </c>
+      <c r="L1721">
+        <v>0</v>
+      </c>
+      <c r="M1721">
+        <v>0</v>
+      </c>
+      <c r="N1721">
+        <v>0</v>
+      </c>
+      <c r="O1721">
+        <v>0</v>
+      </c>
+      <c r="P1721">
+        <v>0</v>
+      </c>
+      <c r="Q1721">
+        <v>0</v>
+      </c>
+      <c r="R1721">
+        <v>0</v>
+      </c>
+      <c r="S1721">
+        <v>0</v>
+      </c>
+      <c r="T1721">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1722" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1722">
+        <v>1</v>
+      </c>
+      <c r="D1722">
+        <v>1</v>
+      </c>
+      <c r="E1722">
+        <v>1</v>
+      </c>
+      <c r="F1722">
+        <v>10</v>
+      </c>
+      <c r="H1722" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1722">
+        <v>0</v>
+      </c>
+      <c r="J1722">
+        <v>0</v>
+      </c>
+      <c r="K1722">
+        <v>111.11</v>
+      </c>
+      <c r="L1722">
+        <v>9</v>
+      </c>
+      <c r="M1722">
+        <v>4</v>
+      </c>
+      <c r="N1722">
+        <v>1</v>
+      </c>
+      <c r="O1722">
+        <v>0</v>
+      </c>
+      <c r="P1722">
+        <v>13.89</v>
+      </c>
+      <c r="Q1722">
+        <v>0</v>
+      </c>
+      <c r="R1722">
+        <v>0</v>
+      </c>
+      <c r="S1722">
+        <v>0</v>
+      </c>
+      <c r="T1722">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1723" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>481</v>
+      </c>
+      <c r="C1723">
+        <v>1</v>
+      </c>
+      <c r="D1723">
+        <v>1</v>
+      </c>
+      <c r="E1723">
+        <v>0</v>
+      </c>
+      <c r="F1723">
+        <v>16</v>
+      </c>
+      <c r="G1723">
+        <v>16</v>
+      </c>
+      <c r="H1723">
+        <v>16</v>
+      </c>
+      <c r="I1723">
+        <v>0</v>
+      </c>
+      <c r="J1723">
+        <v>0</v>
+      </c>
+      <c r="K1723">
+        <v>55.17</v>
+      </c>
+      <c r="L1723">
+        <v>29</v>
+      </c>
+      <c r="M1723">
+        <v>18</v>
+      </c>
+      <c r="N1723">
+        <v>1</v>
+      </c>
+      <c r="O1723">
+        <v>0</v>
+      </c>
+      <c r="P1723">
+        <v>22.54</v>
+      </c>
+      <c r="Q1723">
+        <v>0</v>
+      </c>
+      <c r="R1723">
+        <v>0</v>
+      </c>
+      <c r="S1723">
+        <v>0</v>
+      </c>
+      <c r="T1723">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1724" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>480</v>
+      </c>
+      <c r="C1724">
+        <v>1</v>
+      </c>
+      <c r="D1724">
+        <v>1</v>
+      </c>
+      <c r="E1724">
+        <v>1</v>
+      </c>
+      <c r="F1724">
+        <v>1</v>
+      </c>
+      <c r="H1724" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1724">
+        <v>0</v>
+      </c>
+      <c r="J1724">
+        <v>0</v>
+      </c>
+      <c r="K1724">
+        <v>50</v>
+      </c>
+      <c r="L1724">
+        <v>2</v>
+      </c>
+      <c r="M1724">
+        <v>1</v>
+      </c>
+      <c r="N1724">
+        <v>0</v>
+      </c>
+      <c r="O1724">
+        <v>0</v>
+      </c>
+      <c r="P1724">
+        <v>1.41</v>
+      </c>
+      <c r="Q1724">
+        <v>0</v>
+      </c>
+      <c r="R1724">
+        <v>0</v>
+      </c>
+      <c r="S1724">
+        <v>0</v>
+      </c>
+      <c r="T1724">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1725" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1725">
+        <v>1</v>
+      </c>
+      <c r="D1725">
+        <v>1</v>
+      </c>
+      <c r="E1725">
+        <v>0</v>
+      </c>
+      <c r="F1725">
+        <v>9</v>
+      </c>
+      <c r="G1725">
+        <v>9</v>
+      </c>
+      <c r="H1725">
+        <v>9</v>
+      </c>
+      <c r="I1725">
+        <v>0</v>
+      </c>
+      <c r="J1725">
+        <v>0</v>
+      </c>
+      <c r="K1725">
+        <v>128.57</v>
+      </c>
+      <c r="L1725">
+        <v>7</v>
+      </c>
+      <c r="M1725">
+        <v>4</v>
+      </c>
+      <c r="N1725">
+        <v>2</v>
+      </c>
+      <c r="O1725">
+        <v>0</v>
+      </c>
+      <c r="P1725">
+        <v>12.5</v>
+      </c>
+      <c r="Q1725">
+        <v>0</v>
+      </c>
+      <c r="R1725">
+        <v>0</v>
+      </c>
+      <c r="S1725">
+        <v>0</v>
+      </c>
+      <c r="T1725">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1726" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1726">
+        <v>1</v>
+      </c>
+      <c r="D1726">
+        <v>1</v>
+      </c>
+      <c r="E1726">
+        <v>0</v>
+      </c>
+      <c r="F1726">
+        <v>9</v>
+      </c>
+      <c r="G1726">
+        <v>9</v>
+      </c>
+      <c r="H1726">
+        <v>9</v>
+      </c>
+      <c r="I1726">
+        <v>0</v>
+      </c>
+      <c r="J1726">
+        <v>0</v>
+      </c>
+      <c r="K1726">
+        <v>42.86</v>
+      </c>
+      <c r="L1726">
+        <v>21</v>
+      </c>
+      <c r="M1726">
+        <v>12</v>
+      </c>
+      <c r="N1726">
+        <v>0</v>
+      </c>
+      <c r="O1726">
+        <v>0</v>
+      </c>
+      <c r="P1726">
+        <v>12.68</v>
+      </c>
+      <c r="Q1726">
+        <v>0</v>
+      </c>
+      <c r="R1726">
+        <v>0</v>
+      </c>
+      <c r="S1726">
+        <v>0</v>
+      </c>
+      <c r="T1726">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1727" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1727">
+        <v>1</v>
+      </c>
+      <c r="D1727">
+        <v>0</v>
+      </c>
+      <c r="E1727">
+        <v>0</v>
+      </c>
+      <c r="F1727">
+        <v>0</v>
+      </c>
+      <c r="I1727">
+        <v>0</v>
+      </c>
+      <c r="J1727">
+        <v>0</v>
+      </c>
+      <c r="L1727">
+        <v>0</v>
+      </c>
+      <c r="M1727">
+        <v>0</v>
+      </c>
+      <c r="N1727">
+        <v>0</v>
+      </c>
+      <c r="O1727">
+        <v>0</v>
+      </c>
+      <c r="P1727">
+        <v>0</v>
+      </c>
+      <c r="Q1727">
+        <v>0</v>
+      </c>
+      <c r="R1727">
+        <v>0</v>
+      </c>
+      <c r="S1727">
+        <v>0</v>
+      </c>
+      <c r="T1727">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1728" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1728">
+        <v>1</v>
+      </c>
+      <c r="D1728">
+        <v>0</v>
+      </c>
+      <c r="E1728">
+        <v>0</v>
+      </c>
+      <c r="F1728">
+        <v>0</v>
+      </c>
+      <c r="I1728">
+        <v>0</v>
+      </c>
+      <c r="J1728">
+        <v>0</v>
+      </c>
+      <c r="L1728">
+        <v>0</v>
+      </c>
+      <c r="M1728">
+        <v>0</v>
+      </c>
+      <c r="N1728">
+        <v>0</v>
+      </c>
+      <c r="O1728">
+        <v>0</v>
+      </c>
+      <c r="P1728">
+        <v>0</v>
+      </c>
+      <c r="Q1728">
+        <v>0</v>
+      </c>
+      <c r="R1728">
+        <v>0</v>
+      </c>
+      <c r="S1728">
+        <v>0</v>
+      </c>
+      <c r="T1728">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1729" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1729">
+        <v>1</v>
+      </c>
+      <c r="D1729">
+        <v>0</v>
+      </c>
+      <c r="E1729">
+        <v>0</v>
+      </c>
+      <c r="F1729">
+        <v>0</v>
+      </c>
+      <c r="I1729">
+        <v>0</v>
+      </c>
+      <c r="J1729">
+        <v>0</v>
+      </c>
+      <c r="L1729">
+        <v>0</v>
+      </c>
+      <c r="M1729">
+        <v>0</v>
+      </c>
+      <c r="N1729">
+        <v>0</v>
+      </c>
+      <c r="O1729">
+        <v>0</v>
+      </c>
+      <c r="P1729">
+        <v>0</v>
+      </c>
+      <c r="Q1729">
+        <v>0</v>
+      </c>
+      <c r="R1729">
+        <v>0</v>
+      </c>
+      <c r="S1729">
+        <v>0</v>
+      </c>
+      <c r="T1729">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1730" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>479</v>
+      </c>
+      <c r="C1730">
+        <v>1</v>
+      </c>
+      <c r="D1730">
+        <v>1</v>
+      </c>
+      <c r="E1730">
+        <v>1</v>
+      </c>
+      <c r="F1730">
+        <v>2</v>
+      </c>
+      <c r="H1730" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1730">
+        <v>0</v>
+      </c>
+      <c r="J1730">
+        <v>0</v>
+      </c>
+      <c r="K1730">
+        <v>50</v>
+      </c>
+      <c r="L1730">
+        <v>4</v>
+      </c>
+      <c r="M1730">
+        <v>2</v>
+      </c>
+      <c r="N1730">
+        <v>0</v>
+      </c>
+      <c r="O1730">
+        <v>0</v>
+      </c>
+      <c r="P1730">
+        <v>2.82</v>
+      </c>
+      <c r="Q1730">
+        <v>0</v>
+      </c>
+      <c r="R1730">
+        <v>0</v>
+      </c>
+      <c r="S1730">
+        <v>0</v>
+      </c>
+      <c r="T1730">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1731" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1731">
+        <v>1</v>
+      </c>
+      <c r="D1731">
+        <v>1</v>
+      </c>
+      <c r="E1731">
+        <v>0</v>
+      </c>
+      <c r="F1731">
+        <v>2</v>
+      </c>
+      <c r="G1731">
+        <v>2</v>
+      </c>
+      <c r="H1731">
+        <v>2</v>
+      </c>
+      <c r="I1731">
+        <v>0</v>
+      </c>
+      <c r="J1731">
+        <v>0</v>
+      </c>
+      <c r="K1731">
+        <v>50</v>
+      </c>
+      <c r="L1731">
+        <v>4</v>
+      </c>
+      <c r="M1731">
+        <v>2</v>
+      </c>
+      <c r="N1731">
+        <v>0</v>
+      </c>
+      <c r="O1731">
+        <v>0</v>
+      </c>
+      <c r="P1731">
+        <v>2.82</v>
+      </c>
+      <c r="Q1731">
+        <v>0</v>
+      </c>
+      <c r="R1731">
+        <v>0</v>
+      </c>
+      <c r="S1731">
+        <v>0</v>
+      </c>
+      <c r="T1731">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1732" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1732">
+        <v>1</v>
+      </c>
+      <c r="D1732">
+        <v>1</v>
+      </c>
+      <c r="E1732">
+        <v>0</v>
+      </c>
+      <c r="F1732">
+        <v>6</v>
+      </c>
+      <c r="G1732">
+        <v>6</v>
+      </c>
+      <c r="H1732">
+        <v>6</v>
+      </c>
+      <c r="I1732">
+        <v>0</v>
+      </c>
+      <c r="J1732">
+        <v>0</v>
+      </c>
+      <c r="K1732">
+        <v>40</v>
+      </c>
+      <c r="L1732">
+        <v>15</v>
+      </c>
+      <c r="M1732">
+        <v>9</v>
+      </c>
+      <c r="N1732">
+        <v>0</v>
+      </c>
+      <c r="O1732">
+        <v>0</v>
+      </c>
+      <c r="P1732">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="Q1732">
+        <v>0</v>
+      </c>
+      <c r="R1732">
+        <v>0</v>
+      </c>
+      <c r="S1732">
+        <v>0</v>
+      </c>
+      <c r="T1732">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1733" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1733">
+        <v>1</v>
+      </c>
+      <c r="D1733">
+        <v>1</v>
+      </c>
+      <c r="E1733">
+        <v>0</v>
+      </c>
+      <c r="F1733">
+        <v>0</v>
+      </c>
+      <c r="G1733">
+        <v>0</v>
+      </c>
+      <c r="H1733">
+        <v>0</v>
+      </c>
+      <c r="I1733">
+        <v>0</v>
+      </c>
+      <c r="J1733">
+        <v>0</v>
+      </c>
+      <c r="K1733">
+        <v>0</v>
+      </c>
+      <c r="L1733">
+        <v>8</v>
+      </c>
+      <c r="M1733">
+        <v>8</v>
+      </c>
+      <c r="N1733">
+        <v>0</v>
+      </c>
+      <c r="O1733">
+        <v>0</v>
+      </c>
+      <c r="P1733">
+        <v>0</v>
+      </c>
+      <c r="Q1733">
+        <v>0</v>
+      </c>
+      <c r="R1733">
+        <v>0</v>
+      </c>
+      <c r="S1733">
+        <v>0</v>
+      </c>
+      <c r="T1733">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1734" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>478</v>
+      </c>
+      <c r="C1734">
+        <v>1</v>
+      </c>
+      <c r="D1734">
+        <v>1</v>
+      </c>
+      <c r="E1734">
+        <v>0</v>
+      </c>
+      <c r="F1734">
+        <v>6</v>
+      </c>
+      <c r="G1734">
+        <v>6</v>
+      </c>
+      <c r="H1734">
+        <v>6</v>
+      </c>
+      <c r="I1734">
+        <v>0</v>
+      </c>
+      <c r="J1734">
+        <v>0</v>
+      </c>
+      <c r="K1734">
+        <v>60</v>
+      </c>
+      <c r="L1734">
+        <v>10</v>
+      </c>
+      <c r="M1734">
+        <v>7</v>
+      </c>
+      <c r="N1734">
+        <v>1</v>
+      </c>
+      <c r="O1734">
+        <v>0</v>
+      </c>
+      <c r="P1734">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="Q1734">
+        <v>0</v>
+      </c>
+      <c r="R1734">
+        <v>0</v>
+      </c>
+      <c r="S1734">
+        <v>0</v>
+      </c>
+      <c r="T1734">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1735" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>227</v>
+      </c>
+      <c r="C1735">
+        <v>1</v>
+      </c>
+      <c r="D1735">
+        <v>1</v>
+      </c>
+      <c r="E1735">
+        <v>0</v>
+      </c>
+      <c r="F1735">
+        <v>0</v>
+      </c>
+      <c r="G1735">
+        <v>0</v>
+      </c>
+      <c r="H1735">
+        <v>0</v>
+      </c>
+      <c r="I1735">
+        <v>0</v>
+      </c>
+      <c r="J1735">
+        <v>0</v>
+      </c>
+      <c r="K1735">
+        <v>0</v>
+      </c>
+      <c r="L1735">
+        <v>6</v>
+      </c>
+      <c r="M1735">
+        <v>6</v>
+      </c>
+      <c r="N1735">
+        <v>0</v>
+      </c>
+      <c r="O1735">
+        <v>0</v>
+      </c>
+      <c r="P1735">
+        <v>0</v>
+      </c>
+      <c r="Q1735">
+        <v>0</v>
+      </c>
+      <c r="R1735">
+        <v>0</v>
+      </c>
+      <c r="S1735">
+        <v>0</v>
+      </c>
+      <c r="T1735">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1736" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1736">
+        <v>1</v>
+      </c>
+      <c r="D1736">
+        <v>1</v>
+      </c>
+      <c r="E1736">
+        <v>1</v>
+      </c>
+      <c r="F1736">
+        <v>22</v>
+      </c>
+      <c r="H1736" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1736">
+        <v>0</v>
+      </c>
+      <c r="J1736">
+        <v>0</v>
+      </c>
+      <c r="K1736">
+        <v>104.76</v>
+      </c>
+      <c r="L1736">
+        <v>21</v>
+      </c>
+      <c r="M1736">
+        <v>10</v>
+      </c>
+      <c r="N1736">
+        <v>3</v>
+      </c>
+      <c r="O1736">
+        <v>0</v>
+      </c>
+      <c r="P1736">
+        <v>30.56</v>
+      </c>
+      <c r="Q1736">
+        <v>0</v>
+      </c>
+      <c r="R1736">
+        <v>0</v>
+      </c>
+      <c r="S1736">
+        <v>0</v>
+      </c>
+      <c r="T1736">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1737" t="s">
+        <v>477</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1737">
+        <v>1</v>
+      </c>
+      <c r="D1737">
+        <v>1</v>
+      </c>
+      <c r="E1737">
+        <v>0</v>
+      </c>
+      <c r="F1737">
+        <v>17</v>
+      </c>
+      <c r="G1737">
+        <v>17</v>
+      </c>
+      <c r="H1737">
+        <v>17</v>
+      </c>
+      <c r="I1737">
+        <v>0</v>
+      </c>
+      <c r="J1737">
+        <v>0</v>
+      </c>
+      <c r="K1737">
+        <v>106.25</v>
+      </c>
+      <c r="L1737">
+        <v>16</v>
+      </c>
+      <c r="M1737">
+        <v>7</v>
+      </c>
+      <c r="N1737">
+        <v>2</v>
+      </c>
+      <c r="O1737">
+        <v>0</v>
+      </c>
+      <c r="P1737">
+        <v>23.61</v>
+      </c>
+      <c r="Q1737">
+        <v>0</v>
+      </c>
+      <c r="R1737">
+        <v>0</v>
+      </c>
+      <c r="S1737">
+        <v>0</v>
+      </c>
+      <c r="T1737">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3826" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="489">
   <si>
     <t>Group</t>
   </si>
@@ -1466,6 +1466,27 @@
   <si>
     <t>Danielle Heron</t>
   </si>
+  <si>
+    <t>CSNI Women 1st XI v Waringstown Women 1st XI, Stormont - 2 August 2026</t>
+  </si>
+  <si>
+    <t>Amy Caulfield</t>
+  </si>
+  <si>
+    <t>62*</t>
+  </si>
+  <si>
+    <t>Holywood Women 1st XI v Lisburn Women 1st XI, Seapark Oval - 2 August 2026</t>
+  </si>
+  <si>
+    <t>120*</t>
+  </si>
+  <si>
+    <t>North Down Women 1st XI v Muckamore Women 1st XI, The Green - 2 August 2026</t>
+  </si>
+  <si>
+    <t>Paula Parker</t>
+  </si>
 </sst>
 </file>
 
@@ -2272,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1737"/>
+  <dimension ref="A1:T1802"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -103952,6 +103973,3790 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1738" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1738" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1738">
+        <v>1</v>
+      </c>
+      <c r="D1738">
+        <v>0</v>
+      </c>
+      <c r="E1738">
+        <v>0</v>
+      </c>
+      <c r="F1738">
+        <v>0</v>
+      </c>
+      <c r="I1738">
+        <v>0</v>
+      </c>
+      <c r="J1738">
+        <v>0</v>
+      </c>
+      <c r="L1738">
+        <v>0</v>
+      </c>
+      <c r="M1738">
+        <v>0</v>
+      </c>
+      <c r="N1738">
+        <v>0</v>
+      </c>
+      <c r="O1738">
+        <v>0</v>
+      </c>
+      <c r="P1738">
+        <v>0</v>
+      </c>
+      <c r="Q1738">
+        <v>0</v>
+      </c>
+      <c r="R1738">
+        <v>0</v>
+      </c>
+      <c r="S1738">
+        <v>0</v>
+      </c>
+      <c r="T1738">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1739" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1739">
+        <v>1</v>
+      </c>
+      <c r="D1739">
+        <v>0</v>
+      </c>
+      <c r="E1739">
+        <v>0</v>
+      </c>
+      <c r="F1739">
+        <v>0</v>
+      </c>
+      <c r="I1739">
+        <v>0</v>
+      </c>
+      <c r="J1739">
+        <v>0</v>
+      </c>
+      <c r="L1739">
+        <v>0</v>
+      </c>
+      <c r="M1739">
+        <v>0</v>
+      </c>
+      <c r="N1739">
+        <v>0</v>
+      </c>
+      <c r="O1739">
+        <v>0</v>
+      </c>
+      <c r="P1739">
+        <v>0</v>
+      </c>
+      <c r="Q1739">
+        <v>0</v>
+      </c>
+      <c r="R1739">
+        <v>0</v>
+      </c>
+      <c r="S1739">
+        <v>0</v>
+      </c>
+      <c r="T1739">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1740" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1740">
+        <v>1</v>
+      </c>
+      <c r="D1740">
+        <v>1</v>
+      </c>
+      <c r="E1740">
+        <v>0</v>
+      </c>
+      <c r="F1740">
+        <v>4</v>
+      </c>
+      <c r="G1740">
+        <v>4</v>
+      </c>
+      <c r="H1740">
+        <v>4</v>
+      </c>
+      <c r="I1740">
+        <v>0</v>
+      </c>
+      <c r="J1740">
+        <v>0</v>
+      </c>
+      <c r="K1740">
+        <v>57.14</v>
+      </c>
+      <c r="L1740">
+        <v>7</v>
+      </c>
+      <c r="M1740">
+        <v>6</v>
+      </c>
+      <c r="N1740">
+        <v>1</v>
+      </c>
+      <c r="O1740">
+        <v>0</v>
+      </c>
+      <c r="P1740">
+        <v>4.55</v>
+      </c>
+      <c r="Q1740">
+        <v>0</v>
+      </c>
+      <c r="R1740">
+        <v>0</v>
+      </c>
+      <c r="S1740">
+        <v>0</v>
+      </c>
+      <c r="T1740">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1741" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1741">
+        <v>1</v>
+      </c>
+      <c r="D1741">
+        <v>1</v>
+      </c>
+      <c r="E1741">
+        <v>1</v>
+      </c>
+      <c r="F1741">
+        <v>17</v>
+      </c>
+      <c r="H1741" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1741">
+        <v>0</v>
+      </c>
+      <c r="J1741">
+        <v>0</v>
+      </c>
+      <c r="K1741">
+        <v>68</v>
+      </c>
+      <c r="L1741">
+        <v>25</v>
+      </c>
+      <c r="M1741">
+        <v>15</v>
+      </c>
+      <c r="N1741">
+        <v>2</v>
+      </c>
+      <c r="O1741">
+        <v>0</v>
+      </c>
+      <c r="P1741">
+        <v>18.68</v>
+      </c>
+      <c r="Q1741">
+        <v>0</v>
+      </c>
+      <c r="R1741">
+        <v>0</v>
+      </c>
+      <c r="S1741">
+        <v>0</v>
+      </c>
+      <c r="T1741">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1742" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1742">
+        <v>1</v>
+      </c>
+      <c r="D1742">
+        <v>0</v>
+      </c>
+      <c r="E1742">
+        <v>0</v>
+      </c>
+      <c r="F1742">
+        <v>0</v>
+      </c>
+      <c r="I1742">
+        <v>0</v>
+      </c>
+      <c r="J1742">
+        <v>0</v>
+      </c>
+      <c r="L1742">
+        <v>0</v>
+      </c>
+      <c r="M1742">
+        <v>0</v>
+      </c>
+      <c r="N1742">
+        <v>0</v>
+      </c>
+      <c r="O1742">
+        <v>0</v>
+      </c>
+      <c r="P1742">
+        <v>0</v>
+      </c>
+      <c r="Q1742">
+        <v>0</v>
+      </c>
+      <c r="R1742">
+        <v>0</v>
+      </c>
+      <c r="S1742">
+        <v>0</v>
+      </c>
+      <c r="T1742">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1743" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1743">
+        <v>1</v>
+      </c>
+      <c r="D1743">
+        <v>0</v>
+      </c>
+      <c r="E1743">
+        <v>0</v>
+      </c>
+      <c r="F1743">
+        <v>0</v>
+      </c>
+      <c r="I1743">
+        <v>0</v>
+      </c>
+      <c r="J1743">
+        <v>0</v>
+      </c>
+      <c r="L1743">
+        <v>0</v>
+      </c>
+      <c r="M1743">
+        <v>0</v>
+      </c>
+      <c r="N1743">
+        <v>0</v>
+      </c>
+      <c r="O1743">
+        <v>0</v>
+      </c>
+      <c r="P1743">
+        <v>0</v>
+      </c>
+      <c r="Q1743">
+        <v>0</v>
+      </c>
+      <c r="R1743">
+        <v>0</v>
+      </c>
+      <c r="S1743">
+        <v>0</v>
+      </c>
+      <c r="T1743">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1744" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1744">
+        <v>1</v>
+      </c>
+      <c r="D1744">
+        <v>1</v>
+      </c>
+      <c r="E1744">
+        <v>0</v>
+      </c>
+      <c r="F1744">
+        <v>0</v>
+      </c>
+      <c r="G1744">
+        <v>0</v>
+      </c>
+      <c r="H1744">
+        <v>0</v>
+      </c>
+      <c r="I1744">
+        <v>0</v>
+      </c>
+      <c r="J1744">
+        <v>0</v>
+      </c>
+      <c r="K1744">
+        <v>0</v>
+      </c>
+      <c r="L1744">
+        <v>3</v>
+      </c>
+      <c r="M1744">
+        <v>3</v>
+      </c>
+      <c r="N1744">
+        <v>0</v>
+      </c>
+      <c r="O1744">
+        <v>0</v>
+      </c>
+      <c r="P1744">
+        <v>0</v>
+      </c>
+      <c r="Q1744">
+        <v>0</v>
+      </c>
+      <c r="R1744">
+        <v>0</v>
+      </c>
+      <c r="S1744">
+        <v>0</v>
+      </c>
+      <c r="T1744">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1745" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1745">
+        <v>1</v>
+      </c>
+      <c r="D1745">
+        <v>1</v>
+      </c>
+      <c r="E1745">
+        <v>0</v>
+      </c>
+      <c r="F1745">
+        <v>0</v>
+      </c>
+      <c r="G1745">
+        <v>0</v>
+      </c>
+      <c r="H1745">
+        <v>0</v>
+      </c>
+      <c r="I1745">
+        <v>0</v>
+      </c>
+      <c r="J1745">
+        <v>0</v>
+      </c>
+      <c r="K1745">
+        <v>0</v>
+      </c>
+      <c r="L1745">
+        <v>5</v>
+      </c>
+      <c r="M1745">
+        <v>5</v>
+      </c>
+      <c r="N1745">
+        <v>0</v>
+      </c>
+      <c r="O1745">
+        <v>0</v>
+      </c>
+      <c r="P1745">
+        <v>0</v>
+      </c>
+      <c r="Q1745">
+        <v>0</v>
+      </c>
+      <c r="R1745">
+        <v>0</v>
+      </c>
+      <c r="S1745">
+        <v>0</v>
+      </c>
+      <c r="T1745">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1746" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1746">
+        <v>1</v>
+      </c>
+      <c r="D1746">
+        <v>1</v>
+      </c>
+      <c r="E1746">
+        <v>1</v>
+      </c>
+      <c r="F1746">
+        <v>51</v>
+      </c>
+      <c r="H1746" t="s">
+        <v>275</v>
+      </c>
+      <c r="I1746">
+        <v>1</v>
+      </c>
+      <c r="J1746">
+        <v>0</v>
+      </c>
+      <c r="K1746">
+        <v>188.89</v>
+      </c>
+      <c r="L1746">
+        <v>27</v>
+      </c>
+      <c r="M1746">
+        <v>9</v>
+      </c>
+      <c r="N1746">
+        <v>11</v>
+      </c>
+      <c r="O1746">
+        <v>0</v>
+      </c>
+      <c r="P1746">
+        <v>57.95</v>
+      </c>
+      <c r="Q1746">
+        <v>0</v>
+      </c>
+      <c r="R1746">
+        <v>0</v>
+      </c>
+      <c r="S1746">
+        <v>0</v>
+      </c>
+      <c r="T1746">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1747" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1747">
+        <v>1</v>
+      </c>
+      <c r="D1747">
+        <v>1</v>
+      </c>
+      <c r="E1747">
+        <v>0</v>
+      </c>
+      <c r="F1747">
+        <v>0</v>
+      </c>
+      <c r="G1747">
+        <v>0</v>
+      </c>
+      <c r="H1747">
+        <v>0</v>
+      </c>
+      <c r="I1747">
+        <v>0</v>
+      </c>
+      <c r="J1747">
+        <v>0</v>
+      </c>
+      <c r="K1747">
+        <v>0</v>
+      </c>
+      <c r="L1747">
+        <v>6</v>
+      </c>
+      <c r="M1747">
+        <v>6</v>
+      </c>
+      <c r="N1747">
+        <v>0</v>
+      </c>
+      <c r="O1747">
+        <v>0</v>
+      </c>
+      <c r="P1747">
+        <v>0</v>
+      </c>
+      <c r="Q1747">
+        <v>0</v>
+      </c>
+      <c r="R1747">
+        <v>0</v>
+      </c>
+      <c r="S1747">
+        <v>0</v>
+      </c>
+      <c r="T1747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1748" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1748">
+        <v>1</v>
+      </c>
+      <c r="D1748">
+        <v>1</v>
+      </c>
+      <c r="E1748">
+        <v>1</v>
+      </c>
+      <c r="F1748">
+        <v>62</v>
+      </c>
+      <c r="H1748" t="s">
+        <v>484</v>
+      </c>
+      <c r="I1748">
+        <v>1</v>
+      </c>
+      <c r="J1748">
+        <v>0</v>
+      </c>
+      <c r="K1748">
+        <v>193.75</v>
+      </c>
+      <c r="L1748">
+        <v>32</v>
+      </c>
+      <c r="M1748">
+        <v>11</v>
+      </c>
+      <c r="N1748">
+        <v>10</v>
+      </c>
+      <c r="O1748">
+        <v>2</v>
+      </c>
+      <c r="P1748">
+        <v>68.13</v>
+      </c>
+      <c r="Q1748">
+        <v>1</v>
+      </c>
+      <c r="R1748">
+        <v>0</v>
+      </c>
+      <c r="S1748">
+        <v>0</v>
+      </c>
+      <c r="T1748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1749" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1749">
+        <v>1</v>
+      </c>
+      <c r="D1749">
+        <v>1</v>
+      </c>
+      <c r="E1749">
+        <v>0</v>
+      </c>
+      <c r="F1749">
+        <v>1</v>
+      </c>
+      <c r="G1749">
+        <v>1</v>
+      </c>
+      <c r="H1749">
+        <v>1</v>
+      </c>
+      <c r="I1749">
+        <v>0</v>
+      </c>
+      <c r="J1749">
+        <v>0</v>
+      </c>
+      <c r="K1749">
+        <v>20</v>
+      </c>
+      <c r="L1749">
+        <v>5</v>
+      </c>
+      <c r="M1749">
+        <v>4</v>
+      </c>
+      <c r="N1749">
+        <v>0</v>
+      </c>
+      <c r="O1749">
+        <v>0</v>
+      </c>
+      <c r="P1749">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="Q1749">
+        <v>0</v>
+      </c>
+      <c r="R1749">
+        <v>0</v>
+      </c>
+      <c r="S1749">
+        <v>0</v>
+      </c>
+      <c r="T1749">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1750" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1750">
+        <v>1</v>
+      </c>
+      <c r="D1750">
+        <v>0</v>
+      </c>
+      <c r="E1750">
+        <v>0</v>
+      </c>
+      <c r="F1750">
+        <v>0</v>
+      </c>
+      <c r="I1750">
+        <v>0</v>
+      </c>
+      <c r="J1750">
+        <v>0</v>
+      </c>
+      <c r="L1750">
+        <v>0</v>
+      </c>
+      <c r="M1750">
+        <v>0</v>
+      </c>
+      <c r="N1750">
+        <v>0</v>
+      </c>
+      <c r="O1750">
+        <v>0</v>
+      </c>
+      <c r="P1750">
+        <v>0</v>
+      </c>
+      <c r="Q1750">
+        <v>0</v>
+      </c>
+      <c r="R1750">
+        <v>0</v>
+      </c>
+      <c r="S1750">
+        <v>0</v>
+      </c>
+      <c r="T1750">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1751" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1751">
+        <v>1</v>
+      </c>
+      <c r="D1751">
+        <v>0</v>
+      </c>
+      <c r="E1751">
+        <v>0</v>
+      </c>
+      <c r="F1751">
+        <v>0</v>
+      </c>
+      <c r="I1751">
+        <v>0</v>
+      </c>
+      <c r="J1751">
+        <v>0</v>
+      </c>
+      <c r="L1751">
+        <v>0</v>
+      </c>
+      <c r="M1751">
+        <v>0</v>
+      </c>
+      <c r="N1751">
+        <v>0</v>
+      </c>
+      <c r="O1751">
+        <v>0</v>
+      </c>
+      <c r="P1751">
+        <v>0</v>
+      </c>
+      <c r="Q1751">
+        <v>0</v>
+      </c>
+      <c r="R1751">
+        <v>0</v>
+      </c>
+      <c r="S1751">
+        <v>0</v>
+      </c>
+      <c r="T1751">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1752" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1752">
+        <v>1</v>
+      </c>
+      <c r="D1752">
+        <v>0</v>
+      </c>
+      <c r="E1752">
+        <v>0</v>
+      </c>
+      <c r="F1752">
+        <v>0</v>
+      </c>
+      <c r="I1752">
+        <v>0</v>
+      </c>
+      <c r="J1752">
+        <v>0</v>
+      </c>
+      <c r="L1752">
+        <v>0</v>
+      </c>
+      <c r="M1752">
+        <v>0</v>
+      </c>
+      <c r="N1752">
+        <v>0</v>
+      </c>
+      <c r="O1752">
+        <v>0</v>
+      </c>
+      <c r="P1752">
+        <v>0</v>
+      </c>
+      <c r="Q1752">
+        <v>0</v>
+      </c>
+      <c r="R1752">
+        <v>0</v>
+      </c>
+      <c r="S1752">
+        <v>0</v>
+      </c>
+      <c r="T1752">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1753" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1753">
+        <v>1</v>
+      </c>
+      <c r="D1753">
+        <v>1</v>
+      </c>
+      <c r="E1753">
+        <v>0</v>
+      </c>
+      <c r="F1753">
+        <v>1</v>
+      </c>
+      <c r="G1753">
+        <v>1</v>
+      </c>
+      <c r="H1753">
+        <v>1</v>
+      </c>
+      <c r="I1753">
+        <v>0</v>
+      </c>
+      <c r="J1753">
+        <v>0</v>
+      </c>
+      <c r="K1753">
+        <v>12.5</v>
+      </c>
+      <c r="L1753">
+        <v>8</v>
+      </c>
+      <c r="M1753">
+        <v>7</v>
+      </c>
+      <c r="N1753">
+        <v>0</v>
+      </c>
+      <c r="O1753">
+        <v>0</v>
+      </c>
+      <c r="P1753">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="Q1753">
+        <v>0</v>
+      </c>
+      <c r="R1753">
+        <v>0</v>
+      </c>
+      <c r="S1753">
+        <v>0</v>
+      </c>
+      <c r="T1753">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1754" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1754">
+        <v>1</v>
+      </c>
+      <c r="D1754">
+        <v>1</v>
+      </c>
+      <c r="E1754">
+        <v>0</v>
+      </c>
+      <c r="F1754">
+        <v>0</v>
+      </c>
+      <c r="G1754">
+        <v>0</v>
+      </c>
+      <c r="H1754">
+        <v>0</v>
+      </c>
+      <c r="I1754">
+        <v>0</v>
+      </c>
+      <c r="J1754">
+        <v>0</v>
+      </c>
+      <c r="K1754">
+        <v>0</v>
+      </c>
+      <c r="L1754">
+        <v>1</v>
+      </c>
+      <c r="M1754">
+        <v>1</v>
+      </c>
+      <c r="N1754">
+        <v>0</v>
+      </c>
+      <c r="O1754">
+        <v>0</v>
+      </c>
+      <c r="P1754">
+        <v>0</v>
+      </c>
+      <c r="Q1754">
+        <v>0</v>
+      </c>
+      <c r="R1754">
+        <v>0</v>
+      </c>
+      <c r="S1754">
+        <v>0</v>
+      </c>
+      <c r="T1754">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1755" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1755">
+        <v>1</v>
+      </c>
+      <c r="D1755">
+        <v>0</v>
+      </c>
+      <c r="E1755">
+        <v>0</v>
+      </c>
+      <c r="F1755">
+        <v>0</v>
+      </c>
+      <c r="I1755">
+        <v>0</v>
+      </c>
+      <c r="J1755">
+        <v>0</v>
+      </c>
+      <c r="L1755">
+        <v>0</v>
+      </c>
+      <c r="M1755">
+        <v>0</v>
+      </c>
+      <c r="N1755">
+        <v>0</v>
+      </c>
+      <c r="O1755">
+        <v>0</v>
+      </c>
+      <c r="P1755">
+        <v>0</v>
+      </c>
+      <c r="Q1755">
+        <v>1</v>
+      </c>
+      <c r="R1755">
+        <v>0</v>
+      </c>
+      <c r="S1755">
+        <v>0</v>
+      </c>
+      <c r="T1755">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1756" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1756">
+        <v>1</v>
+      </c>
+      <c r="D1756">
+        <v>1</v>
+      </c>
+      <c r="E1756">
+        <v>0</v>
+      </c>
+      <c r="F1756">
+        <v>2</v>
+      </c>
+      <c r="G1756">
+        <v>2</v>
+      </c>
+      <c r="H1756">
+        <v>2</v>
+      </c>
+      <c r="I1756">
+        <v>0</v>
+      </c>
+      <c r="J1756">
+        <v>0</v>
+      </c>
+      <c r="K1756">
+        <v>28.57</v>
+      </c>
+      <c r="L1756">
+        <v>7</v>
+      </c>
+      <c r="M1756">
+        <v>5</v>
+      </c>
+      <c r="N1756">
+        <v>0</v>
+      </c>
+      <c r="O1756">
+        <v>0</v>
+      </c>
+      <c r="P1756">
+        <v>2.27</v>
+      </c>
+      <c r="Q1756">
+        <v>0</v>
+      </c>
+      <c r="R1756">
+        <v>0</v>
+      </c>
+      <c r="S1756">
+        <v>0</v>
+      </c>
+      <c r="T1756">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1757" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1757">
+        <v>1</v>
+      </c>
+      <c r="D1757">
+        <v>0</v>
+      </c>
+      <c r="E1757">
+        <v>0</v>
+      </c>
+      <c r="F1757">
+        <v>0</v>
+      </c>
+      <c r="I1757">
+        <v>0</v>
+      </c>
+      <c r="J1757">
+        <v>0</v>
+      </c>
+      <c r="L1757">
+        <v>0</v>
+      </c>
+      <c r="M1757">
+        <v>0</v>
+      </c>
+      <c r="N1757">
+        <v>0</v>
+      </c>
+      <c r="O1757">
+        <v>0</v>
+      </c>
+      <c r="P1757">
+        <v>0</v>
+      </c>
+      <c r="Q1757">
+        <v>0</v>
+      </c>
+      <c r="R1757">
+        <v>0</v>
+      </c>
+      <c r="S1757">
+        <v>0</v>
+      </c>
+      <c r="T1757">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1758" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1758">
+        <v>1</v>
+      </c>
+      <c r="D1758">
+        <v>1</v>
+      </c>
+      <c r="E1758">
+        <v>0</v>
+      </c>
+      <c r="F1758">
+        <v>12</v>
+      </c>
+      <c r="G1758">
+        <v>12</v>
+      </c>
+      <c r="H1758">
+        <v>12</v>
+      </c>
+      <c r="I1758">
+        <v>0</v>
+      </c>
+      <c r="J1758">
+        <v>0</v>
+      </c>
+      <c r="K1758">
+        <v>63.16</v>
+      </c>
+      <c r="L1758">
+        <v>19</v>
+      </c>
+      <c r="M1758">
+        <v>13</v>
+      </c>
+      <c r="N1758">
+        <v>2</v>
+      </c>
+      <c r="O1758">
+        <v>0</v>
+      </c>
+      <c r="P1758">
+        <v>13.64</v>
+      </c>
+      <c r="Q1758">
+        <v>0</v>
+      </c>
+      <c r="R1758">
+        <v>0</v>
+      </c>
+      <c r="S1758">
+        <v>0</v>
+      </c>
+      <c r="T1758">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1759" t="s">
+        <v>482</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1759">
+        <v>1</v>
+      </c>
+      <c r="D1759">
+        <v>1</v>
+      </c>
+      <c r="E1759">
+        <v>0</v>
+      </c>
+      <c r="F1759">
+        <v>2</v>
+      </c>
+      <c r="G1759">
+        <v>2</v>
+      </c>
+      <c r="H1759">
+        <v>2</v>
+      </c>
+      <c r="I1759">
+        <v>0</v>
+      </c>
+      <c r="J1759">
+        <v>0</v>
+      </c>
+      <c r="K1759">
+        <v>14.29</v>
+      </c>
+      <c r="L1759">
+        <v>14</v>
+      </c>
+      <c r="M1759">
+        <v>12</v>
+      </c>
+      <c r="N1759">
+        <v>0</v>
+      </c>
+      <c r="O1759">
+        <v>0</v>
+      </c>
+      <c r="P1759">
+        <v>2.27</v>
+      </c>
+      <c r="Q1759">
+        <v>0</v>
+      </c>
+      <c r="R1759">
+        <v>0</v>
+      </c>
+      <c r="S1759">
+        <v>0</v>
+      </c>
+      <c r="T1759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1760" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>312</v>
+      </c>
+      <c r="C1760">
+        <v>1</v>
+      </c>
+      <c r="D1760">
+        <v>1</v>
+      </c>
+      <c r="E1760">
+        <v>0</v>
+      </c>
+      <c r="F1760">
+        <v>0</v>
+      </c>
+      <c r="G1760">
+        <v>0</v>
+      </c>
+      <c r="H1760">
+        <v>0</v>
+      </c>
+      <c r="I1760">
+        <v>0</v>
+      </c>
+      <c r="J1760">
+        <v>0</v>
+      </c>
+      <c r="K1760">
+        <v>0</v>
+      </c>
+      <c r="L1760">
+        <v>12</v>
+      </c>
+      <c r="M1760">
+        <v>12</v>
+      </c>
+      <c r="N1760">
+        <v>0</v>
+      </c>
+      <c r="O1760">
+        <v>0</v>
+      </c>
+      <c r="P1760">
+        <v>0</v>
+      </c>
+      <c r="Q1760">
+        <v>0</v>
+      </c>
+      <c r="R1760">
+        <v>0</v>
+      </c>
+      <c r="S1760">
+        <v>0</v>
+      </c>
+      <c r="T1760">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1761" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1761">
+        <v>1</v>
+      </c>
+      <c r="D1761">
+        <v>0</v>
+      </c>
+      <c r="E1761">
+        <v>0</v>
+      </c>
+      <c r="F1761">
+        <v>0</v>
+      </c>
+      <c r="I1761">
+        <v>0</v>
+      </c>
+      <c r="J1761">
+        <v>0</v>
+      </c>
+      <c r="L1761">
+        <v>0</v>
+      </c>
+      <c r="M1761">
+        <v>0</v>
+      </c>
+      <c r="N1761">
+        <v>0</v>
+      </c>
+      <c r="O1761">
+        <v>0</v>
+      </c>
+      <c r="P1761">
+        <v>0</v>
+      </c>
+      <c r="Q1761">
+        <v>0</v>
+      </c>
+      <c r="R1761">
+        <v>0</v>
+      </c>
+      <c r="S1761">
+        <v>0</v>
+      </c>
+      <c r="T1761">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1762" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1762">
+        <v>1</v>
+      </c>
+      <c r="D1762">
+        <v>1</v>
+      </c>
+      <c r="E1762">
+        <v>0</v>
+      </c>
+      <c r="F1762">
+        <v>22</v>
+      </c>
+      <c r="G1762">
+        <v>22</v>
+      </c>
+      <c r="H1762">
+        <v>22</v>
+      </c>
+      <c r="I1762">
+        <v>0</v>
+      </c>
+      <c r="J1762">
+        <v>0</v>
+      </c>
+      <c r="K1762">
+        <v>56.41</v>
+      </c>
+      <c r="L1762">
+        <v>39</v>
+      </c>
+      <c r="M1762">
+        <v>26</v>
+      </c>
+      <c r="N1762">
+        <v>2</v>
+      </c>
+      <c r="O1762">
+        <v>0</v>
+      </c>
+      <c r="P1762">
+        <v>10.89</v>
+      </c>
+      <c r="Q1762">
+        <v>0</v>
+      </c>
+      <c r="R1762">
+        <v>0</v>
+      </c>
+      <c r="S1762">
+        <v>0</v>
+      </c>
+      <c r="T1762">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1763" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1763">
+        <v>1</v>
+      </c>
+      <c r="D1763">
+        <v>0</v>
+      </c>
+      <c r="E1763">
+        <v>0</v>
+      </c>
+      <c r="F1763">
+        <v>0</v>
+      </c>
+      <c r="I1763">
+        <v>0</v>
+      </c>
+      <c r="J1763">
+        <v>0</v>
+      </c>
+      <c r="L1763">
+        <v>0</v>
+      </c>
+      <c r="M1763">
+        <v>0</v>
+      </c>
+      <c r="N1763">
+        <v>0</v>
+      </c>
+      <c r="O1763">
+        <v>0</v>
+      </c>
+      <c r="P1763">
+        <v>0</v>
+      </c>
+      <c r="Q1763">
+        <v>0</v>
+      </c>
+      <c r="R1763">
+        <v>0</v>
+      </c>
+      <c r="S1763">
+        <v>0</v>
+      </c>
+      <c r="T1763">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1764" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1764">
+        <v>1</v>
+      </c>
+      <c r="D1764">
+        <v>0</v>
+      </c>
+      <c r="E1764">
+        <v>0</v>
+      </c>
+      <c r="F1764">
+        <v>0</v>
+      </c>
+      <c r="I1764">
+        <v>0</v>
+      </c>
+      <c r="J1764">
+        <v>0</v>
+      </c>
+      <c r="L1764">
+        <v>0</v>
+      </c>
+      <c r="M1764">
+        <v>0</v>
+      </c>
+      <c r="N1764">
+        <v>0</v>
+      </c>
+      <c r="O1764">
+        <v>0</v>
+      </c>
+      <c r="P1764">
+        <v>0</v>
+      </c>
+      <c r="Q1764">
+        <v>1</v>
+      </c>
+      <c r="R1764">
+        <v>0</v>
+      </c>
+      <c r="S1764">
+        <v>0</v>
+      </c>
+      <c r="T1764">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1765" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1765">
+        <v>1</v>
+      </c>
+      <c r="D1765">
+        <v>0</v>
+      </c>
+      <c r="E1765">
+        <v>0</v>
+      </c>
+      <c r="F1765">
+        <v>0</v>
+      </c>
+      <c r="I1765">
+        <v>0</v>
+      </c>
+      <c r="J1765">
+        <v>0</v>
+      </c>
+      <c r="L1765">
+        <v>0</v>
+      </c>
+      <c r="M1765">
+        <v>0</v>
+      </c>
+      <c r="N1765">
+        <v>0</v>
+      </c>
+      <c r="O1765">
+        <v>0</v>
+      </c>
+      <c r="P1765">
+        <v>0</v>
+      </c>
+      <c r="Q1765">
+        <v>0</v>
+      </c>
+      <c r="R1765">
+        <v>0</v>
+      </c>
+      <c r="S1765">
+        <v>0</v>
+      </c>
+      <c r="T1765">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1766" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1766">
+        <v>1</v>
+      </c>
+      <c r="D1766">
+        <v>1</v>
+      </c>
+      <c r="E1766">
+        <v>0</v>
+      </c>
+      <c r="F1766">
+        <v>2</v>
+      </c>
+      <c r="G1766">
+        <v>2</v>
+      </c>
+      <c r="H1766">
+        <v>2</v>
+      </c>
+      <c r="I1766">
+        <v>0</v>
+      </c>
+      <c r="J1766">
+        <v>0</v>
+      </c>
+      <c r="K1766">
+        <v>100</v>
+      </c>
+      <c r="L1766">
+        <v>2</v>
+      </c>
+      <c r="M1766">
+        <v>1</v>
+      </c>
+      <c r="N1766">
+        <v>0</v>
+      </c>
+      <c r="O1766">
+        <v>0</v>
+      </c>
+      <c r="P1766">
+        <v>2.9</v>
+      </c>
+      <c r="Q1766">
+        <v>0</v>
+      </c>
+      <c r="R1766">
+        <v>0</v>
+      </c>
+      <c r="S1766">
+        <v>0</v>
+      </c>
+      <c r="T1766">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1767" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>470</v>
+      </c>
+      <c r="C1767">
+        <v>1</v>
+      </c>
+      <c r="D1767">
+        <v>1</v>
+      </c>
+      <c r="E1767">
+        <v>0</v>
+      </c>
+      <c r="F1767">
+        <v>8</v>
+      </c>
+      <c r="G1767">
+        <v>8</v>
+      </c>
+      <c r="H1767">
+        <v>8</v>
+      </c>
+      <c r="I1767">
+        <v>0</v>
+      </c>
+      <c r="J1767">
+        <v>0</v>
+      </c>
+      <c r="K1767">
+        <v>42.11</v>
+      </c>
+      <c r="L1767">
+        <v>19</v>
+      </c>
+      <c r="M1767">
+        <v>13</v>
+      </c>
+      <c r="N1767">
+        <v>0</v>
+      </c>
+      <c r="O1767">
+        <v>0</v>
+      </c>
+      <c r="P1767">
+        <v>11.59</v>
+      </c>
+      <c r="Q1767">
+        <v>0</v>
+      </c>
+      <c r="R1767">
+        <v>0</v>
+      </c>
+      <c r="S1767">
+        <v>0</v>
+      </c>
+      <c r="T1767">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1768" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1768">
+        <v>1</v>
+      </c>
+      <c r="D1768">
+        <v>1</v>
+      </c>
+      <c r="E1768">
+        <v>1</v>
+      </c>
+      <c r="F1768">
+        <v>2</v>
+      </c>
+      <c r="H1768" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1768">
+        <v>0</v>
+      </c>
+      <c r="J1768">
+        <v>0</v>
+      </c>
+      <c r="K1768">
+        <v>33.33</v>
+      </c>
+      <c r="L1768">
+        <v>6</v>
+      </c>
+      <c r="M1768">
+        <v>4</v>
+      </c>
+      <c r="N1768">
+        <v>0</v>
+      </c>
+      <c r="O1768">
+        <v>0</v>
+      </c>
+      <c r="P1768">
+        <v>2.9</v>
+      </c>
+      <c r="Q1768">
+        <v>0</v>
+      </c>
+      <c r="R1768">
+        <v>0</v>
+      </c>
+      <c r="S1768">
+        <v>0</v>
+      </c>
+      <c r="T1768">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1769" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1769">
+        <v>1</v>
+      </c>
+      <c r="D1769">
+        <v>1</v>
+      </c>
+      <c r="E1769">
+        <v>0</v>
+      </c>
+      <c r="F1769">
+        <v>3</v>
+      </c>
+      <c r="G1769">
+        <v>3</v>
+      </c>
+      <c r="H1769">
+        <v>3</v>
+      </c>
+      <c r="I1769">
+        <v>0</v>
+      </c>
+      <c r="J1769">
+        <v>0</v>
+      </c>
+      <c r="K1769">
+        <v>18.75</v>
+      </c>
+      <c r="L1769">
+        <v>16</v>
+      </c>
+      <c r="M1769">
+        <v>13</v>
+      </c>
+      <c r="N1769">
+        <v>0</v>
+      </c>
+      <c r="O1769">
+        <v>0</v>
+      </c>
+      <c r="P1769">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="Q1769">
+        <v>0</v>
+      </c>
+      <c r="R1769">
+        <v>0</v>
+      </c>
+      <c r="S1769">
+        <v>0</v>
+      </c>
+      <c r="T1769">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1770" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1770">
+        <v>1</v>
+      </c>
+      <c r="D1770">
+        <v>1</v>
+      </c>
+      <c r="E1770">
+        <v>0</v>
+      </c>
+      <c r="F1770">
+        <v>13</v>
+      </c>
+      <c r="G1770">
+        <v>13</v>
+      </c>
+      <c r="H1770">
+        <v>13</v>
+      </c>
+      <c r="I1770">
+        <v>0</v>
+      </c>
+      <c r="J1770">
+        <v>0</v>
+      </c>
+      <c r="K1770">
+        <v>130</v>
+      </c>
+      <c r="L1770">
+        <v>10</v>
+      </c>
+      <c r="M1770">
+        <v>4</v>
+      </c>
+      <c r="N1770">
+        <v>1</v>
+      </c>
+      <c r="O1770">
+        <v>0</v>
+      </c>
+      <c r="P1770">
+        <v>18.84</v>
+      </c>
+      <c r="Q1770">
+        <v>1</v>
+      </c>
+      <c r="R1770">
+        <v>0</v>
+      </c>
+      <c r="S1770">
+        <v>0</v>
+      </c>
+      <c r="T1770">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1771" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1771">
+        <v>1</v>
+      </c>
+      <c r="D1771">
+        <v>1</v>
+      </c>
+      <c r="E1771">
+        <v>0</v>
+      </c>
+      <c r="F1771">
+        <v>1</v>
+      </c>
+      <c r="G1771">
+        <v>1</v>
+      </c>
+      <c r="H1771">
+        <v>1</v>
+      </c>
+      <c r="I1771">
+        <v>0</v>
+      </c>
+      <c r="J1771">
+        <v>0</v>
+      </c>
+      <c r="K1771">
+        <v>14.29</v>
+      </c>
+      <c r="L1771">
+        <v>7</v>
+      </c>
+      <c r="M1771">
+        <v>6</v>
+      </c>
+      <c r="N1771">
+        <v>0</v>
+      </c>
+      <c r="O1771">
+        <v>0</v>
+      </c>
+      <c r="P1771">
+        <v>0.5</v>
+      </c>
+      <c r="Q1771">
+        <v>1</v>
+      </c>
+      <c r="R1771">
+        <v>0</v>
+      </c>
+      <c r="S1771">
+        <v>0</v>
+      </c>
+      <c r="T1771">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1772" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1772">
+        <v>1</v>
+      </c>
+      <c r="D1772">
+        <v>1</v>
+      </c>
+      <c r="E1772">
+        <v>0</v>
+      </c>
+      <c r="F1772">
+        <v>17</v>
+      </c>
+      <c r="G1772">
+        <v>17</v>
+      </c>
+      <c r="H1772">
+        <v>17</v>
+      </c>
+      <c r="I1772">
+        <v>0</v>
+      </c>
+      <c r="J1772">
+        <v>0</v>
+      </c>
+      <c r="K1772">
+        <v>130.77000000000001</v>
+      </c>
+      <c r="L1772">
+        <v>13</v>
+      </c>
+      <c r="M1772">
+        <v>8</v>
+      </c>
+      <c r="N1772">
+        <v>4</v>
+      </c>
+      <c r="O1772">
+        <v>0</v>
+      </c>
+      <c r="P1772">
+        <v>8.42</v>
+      </c>
+      <c r="Q1772">
+        <v>1</v>
+      </c>
+      <c r="R1772">
+        <v>0</v>
+      </c>
+      <c r="S1772">
+        <v>0</v>
+      </c>
+      <c r="T1772">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1773" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1773">
+        <v>1</v>
+      </c>
+      <c r="D1773">
+        <v>0</v>
+      </c>
+      <c r="E1773">
+        <v>0</v>
+      </c>
+      <c r="F1773">
+        <v>0</v>
+      </c>
+      <c r="I1773">
+        <v>0</v>
+      </c>
+      <c r="J1773">
+        <v>0</v>
+      </c>
+      <c r="L1773">
+        <v>0</v>
+      </c>
+      <c r="M1773">
+        <v>0</v>
+      </c>
+      <c r="N1773">
+        <v>0</v>
+      </c>
+      <c r="O1773">
+        <v>0</v>
+      </c>
+      <c r="P1773">
+        <v>0</v>
+      </c>
+      <c r="Q1773">
+        <v>0</v>
+      </c>
+      <c r="R1773">
+        <v>0</v>
+      </c>
+      <c r="S1773">
+        <v>0</v>
+      </c>
+      <c r="T1773">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1774" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1774">
+        <v>1</v>
+      </c>
+      <c r="D1774">
+        <v>1</v>
+      </c>
+      <c r="E1774">
+        <v>1</v>
+      </c>
+      <c r="F1774">
+        <v>120</v>
+      </c>
+      <c r="H1774" t="s">
+        <v>486</v>
+      </c>
+      <c r="I1774">
+        <v>0</v>
+      </c>
+      <c r="J1774">
+        <v>1</v>
+      </c>
+      <c r="K1774">
+        <v>230.77</v>
+      </c>
+      <c r="L1774">
+        <v>52</v>
+      </c>
+      <c r="M1774">
+        <v>10</v>
+      </c>
+      <c r="N1774">
+        <v>19</v>
+      </c>
+      <c r="O1774">
+        <v>2</v>
+      </c>
+      <c r="P1774">
+        <v>59.41</v>
+      </c>
+      <c r="Q1774">
+        <v>0</v>
+      </c>
+      <c r="R1774">
+        <v>0</v>
+      </c>
+      <c r="S1774">
+        <v>0</v>
+      </c>
+      <c r="T1774">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1775" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1775">
+        <v>1</v>
+      </c>
+      <c r="D1775">
+        <v>1</v>
+      </c>
+      <c r="E1775">
+        <v>0</v>
+      </c>
+      <c r="F1775">
+        <v>6</v>
+      </c>
+      <c r="G1775">
+        <v>6</v>
+      </c>
+      <c r="H1775">
+        <v>6</v>
+      </c>
+      <c r="I1775">
+        <v>0</v>
+      </c>
+      <c r="J1775">
+        <v>0</v>
+      </c>
+      <c r="K1775">
+        <v>100</v>
+      </c>
+      <c r="L1775">
+        <v>6</v>
+      </c>
+      <c r="M1775">
+        <v>4</v>
+      </c>
+      <c r="N1775">
+        <v>1</v>
+      </c>
+      <c r="O1775">
+        <v>0</v>
+      </c>
+      <c r="P1775">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q1775">
+        <v>0</v>
+      </c>
+      <c r="R1775">
+        <v>0</v>
+      </c>
+      <c r="S1775">
+        <v>0</v>
+      </c>
+      <c r="T1775">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1776" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1776">
+        <v>1</v>
+      </c>
+      <c r="D1776">
+        <v>0</v>
+      </c>
+      <c r="E1776">
+        <v>0</v>
+      </c>
+      <c r="F1776">
+        <v>0</v>
+      </c>
+      <c r="I1776">
+        <v>0</v>
+      </c>
+      <c r="J1776">
+        <v>0</v>
+      </c>
+      <c r="L1776">
+        <v>0</v>
+      </c>
+      <c r="M1776">
+        <v>0</v>
+      </c>
+      <c r="N1776">
+        <v>0</v>
+      </c>
+      <c r="O1776">
+        <v>0</v>
+      </c>
+      <c r="P1776">
+        <v>0</v>
+      </c>
+      <c r="Q1776">
+        <v>0</v>
+      </c>
+      <c r="R1776">
+        <v>0</v>
+      </c>
+      <c r="S1776">
+        <v>0</v>
+      </c>
+      <c r="T1776">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1777" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1777">
+        <v>1</v>
+      </c>
+      <c r="D1777">
+        <v>1</v>
+      </c>
+      <c r="E1777">
+        <v>1</v>
+      </c>
+      <c r="F1777">
+        <v>18</v>
+      </c>
+      <c r="H1777" t="s">
+        <v>253</v>
+      </c>
+      <c r="I1777">
+        <v>0</v>
+      </c>
+      <c r="J1777">
+        <v>0</v>
+      </c>
+      <c r="K1777">
+        <v>128.57</v>
+      </c>
+      <c r="L1777">
+        <v>14</v>
+      </c>
+      <c r="M1777">
+        <v>5</v>
+      </c>
+      <c r="N1777">
+        <v>2</v>
+      </c>
+      <c r="O1777">
+        <v>0</v>
+      </c>
+      <c r="P1777">
+        <v>8.91</v>
+      </c>
+      <c r="Q1777">
+        <v>0</v>
+      </c>
+      <c r="R1777">
+        <v>0</v>
+      </c>
+      <c r="S1777">
+        <v>0</v>
+      </c>
+      <c r="T1777">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1778" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>303</v>
+      </c>
+      <c r="C1778">
+        <v>1</v>
+      </c>
+      <c r="D1778">
+        <v>1</v>
+      </c>
+      <c r="E1778">
+        <v>0</v>
+      </c>
+      <c r="F1778">
+        <v>8</v>
+      </c>
+      <c r="G1778">
+        <v>8</v>
+      </c>
+      <c r="H1778">
+        <v>8</v>
+      </c>
+      <c r="I1778">
+        <v>0</v>
+      </c>
+      <c r="J1778">
+        <v>0</v>
+      </c>
+      <c r="K1778">
+        <v>88.89</v>
+      </c>
+      <c r="L1778">
+        <v>9</v>
+      </c>
+      <c r="M1778">
+        <v>5</v>
+      </c>
+      <c r="N1778">
+        <v>1</v>
+      </c>
+      <c r="O1778">
+        <v>0</v>
+      </c>
+      <c r="P1778">
+        <v>11.59</v>
+      </c>
+      <c r="Q1778">
+        <v>0</v>
+      </c>
+      <c r="R1778">
+        <v>0</v>
+      </c>
+      <c r="S1778">
+        <v>0</v>
+      </c>
+      <c r="T1778">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1779" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1779">
+        <v>1</v>
+      </c>
+      <c r="D1779">
+        <v>1</v>
+      </c>
+      <c r="E1779">
+        <v>0</v>
+      </c>
+      <c r="F1779">
+        <v>8</v>
+      </c>
+      <c r="G1779">
+        <v>8</v>
+      </c>
+      <c r="H1779">
+        <v>8</v>
+      </c>
+      <c r="I1779">
+        <v>0</v>
+      </c>
+      <c r="J1779">
+        <v>0</v>
+      </c>
+      <c r="K1779">
+        <v>88.89</v>
+      </c>
+      <c r="L1779">
+        <v>9</v>
+      </c>
+      <c r="M1779">
+        <v>4</v>
+      </c>
+      <c r="N1779">
+        <v>1</v>
+      </c>
+      <c r="O1779">
+        <v>0</v>
+      </c>
+      <c r="P1779">
+        <v>11.59</v>
+      </c>
+      <c r="Q1779">
+        <v>0</v>
+      </c>
+      <c r="R1779">
+        <v>0</v>
+      </c>
+      <c r="S1779">
+        <v>0</v>
+      </c>
+      <c r="T1779">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1780" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1780">
+        <v>1</v>
+      </c>
+      <c r="D1780">
+        <v>1</v>
+      </c>
+      <c r="E1780">
+        <v>0</v>
+      </c>
+      <c r="F1780">
+        <v>0</v>
+      </c>
+      <c r="G1780">
+        <v>0</v>
+      </c>
+      <c r="H1780">
+        <v>0</v>
+      </c>
+      <c r="I1780">
+        <v>0</v>
+      </c>
+      <c r="J1780">
+        <v>0</v>
+      </c>
+      <c r="K1780">
+        <v>0</v>
+      </c>
+      <c r="L1780">
+        <v>2</v>
+      </c>
+      <c r="M1780">
+        <v>2</v>
+      </c>
+      <c r="N1780">
+        <v>0</v>
+      </c>
+      <c r="O1780">
+        <v>0</v>
+      </c>
+      <c r="P1780">
+        <v>0</v>
+      </c>
+      <c r="Q1780">
+        <v>1</v>
+      </c>
+      <c r="R1780">
+        <v>0</v>
+      </c>
+      <c r="S1780">
+        <v>0</v>
+      </c>
+      <c r="T1780">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1781" t="s">
+        <v>485</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1781">
+        <v>1</v>
+      </c>
+      <c r="D1781">
+        <v>1</v>
+      </c>
+      <c r="E1781">
+        <v>0</v>
+      </c>
+      <c r="F1781">
+        <v>0</v>
+      </c>
+      <c r="G1781">
+        <v>0</v>
+      </c>
+      <c r="H1781">
+        <v>0</v>
+      </c>
+      <c r="I1781">
+        <v>0</v>
+      </c>
+      <c r="J1781">
+        <v>0</v>
+      </c>
+      <c r="K1781">
+        <v>0</v>
+      </c>
+      <c r="L1781">
+        <v>5</v>
+      </c>
+      <c r="M1781">
+        <v>5</v>
+      </c>
+      <c r="N1781">
+        <v>0</v>
+      </c>
+      <c r="O1781">
+        <v>0</v>
+      </c>
+      <c r="P1781">
+        <v>0</v>
+      </c>
+      <c r="Q1781">
+        <v>0</v>
+      </c>
+      <c r="R1781">
+        <v>0</v>
+      </c>
+      <c r="S1781">
+        <v>0</v>
+      </c>
+      <c r="T1781">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1782" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1782">
+        <v>1</v>
+      </c>
+      <c r="D1782">
+        <v>1</v>
+      </c>
+      <c r="E1782">
+        <v>1</v>
+      </c>
+      <c r="F1782">
+        <v>27</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1782">
+        <v>0</v>
+      </c>
+      <c r="J1782">
+        <v>0</v>
+      </c>
+      <c r="K1782">
+        <v>84.38</v>
+      </c>
+      <c r="L1782">
+        <v>32</v>
+      </c>
+      <c r="M1782">
+        <v>17</v>
+      </c>
+      <c r="N1782">
+        <v>4</v>
+      </c>
+      <c r="O1782">
+        <v>0</v>
+      </c>
+      <c r="P1782">
+        <v>25.23</v>
+      </c>
+      <c r="Q1782">
+        <v>0</v>
+      </c>
+      <c r="R1782">
+        <v>0</v>
+      </c>
+      <c r="S1782">
+        <v>0</v>
+      </c>
+      <c r="T1782">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1783" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1783">
+        <v>1</v>
+      </c>
+      <c r="D1783">
+        <v>1</v>
+      </c>
+      <c r="E1783">
+        <v>0</v>
+      </c>
+      <c r="F1783">
+        <v>25</v>
+      </c>
+      <c r="G1783">
+        <v>25</v>
+      </c>
+      <c r="H1783">
+        <v>25</v>
+      </c>
+      <c r="I1783">
+        <v>0</v>
+      </c>
+      <c r="J1783">
+        <v>0</v>
+      </c>
+      <c r="K1783">
+        <v>86.21</v>
+      </c>
+      <c r="L1783">
+        <v>29</v>
+      </c>
+      <c r="M1783">
+        <v>14</v>
+      </c>
+      <c r="N1783">
+        <v>3</v>
+      </c>
+      <c r="O1783">
+        <v>0</v>
+      </c>
+      <c r="P1783">
+        <v>23.36</v>
+      </c>
+      <c r="Q1783">
+        <v>0</v>
+      </c>
+      <c r="R1783">
+        <v>0</v>
+      </c>
+      <c r="S1783">
+        <v>0</v>
+      </c>
+      <c r="T1783">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1784" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>427</v>
+      </c>
+      <c r="C1784">
+        <v>1</v>
+      </c>
+      <c r="D1784">
+        <v>0</v>
+      </c>
+      <c r="E1784">
+        <v>0</v>
+      </c>
+      <c r="F1784">
+        <v>0</v>
+      </c>
+      <c r="I1784">
+        <v>0</v>
+      </c>
+      <c r="J1784">
+        <v>0</v>
+      </c>
+      <c r="L1784">
+        <v>0</v>
+      </c>
+      <c r="M1784">
+        <v>0</v>
+      </c>
+      <c r="N1784">
+        <v>0</v>
+      </c>
+      <c r="O1784">
+        <v>0</v>
+      </c>
+      <c r="P1784">
+        <v>0</v>
+      </c>
+      <c r="Q1784">
+        <v>0</v>
+      </c>
+      <c r="R1784">
+        <v>0</v>
+      </c>
+      <c r="S1784">
+        <v>0</v>
+      </c>
+      <c r="T1784">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1785" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>105</v>
+      </c>
+      <c r="C1785">
+        <v>1</v>
+      </c>
+      <c r="D1785">
+        <v>0</v>
+      </c>
+      <c r="E1785">
+        <v>0</v>
+      </c>
+      <c r="F1785">
+        <v>0</v>
+      </c>
+      <c r="I1785">
+        <v>0</v>
+      </c>
+      <c r="J1785">
+        <v>0</v>
+      </c>
+      <c r="L1785">
+        <v>0</v>
+      </c>
+      <c r="M1785">
+        <v>0</v>
+      </c>
+      <c r="N1785">
+        <v>0</v>
+      </c>
+      <c r="O1785">
+        <v>0</v>
+      </c>
+      <c r="P1785">
+        <v>0</v>
+      </c>
+      <c r="Q1785">
+        <v>0</v>
+      </c>
+      <c r="R1785">
+        <v>0</v>
+      </c>
+      <c r="S1785">
+        <v>0</v>
+      </c>
+      <c r="T1785">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1786" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1786">
+        <v>1</v>
+      </c>
+      <c r="D1786">
+        <v>1</v>
+      </c>
+      <c r="E1786">
+        <v>0</v>
+      </c>
+      <c r="F1786">
+        <v>1</v>
+      </c>
+      <c r="G1786">
+        <v>1</v>
+      </c>
+      <c r="H1786">
+        <v>1</v>
+      </c>
+      <c r="I1786">
+        <v>0</v>
+      </c>
+      <c r="J1786">
+        <v>0</v>
+      </c>
+      <c r="K1786">
+        <v>11.11</v>
+      </c>
+      <c r="L1786">
+        <v>9</v>
+      </c>
+      <c r="M1786">
+        <v>8</v>
+      </c>
+      <c r="N1786">
+        <v>0</v>
+      </c>
+      <c r="O1786">
+        <v>0</v>
+      </c>
+      <c r="P1786">
+        <v>0.93</v>
+      </c>
+      <c r="Q1786">
+        <v>0</v>
+      </c>
+      <c r="R1786">
+        <v>0</v>
+      </c>
+      <c r="S1786">
+        <v>0</v>
+      </c>
+      <c r="T1786">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1787" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1787">
+        <v>1</v>
+      </c>
+      <c r="D1787">
+        <v>0</v>
+      </c>
+      <c r="E1787">
+        <v>0</v>
+      </c>
+      <c r="F1787">
+        <v>0</v>
+      </c>
+      <c r="I1787">
+        <v>0</v>
+      </c>
+      <c r="J1787">
+        <v>0</v>
+      </c>
+      <c r="L1787">
+        <v>0</v>
+      </c>
+      <c r="M1787">
+        <v>0</v>
+      </c>
+      <c r="N1787">
+        <v>0</v>
+      </c>
+      <c r="O1787">
+        <v>0</v>
+      </c>
+      <c r="P1787">
+        <v>0</v>
+      </c>
+      <c r="Q1787">
+        <v>0</v>
+      </c>
+      <c r="R1787">
+        <v>0</v>
+      </c>
+      <c r="S1787">
+        <v>0</v>
+      </c>
+      <c r="T1787">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1788" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1788">
+        <v>1</v>
+      </c>
+      <c r="D1788">
+        <v>1</v>
+      </c>
+      <c r="E1788">
+        <v>0</v>
+      </c>
+      <c r="F1788">
+        <v>3</v>
+      </c>
+      <c r="G1788">
+        <v>3</v>
+      </c>
+      <c r="H1788">
+        <v>3</v>
+      </c>
+      <c r="I1788">
+        <v>0</v>
+      </c>
+      <c r="J1788">
+        <v>0</v>
+      </c>
+      <c r="K1788">
+        <v>23.08</v>
+      </c>
+      <c r="L1788">
+        <v>13</v>
+      </c>
+      <c r="M1788">
+        <v>10</v>
+      </c>
+      <c r="N1788">
+        <v>0</v>
+      </c>
+      <c r="O1788">
+        <v>0</v>
+      </c>
+      <c r="P1788">
+        <v>2.8</v>
+      </c>
+      <c r="Q1788">
+        <v>0</v>
+      </c>
+      <c r="R1788">
+        <v>0</v>
+      </c>
+      <c r="S1788">
+        <v>0</v>
+      </c>
+      <c r="T1788">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1789" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1789">
+        <v>1</v>
+      </c>
+      <c r="D1789">
+        <v>1</v>
+      </c>
+      <c r="E1789">
+        <v>0</v>
+      </c>
+      <c r="F1789">
+        <v>9</v>
+      </c>
+      <c r="G1789">
+        <v>9</v>
+      </c>
+      <c r="H1789">
+        <v>9</v>
+      </c>
+      <c r="I1789">
+        <v>0</v>
+      </c>
+      <c r="J1789">
+        <v>0</v>
+      </c>
+      <c r="K1789">
+        <v>39.130000000000003</v>
+      </c>
+      <c r="L1789">
+        <v>23</v>
+      </c>
+      <c r="M1789">
+        <v>16</v>
+      </c>
+      <c r="N1789">
+        <v>0</v>
+      </c>
+      <c r="O1789">
+        <v>0</v>
+      </c>
+      <c r="P1789">
+        <v>8.41</v>
+      </c>
+      <c r="Q1789">
+        <v>0</v>
+      </c>
+      <c r="R1789">
+        <v>2</v>
+      </c>
+      <c r="S1789">
+        <v>0</v>
+      </c>
+      <c r="T1789">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1790" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1790">
+        <v>1</v>
+      </c>
+      <c r="D1790">
+        <v>0</v>
+      </c>
+      <c r="E1790">
+        <v>0</v>
+      </c>
+      <c r="F1790">
+        <v>0</v>
+      </c>
+      <c r="I1790">
+        <v>0</v>
+      </c>
+      <c r="J1790">
+        <v>0</v>
+      </c>
+      <c r="L1790">
+        <v>0</v>
+      </c>
+      <c r="M1790">
+        <v>0</v>
+      </c>
+      <c r="N1790">
+        <v>0</v>
+      </c>
+      <c r="O1790">
+        <v>0</v>
+      </c>
+      <c r="P1790">
+        <v>0</v>
+      </c>
+      <c r="Q1790">
+        <v>0</v>
+      </c>
+      <c r="R1790">
+        <v>0</v>
+      </c>
+      <c r="S1790">
+        <v>0</v>
+      </c>
+      <c r="T1790">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1791" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1791">
+        <v>1</v>
+      </c>
+      <c r="D1791">
+        <v>1</v>
+      </c>
+      <c r="E1791">
+        <v>0</v>
+      </c>
+      <c r="F1791">
+        <v>28</v>
+      </c>
+      <c r="G1791">
+        <v>28</v>
+      </c>
+      <c r="H1791">
+        <v>28</v>
+      </c>
+      <c r="I1791">
+        <v>0</v>
+      </c>
+      <c r="J1791">
+        <v>0</v>
+      </c>
+      <c r="K1791">
+        <v>84.85</v>
+      </c>
+      <c r="L1791">
+        <v>33</v>
+      </c>
+      <c r="M1791">
+        <v>16</v>
+      </c>
+      <c r="N1791">
+        <v>3</v>
+      </c>
+      <c r="O1791">
+        <v>0</v>
+      </c>
+      <c r="P1791">
+        <v>16.09</v>
+      </c>
+      <c r="Q1791">
+        <v>0</v>
+      </c>
+      <c r="R1791">
+        <v>0</v>
+      </c>
+      <c r="S1791">
+        <v>0</v>
+      </c>
+      <c r="T1791">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1792" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1792">
+        <v>1</v>
+      </c>
+      <c r="D1792">
+        <v>1</v>
+      </c>
+      <c r="E1792">
+        <v>0</v>
+      </c>
+      <c r="F1792">
+        <v>6</v>
+      </c>
+      <c r="G1792">
+        <v>6</v>
+      </c>
+      <c r="H1792">
+        <v>6</v>
+      </c>
+      <c r="I1792">
+        <v>0</v>
+      </c>
+      <c r="J1792">
+        <v>0</v>
+      </c>
+      <c r="K1792">
+        <v>75</v>
+      </c>
+      <c r="L1792">
+        <v>8</v>
+      </c>
+      <c r="M1792">
+        <v>5</v>
+      </c>
+      <c r="N1792">
+        <v>1</v>
+      </c>
+      <c r="O1792">
+        <v>0</v>
+      </c>
+      <c r="P1792">
+        <v>3.45</v>
+      </c>
+      <c r="Q1792">
+        <v>0</v>
+      </c>
+      <c r="R1792">
+        <v>0</v>
+      </c>
+      <c r="S1792">
+        <v>0</v>
+      </c>
+      <c r="T1792">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1793" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1793">
+        <v>1</v>
+      </c>
+      <c r="D1793">
+        <v>1</v>
+      </c>
+      <c r="E1793">
+        <v>1</v>
+      </c>
+      <c r="F1793">
+        <v>1</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1793">
+        <v>0</v>
+      </c>
+      <c r="J1793">
+        <v>0</v>
+      </c>
+      <c r="K1793">
+        <v>50</v>
+      </c>
+      <c r="L1793">
+        <v>2</v>
+      </c>
+      <c r="M1793">
+        <v>1</v>
+      </c>
+      <c r="N1793">
+        <v>0</v>
+      </c>
+      <c r="O1793">
+        <v>0</v>
+      </c>
+      <c r="P1793">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="Q1793">
+        <v>0</v>
+      </c>
+      <c r="R1793">
+        <v>0</v>
+      </c>
+      <c r="S1793">
+        <v>0</v>
+      </c>
+      <c r="T1793">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1794" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1794">
+        <v>1</v>
+      </c>
+      <c r="D1794">
+        <v>0</v>
+      </c>
+      <c r="E1794">
+        <v>0</v>
+      </c>
+      <c r="F1794">
+        <v>0</v>
+      </c>
+      <c r="I1794">
+        <v>0</v>
+      </c>
+      <c r="J1794">
+        <v>0</v>
+      </c>
+      <c r="L1794">
+        <v>0</v>
+      </c>
+      <c r="M1794">
+        <v>0</v>
+      </c>
+      <c r="N1794">
+        <v>0</v>
+      </c>
+      <c r="O1794">
+        <v>0</v>
+      </c>
+      <c r="P1794">
+        <v>0</v>
+      </c>
+      <c r="Q1794">
+        <v>0</v>
+      </c>
+      <c r="R1794">
+        <v>0</v>
+      </c>
+      <c r="S1794">
+        <v>0</v>
+      </c>
+      <c r="T1794">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1795" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1795">
+        <v>1</v>
+      </c>
+      <c r="D1795">
+        <v>1</v>
+      </c>
+      <c r="E1795">
+        <v>0</v>
+      </c>
+      <c r="F1795">
+        <v>16</v>
+      </c>
+      <c r="G1795">
+        <v>16</v>
+      </c>
+      <c r="H1795">
+        <v>16</v>
+      </c>
+      <c r="I1795">
+        <v>0</v>
+      </c>
+      <c r="J1795">
+        <v>0</v>
+      </c>
+      <c r="K1795">
+        <v>76.19</v>
+      </c>
+      <c r="L1795">
+        <v>21</v>
+      </c>
+      <c r="M1795">
+        <v>13</v>
+      </c>
+      <c r="N1795">
+        <v>2</v>
+      </c>
+      <c r="O1795">
+        <v>0</v>
+      </c>
+      <c r="P1795">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q1795">
+        <v>0</v>
+      </c>
+      <c r="R1795">
+        <v>0</v>
+      </c>
+      <c r="S1795">
+        <v>0</v>
+      </c>
+      <c r="T1795">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1796" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1796">
+        <v>1</v>
+      </c>
+      <c r="D1796">
+        <v>1</v>
+      </c>
+      <c r="E1796">
+        <v>1</v>
+      </c>
+      <c r="F1796">
+        <v>13</v>
+      </c>
+      <c r="H1796" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1796">
+        <v>0</v>
+      </c>
+      <c r="J1796">
+        <v>0</v>
+      </c>
+      <c r="K1796">
+        <v>100</v>
+      </c>
+      <c r="L1796">
+        <v>13</v>
+      </c>
+      <c r="M1796">
+        <v>6</v>
+      </c>
+      <c r="N1796">
+        <v>2</v>
+      </c>
+      <c r="O1796">
+        <v>0</v>
+      </c>
+      <c r="P1796">
+        <v>7.47</v>
+      </c>
+      <c r="Q1796">
+        <v>0</v>
+      </c>
+      <c r="R1796">
+        <v>0</v>
+      </c>
+      <c r="S1796">
+        <v>0</v>
+      </c>
+      <c r="T1796">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1797" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1797">
+        <v>1</v>
+      </c>
+      <c r="D1797">
+        <v>0</v>
+      </c>
+      <c r="E1797">
+        <v>0</v>
+      </c>
+      <c r="F1797">
+        <v>0</v>
+      </c>
+      <c r="I1797">
+        <v>0</v>
+      </c>
+      <c r="J1797">
+        <v>0</v>
+      </c>
+      <c r="L1797">
+        <v>0</v>
+      </c>
+      <c r="M1797">
+        <v>0</v>
+      </c>
+      <c r="N1797">
+        <v>0</v>
+      </c>
+      <c r="O1797">
+        <v>0</v>
+      </c>
+      <c r="P1797">
+        <v>0</v>
+      </c>
+      <c r="Q1797">
+        <v>0</v>
+      </c>
+      <c r="R1797">
+        <v>0</v>
+      </c>
+      <c r="S1797">
+        <v>0</v>
+      </c>
+      <c r="T1797">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1798" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1798">
+        <v>1</v>
+      </c>
+      <c r="D1798">
+        <v>1</v>
+      </c>
+      <c r="E1798">
+        <v>0</v>
+      </c>
+      <c r="F1798">
+        <v>85</v>
+      </c>
+      <c r="G1798">
+        <v>85</v>
+      </c>
+      <c r="H1798">
+        <v>85</v>
+      </c>
+      <c r="I1798">
+        <v>1</v>
+      </c>
+      <c r="J1798">
+        <v>0</v>
+      </c>
+      <c r="K1798">
+        <v>184.78</v>
+      </c>
+      <c r="L1798">
+        <v>46</v>
+      </c>
+      <c r="M1798">
+        <v>10</v>
+      </c>
+      <c r="N1798">
+        <v>15</v>
+      </c>
+      <c r="O1798">
+        <v>0</v>
+      </c>
+      <c r="P1798">
+        <v>48.85</v>
+      </c>
+      <c r="Q1798">
+        <v>0</v>
+      </c>
+      <c r="R1798">
+        <v>0</v>
+      </c>
+      <c r="S1798">
+        <v>0</v>
+      </c>
+      <c r="T1798">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1799" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1799">
+        <v>1</v>
+      </c>
+      <c r="D1799">
+        <v>1</v>
+      </c>
+      <c r="E1799">
+        <v>1</v>
+      </c>
+      <c r="F1799">
+        <v>13</v>
+      </c>
+      <c r="H1799" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1799">
+        <v>0</v>
+      </c>
+      <c r="J1799">
+        <v>0</v>
+      </c>
+      <c r="K1799">
+        <v>65</v>
+      </c>
+      <c r="L1799">
+        <v>20</v>
+      </c>
+      <c r="M1799">
+        <v>9</v>
+      </c>
+      <c r="N1799">
+        <v>0</v>
+      </c>
+      <c r="O1799">
+        <v>0</v>
+      </c>
+      <c r="P1799">
+        <v>12.15</v>
+      </c>
+      <c r="Q1799">
+        <v>0</v>
+      </c>
+      <c r="R1799">
+        <v>0</v>
+      </c>
+      <c r="S1799">
+        <v>0</v>
+      </c>
+      <c r="T1799">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1800" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1800">
+        <v>1</v>
+      </c>
+      <c r="D1800">
+        <v>0</v>
+      </c>
+      <c r="E1800">
+        <v>0</v>
+      </c>
+      <c r="F1800">
+        <v>0</v>
+      </c>
+      <c r="I1800">
+        <v>0</v>
+      </c>
+      <c r="J1800">
+        <v>0</v>
+      </c>
+      <c r="L1800">
+        <v>0</v>
+      </c>
+      <c r="M1800">
+        <v>0</v>
+      </c>
+      <c r="N1800">
+        <v>0</v>
+      </c>
+      <c r="O1800">
+        <v>0</v>
+      </c>
+      <c r="P1800">
+        <v>0</v>
+      </c>
+      <c r="Q1800">
+        <v>0</v>
+      </c>
+      <c r="R1800">
+        <v>0</v>
+      </c>
+      <c r="S1800">
+        <v>0</v>
+      </c>
+      <c r="T1800">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1801" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1801">
+        <v>1</v>
+      </c>
+      <c r="D1801">
+        <v>0</v>
+      </c>
+      <c r="E1801">
+        <v>0</v>
+      </c>
+      <c r="F1801">
+        <v>0</v>
+      </c>
+      <c r="I1801">
+        <v>0</v>
+      </c>
+      <c r="J1801">
+        <v>0</v>
+      </c>
+      <c r="L1801">
+        <v>0</v>
+      </c>
+      <c r="M1801">
+        <v>0</v>
+      </c>
+      <c r="N1801">
+        <v>0</v>
+      </c>
+      <c r="O1801">
+        <v>0</v>
+      </c>
+      <c r="P1801">
+        <v>0</v>
+      </c>
+      <c r="Q1801">
+        <v>0</v>
+      </c>
+      <c r="R1801">
+        <v>0</v>
+      </c>
+      <c r="S1801">
+        <v>0</v>
+      </c>
+      <c r="T1801">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1802" t="s">
+        <v>487</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1802">
+        <v>1</v>
+      </c>
+      <c r="D1802">
+        <v>0</v>
+      </c>
+      <c r="E1802">
+        <v>0</v>
+      </c>
+      <c r="F1802">
+        <v>0</v>
+      </c>
+      <c r="I1802">
+        <v>0</v>
+      </c>
+      <c r="J1802">
+        <v>0</v>
+      </c>
+      <c r="L1802">
+        <v>0</v>
+      </c>
+      <c r="M1802">
+        <v>0</v>
+      </c>
+      <c r="N1802">
+        <v>0</v>
+      </c>
+      <c r="O1802">
+        <v>0</v>
+      </c>
+      <c r="P1802">
+        <v>0</v>
+      </c>
+      <c r="Q1802">
+        <v>0</v>
+      </c>
+      <c r="R1802">
+        <v>0</v>
+      </c>
+      <c r="S1802">
+        <v>0</v>
+      </c>
+      <c r="T1802">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="500">
   <si>
     <t>Group</t>
   </si>
@@ -1487,6 +1487,39 @@
   <si>
     <t>Paula Parker</t>
   </si>
+  <si>
+    <t>Dundrum Women 1st XI v CSNI Women 2nd XI, The Meadow - 3 August 2026</t>
+  </si>
+  <si>
+    <t>K Harper</t>
+  </si>
+  <si>
+    <t>Holywood Women 2nd XI v Bangor Women 1st XI, Seapark Oval - 3 August 2026</t>
+  </si>
+  <si>
+    <t>Olivia Hall</t>
+  </si>
+  <si>
+    <t>Jia Kava</t>
+  </si>
+  <si>
+    <t>Mabel Rea</t>
+  </si>
+  <si>
+    <t>Instonians Women 2nd XI v Waringstown Women 2nd XI, Shaw's Bridge - 3 August 2026</t>
+  </si>
+  <si>
+    <t>E Stoddart</t>
+  </si>
+  <si>
+    <t>Muckamore Women 2nd XI v Lisburn Women 2nd XI, Moylena - 3 August 2026</t>
+  </si>
+  <si>
+    <t>Amy Atkinson</t>
+  </si>
+  <si>
+    <t>Jade Neely</t>
+  </si>
 </sst>
 </file>
 
@@ -2293,7 +2326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1802"/>
+  <dimension ref="A1:T1890"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -107757,6 +107790,5267 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1803" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1803" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>417</v>
+      </c>
+      <c r="C1803">
+        <v>1</v>
+      </c>
+      <c r="D1803">
+        <v>0</v>
+      </c>
+      <c r="E1803">
+        <v>0</v>
+      </c>
+      <c r="F1803">
+        <v>0</v>
+      </c>
+      <c r="I1803">
+        <v>0</v>
+      </c>
+      <c r="J1803">
+        <v>0</v>
+      </c>
+      <c r="L1803">
+        <v>0</v>
+      </c>
+      <c r="M1803">
+        <v>0</v>
+      </c>
+      <c r="N1803">
+        <v>0</v>
+      </c>
+      <c r="O1803">
+        <v>0</v>
+      </c>
+      <c r="P1803">
+        <v>0</v>
+      </c>
+      <c r="Q1803">
+        <v>0</v>
+      </c>
+      <c r="R1803">
+        <v>0</v>
+      </c>
+      <c r="S1803">
+        <v>0</v>
+      </c>
+      <c r="T1803">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1804" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1804">
+        <v>1</v>
+      </c>
+      <c r="D1804">
+        <v>1</v>
+      </c>
+      <c r="E1804">
+        <v>1</v>
+      </c>
+      <c r="F1804">
+        <v>0</v>
+      </c>
+      <c r="H1804" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1804">
+        <v>0</v>
+      </c>
+      <c r="J1804">
+        <v>0</v>
+      </c>
+      <c r="K1804">
+        <v>0</v>
+      </c>
+      <c r="L1804">
+        <v>4</v>
+      </c>
+      <c r="M1804">
+        <v>4</v>
+      </c>
+      <c r="N1804">
+        <v>0</v>
+      </c>
+      <c r="O1804">
+        <v>0</v>
+      </c>
+      <c r="P1804">
+        <v>0</v>
+      </c>
+      <c r="Q1804">
+        <v>0</v>
+      </c>
+      <c r="R1804">
+        <v>0</v>
+      </c>
+      <c r="S1804">
+        <v>0</v>
+      </c>
+      <c r="T1804">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1805" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1805">
+        <v>1</v>
+      </c>
+      <c r="D1805">
+        <v>0</v>
+      </c>
+      <c r="E1805">
+        <v>0</v>
+      </c>
+      <c r="F1805">
+        <v>0</v>
+      </c>
+      <c r="I1805">
+        <v>0</v>
+      </c>
+      <c r="J1805">
+        <v>0</v>
+      </c>
+      <c r="L1805">
+        <v>0</v>
+      </c>
+      <c r="M1805">
+        <v>0</v>
+      </c>
+      <c r="N1805">
+        <v>0</v>
+      </c>
+      <c r="O1805">
+        <v>0</v>
+      </c>
+      <c r="P1805">
+        <v>0</v>
+      </c>
+      <c r="Q1805">
+        <v>0</v>
+      </c>
+      <c r="R1805">
+        <v>0</v>
+      </c>
+      <c r="S1805">
+        <v>0</v>
+      </c>
+      <c r="T1805">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1806" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>190</v>
+      </c>
+      <c r="C1806">
+        <v>1</v>
+      </c>
+      <c r="D1806">
+        <v>0</v>
+      </c>
+      <c r="E1806">
+        <v>0</v>
+      </c>
+      <c r="F1806">
+        <v>0</v>
+      </c>
+      <c r="I1806">
+        <v>0</v>
+      </c>
+      <c r="J1806">
+        <v>0</v>
+      </c>
+      <c r="L1806">
+        <v>0</v>
+      </c>
+      <c r="M1806">
+        <v>0</v>
+      </c>
+      <c r="N1806">
+        <v>0</v>
+      </c>
+      <c r="O1806">
+        <v>0</v>
+      </c>
+      <c r="P1806">
+        <v>0</v>
+      </c>
+      <c r="Q1806">
+        <v>0</v>
+      </c>
+      <c r="R1806">
+        <v>0</v>
+      </c>
+      <c r="S1806">
+        <v>0</v>
+      </c>
+      <c r="T1806">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1807" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1807">
+        <v>1</v>
+      </c>
+      <c r="D1807">
+        <v>1</v>
+      </c>
+      <c r="E1807">
+        <v>0</v>
+      </c>
+      <c r="F1807">
+        <v>13</v>
+      </c>
+      <c r="G1807">
+        <v>13</v>
+      </c>
+      <c r="H1807">
+        <v>13</v>
+      </c>
+      <c r="I1807">
+        <v>0</v>
+      </c>
+      <c r="J1807">
+        <v>0</v>
+      </c>
+      <c r="K1807">
+        <v>56.52</v>
+      </c>
+      <c r="L1807">
+        <v>23</v>
+      </c>
+      <c r="M1807">
+        <v>14</v>
+      </c>
+      <c r="N1807">
+        <v>1</v>
+      </c>
+      <c r="O1807">
+        <v>0</v>
+      </c>
+      <c r="P1807">
+        <v>12.15</v>
+      </c>
+      <c r="Q1807">
+        <v>0</v>
+      </c>
+      <c r="R1807">
+        <v>0</v>
+      </c>
+      <c r="S1807">
+        <v>0</v>
+      </c>
+      <c r="T1807">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1808" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1808">
+        <v>1</v>
+      </c>
+      <c r="D1808">
+        <v>1</v>
+      </c>
+      <c r="E1808">
+        <v>0</v>
+      </c>
+      <c r="F1808">
+        <v>14</v>
+      </c>
+      <c r="G1808">
+        <v>14</v>
+      </c>
+      <c r="H1808">
+        <v>14</v>
+      </c>
+      <c r="I1808">
+        <v>0</v>
+      </c>
+      <c r="J1808">
+        <v>0</v>
+      </c>
+      <c r="K1808">
+        <v>50</v>
+      </c>
+      <c r="L1808">
+        <v>28</v>
+      </c>
+      <c r="M1808">
+        <v>18</v>
+      </c>
+      <c r="N1808">
+        <v>1</v>
+      </c>
+      <c r="O1808">
+        <v>0</v>
+      </c>
+      <c r="P1808">
+        <v>13.46</v>
+      </c>
+      <c r="Q1808">
+        <v>0</v>
+      </c>
+      <c r="R1808">
+        <v>0</v>
+      </c>
+      <c r="S1808">
+        <v>0</v>
+      </c>
+      <c r="T1808">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1809" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1809">
+        <v>1</v>
+      </c>
+      <c r="D1809">
+        <v>1</v>
+      </c>
+      <c r="E1809">
+        <v>0</v>
+      </c>
+      <c r="F1809">
+        <v>14</v>
+      </c>
+      <c r="G1809">
+        <v>14</v>
+      </c>
+      <c r="H1809">
+        <v>14</v>
+      </c>
+      <c r="I1809">
+        <v>0</v>
+      </c>
+      <c r="J1809">
+        <v>0</v>
+      </c>
+      <c r="K1809">
+        <v>77.78</v>
+      </c>
+      <c r="L1809">
+        <v>18</v>
+      </c>
+      <c r="M1809">
+        <v>13</v>
+      </c>
+      <c r="N1809">
+        <v>3</v>
+      </c>
+      <c r="O1809">
+        <v>0</v>
+      </c>
+      <c r="P1809">
+        <v>13.46</v>
+      </c>
+      <c r="Q1809">
+        <v>0</v>
+      </c>
+      <c r="R1809">
+        <v>0</v>
+      </c>
+      <c r="S1809">
+        <v>0</v>
+      </c>
+      <c r="T1809">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1810" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1810" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1810">
+        <v>1</v>
+      </c>
+      <c r="D1810">
+        <v>1</v>
+      </c>
+      <c r="E1810">
+        <v>0</v>
+      </c>
+      <c r="F1810">
+        <v>14</v>
+      </c>
+      <c r="G1810">
+        <v>14</v>
+      </c>
+      <c r="H1810">
+        <v>14</v>
+      </c>
+      <c r="I1810">
+        <v>0</v>
+      </c>
+      <c r="J1810">
+        <v>0</v>
+      </c>
+      <c r="K1810">
+        <v>56</v>
+      </c>
+      <c r="L1810">
+        <v>25</v>
+      </c>
+      <c r="M1810">
+        <v>16</v>
+      </c>
+      <c r="N1810">
+        <v>1</v>
+      </c>
+      <c r="O1810">
+        <v>0</v>
+      </c>
+      <c r="P1810">
+        <v>13.08</v>
+      </c>
+      <c r="Q1810">
+        <v>0</v>
+      </c>
+      <c r="R1810">
+        <v>0</v>
+      </c>
+      <c r="S1810">
+        <v>0</v>
+      </c>
+      <c r="T1810">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1811" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1811" t="s">
+        <v>490</v>
+      </c>
+      <c r="C1811">
+        <v>1</v>
+      </c>
+      <c r="D1811">
+        <v>0</v>
+      </c>
+      <c r="E1811">
+        <v>0</v>
+      </c>
+      <c r="F1811">
+        <v>0</v>
+      </c>
+      <c r="I1811">
+        <v>0</v>
+      </c>
+      <c r="J1811">
+        <v>0</v>
+      </c>
+      <c r="L1811">
+        <v>0</v>
+      </c>
+      <c r="M1811">
+        <v>0</v>
+      </c>
+      <c r="N1811">
+        <v>0</v>
+      </c>
+      <c r="O1811">
+        <v>0</v>
+      </c>
+      <c r="P1811">
+        <v>0</v>
+      </c>
+      <c r="Q1811">
+        <v>0</v>
+      </c>
+      <c r="R1811">
+        <v>0</v>
+      </c>
+      <c r="S1811">
+        <v>0</v>
+      </c>
+      <c r="T1811">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1812" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1812" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1812">
+        <v>1</v>
+      </c>
+      <c r="D1812">
+        <v>1</v>
+      </c>
+      <c r="E1812">
+        <v>1</v>
+      </c>
+      <c r="F1812">
+        <v>0</v>
+      </c>
+      <c r="H1812" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1812">
+        <v>0</v>
+      </c>
+      <c r="J1812">
+        <v>0</v>
+      </c>
+      <c r="K1812">
+        <v>0</v>
+      </c>
+      <c r="L1812">
+        <v>4</v>
+      </c>
+      <c r="M1812">
+        <v>4</v>
+      </c>
+      <c r="N1812">
+        <v>0</v>
+      </c>
+      <c r="O1812">
+        <v>0</v>
+      </c>
+      <c r="P1812">
+        <v>0</v>
+      </c>
+      <c r="Q1812">
+        <v>0</v>
+      </c>
+      <c r="R1812">
+        <v>0</v>
+      </c>
+      <c r="S1812">
+        <v>0</v>
+      </c>
+      <c r="T1812">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1813" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1813" t="s">
+        <v>401</v>
+      </c>
+      <c r="C1813">
+        <v>1</v>
+      </c>
+      <c r="D1813">
+        <v>1</v>
+      </c>
+      <c r="E1813">
+        <v>0</v>
+      </c>
+      <c r="F1813">
+        <v>7</v>
+      </c>
+      <c r="G1813">
+        <v>7</v>
+      </c>
+      <c r="H1813">
+        <v>7</v>
+      </c>
+      <c r="I1813">
+        <v>0</v>
+      </c>
+      <c r="J1813">
+        <v>0</v>
+      </c>
+      <c r="K1813">
+        <v>58.33</v>
+      </c>
+      <c r="L1813">
+        <v>12</v>
+      </c>
+      <c r="M1813">
+        <v>7</v>
+      </c>
+      <c r="N1813">
+        <v>0</v>
+      </c>
+      <c r="O1813">
+        <v>0</v>
+      </c>
+      <c r="P1813">
+        <v>6.73</v>
+      </c>
+      <c r="Q1813">
+        <v>0</v>
+      </c>
+      <c r="R1813">
+        <v>0</v>
+      </c>
+      <c r="S1813">
+        <v>0</v>
+      </c>
+      <c r="T1813">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1814" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1814" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1814">
+        <v>1</v>
+      </c>
+      <c r="D1814">
+        <v>1</v>
+      </c>
+      <c r="E1814">
+        <v>1</v>
+      </c>
+      <c r="F1814">
+        <v>17</v>
+      </c>
+      <c r="H1814" t="s">
+        <v>161</v>
+      </c>
+      <c r="I1814">
+        <v>0</v>
+      </c>
+      <c r="J1814">
+        <v>0</v>
+      </c>
+      <c r="K1814">
+        <v>44.74</v>
+      </c>
+      <c r="L1814">
+        <v>38</v>
+      </c>
+      <c r="M1814">
+        <v>27</v>
+      </c>
+      <c r="N1814">
+        <v>1</v>
+      </c>
+      <c r="O1814">
+        <v>0</v>
+      </c>
+      <c r="P1814">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="Q1814">
+        <v>0</v>
+      </c>
+      <c r="R1814">
+        <v>0</v>
+      </c>
+      <c r="S1814">
+        <v>0</v>
+      </c>
+      <c r="T1814">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1815" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1815" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1815">
+        <v>1</v>
+      </c>
+      <c r="D1815">
+        <v>1</v>
+      </c>
+      <c r="E1815">
+        <v>0</v>
+      </c>
+      <c r="F1815">
+        <v>40</v>
+      </c>
+      <c r="G1815">
+        <v>40</v>
+      </c>
+      <c r="H1815">
+        <v>40</v>
+      </c>
+      <c r="I1815">
+        <v>0</v>
+      </c>
+      <c r="J1815">
+        <v>0</v>
+      </c>
+      <c r="K1815">
+        <v>111.11</v>
+      </c>
+      <c r="L1815">
+        <v>36</v>
+      </c>
+      <c r="M1815">
+        <v>16</v>
+      </c>
+      <c r="N1815">
+        <v>6</v>
+      </c>
+      <c r="O1815">
+        <v>0</v>
+      </c>
+      <c r="P1815">
+        <v>37.380000000000003</v>
+      </c>
+      <c r="Q1815">
+        <v>1</v>
+      </c>
+      <c r="R1815">
+        <v>0</v>
+      </c>
+      <c r="S1815">
+        <v>0</v>
+      </c>
+      <c r="T1815">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1816" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1816" t="s">
+        <v>369</v>
+      </c>
+      <c r="C1816">
+        <v>1</v>
+      </c>
+      <c r="D1816">
+        <v>0</v>
+      </c>
+      <c r="E1816">
+        <v>0</v>
+      </c>
+      <c r="F1816">
+        <v>0</v>
+      </c>
+      <c r="I1816">
+        <v>0</v>
+      </c>
+      <c r="J1816">
+        <v>0</v>
+      </c>
+      <c r="L1816">
+        <v>0</v>
+      </c>
+      <c r="M1816">
+        <v>0</v>
+      </c>
+      <c r="N1816">
+        <v>0</v>
+      </c>
+      <c r="O1816">
+        <v>0</v>
+      </c>
+      <c r="P1816">
+        <v>0</v>
+      </c>
+      <c r="Q1816">
+        <v>0</v>
+      </c>
+      <c r="R1816">
+        <v>0</v>
+      </c>
+      <c r="S1816">
+        <v>0</v>
+      </c>
+      <c r="T1816">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1817" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1817" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1817">
+        <v>1</v>
+      </c>
+      <c r="D1817">
+        <v>1</v>
+      </c>
+      <c r="E1817">
+        <v>0</v>
+      </c>
+      <c r="F1817">
+        <v>17</v>
+      </c>
+      <c r="G1817">
+        <v>17</v>
+      </c>
+      <c r="H1817">
+        <v>17</v>
+      </c>
+      <c r="I1817">
+        <v>0</v>
+      </c>
+      <c r="J1817">
+        <v>0</v>
+      </c>
+      <c r="K1817">
+        <v>65.38</v>
+      </c>
+      <c r="L1817">
+        <v>26</v>
+      </c>
+      <c r="M1817">
+        <v>16</v>
+      </c>
+      <c r="N1817">
+        <v>2</v>
+      </c>
+      <c r="O1817">
+        <v>0</v>
+      </c>
+      <c r="P1817">
+        <v>15.89</v>
+      </c>
+      <c r="Q1817">
+        <v>1</v>
+      </c>
+      <c r="R1817">
+        <v>0</v>
+      </c>
+      <c r="S1817">
+        <v>0</v>
+      </c>
+      <c r="T1817">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1818" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1818" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1818">
+        <v>1</v>
+      </c>
+      <c r="D1818">
+        <v>1</v>
+      </c>
+      <c r="E1818">
+        <v>0</v>
+      </c>
+      <c r="F1818">
+        <v>8</v>
+      </c>
+      <c r="G1818">
+        <v>8</v>
+      </c>
+      <c r="H1818">
+        <v>8</v>
+      </c>
+      <c r="I1818">
+        <v>0</v>
+      </c>
+      <c r="J1818">
+        <v>0</v>
+      </c>
+      <c r="K1818">
+        <v>72.73</v>
+      </c>
+      <c r="L1818">
+        <v>11</v>
+      </c>
+      <c r="M1818">
+        <v>6</v>
+      </c>
+      <c r="N1818">
+        <v>1</v>
+      </c>
+      <c r="O1818">
+        <v>0</v>
+      </c>
+      <c r="P1818">
+        <v>7.69</v>
+      </c>
+      <c r="Q1818">
+        <v>0</v>
+      </c>
+      <c r="R1818">
+        <v>0</v>
+      </c>
+      <c r="S1818">
+        <v>0</v>
+      </c>
+      <c r="T1818">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1819" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1819" t="s">
+        <v>306</v>
+      </c>
+      <c r="C1819">
+        <v>1</v>
+      </c>
+      <c r="D1819">
+        <v>0</v>
+      </c>
+      <c r="E1819">
+        <v>0</v>
+      </c>
+      <c r="F1819">
+        <v>0</v>
+      </c>
+      <c r="I1819">
+        <v>0</v>
+      </c>
+      <c r="J1819">
+        <v>0</v>
+      </c>
+      <c r="L1819">
+        <v>0</v>
+      </c>
+      <c r="M1819">
+        <v>0</v>
+      </c>
+      <c r="N1819">
+        <v>0</v>
+      </c>
+      <c r="O1819">
+        <v>0</v>
+      </c>
+      <c r="P1819">
+        <v>0</v>
+      </c>
+      <c r="Q1819">
+        <v>2</v>
+      </c>
+      <c r="R1819">
+        <v>0</v>
+      </c>
+      <c r="S1819">
+        <v>0</v>
+      </c>
+      <c r="T1819">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1820" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1820" t="s">
+        <v>307</v>
+      </c>
+      <c r="C1820">
+        <v>1</v>
+      </c>
+      <c r="D1820">
+        <v>1</v>
+      </c>
+      <c r="E1820">
+        <v>0</v>
+      </c>
+      <c r="F1820">
+        <v>2</v>
+      </c>
+      <c r="G1820">
+        <v>2</v>
+      </c>
+      <c r="H1820">
+        <v>2</v>
+      </c>
+      <c r="I1820">
+        <v>0</v>
+      </c>
+      <c r="J1820">
+        <v>0</v>
+      </c>
+      <c r="K1820">
+        <v>28.57</v>
+      </c>
+      <c r="L1820">
+        <v>7</v>
+      </c>
+      <c r="M1820">
+        <v>5</v>
+      </c>
+      <c r="N1820">
+        <v>0</v>
+      </c>
+      <c r="O1820">
+        <v>0</v>
+      </c>
+      <c r="P1820">
+        <v>1.87</v>
+      </c>
+      <c r="Q1820">
+        <v>0</v>
+      </c>
+      <c r="R1820">
+        <v>0</v>
+      </c>
+      <c r="S1820">
+        <v>0</v>
+      </c>
+      <c r="T1820">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1821" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1821" t="s">
+        <v>176</v>
+      </c>
+      <c r="C1821">
+        <v>1</v>
+      </c>
+      <c r="D1821">
+        <v>1</v>
+      </c>
+      <c r="E1821">
+        <v>1</v>
+      </c>
+      <c r="F1821">
+        <v>2</v>
+      </c>
+      <c r="H1821" t="s">
+        <v>160</v>
+      </c>
+      <c r="I1821">
+        <v>0</v>
+      </c>
+      <c r="J1821">
+        <v>0</v>
+      </c>
+      <c r="K1821">
+        <v>20</v>
+      </c>
+      <c r="L1821">
+        <v>10</v>
+      </c>
+      <c r="M1821">
+        <v>8</v>
+      </c>
+      <c r="N1821">
+        <v>0</v>
+      </c>
+      <c r="O1821">
+        <v>0</v>
+      </c>
+      <c r="P1821">
+        <v>1.92</v>
+      </c>
+      <c r="Q1821">
+        <v>0</v>
+      </c>
+      <c r="R1821">
+        <v>0</v>
+      </c>
+      <c r="S1821">
+        <v>0</v>
+      </c>
+      <c r="T1821">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1822" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1822" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1822">
+        <v>1</v>
+      </c>
+      <c r="D1822">
+        <v>1</v>
+      </c>
+      <c r="E1822">
+        <v>1</v>
+      </c>
+      <c r="F1822">
+        <v>4</v>
+      </c>
+      <c r="H1822" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1822">
+        <v>0</v>
+      </c>
+      <c r="J1822">
+        <v>0</v>
+      </c>
+      <c r="K1822">
+        <v>133.33000000000001</v>
+      </c>
+      <c r="L1822">
+        <v>3</v>
+      </c>
+      <c r="M1822">
+        <v>2</v>
+      </c>
+      <c r="N1822">
+        <v>1</v>
+      </c>
+      <c r="O1822">
+        <v>0</v>
+      </c>
+      <c r="P1822">
+        <v>3.74</v>
+      </c>
+      <c r="Q1822">
+        <v>0</v>
+      </c>
+      <c r="R1822">
+        <v>0</v>
+      </c>
+      <c r="S1822">
+        <v>0</v>
+      </c>
+      <c r="T1822">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1823" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1823" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1823">
+        <v>1</v>
+      </c>
+      <c r="D1823">
+        <v>1</v>
+      </c>
+      <c r="E1823">
+        <v>0</v>
+      </c>
+      <c r="F1823">
+        <v>6</v>
+      </c>
+      <c r="G1823">
+        <v>6</v>
+      </c>
+      <c r="H1823">
+        <v>6</v>
+      </c>
+      <c r="I1823">
+        <v>0</v>
+      </c>
+      <c r="J1823">
+        <v>0</v>
+      </c>
+      <c r="K1823">
+        <v>200</v>
+      </c>
+      <c r="L1823">
+        <v>3</v>
+      </c>
+      <c r="M1823">
+        <v>1</v>
+      </c>
+      <c r="N1823">
+        <v>1</v>
+      </c>
+      <c r="O1823">
+        <v>0</v>
+      </c>
+      <c r="P1823">
+        <v>5.77</v>
+      </c>
+      <c r="Q1823">
+        <v>0</v>
+      </c>
+      <c r="R1823">
+        <v>0</v>
+      </c>
+      <c r="S1823">
+        <v>0</v>
+      </c>
+      <c r="T1823">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1824" t="s">
+        <v>489</v>
+      </c>
+      <c r="B1824" t="s">
+        <v>270</v>
+      </c>
+      <c r="C1824">
+        <v>1</v>
+      </c>
+      <c r="D1824">
+        <v>0</v>
+      </c>
+      <c r="E1824">
+        <v>0</v>
+      </c>
+      <c r="F1824">
+        <v>0</v>
+      </c>
+      <c r="I1824">
+        <v>0</v>
+      </c>
+      <c r="J1824">
+        <v>0</v>
+      </c>
+      <c r="L1824">
+        <v>0</v>
+      </c>
+      <c r="M1824">
+        <v>0</v>
+      </c>
+      <c r="N1824">
+        <v>0</v>
+      </c>
+      <c r="O1824">
+        <v>0</v>
+      </c>
+      <c r="P1824">
+        <v>0</v>
+      </c>
+      <c r="Q1824">
+        <v>0</v>
+      </c>
+      <c r="R1824">
+        <v>0</v>
+      </c>
+      <c r="S1824">
+        <v>0</v>
+      </c>
+      <c r="T1824">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1825" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1825" t="s">
+        <v>463</v>
+      </c>
+      <c r="C1825">
+        <v>1</v>
+      </c>
+      <c r="D1825">
+        <v>1</v>
+      </c>
+      <c r="E1825">
+        <v>0</v>
+      </c>
+      <c r="F1825">
+        <v>3</v>
+      </c>
+      <c r="G1825">
+        <v>3</v>
+      </c>
+      <c r="H1825">
+        <v>3</v>
+      </c>
+      <c r="I1825">
+        <v>0</v>
+      </c>
+      <c r="J1825">
+        <v>0</v>
+      </c>
+      <c r="K1825">
+        <v>27.27</v>
+      </c>
+      <c r="L1825">
+        <v>11</v>
+      </c>
+      <c r="M1825">
+        <v>8</v>
+      </c>
+      <c r="N1825">
+        <v>0</v>
+      </c>
+      <c r="O1825">
+        <v>0</v>
+      </c>
+      <c r="P1825">
+        <v>4.76</v>
+      </c>
+      <c r="Q1825">
+        <v>0</v>
+      </c>
+      <c r="R1825">
+        <v>0</v>
+      </c>
+      <c r="S1825">
+        <v>0</v>
+      </c>
+      <c r="T1825">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1826" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1826" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1826">
+        <v>1</v>
+      </c>
+      <c r="D1826">
+        <v>1</v>
+      </c>
+      <c r="E1826">
+        <v>0</v>
+      </c>
+      <c r="F1826">
+        <v>8</v>
+      </c>
+      <c r="G1826">
+        <v>8</v>
+      </c>
+      <c r="H1826">
+        <v>8</v>
+      </c>
+      <c r="I1826">
+        <v>0</v>
+      </c>
+      <c r="J1826">
+        <v>0</v>
+      </c>
+      <c r="K1826">
+        <v>80</v>
+      </c>
+      <c r="L1826">
+        <v>10</v>
+      </c>
+      <c r="M1826">
+        <v>7</v>
+      </c>
+      <c r="N1826">
+        <v>1</v>
+      </c>
+      <c r="O1826">
+        <v>0</v>
+      </c>
+      <c r="P1826">
+        <v>12.7</v>
+      </c>
+      <c r="Q1826">
+        <v>0</v>
+      </c>
+      <c r="R1826">
+        <v>0</v>
+      </c>
+      <c r="S1826">
+        <v>0</v>
+      </c>
+      <c r="T1826">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1827" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1827" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1827">
+        <v>1</v>
+      </c>
+      <c r="D1827">
+        <v>0</v>
+      </c>
+      <c r="E1827">
+        <v>0</v>
+      </c>
+      <c r="F1827">
+        <v>0</v>
+      </c>
+      <c r="I1827">
+        <v>0</v>
+      </c>
+      <c r="J1827">
+        <v>0</v>
+      </c>
+      <c r="L1827">
+        <v>0</v>
+      </c>
+      <c r="M1827">
+        <v>0</v>
+      </c>
+      <c r="N1827">
+        <v>0</v>
+      </c>
+      <c r="O1827">
+        <v>0</v>
+      </c>
+      <c r="P1827">
+        <v>0</v>
+      </c>
+      <c r="Q1827">
+        <v>0</v>
+      </c>
+      <c r="R1827">
+        <v>0</v>
+      </c>
+      <c r="S1827">
+        <v>0</v>
+      </c>
+      <c r="T1827">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1828" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1828" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1828">
+        <v>1</v>
+      </c>
+      <c r="D1828">
+        <v>1</v>
+      </c>
+      <c r="E1828">
+        <v>1</v>
+      </c>
+      <c r="F1828">
+        <v>9</v>
+      </c>
+      <c r="H1828" t="s">
+        <v>195</v>
+      </c>
+      <c r="I1828">
+        <v>0</v>
+      </c>
+      <c r="J1828">
+        <v>0</v>
+      </c>
+      <c r="K1828">
+        <v>50</v>
+      </c>
+      <c r="L1828">
+        <v>18</v>
+      </c>
+      <c r="M1828">
+        <v>12</v>
+      </c>
+      <c r="N1828">
+        <v>1</v>
+      </c>
+      <c r="O1828">
+        <v>0</v>
+      </c>
+      <c r="P1828">
+        <v>14.06</v>
+      </c>
+      <c r="Q1828">
+        <v>0</v>
+      </c>
+      <c r="R1828">
+        <v>0</v>
+      </c>
+      <c r="S1828">
+        <v>0</v>
+      </c>
+      <c r="T1828">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1829" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1829" t="s">
+        <v>492</v>
+      </c>
+      <c r="C1829">
+        <v>1</v>
+      </c>
+      <c r="D1829">
+        <v>1</v>
+      </c>
+      <c r="E1829">
+        <v>0</v>
+      </c>
+      <c r="F1829">
+        <v>0</v>
+      </c>
+      <c r="G1829">
+        <v>0</v>
+      </c>
+      <c r="H1829">
+        <v>0</v>
+      </c>
+      <c r="I1829">
+        <v>0</v>
+      </c>
+      <c r="J1829">
+        <v>0</v>
+      </c>
+      <c r="K1829">
+        <v>0</v>
+      </c>
+      <c r="L1829">
+        <v>1</v>
+      </c>
+      <c r="M1829">
+        <v>1</v>
+      </c>
+      <c r="N1829">
+        <v>0</v>
+      </c>
+      <c r="O1829">
+        <v>0</v>
+      </c>
+      <c r="P1829">
+        <v>0</v>
+      </c>
+      <c r="Q1829">
+        <v>0</v>
+      </c>
+      <c r="R1829">
+        <v>0</v>
+      </c>
+      <c r="S1829">
+        <v>0</v>
+      </c>
+      <c r="T1829">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1830" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1830" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1830">
+        <v>1</v>
+      </c>
+      <c r="D1830">
+        <v>1</v>
+      </c>
+      <c r="E1830">
+        <v>0</v>
+      </c>
+      <c r="F1830">
+        <v>1</v>
+      </c>
+      <c r="G1830">
+        <v>1</v>
+      </c>
+      <c r="H1830">
+        <v>1</v>
+      </c>
+      <c r="I1830">
+        <v>0</v>
+      </c>
+      <c r="J1830">
+        <v>0</v>
+      </c>
+      <c r="K1830">
+        <v>12.5</v>
+      </c>
+      <c r="L1830">
+        <v>8</v>
+      </c>
+      <c r="M1830">
+        <v>7</v>
+      </c>
+      <c r="N1830">
+        <v>0</v>
+      </c>
+      <c r="O1830">
+        <v>0</v>
+      </c>
+      <c r="P1830">
+        <v>1.56</v>
+      </c>
+      <c r="Q1830">
+        <v>0</v>
+      </c>
+      <c r="R1830">
+        <v>0</v>
+      </c>
+      <c r="S1830">
+        <v>0</v>
+      </c>
+      <c r="T1830">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1831" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1831" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1831">
+        <v>1</v>
+      </c>
+      <c r="D1831">
+        <v>0</v>
+      </c>
+      <c r="E1831">
+        <v>0</v>
+      </c>
+      <c r="F1831">
+        <v>0</v>
+      </c>
+      <c r="I1831">
+        <v>0</v>
+      </c>
+      <c r="J1831">
+        <v>0</v>
+      </c>
+      <c r="L1831">
+        <v>0</v>
+      </c>
+      <c r="M1831">
+        <v>0</v>
+      </c>
+      <c r="N1831">
+        <v>0</v>
+      </c>
+      <c r="O1831">
+        <v>0</v>
+      </c>
+      <c r="P1831">
+        <v>0</v>
+      </c>
+      <c r="Q1831">
+        <v>0</v>
+      </c>
+      <c r="R1831">
+        <v>0</v>
+      </c>
+      <c r="S1831">
+        <v>0</v>
+      </c>
+      <c r="T1831">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1832" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1832" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1832">
+        <v>1</v>
+      </c>
+      <c r="D1832">
+        <v>1</v>
+      </c>
+      <c r="E1832">
+        <v>0</v>
+      </c>
+      <c r="F1832">
+        <v>2</v>
+      </c>
+      <c r="G1832">
+        <v>2</v>
+      </c>
+      <c r="H1832">
+        <v>2</v>
+      </c>
+      <c r="I1832">
+        <v>0</v>
+      </c>
+      <c r="J1832">
+        <v>0</v>
+      </c>
+      <c r="K1832">
+        <v>18.18</v>
+      </c>
+      <c r="L1832">
+        <v>11</v>
+      </c>
+      <c r="M1832">
+        <v>10</v>
+      </c>
+      <c r="N1832">
+        <v>0</v>
+      </c>
+      <c r="O1832">
+        <v>0</v>
+      </c>
+      <c r="P1832">
+        <v>3.17</v>
+      </c>
+      <c r="Q1832">
+        <v>1</v>
+      </c>
+      <c r="R1832">
+        <v>0</v>
+      </c>
+      <c r="S1832">
+        <v>0</v>
+      </c>
+      <c r="T1832">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1833" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1833" t="s">
+        <v>493</v>
+      </c>
+      <c r="C1833">
+        <v>1</v>
+      </c>
+      <c r="D1833">
+        <v>1</v>
+      </c>
+      <c r="E1833">
+        <v>0</v>
+      </c>
+      <c r="F1833">
+        <v>0</v>
+      </c>
+      <c r="G1833">
+        <v>0</v>
+      </c>
+      <c r="H1833">
+        <v>0</v>
+      </c>
+      <c r="I1833">
+        <v>0</v>
+      </c>
+      <c r="J1833">
+        <v>0</v>
+      </c>
+      <c r="K1833">
+        <v>0</v>
+      </c>
+      <c r="L1833">
+        <v>1</v>
+      </c>
+      <c r="M1833">
+        <v>1</v>
+      </c>
+      <c r="N1833">
+        <v>0</v>
+      </c>
+      <c r="O1833">
+        <v>0</v>
+      </c>
+      <c r="P1833">
+        <v>0</v>
+      </c>
+      <c r="Q1833">
+        <v>0</v>
+      </c>
+      <c r="R1833">
+        <v>0</v>
+      </c>
+      <c r="S1833">
+        <v>0</v>
+      </c>
+      <c r="T1833">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1834" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1834" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1834">
+        <v>1</v>
+      </c>
+      <c r="D1834">
+        <v>0</v>
+      </c>
+      <c r="E1834">
+        <v>0</v>
+      </c>
+      <c r="F1834">
+        <v>0</v>
+      </c>
+      <c r="I1834">
+        <v>0</v>
+      </c>
+      <c r="J1834">
+        <v>0</v>
+      </c>
+      <c r="L1834">
+        <v>0</v>
+      </c>
+      <c r="M1834">
+        <v>0</v>
+      </c>
+      <c r="N1834">
+        <v>0</v>
+      </c>
+      <c r="O1834">
+        <v>0</v>
+      </c>
+      <c r="P1834">
+        <v>0</v>
+      </c>
+      <c r="Q1834">
+        <v>0</v>
+      </c>
+      <c r="R1834">
+        <v>0</v>
+      </c>
+      <c r="S1834">
+        <v>0</v>
+      </c>
+      <c r="T1834">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1835" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1835" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1835">
+        <v>1</v>
+      </c>
+      <c r="D1835">
+        <v>1</v>
+      </c>
+      <c r="E1835">
+        <v>1</v>
+      </c>
+      <c r="F1835">
+        <v>1</v>
+      </c>
+      <c r="H1835" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1835">
+        <v>0</v>
+      </c>
+      <c r="J1835">
+        <v>0</v>
+      </c>
+      <c r="K1835">
+        <v>10</v>
+      </c>
+      <c r="L1835">
+        <v>10</v>
+      </c>
+      <c r="M1835">
+        <v>9</v>
+      </c>
+      <c r="N1835">
+        <v>0</v>
+      </c>
+      <c r="O1835">
+        <v>0</v>
+      </c>
+      <c r="P1835">
+        <v>1.59</v>
+      </c>
+      <c r="Q1835">
+        <v>0</v>
+      </c>
+      <c r="R1835">
+        <v>0</v>
+      </c>
+      <c r="S1835">
+        <v>0</v>
+      </c>
+      <c r="T1835">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1836" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1836" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1836">
+        <v>1</v>
+      </c>
+      <c r="D1836">
+        <v>1</v>
+      </c>
+      <c r="E1836">
+        <v>0</v>
+      </c>
+      <c r="F1836">
+        <v>0</v>
+      </c>
+      <c r="G1836">
+        <v>0</v>
+      </c>
+      <c r="H1836">
+        <v>0</v>
+      </c>
+      <c r="I1836">
+        <v>0</v>
+      </c>
+      <c r="J1836">
+        <v>0</v>
+      </c>
+      <c r="K1836">
+        <v>0</v>
+      </c>
+      <c r="L1836">
+        <v>2</v>
+      </c>
+      <c r="M1836">
+        <v>2</v>
+      </c>
+      <c r="N1836">
+        <v>0</v>
+      </c>
+      <c r="O1836">
+        <v>0</v>
+      </c>
+      <c r="P1836">
+        <v>0</v>
+      </c>
+      <c r="Q1836">
+        <v>0</v>
+      </c>
+      <c r="R1836">
+        <v>0</v>
+      </c>
+      <c r="S1836">
+        <v>0</v>
+      </c>
+      <c r="T1836">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1837" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1837" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1837">
+        <v>1</v>
+      </c>
+      <c r="D1837">
+        <v>1</v>
+      </c>
+      <c r="E1837">
+        <v>0</v>
+      </c>
+      <c r="F1837">
+        <v>12</v>
+      </c>
+      <c r="G1837">
+        <v>12</v>
+      </c>
+      <c r="H1837">
+        <v>12</v>
+      </c>
+      <c r="I1837">
+        <v>0</v>
+      </c>
+      <c r="J1837">
+        <v>0</v>
+      </c>
+      <c r="K1837">
+        <v>92.31</v>
+      </c>
+      <c r="L1837">
+        <v>13</v>
+      </c>
+      <c r="M1837">
+        <v>7</v>
+      </c>
+      <c r="N1837">
+        <v>1</v>
+      </c>
+      <c r="O1837">
+        <v>0</v>
+      </c>
+      <c r="P1837">
+        <v>19.05</v>
+      </c>
+      <c r="Q1837">
+        <v>0</v>
+      </c>
+      <c r="R1837">
+        <v>0</v>
+      </c>
+      <c r="S1837">
+        <v>0</v>
+      </c>
+      <c r="T1837">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1838" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1838" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1838">
+        <v>1</v>
+      </c>
+      <c r="D1838">
+        <v>1</v>
+      </c>
+      <c r="E1838">
+        <v>0</v>
+      </c>
+      <c r="F1838">
+        <v>0</v>
+      </c>
+      <c r="G1838">
+        <v>0</v>
+      </c>
+      <c r="H1838">
+        <v>0</v>
+      </c>
+      <c r="I1838">
+        <v>0</v>
+      </c>
+      <c r="J1838">
+        <v>0</v>
+      </c>
+      <c r="K1838">
+        <v>0</v>
+      </c>
+      <c r="L1838">
+        <v>1</v>
+      </c>
+      <c r="M1838">
+        <v>1</v>
+      </c>
+      <c r="N1838">
+        <v>0</v>
+      </c>
+      <c r="O1838">
+        <v>0</v>
+      </c>
+      <c r="P1838">
+        <v>0</v>
+      </c>
+      <c r="Q1838">
+        <v>0</v>
+      </c>
+      <c r="R1838">
+        <v>0</v>
+      </c>
+      <c r="S1838">
+        <v>0</v>
+      </c>
+      <c r="T1838">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1839" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1839" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1839">
+        <v>1</v>
+      </c>
+      <c r="D1839">
+        <v>1</v>
+      </c>
+      <c r="E1839">
+        <v>0</v>
+      </c>
+      <c r="F1839">
+        <v>0</v>
+      </c>
+      <c r="G1839">
+        <v>0</v>
+      </c>
+      <c r="H1839">
+        <v>0</v>
+      </c>
+      <c r="I1839">
+        <v>0</v>
+      </c>
+      <c r="J1839">
+        <v>0</v>
+      </c>
+      <c r="K1839">
+        <v>0</v>
+      </c>
+      <c r="L1839">
+        <v>1</v>
+      </c>
+      <c r="M1839">
+        <v>1</v>
+      </c>
+      <c r="N1839">
+        <v>0</v>
+      </c>
+      <c r="O1839">
+        <v>0</v>
+      </c>
+      <c r="P1839">
+        <v>0</v>
+      </c>
+      <c r="Q1839">
+        <v>0</v>
+      </c>
+      <c r="R1839">
+        <v>0</v>
+      </c>
+      <c r="S1839">
+        <v>0</v>
+      </c>
+      <c r="T1839">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1840" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1840" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1840">
+        <v>1</v>
+      </c>
+      <c r="D1840">
+        <v>0</v>
+      </c>
+      <c r="E1840">
+        <v>0</v>
+      </c>
+      <c r="F1840">
+        <v>0</v>
+      </c>
+      <c r="I1840">
+        <v>0</v>
+      </c>
+      <c r="J1840">
+        <v>0</v>
+      </c>
+      <c r="L1840">
+        <v>0</v>
+      </c>
+      <c r="M1840">
+        <v>0</v>
+      </c>
+      <c r="N1840">
+        <v>0</v>
+      </c>
+      <c r="O1840">
+        <v>0</v>
+      </c>
+      <c r="P1840">
+        <v>0</v>
+      </c>
+      <c r="Q1840">
+        <v>0</v>
+      </c>
+      <c r="R1840">
+        <v>0</v>
+      </c>
+      <c r="S1840">
+        <v>0</v>
+      </c>
+      <c r="T1840">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1841" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1841" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1841">
+        <v>1</v>
+      </c>
+      <c r="D1841">
+        <v>1</v>
+      </c>
+      <c r="E1841">
+        <v>0</v>
+      </c>
+      <c r="F1841">
+        <v>1</v>
+      </c>
+      <c r="G1841">
+        <v>1</v>
+      </c>
+      <c r="H1841">
+        <v>1</v>
+      </c>
+      <c r="I1841">
+        <v>0</v>
+      </c>
+      <c r="J1841">
+        <v>0</v>
+      </c>
+      <c r="K1841">
+        <v>20</v>
+      </c>
+      <c r="L1841">
+        <v>5</v>
+      </c>
+      <c r="M1841">
+        <v>4</v>
+      </c>
+      <c r="N1841">
+        <v>0</v>
+      </c>
+      <c r="O1841">
+        <v>0</v>
+      </c>
+      <c r="P1841">
+        <v>1.56</v>
+      </c>
+      <c r="Q1841">
+        <v>0</v>
+      </c>
+      <c r="R1841">
+        <v>0</v>
+      </c>
+      <c r="S1841">
+        <v>0</v>
+      </c>
+      <c r="T1841">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1842" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1842" t="s">
+        <v>494</v>
+      </c>
+      <c r="C1842">
+        <v>1</v>
+      </c>
+      <c r="D1842">
+        <v>1</v>
+      </c>
+      <c r="E1842">
+        <v>0</v>
+      </c>
+      <c r="F1842">
+        <v>4</v>
+      </c>
+      <c r="G1842">
+        <v>4</v>
+      </c>
+      <c r="H1842">
+        <v>4</v>
+      </c>
+      <c r="I1842">
+        <v>0</v>
+      </c>
+      <c r="J1842">
+        <v>0</v>
+      </c>
+      <c r="K1842">
+        <v>13.79</v>
+      </c>
+      <c r="L1842">
+        <v>29</v>
+      </c>
+      <c r="M1842">
+        <v>26</v>
+      </c>
+      <c r="N1842">
+        <v>0</v>
+      </c>
+      <c r="O1842">
+        <v>0</v>
+      </c>
+      <c r="P1842">
+        <v>6.35</v>
+      </c>
+      <c r="Q1842">
+        <v>0</v>
+      </c>
+      <c r="R1842">
+        <v>0</v>
+      </c>
+      <c r="S1842">
+        <v>0</v>
+      </c>
+      <c r="T1842">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1843" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1843" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1843">
+        <v>1</v>
+      </c>
+      <c r="D1843">
+        <v>1</v>
+      </c>
+      <c r="E1843">
+        <v>0</v>
+      </c>
+      <c r="F1843">
+        <v>5</v>
+      </c>
+      <c r="G1843">
+        <v>5</v>
+      </c>
+      <c r="H1843">
+        <v>5</v>
+      </c>
+      <c r="I1843">
+        <v>0</v>
+      </c>
+      <c r="J1843">
+        <v>0</v>
+      </c>
+      <c r="K1843">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1843">
+        <v>7</v>
+      </c>
+      <c r="M1843">
+        <v>2</v>
+      </c>
+      <c r="N1843">
+        <v>0</v>
+      </c>
+      <c r="O1843">
+        <v>0</v>
+      </c>
+      <c r="P1843">
+        <v>7.94</v>
+      </c>
+      <c r="Q1843">
+        <v>0</v>
+      </c>
+      <c r="R1843">
+        <v>0</v>
+      </c>
+      <c r="S1843">
+        <v>0</v>
+      </c>
+      <c r="T1843">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1844" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1844" t="s">
+        <v>229</v>
+      </c>
+      <c r="C1844">
+        <v>1</v>
+      </c>
+      <c r="D1844">
+        <v>1</v>
+      </c>
+      <c r="E1844">
+        <v>1</v>
+      </c>
+      <c r="F1844">
+        <v>23</v>
+      </c>
+      <c r="H1844" t="s">
+        <v>177</v>
+      </c>
+      <c r="I1844">
+        <v>0</v>
+      </c>
+      <c r="J1844">
+        <v>0</v>
+      </c>
+      <c r="K1844">
+        <v>92</v>
+      </c>
+      <c r="L1844">
+        <v>25</v>
+      </c>
+      <c r="M1844">
+        <v>13</v>
+      </c>
+      <c r="N1844">
+        <v>3</v>
+      </c>
+      <c r="O1844">
+        <v>0</v>
+      </c>
+      <c r="P1844">
+        <v>35.94</v>
+      </c>
+      <c r="Q1844">
+        <v>0</v>
+      </c>
+      <c r="R1844">
+        <v>0</v>
+      </c>
+      <c r="S1844">
+        <v>0</v>
+      </c>
+      <c r="T1844">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1845" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1845" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1845">
+        <v>1</v>
+      </c>
+      <c r="D1845">
+        <v>1</v>
+      </c>
+      <c r="E1845">
+        <v>0</v>
+      </c>
+      <c r="F1845">
+        <v>10</v>
+      </c>
+      <c r="G1845">
+        <v>10</v>
+      </c>
+      <c r="H1845">
+        <v>10</v>
+      </c>
+      <c r="I1845">
+        <v>0</v>
+      </c>
+      <c r="J1845">
+        <v>0</v>
+      </c>
+      <c r="K1845">
+        <v>47.62</v>
+      </c>
+      <c r="L1845">
+        <v>21</v>
+      </c>
+      <c r="M1845">
+        <v>16</v>
+      </c>
+      <c r="N1845">
+        <v>1</v>
+      </c>
+      <c r="O1845">
+        <v>0</v>
+      </c>
+      <c r="P1845">
+        <v>15.63</v>
+      </c>
+      <c r="Q1845">
+        <v>1</v>
+      </c>
+      <c r="R1845">
+        <v>0</v>
+      </c>
+      <c r="S1845">
+        <v>0</v>
+      </c>
+      <c r="T1845">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1846" t="s">
+        <v>491</v>
+      </c>
+      <c r="B1846" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1846">
+        <v>1</v>
+      </c>
+      <c r="D1846">
+        <v>1</v>
+      </c>
+      <c r="E1846">
+        <v>0</v>
+      </c>
+      <c r="F1846">
+        <v>6</v>
+      </c>
+      <c r="G1846">
+        <v>6</v>
+      </c>
+      <c r="H1846">
+        <v>6</v>
+      </c>
+      <c r="I1846">
+        <v>0</v>
+      </c>
+      <c r="J1846">
+        <v>0</v>
+      </c>
+      <c r="K1846">
+        <v>75</v>
+      </c>
+      <c r="L1846">
+        <v>8</v>
+      </c>
+      <c r="M1846">
+        <v>5</v>
+      </c>
+      <c r="N1846">
+        <v>1</v>
+      </c>
+      <c r="O1846">
+        <v>0</v>
+      </c>
+      <c r="P1846">
+        <v>9.3800000000000008</v>
+      </c>
+      <c r="Q1846">
+        <v>0</v>
+      </c>
+      <c r="R1846">
+        <v>0</v>
+      </c>
+      <c r="S1846">
+        <v>0</v>
+      </c>
+      <c r="T1846">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1847" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1847" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1847">
+        <v>1</v>
+      </c>
+      <c r="D1847">
+        <v>1</v>
+      </c>
+      <c r="E1847">
+        <v>0</v>
+      </c>
+      <c r="F1847">
+        <v>8</v>
+      </c>
+      <c r="G1847">
+        <v>8</v>
+      </c>
+      <c r="H1847">
+        <v>8</v>
+      </c>
+      <c r="I1847">
+        <v>0</v>
+      </c>
+      <c r="J1847">
+        <v>0</v>
+      </c>
+      <c r="K1847">
+        <v>50</v>
+      </c>
+      <c r="L1847">
+        <v>16</v>
+      </c>
+      <c r="M1847">
+        <v>9</v>
+      </c>
+      <c r="N1847">
+        <v>0</v>
+      </c>
+      <c r="O1847">
+        <v>0</v>
+      </c>
+      <c r="P1847">
+        <v>7.77</v>
+      </c>
+      <c r="Q1847">
+        <v>0</v>
+      </c>
+      <c r="R1847">
+        <v>0</v>
+      </c>
+      <c r="S1847">
+        <v>0</v>
+      </c>
+      <c r="T1847">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1848" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1848" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1848">
+        <v>1</v>
+      </c>
+      <c r="D1848">
+        <v>1</v>
+      </c>
+      <c r="E1848">
+        <v>0</v>
+      </c>
+      <c r="F1848">
+        <v>0</v>
+      </c>
+      <c r="G1848">
+        <v>0</v>
+      </c>
+      <c r="H1848">
+        <v>0</v>
+      </c>
+      <c r="I1848">
+        <v>0</v>
+      </c>
+      <c r="J1848">
+        <v>0</v>
+      </c>
+      <c r="K1848">
+        <v>0</v>
+      </c>
+      <c r="L1848">
+        <v>7</v>
+      </c>
+      <c r="M1848">
+        <v>7</v>
+      </c>
+      <c r="N1848">
+        <v>0</v>
+      </c>
+      <c r="O1848">
+        <v>0</v>
+      </c>
+      <c r="P1848">
+        <v>0</v>
+      </c>
+      <c r="Q1848">
+        <v>0</v>
+      </c>
+      <c r="R1848">
+        <v>2</v>
+      </c>
+      <c r="S1848">
+        <v>0</v>
+      </c>
+      <c r="T1848">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1849" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1849" t="s">
+        <v>233</v>
+      </c>
+      <c r="C1849">
+        <v>1</v>
+      </c>
+      <c r="D1849">
+        <v>1</v>
+      </c>
+      <c r="E1849">
+        <v>0</v>
+      </c>
+      <c r="F1849">
+        <v>0</v>
+      </c>
+      <c r="G1849">
+        <v>0</v>
+      </c>
+      <c r="H1849">
+        <v>0</v>
+      </c>
+      <c r="I1849">
+        <v>0</v>
+      </c>
+      <c r="J1849">
+        <v>0</v>
+      </c>
+      <c r="K1849">
+        <v>0</v>
+      </c>
+      <c r="L1849">
+        <v>4</v>
+      </c>
+      <c r="M1849">
+        <v>4</v>
+      </c>
+      <c r="N1849">
+        <v>0</v>
+      </c>
+      <c r="O1849">
+        <v>0</v>
+      </c>
+      <c r="P1849">
+        <v>0</v>
+      </c>
+      <c r="Q1849">
+        <v>0</v>
+      </c>
+      <c r="R1849">
+        <v>0</v>
+      </c>
+      <c r="S1849">
+        <v>0</v>
+      </c>
+      <c r="T1849">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1850" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1850">
+        <v>1</v>
+      </c>
+      <c r="D1850">
+        <v>1</v>
+      </c>
+      <c r="E1850">
+        <v>0</v>
+      </c>
+      <c r="F1850">
+        <v>6</v>
+      </c>
+      <c r="G1850">
+        <v>6</v>
+      </c>
+      <c r="H1850">
+        <v>6</v>
+      </c>
+      <c r="I1850">
+        <v>0</v>
+      </c>
+      <c r="J1850">
+        <v>0</v>
+      </c>
+      <c r="K1850">
+        <v>66.67</v>
+      </c>
+      <c r="L1850">
+        <v>9</v>
+      </c>
+      <c r="M1850">
+        <v>3</v>
+      </c>
+      <c r="N1850">
+        <v>0</v>
+      </c>
+      <c r="O1850">
+        <v>0</v>
+      </c>
+      <c r="P1850">
+        <v>5.83</v>
+      </c>
+      <c r="Q1850">
+        <v>0</v>
+      </c>
+      <c r="R1850">
+        <v>0</v>
+      </c>
+      <c r="S1850">
+        <v>0</v>
+      </c>
+      <c r="T1850">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1851" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1851">
+        <v>1</v>
+      </c>
+      <c r="D1851">
+        <v>1</v>
+      </c>
+      <c r="E1851">
+        <v>0</v>
+      </c>
+      <c r="F1851">
+        <v>1</v>
+      </c>
+      <c r="G1851">
+        <v>1</v>
+      </c>
+      <c r="H1851">
+        <v>1</v>
+      </c>
+      <c r="I1851">
+        <v>0</v>
+      </c>
+      <c r="J1851">
+        <v>0</v>
+      </c>
+      <c r="K1851">
+        <v>50</v>
+      </c>
+      <c r="L1851">
+        <v>2</v>
+      </c>
+      <c r="M1851">
+        <v>1</v>
+      </c>
+      <c r="N1851">
+        <v>0</v>
+      </c>
+      <c r="O1851">
+        <v>0</v>
+      </c>
+      <c r="P1851">
+        <v>0.97</v>
+      </c>
+      <c r="Q1851">
+        <v>0</v>
+      </c>
+      <c r="R1851">
+        <v>0</v>
+      </c>
+      <c r="S1851">
+        <v>0</v>
+      </c>
+      <c r="T1851">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1852" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1852">
+        <v>1</v>
+      </c>
+      <c r="D1852">
+        <v>1</v>
+      </c>
+      <c r="E1852">
+        <v>0</v>
+      </c>
+      <c r="F1852">
+        <v>39</v>
+      </c>
+      <c r="G1852">
+        <v>39</v>
+      </c>
+      <c r="H1852">
+        <v>39</v>
+      </c>
+      <c r="I1852">
+        <v>0</v>
+      </c>
+      <c r="J1852">
+        <v>0</v>
+      </c>
+      <c r="K1852">
+        <v>88.64</v>
+      </c>
+      <c r="L1852">
+        <v>44</v>
+      </c>
+      <c r="M1852">
+        <v>20</v>
+      </c>
+      <c r="N1852">
+        <v>5</v>
+      </c>
+      <c r="O1852">
+        <v>0</v>
+      </c>
+      <c r="P1852">
+        <v>37.86</v>
+      </c>
+      <c r="Q1852">
+        <v>0</v>
+      </c>
+      <c r="R1852">
+        <v>0</v>
+      </c>
+      <c r="S1852">
+        <v>0</v>
+      </c>
+      <c r="T1852">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1853" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>315</v>
+      </c>
+      <c r="C1853">
+        <v>1</v>
+      </c>
+      <c r="D1853">
+        <v>1</v>
+      </c>
+      <c r="E1853">
+        <v>0</v>
+      </c>
+      <c r="F1853">
+        <v>13</v>
+      </c>
+      <c r="G1853">
+        <v>13</v>
+      </c>
+      <c r="H1853">
+        <v>13</v>
+      </c>
+      <c r="I1853">
+        <v>0</v>
+      </c>
+      <c r="J1853">
+        <v>0</v>
+      </c>
+      <c r="K1853">
+        <v>108.33</v>
+      </c>
+      <c r="L1853">
+        <v>12</v>
+      </c>
+      <c r="M1853">
+        <v>5</v>
+      </c>
+      <c r="N1853">
+        <v>1</v>
+      </c>
+      <c r="O1853">
+        <v>0</v>
+      </c>
+      <c r="P1853">
+        <v>15.29</v>
+      </c>
+      <c r="Q1853">
+        <v>0</v>
+      </c>
+      <c r="R1853">
+        <v>0</v>
+      </c>
+      <c r="S1853">
+        <v>0</v>
+      </c>
+      <c r="T1853">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1854" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>132</v>
+      </c>
+      <c r="C1854">
+        <v>1</v>
+      </c>
+      <c r="D1854">
+        <v>1</v>
+      </c>
+      <c r="E1854">
+        <v>0</v>
+      </c>
+      <c r="F1854">
+        <v>5</v>
+      </c>
+      <c r="G1854">
+        <v>5</v>
+      </c>
+      <c r="H1854">
+        <v>5</v>
+      </c>
+      <c r="I1854">
+        <v>0</v>
+      </c>
+      <c r="J1854">
+        <v>0</v>
+      </c>
+      <c r="K1854">
+        <v>100</v>
+      </c>
+      <c r="L1854">
+        <v>5</v>
+      </c>
+      <c r="M1854">
+        <v>3</v>
+      </c>
+      <c r="N1854">
+        <v>1</v>
+      </c>
+      <c r="O1854">
+        <v>0</v>
+      </c>
+      <c r="P1854">
+        <v>5.88</v>
+      </c>
+      <c r="Q1854">
+        <v>0</v>
+      </c>
+      <c r="R1854">
+        <v>0</v>
+      </c>
+      <c r="S1854">
+        <v>0</v>
+      </c>
+      <c r="T1854">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1855" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1855">
+        <v>1</v>
+      </c>
+      <c r="D1855">
+        <v>1</v>
+      </c>
+      <c r="E1855">
+        <v>0</v>
+      </c>
+      <c r="F1855">
+        <v>12</v>
+      </c>
+      <c r="G1855">
+        <v>12</v>
+      </c>
+      <c r="H1855">
+        <v>12</v>
+      </c>
+      <c r="I1855">
+        <v>0</v>
+      </c>
+      <c r="J1855">
+        <v>0</v>
+      </c>
+      <c r="K1855">
+        <v>120</v>
+      </c>
+      <c r="L1855">
+        <v>10</v>
+      </c>
+      <c r="M1855">
+        <v>3</v>
+      </c>
+      <c r="N1855">
+        <v>1</v>
+      </c>
+      <c r="O1855">
+        <v>0</v>
+      </c>
+      <c r="P1855">
+        <v>14.12</v>
+      </c>
+      <c r="Q1855">
+        <v>0</v>
+      </c>
+      <c r="R1855">
+        <v>0</v>
+      </c>
+      <c r="S1855">
+        <v>0</v>
+      </c>
+      <c r="T1855">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1856" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1856">
+        <v>1</v>
+      </c>
+      <c r="D1856">
+        <v>1</v>
+      </c>
+      <c r="E1856">
+        <v>0</v>
+      </c>
+      <c r="F1856">
+        <v>33</v>
+      </c>
+      <c r="G1856">
+        <v>33</v>
+      </c>
+      <c r="H1856">
+        <v>33</v>
+      </c>
+      <c r="I1856">
+        <v>0</v>
+      </c>
+      <c r="J1856">
+        <v>0</v>
+      </c>
+      <c r="K1856">
+        <v>97.06</v>
+      </c>
+      <c r="L1856">
+        <v>34</v>
+      </c>
+      <c r="M1856">
+        <v>13</v>
+      </c>
+      <c r="N1856">
+        <v>4</v>
+      </c>
+      <c r="O1856">
+        <v>0</v>
+      </c>
+      <c r="P1856">
+        <v>32.04</v>
+      </c>
+      <c r="Q1856">
+        <v>3</v>
+      </c>
+      <c r="R1856">
+        <v>0</v>
+      </c>
+      <c r="S1856">
+        <v>0</v>
+      </c>
+      <c r="T1856">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1857" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1857">
+        <v>1</v>
+      </c>
+      <c r="D1857">
+        <v>0</v>
+      </c>
+      <c r="E1857">
+        <v>0</v>
+      </c>
+      <c r="F1857">
+        <v>0</v>
+      </c>
+      <c r="I1857">
+        <v>0</v>
+      </c>
+      <c r="J1857">
+        <v>0</v>
+      </c>
+      <c r="L1857">
+        <v>0</v>
+      </c>
+      <c r="M1857">
+        <v>0</v>
+      </c>
+      <c r="N1857">
+        <v>0</v>
+      </c>
+      <c r="O1857">
+        <v>0</v>
+      </c>
+      <c r="P1857">
+        <v>0</v>
+      </c>
+      <c r="Q1857">
+        <v>0</v>
+      </c>
+      <c r="R1857">
+        <v>0</v>
+      </c>
+      <c r="S1857">
+        <v>0</v>
+      </c>
+      <c r="T1857">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1858" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1858">
+        <v>1</v>
+      </c>
+      <c r="D1858">
+        <v>1</v>
+      </c>
+      <c r="E1858">
+        <v>1</v>
+      </c>
+      <c r="F1858">
+        <v>1</v>
+      </c>
+      <c r="H1858" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1858">
+        <v>0</v>
+      </c>
+      <c r="J1858">
+        <v>0</v>
+      </c>
+      <c r="K1858">
+        <v>10</v>
+      </c>
+      <c r="L1858">
+        <v>10</v>
+      </c>
+      <c r="M1858">
+        <v>9</v>
+      </c>
+      <c r="N1858">
+        <v>0</v>
+      </c>
+      <c r="O1858">
+        <v>0</v>
+      </c>
+      <c r="P1858">
+        <v>1.18</v>
+      </c>
+      <c r="Q1858">
+        <v>0</v>
+      </c>
+      <c r="R1858">
+        <v>0</v>
+      </c>
+      <c r="S1858">
+        <v>0</v>
+      </c>
+      <c r="T1858">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1859" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1859">
+        <v>1</v>
+      </c>
+      <c r="D1859">
+        <v>1</v>
+      </c>
+      <c r="E1859">
+        <v>1</v>
+      </c>
+      <c r="F1859">
+        <v>0</v>
+      </c>
+      <c r="H1859" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1859">
+        <v>0</v>
+      </c>
+      <c r="J1859">
+        <v>0</v>
+      </c>
+      <c r="K1859">
+        <v>0</v>
+      </c>
+      <c r="L1859">
+        <v>3</v>
+      </c>
+      <c r="M1859">
+        <v>3</v>
+      </c>
+      <c r="N1859">
+        <v>0</v>
+      </c>
+      <c r="O1859">
+        <v>0</v>
+      </c>
+      <c r="P1859">
+        <v>0</v>
+      </c>
+      <c r="Q1859">
+        <v>0</v>
+      </c>
+      <c r="R1859">
+        <v>0</v>
+      </c>
+      <c r="S1859">
+        <v>0</v>
+      </c>
+      <c r="T1859">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1860" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1860">
+        <v>1</v>
+      </c>
+      <c r="D1860">
+        <v>1</v>
+      </c>
+      <c r="E1860">
+        <v>0</v>
+      </c>
+      <c r="F1860">
+        <v>0</v>
+      </c>
+      <c r="G1860">
+        <v>0</v>
+      </c>
+      <c r="H1860">
+        <v>0</v>
+      </c>
+      <c r="I1860">
+        <v>0</v>
+      </c>
+      <c r="J1860">
+        <v>0</v>
+      </c>
+      <c r="K1860">
+        <v>0</v>
+      </c>
+      <c r="L1860">
+        <v>3</v>
+      </c>
+      <c r="M1860">
+        <v>3</v>
+      </c>
+      <c r="N1860">
+        <v>0</v>
+      </c>
+      <c r="O1860">
+        <v>0</v>
+      </c>
+      <c r="P1860">
+        <v>0</v>
+      </c>
+      <c r="Q1860">
+        <v>0</v>
+      </c>
+      <c r="R1860">
+        <v>0</v>
+      </c>
+      <c r="S1860">
+        <v>0</v>
+      </c>
+      <c r="T1860">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1861" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1861">
+        <v>1</v>
+      </c>
+      <c r="D1861">
+        <v>1</v>
+      </c>
+      <c r="E1861">
+        <v>0</v>
+      </c>
+      <c r="F1861">
+        <v>3</v>
+      </c>
+      <c r="G1861">
+        <v>3</v>
+      </c>
+      <c r="H1861">
+        <v>3</v>
+      </c>
+      <c r="I1861">
+        <v>0</v>
+      </c>
+      <c r="J1861">
+        <v>0</v>
+      </c>
+      <c r="K1861">
+        <v>60</v>
+      </c>
+      <c r="L1861">
+        <v>5</v>
+      </c>
+      <c r="M1861">
+        <v>2</v>
+      </c>
+      <c r="N1861">
+        <v>0</v>
+      </c>
+      <c r="O1861">
+        <v>0</v>
+      </c>
+      <c r="P1861">
+        <v>3.53</v>
+      </c>
+      <c r="Q1861">
+        <v>0</v>
+      </c>
+      <c r="R1861">
+        <v>0</v>
+      </c>
+      <c r="S1861">
+        <v>0</v>
+      </c>
+      <c r="T1861">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1862" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1862">
+        <v>1</v>
+      </c>
+      <c r="D1862">
+        <v>1</v>
+      </c>
+      <c r="E1862">
+        <v>0</v>
+      </c>
+      <c r="F1862">
+        <v>1</v>
+      </c>
+      <c r="G1862">
+        <v>1</v>
+      </c>
+      <c r="H1862">
+        <v>1</v>
+      </c>
+      <c r="I1862">
+        <v>0</v>
+      </c>
+      <c r="J1862">
+        <v>0</v>
+      </c>
+      <c r="K1862">
+        <v>20</v>
+      </c>
+      <c r="L1862">
+        <v>5</v>
+      </c>
+      <c r="M1862">
+        <v>4</v>
+      </c>
+      <c r="N1862">
+        <v>0</v>
+      </c>
+      <c r="O1862">
+        <v>0</v>
+      </c>
+      <c r="P1862">
+        <v>1.18</v>
+      </c>
+      <c r="Q1862">
+        <v>0</v>
+      </c>
+      <c r="R1862">
+        <v>0</v>
+      </c>
+      <c r="S1862">
+        <v>0</v>
+      </c>
+      <c r="T1862">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1863" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1863">
+        <v>1</v>
+      </c>
+      <c r="D1863">
+        <v>1</v>
+      </c>
+      <c r="E1863">
+        <v>0</v>
+      </c>
+      <c r="F1863">
+        <v>3</v>
+      </c>
+      <c r="G1863">
+        <v>3</v>
+      </c>
+      <c r="H1863">
+        <v>3</v>
+      </c>
+      <c r="I1863">
+        <v>0</v>
+      </c>
+      <c r="J1863">
+        <v>0</v>
+      </c>
+      <c r="K1863">
+        <v>37.5</v>
+      </c>
+      <c r="L1863">
+        <v>8</v>
+      </c>
+      <c r="M1863">
+        <v>5</v>
+      </c>
+      <c r="N1863">
+        <v>0</v>
+      </c>
+      <c r="O1863">
+        <v>0</v>
+      </c>
+      <c r="P1863">
+        <v>3.53</v>
+      </c>
+      <c r="Q1863">
+        <v>0</v>
+      </c>
+      <c r="R1863">
+        <v>0</v>
+      </c>
+      <c r="S1863">
+        <v>0</v>
+      </c>
+      <c r="T1863">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1864" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1864">
+        <v>1</v>
+      </c>
+      <c r="D1864">
+        <v>1</v>
+      </c>
+      <c r="E1864">
+        <v>0</v>
+      </c>
+      <c r="F1864">
+        <v>22</v>
+      </c>
+      <c r="G1864">
+        <v>22</v>
+      </c>
+      <c r="H1864">
+        <v>22</v>
+      </c>
+      <c r="I1864">
+        <v>0</v>
+      </c>
+      <c r="J1864">
+        <v>0</v>
+      </c>
+      <c r="K1864">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="L1864">
+        <v>34</v>
+      </c>
+      <c r="M1864">
+        <v>23</v>
+      </c>
+      <c r="N1864">
+        <v>3</v>
+      </c>
+      <c r="O1864">
+        <v>0</v>
+      </c>
+      <c r="P1864">
+        <v>25.88</v>
+      </c>
+      <c r="Q1864">
+        <v>0</v>
+      </c>
+      <c r="R1864">
+        <v>0</v>
+      </c>
+      <c r="S1864">
+        <v>0</v>
+      </c>
+      <c r="T1864">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1865" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>496</v>
+      </c>
+      <c r="C1865">
+        <v>1</v>
+      </c>
+      <c r="D1865">
+        <v>1</v>
+      </c>
+      <c r="E1865">
+        <v>0</v>
+      </c>
+      <c r="F1865">
+        <v>0</v>
+      </c>
+      <c r="G1865">
+        <v>0</v>
+      </c>
+      <c r="H1865">
+        <v>0</v>
+      </c>
+      <c r="I1865">
+        <v>0</v>
+      </c>
+      <c r="J1865">
+        <v>0</v>
+      </c>
+      <c r="K1865">
+        <v>0</v>
+      </c>
+      <c r="L1865">
+        <v>3</v>
+      </c>
+      <c r="M1865">
+        <v>3</v>
+      </c>
+      <c r="N1865">
+        <v>0</v>
+      </c>
+      <c r="O1865">
+        <v>0</v>
+      </c>
+      <c r="P1865">
+        <v>0</v>
+      </c>
+      <c r="Q1865">
+        <v>0</v>
+      </c>
+      <c r="R1865">
+        <v>0</v>
+      </c>
+      <c r="S1865">
+        <v>0</v>
+      </c>
+      <c r="T1865">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1866" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1866">
+        <v>1</v>
+      </c>
+      <c r="D1866">
+        <v>1</v>
+      </c>
+      <c r="E1866">
+        <v>0</v>
+      </c>
+      <c r="F1866">
+        <v>2</v>
+      </c>
+      <c r="G1866">
+        <v>2</v>
+      </c>
+      <c r="H1866">
+        <v>2</v>
+      </c>
+      <c r="I1866">
+        <v>0</v>
+      </c>
+      <c r="J1866">
+        <v>0</v>
+      </c>
+      <c r="K1866">
+        <v>22.22</v>
+      </c>
+      <c r="L1866">
+        <v>9</v>
+      </c>
+      <c r="M1866">
+        <v>7</v>
+      </c>
+      <c r="N1866">
+        <v>0</v>
+      </c>
+      <c r="O1866">
+        <v>0</v>
+      </c>
+      <c r="P1866">
+        <v>2.35</v>
+      </c>
+      <c r="Q1866">
+        <v>0</v>
+      </c>
+      <c r="R1866">
+        <v>0</v>
+      </c>
+      <c r="S1866">
+        <v>0</v>
+      </c>
+      <c r="T1866">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1867" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1867">
+        <v>1</v>
+      </c>
+      <c r="D1867">
+        <v>1</v>
+      </c>
+      <c r="E1867">
+        <v>0</v>
+      </c>
+      <c r="F1867">
+        <v>2</v>
+      </c>
+      <c r="G1867">
+        <v>2</v>
+      </c>
+      <c r="H1867">
+        <v>2</v>
+      </c>
+      <c r="I1867">
+        <v>0</v>
+      </c>
+      <c r="J1867">
+        <v>0</v>
+      </c>
+      <c r="K1867">
+        <v>25</v>
+      </c>
+      <c r="L1867">
+        <v>8</v>
+      </c>
+      <c r="M1867">
+        <v>6</v>
+      </c>
+      <c r="N1867">
+        <v>0</v>
+      </c>
+      <c r="O1867">
+        <v>0</v>
+      </c>
+      <c r="P1867">
+        <v>2.35</v>
+      </c>
+      <c r="Q1867">
+        <v>0</v>
+      </c>
+      <c r="R1867">
+        <v>0</v>
+      </c>
+      <c r="S1867">
+        <v>0</v>
+      </c>
+      <c r="T1867">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1868" t="s">
+        <v>495</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1868">
+        <v>1</v>
+      </c>
+      <c r="D1868">
+        <v>1</v>
+      </c>
+      <c r="E1868">
+        <v>0</v>
+      </c>
+      <c r="F1868">
+        <v>1</v>
+      </c>
+      <c r="G1868">
+        <v>1</v>
+      </c>
+      <c r="H1868">
+        <v>1</v>
+      </c>
+      <c r="I1868">
+        <v>0</v>
+      </c>
+      <c r="J1868">
+        <v>0</v>
+      </c>
+      <c r="K1868">
+        <v>16.670000000000002</v>
+      </c>
+      <c r="L1868">
+        <v>6</v>
+      </c>
+      <c r="M1868">
+        <v>5</v>
+      </c>
+      <c r="N1868">
+        <v>0</v>
+      </c>
+      <c r="O1868">
+        <v>0</v>
+      </c>
+      <c r="P1868">
+        <v>1.18</v>
+      </c>
+      <c r="Q1868">
+        <v>0</v>
+      </c>
+      <c r="R1868">
+        <v>1</v>
+      </c>
+      <c r="S1868">
+        <v>1</v>
+      </c>
+      <c r="T1868">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1869" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>374</v>
+      </c>
+      <c r="C1869">
+        <v>1</v>
+      </c>
+      <c r="D1869">
+        <v>1</v>
+      </c>
+      <c r="E1869">
+        <v>1</v>
+      </c>
+      <c r="F1869">
+        <v>50</v>
+      </c>
+      <c r="H1869" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1869">
+        <v>1</v>
+      </c>
+      <c r="J1869">
+        <v>0</v>
+      </c>
+      <c r="K1869">
+        <v>121.95</v>
+      </c>
+      <c r="L1869">
+        <v>41</v>
+      </c>
+      <c r="M1869">
+        <v>10</v>
+      </c>
+      <c r="N1869">
+        <v>5</v>
+      </c>
+      <c r="O1869">
+        <v>0</v>
+      </c>
+      <c r="P1869">
+        <v>41.32</v>
+      </c>
+      <c r="Q1869">
+        <v>0</v>
+      </c>
+      <c r="R1869">
+        <v>0</v>
+      </c>
+      <c r="S1869">
+        <v>0</v>
+      </c>
+      <c r="T1869">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1870" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>498</v>
+      </c>
+      <c r="C1870">
+        <v>1</v>
+      </c>
+      <c r="D1870">
+        <v>0</v>
+      </c>
+      <c r="E1870">
+        <v>0</v>
+      </c>
+      <c r="F1870">
+        <v>0</v>
+      </c>
+      <c r="I1870">
+        <v>0</v>
+      </c>
+      <c r="J1870">
+        <v>0</v>
+      </c>
+      <c r="L1870">
+        <v>0</v>
+      </c>
+      <c r="M1870">
+        <v>0</v>
+      </c>
+      <c r="N1870">
+        <v>0</v>
+      </c>
+      <c r="O1870">
+        <v>0</v>
+      </c>
+      <c r="P1870">
+        <v>0</v>
+      </c>
+      <c r="Q1870">
+        <v>0</v>
+      </c>
+      <c r="R1870">
+        <v>0</v>
+      </c>
+      <c r="S1870">
+        <v>0</v>
+      </c>
+      <c r="T1870">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1871" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>313</v>
+      </c>
+      <c r="C1871">
+        <v>1</v>
+      </c>
+      <c r="D1871">
+        <v>1</v>
+      </c>
+      <c r="E1871">
+        <v>1</v>
+      </c>
+      <c r="F1871">
+        <v>4</v>
+      </c>
+      <c r="H1871" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1871">
+        <v>0</v>
+      </c>
+      <c r="J1871">
+        <v>0</v>
+      </c>
+      <c r="K1871">
+        <v>57.14</v>
+      </c>
+      <c r="L1871">
+        <v>7</v>
+      </c>
+      <c r="M1871">
+        <v>4</v>
+      </c>
+      <c r="N1871">
+        <v>0</v>
+      </c>
+      <c r="O1871">
+        <v>0</v>
+      </c>
+      <c r="P1871">
+        <v>3.31</v>
+      </c>
+      <c r="Q1871">
+        <v>0</v>
+      </c>
+      <c r="R1871">
+        <v>0</v>
+      </c>
+      <c r="S1871">
+        <v>0</v>
+      </c>
+      <c r="T1871">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1872" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1872" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1872">
+        <v>1</v>
+      </c>
+      <c r="D1872">
+        <v>1</v>
+      </c>
+      <c r="E1872">
+        <v>0</v>
+      </c>
+      <c r="F1872">
+        <v>2</v>
+      </c>
+      <c r="G1872">
+        <v>2</v>
+      </c>
+      <c r="H1872">
+        <v>2</v>
+      </c>
+      <c r="I1872">
+        <v>0</v>
+      </c>
+      <c r="J1872">
+        <v>0</v>
+      </c>
+      <c r="K1872">
+        <v>40</v>
+      </c>
+      <c r="L1872">
+        <v>5</v>
+      </c>
+      <c r="M1872">
+        <v>3</v>
+      </c>
+      <c r="N1872">
+        <v>0</v>
+      </c>
+      <c r="O1872">
+        <v>0</v>
+      </c>
+      <c r="P1872">
+        <v>1.65</v>
+      </c>
+      <c r="Q1872">
+        <v>0</v>
+      </c>
+      <c r="R1872">
+        <v>0</v>
+      </c>
+      <c r="S1872">
+        <v>0</v>
+      </c>
+      <c r="T1872">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1873" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1873" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1873">
+        <v>1</v>
+      </c>
+      <c r="D1873">
+        <v>0</v>
+      </c>
+      <c r="E1873">
+        <v>0</v>
+      </c>
+      <c r="F1873">
+        <v>0</v>
+      </c>
+      <c r="I1873">
+        <v>0</v>
+      </c>
+      <c r="J1873">
+        <v>0</v>
+      </c>
+      <c r="L1873">
+        <v>0</v>
+      </c>
+      <c r="M1873">
+        <v>0</v>
+      </c>
+      <c r="N1873">
+        <v>0</v>
+      </c>
+      <c r="O1873">
+        <v>0</v>
+      </c>
+      <c r="P1873">
+        <v>0</v>
+      </c>
+      <c r="Q1873">
+        <v>0</v>
+      </c>
+      <c r="R1873">
+        <v>0</v>
+      </c>
+      <c r="S1873">
+        <v>0</v>
+      </c>
+      <c r="T1873">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1874" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1874" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1874">
+        <v>1</v>
+      </c>
+      <c r="D1874">
+        <v>1</v>
+      </c>
+      <c r="E1874">
+        <v>1</v>
+      </c>
+      <c r="F1874">
+        <v>37</v>
+      </c>
+      <c r="H1874" t="s">
+        <v>392</v>
+      </c>
+      <c r="I1874">
+        <v>0</v>
+      </c>
+      <c r="J1874">
+        <v>0</v>
+      </c>
+      <c r="K1874">
+        <v>88.1</v>
+      </c>
+      <c r="L1874">
+        <v>42</v>
+      </c>
+      <c r="M1874">
+        <v>19</v>
+      </c>
+      <c r="N1874">
+        <v>4</v>
+      </c>
+      <c r="O1874">
+        <v>0</v>
+      </c>
+      <c r="P1874">
+        <v>30.33</v>
+      </c>
+      <c r="Q1874">
+        <v>0</v>
+      </c>
+      <c r="R1874">
+        <v>1</v>
+      </c>
+      <c r="S1874">
+        <v>0</v>
+      </c>
+      <c r="T1874">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1875" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1875" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1875">
+        <v>1</v>
+      </c>
+      <c r="D1875">
+        <v>1</v>
+      </c>
+      <c r="E1875">
+        <v>0</v>
+      </c>
+      <c r="F1875">
+        <v>8</v>
+      </c>
+      <c r="G1875">
+        <v>8</v>
+      </c>
+      <c r="H1875">
+        <v>8</v>
+      </c>
+      <c r="I1875">
+        <v>0</v>
+      </c>
+      <c r="J1875">
+        <v>0</v>
+      </c>
+      <c r="K1875">
+        <v>88.89</v>
+      </c>
+      <c r="L1875">
+        <v>9</v>
+      </c>
+      <c r="M1875">
+        <v>4</v>
+      </c>
+      <c r="N1875">
+        <v>1</v>
+      </c>
+      <c r="O1875">
+        <v>0</v>
+      </c>
+      <c r="P1875">
+        <v>6.56</v>
+      </c>
+      <c r="Q1875">
+        <v>0</v>
+      </c>
+      <c r="R1875">
+        <v>0</v>
+      </c>
+      <c r="S1875">
+        <v>0</v>
+      </c>
+      <c r="T1875">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1876" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1876" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1876">
+        <v>1</v>
+      </c>
+      <c r="D1876">
+        <v>1</v>
+      </c>
+      <c r="E1876">
+        <v>0</v>
+      </c>
+      <c r="F1876">
+        <v>5</v>
+      </c>
+      <c r="G1876">
+        <v>5</v>
+      </c>
+      <c r="H1876">
+        <v>5</v>
+      </c>
+      <c r="I1876">
+        <v>0</v>
+      </c>
+      <c r="J1876">
+        <v>0</v>
+      </c>
+      <c r="K1876">
+        <v>55.56</v>
+      </c>
+      <c r="L1876">
+        <v>9</v>
+      </c>
+      <c r="M1876">
+        <v>5</v>
+      </c>
+      <c r="N1876">
+        <v>0</v>
+      </c>
+      <c r="O1876">
+        <v>0</v>
+      </c>
+      <c r="P1876">
+        <v>4.13</v>
+      </c>
+      <c r="Q1876">
+        <v>0</v>
+      </c>
+      <c r="R1876">
+        <v>0</v>
+      </c>
+      <c r="S1876">
+        <v>0</v>
+      </c>
+      <c r="T1876">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1877" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1877" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1877">
+        <v>1</v>
+      </c>
+      <c r="D1877">
+        <v>1</v>
+      </c>
+      <c r="E1877">
+        <v>0</v>
+      </c>
+      <c r="F1877">
+        <v>0</v>
+      </c>
+      <c r="G1877">
+        <v>0</v>
+      </c>
+      <c r="H1877">
+        <v>0</v>
+      </c>
+      <c r="I1877">
+        <v>0</v>
+      </c>
+      <c r="J1877">
+        <v>0</v>
+      </c>
+      <c r="K1877">
+        <v>0</v>
+      </c>
+      <c r="L1877">
+        <v>1</v>
+      </c>
+      <c r="M1877">
+        <v>1</v>
+      </c>
+      <c r="N1877">
+        <v>0</v>
+      </c>
+      <c r="O1877">
+        <v>0</v>
+      </c>
+      <c r="P1877">
+        <v>0</v>
+      </c>
+      <c r="Q1877">
+        <v>2</v>
+      </c>
+      <c r="R1877">
+        <v>0</v>
+      </c>
+      <c r="S1877">
+        <v>0</v>
+      </c>
+      <c r="T1877">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1878" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1878" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1878">
+        <v>1</v>
+      </c>
+      <c r="D1878">
+        <v>1</v>
+      </c>
+      <c r="E1878">
+        <v>1</v>
+      </c>
+      <c r="F1878">
+        <v>28</v>
+      </c>
+      <c r="H1878" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1878">
+        <v>0</v>
+      </c>
+      <c r="J1878">
+        <v>0</v>
+      </c>
+      <c r="K1878">
+        <v>121.74</v>
+      </c>
+      <c r="L1878">
+        <v>23</v>
+      </c>
+      <c r="M1878">
+        <v>10</v>
+      </c>
+      <c r="N1878">
+        <v>3</v>
+      </c>
+      <c r="O1878">
+        <v>1</v>
+      </c>
+      <c r="P1878">
+        <v>22.95</v>
+      </c>
+      <c r="Q1878">
+        <v>0</v>
+      </c>
+      <c r="R1878">
+        <v>0</v>
+      </c>
+      <c r="S1878">
+        <v>0</v>
+      </c>
+      <c r="T1878">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1879" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1879" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1879">
+        <v>1</v>
+      </c>
+      <c r="D1879">
+        <v>1</v>
+      </c>
+      <c r="E1879">
+        <v>0</v>
+      </c>
+      <c r="F1879">
+        <v>20</v>
+      </c>
+      <c r="G1879">
+        <v>20</v>
+      </c>
+      <c r="H1879">
+        <v>20</v>
+      </c>
+      <c r="I1879">
+        <v>0</v>
+      </c>
+      <c r="J1879">
+        <v>0</v>
+      </c>
+      <c r="K1879">
+        <v>90.91</v>
+      </c>
+      <c r="L1879">
+        <v>22</v>
+      </c>
+      <c r="M1879">
+        <v>13</v>
+      </c>
+      <c r="N1879">
+        <v>2</v>
+      </c>
+      <c r="O1879">
+        <v>0</v>
+      </c>
+      <c r="P1879">
+        <v>16.39</v>
+      </c>
+      <c r="Q1879">
+        <v>1</v>
+      </c>
+      <c r="R1879">
+        <v>0</v>
+      </c>
+      <c r="S1879">
+        <v>0</v>
+      </c>
+      <c r="T1879">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1880" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1880" t="s">
+        <v>319</v>
+      </c>
+      <c r="C1880">
+        <v>1</v>
+      </c>
+      <c r="D1880">
+        <v>1</v>
+      </c>
+      <c r="E1880">
+        <v>0</v>
+      </c>
+      <c r="F1880">
+        <v>8</v>
+      </c>
+      <c r="G1880">
+        <v>8</v>
+      </c>
+      <c r="H1880">
+        <v>8</v>
+      </c>
+      <c r="I1880">
+        <v>0</v>
+      </c>
+      <c r="J1880">
+        <v>0</v>
+      </c>
+      <c r="K1880">
+        <v>80</v>
+      </c>
+      <c r="L1880">
+        <v>10</v>
+      </c>
+      <c r="M1880">
+        <v>5</v>
+      </c>
+      <c r="N1880">
+        <v>1</v>
+      </c>
+      <c r="O1880">
+        <v>0</v>
+      </c>
+      <c r="P1880">
+        <v>6.61</v>
+      </c>
+      <c r="Q1880">
+        <v>0</v>
+      </c>
+      <c r="R1880">
+        <v>0</v>
+      </c>
+      <c r="S1880">
+        <v>0</v>
+      </c>
+      <c r="T1880">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1881" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1881" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1881">
+        <v>1</v>
+      </c>
+      <c r="D1881">
+        <v>0</v>
+      </c>
+      <c r="E1881">
+        <v>0</v>
+      </c>
+      <c r="F1881">
+        <v>0</v>
+      </c>
+      <c r="I1881">
+        <v>0</v>
+      </c>
+      <c r="J1881">
+        <v>0</v>
+      </c>
+      <c r="L1881">
+        <v>0</v>
+      </c>
+      <c r="M1881">
+        <v>0</v>
+      </c>
+      <c r="N1881">
+        <v>0</v>
+      </c>
+      <c r="O1881">
+        <v>0</v>
+      </c>
+      <c r="P1881">
+        <v>0</v>
+      </c>
+      <c r="Q1881">
+        <v>0</v>
+      </c>
+      <c r="R1881">
+        <v>0</v>
+      </c>
+      <c r="S1881">
+        <v>0</v>
+      </c>
+      <c r="T1881">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1882" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1882" t="s">
+        <v>317</v>
+      </c>
+      <c r="C1882">
+        <v>1</v>
+      </c>
+      <c r="D1882">
+        <v>1</v>
+      </c>
+      <c r="E1882">
+        <v>0</v>
+      </c>
+      <c r="F1882">
+        <v>8</v>
+      </c>
+      <c r="G1882">
+        <v>8</v>
+      </c>
+      <c r="H1882">
+        <v>8</v>
+      </c>
+      <c r="I1882">
+        <v>0</v>
+      </c>
+      <c r="J1882">
+        <v>0</v>
+      </c>
+      <c r="K1882">
+        <v>57.14</v>
+      </c>
+      <c r="L1882">
+        <v>14</v>
+      </c>
+      <c r="M1882">
+        <v>6</v>
+      </c>
+      <c r="N1882">
+        <v>0</v>
+      </c>
+      <c r="O1882">
+        <v>0</v>
+      </c>
+      <c r="P1882">
+        <v>6.61</v>
+      </c>
+      <c r="Q1882">
+        <v>0</v>
+      </c>
+      <c r="R1882">
+        <v>0</v>
+      </c>
+      <c r="S1882">
+        <v>0</v>
+      </c>
+      <c r="T1882">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1883" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1883" t="s">
+        <v>499</v>
+      </c>
+      <c r="C1883">
+        <v>1</v>
+      </c>
+      <c r="D1883">
+        <v>1</v>
+      </c>
+      <c r="E1883">
+        <v>0</v>
+      </c>
+      <c r="F1883">
+        <v>5</v>
+      </c>
+      <c r="G1883">
+        <v>5</v>
+      </c>
+      <c r="H1883">
+        <v>5</v>
+      </c>
+      <c r="I1883">
+        <v>0</v>
+      </c>
+      <c r="J1883">
+        <v>0</v>
+      </c>
+      <c r="K1883">
+        <v>100</v>
+      </c>
+      <c r="L1883">
+        <v>5</v>
+      </c>
+      <c r="M1883">
+        <v>3</v>
+      </c>
+      <c r="N1883">
+        <v>1</v>
+      </c>
+      <c r="O1883">
+        <v>0</v>
+      </c>
+      <c r="P1883">
+        <v>4.13</v>
+      </c>
+      <c r="Q1883">
+        <v>0</v>
+      </c>
+      <c r="R1883">
+        <v>0</v>
+      </c>
+      <c r="S1883">
+        <v>0</v>
+      </c>
+      <c r="T1883">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1884" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1884" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1884">
+        <v>1</v>
+      </c>
+      <c r="D1884">
+        <v>0</v>
+      </c>
+      <c r="E1884">
+        <v>0</v>
+      </c>
+      <c r="F1884">
+        <v>0</v>
+      </c>
+      <c r="I1884">
+        <v>0</v>
+      </c>
+      <c r="J1884">
+        <v>0</v>
+      </c>
+      <c r="L1884">
+        <v>0</v>
+      </c>
+      <c r="M1884">
+        <v>0</v>
+      </c>
+      <c r="N1884">
+        <v>0</v>
+      </c>
+      <c r="O1884">
+        <v>0</v>
+      </c>
+      <c r="P1884">
+        <v>0</v>
+      </c>
+      <c r="Q1884">
+        <v>1</v>
+      </c>
+      <c r="R1884">
+        <v>0</v>
+      </c>
+      <c r="S1884">
+        <v>0</v>
+      </c>
+      <c r="T1884">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1885" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1885" t="s">
+        <v>155</v>
+      </c>
+      <c r="C1885">
+        <v>1</v>
+      </c>
+      <c r="D1885">
+        <v>1</v>
+      </c>
+      <c r="E1885">
+        <v>0</v>
+      </c>
+      <c r="F1885">
+        <v>0</v>
+      </c>
+      <c r="G1885">
+        <v>0</v>
+      </c>
+      <c r="H1885">
+        <v>0</v>
+      </c>
+      <c r="I1885">
+        <v>0</v>
+      </c>
+      <c r="J1885">
+        <v>0</v>
+      </c>
+      <c r="K1885">
+        <v>0</v>
+      </c>
+      <c r="L1885">
+        <v>3</v>
+      </c>
+      <c r="M1885">
+        <v>3</v>
+      </c>
+      <c r="N1885">
+        <v>0</v>
+      </c>
+      <c r="O1885">
+        <v>0</v>
+      </c>
+      <c r="P1885">
+        <v>0</v>
+      </c>
+      <c r="Q1885">
+        <v>0</v>
+      </c>
+      <c r="R1885">
+        <v>0</v>
+      </c>
+      <c r="S1885">
+        <v>0</v>
+      </c>
+      <c r="T1885">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1886" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1886" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1886">
+        <v>1</v>
+      </c>
+      <c r="D1886">
+        <v>1</v>
+      </c>
+      <c r="E1886">
+        <v>0</v>
+      </c>
+      <c r="F1886">
+        <v>3</v>
+      </c>
+      <c r="G1886">
+        <v>3</v>
+      </c>
+      <c r="H1886">
+        <v>3</v>
+      </c>
+      <c r="I1886">
+        <v>0</v>
+      </c>
+      <c r="J1886">
+        <v>0</v>
+      </c>
+      <c r="K1886">
+        <v>42.86</v>
+      </c>
+      <c r="L1886">
+        <v>7</v>
+      </c>
+      <c r="M1886">
+        <v>4</v>
+      </c>
+      <c r="N1886">
+        <v>0</v>
+      </c>
+      <c r="O1886">
+        <v>0</v>
+      </c>
+      <c r="P1886">
+        <v>2.46</v>
+      </c>
+      <c r="Q1886">
+        <v>0</v>
+      </c>
+      <c r="R1886">
+        <v>0</v>
+      </c>
+      <c r="S1886">
+        <v>0</v>
+      </c>
+      <c r="T1886">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1887" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1887" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1887">
+        <v>1</v>
+      </c>
+      <c r="D1887">
+        <v>0</v>
+      </c>
+      <c r="E1887">
+        <v>0</v>
+      </c>
+      <c r="F1887">
+        <v>0</v>
+      </c>
+      <c r="I1887">
+        <v>0</v>
+      </c>
+      <c r="J1887">
+        <v>0</v>
+      </c>
+      <c r="L1887">
+        <v>0</v>
+      </c>
+      <c r="M1887">
+        <v>0</v>
+      </c>
+      <c r="N1887">
+        <v>0</v>
+      </c>
+      <c r="O1887">
+        <v>0</v>
+      </c>
+      <c r="P1887">
+        <v>0</v>
+      </c>
+      <c r="Q1887">
+        <v>0</v>
+      </c>
+      <c r="R1887">
+        <v>0</v>
+      </c>
+      <c r="S1887">
+        <v>0</v>
+      </c>
+      <c r="T1887">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1888" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1888" t="s">
+        <v>318</v>
+      </c>
+      <c r="C1888">
+        <v>1</v>
+      </c>
+      <c r="D1888">
+        <v>1</v>
+      </c>
+      <c r="E1888">
+        <v>0</v>
+      </c>
+      <c r="F1888">
+        <v>13</v>
+      </c>
+      <c r="G1888">
+        <v>13</v>
+      </c>
+      <c r="H1888">
+        <v>13</v>
+      </c>
+      <c r="I1888">
+        <v>0</v>
+      </c>
+      <c r="J1888">
+        <v>0</v>
+      </c>
+      <c r="K1888">
+        <v>86.67</v>
+      </c>
+      <c r="L1888">
+        <v>15</v>
+      </c>
+      <c r="M1888">
+        <v>6</v>
+      </c>
+      <c r="N1888">
+        <v>0</v>
+      </c>
+      <c r="O1888">
+        <v>0</v>
+      </c>
+      <c r="P1888">
+        <v>10.74</v>
+      </c>
+      <c r="Q1888">
+        <v>0</v>
+      </c>
+      <c r="R1888">
+        <v>0</v>
+      </c>
+      <c r="S1888">
+        <v>0</v>
+      </c>
+      <c r="T1888">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1889" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1889" t="s">
+        <v>139</v>
+      </c>
+      <c r="C1889">
+        <v>1</v>
+      </c>
+      <c r="D1889">
+        <v>1</v>
+      </c>
+      <c r="E1889">
+        <v>0</v>
+      </c>
+      <c r="F1889">
+        <v>1</v>
+      </c>
+      <c r="G1889">
+        <v>1</v>
+      </c>
+      <c r="H1889">
+        <v>1</v>
+      </c>
+      <c r="I1889">
+        <v>0</v>
+      </c>
+      <c r="J1889">
+        <v>0</v>
+      </c>
+      <c r="K1889">
+        <v>25</v>
+      </c>
+      <c r="L1889">
+        <v>4</v>
+      </c>
+      <c r="M1889">
+        <v>3</v>
+      </c>
+      <c r="N1889">
+        <v>0</v>
+      </c>
+      <c r="O1889">
+        <v>0</v>
+      </c>
+      <c r="P1889">
+        <v>0.83</v>
+      </c>
+      <c r="Q1889">
+        <v>0</v>
+      </c>
+      <c r="R1889">
+        <v>0</v>
+      </c>
+      <c r="S1889">
+        <v>0</v>
+      </c>
+      <c r="T1889">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1890" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1890" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1890">
+        <v>1</v>
+      </c>
+      <c r="D1890">
+        <v>1</v>
+      </c>
+      <c r="E1890">
+        <v>0</v>
+      </c>
+      <c r="F1890">
+        <v>6</v>
+      </c>
+      <c r="G1890">
+        <v>6</v>
+      </c>
+      <c r="H1890">
+        <v>6</v>
+      </c>
+      <c r="I1890">
+        <v>0</v>
+      </c>
+      <c r="J1890">
+        <v>0</v>
+      </c>
+      <c r="K1890">
+        <v>85.71</v>
+      </c>
+      <c r="L1890">
+        <v>7</v>
+      </c>
+      <c r="M1890">
+        <v>5</v>
+      </c>
+      <c r="N1890">
+        <v>1</v>
+      </c>
+      <c r="O1890">
+        <v>0</v>
+      </c>
+      <c r="P1890">
+        <v>4.92</v>
+      </c>
+      <c r="Q1890">
+        <v>0</v>
+      </c>
+      <c r="R1890">
+        <v>0</v>
+      </c>
+      <c r="S1890">
+        <v>0</v>
+      </c>
+      <c r="T1890">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4156" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4203" uniqueCount="503">
   <si>
     <t>Group</t>
   </si>
@@ -1520,6 +1520,15 @@
   <si>
     <t>Jade Neely</t>
   </si>
+  <si>
+    <t>Waringstown Women 1st XI v North Down Women 1st XI, The Lawn - 9 August 2026</t>
+  </si>
+  <si>
+    <t>Sophie Bourne</t>
+  </si>
+  <si>
+    <t>Cara Murray</t>
+  </si>
 </sst>
 </file>
 
@@ -2326,7 +2335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1890"/>
+  <dimension ref="A1:T1912"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -113051,6 +113060,1205 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1891" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1891" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1891" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1891">
+        <v>1</v>
+      </c>
+      <c r="D1891">
+        <v>0</v>
+      </c>
+      <c r="E1891">
+        <v>0</v>
+      </c>
+      <c r="F1891">
+        <v>0</v>
+      </c>
+      <c r="I1891">
+        <v>0</v>
+      </c>
+      <c r="J1891">
+        <v>0</v>
+      </c>
+      <c r="L1891">
+        <v>0</v>
+      </c>
+      <c r="M1891">
+        <v>0</v>
+      </c>
+      <c r="N1891">
+        <v>0</v>
+      </c>
+      <c r="O1891">
+        <v>0</v>
+      </c>
+      <c r="P1891">
+        <v>0</v>
+      </c>
+      <c r="Q1891">
+        <v>0</v>
+      </c>
+      <c r="R1891">
+        <v>0</v>
+      </c>
+      <c r="S1891">
+        <v>0</v>
+      </c>
+      <c r="T1891">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1892" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1892" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1892">
+        <v>1</v>
+      </c>
+      <c r="D1892">
+        <v>0</v>
+      </c>
+      <c r="E1892">
+        <v>0</v>
+      </c>
+      <c r="F1892">
+        <v>0</v>
+      </c>
+      <c r="I1892">
+        <v>0</v>
+      </c>
+      <c r="J1892">
+        <v>0</v>
+      </c>
+      <c r="L1892">
+        <v>0</v>
+      </c>
+      <c r="M1892">
+        <v>0</v>
+      </c>
+      <c r="N1892">
+        <v>0</v>
+      </c>
+      <c r="O1892">
+        <v>0</v>
+      </c>
+      <c r="P1892">
+        <v>0</v>
+      </c>
+      <c r="Q1892">
+        <v>0</v>
+      </c>
+      <c r="R1892">
+        <v>0</v>
+      </c>
+      <c r="S1892">
+        <v>0</v>
+      </c>
+      <c r="T1892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1893" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1893" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1893">
+        <v>1</v>
+      </c>
+      <c r="D1893">
+        <v>0</v>
+      </c>
+      <c r="E1893">
+        <v>0</v>
+      </c>
+      <c r="F1893">
+        <v>0</v>
+      </c>
+      <c r="I1893">
+        <v>0</v>
+      </c>
+      <c r="J1893">
+        <v>0</v>
+      </c>
+      <c r="L1893">
+        <v>0</v>
+      </c>
+      <c r="M1893">
+        <v>0</v>
+      </c>
+      <c r="N1893">
+        <v>0</v>
+      </c>
+      <c r="O1893">
+        <v>0</v>
+      </c>
+      <c r="P1893">
+        <v>0</v>
+      </c>
+      <c r="Q1893">
+        <v>0</v>
+      </c>
+      <c r="R1893">
+        <v>0</v>
+      </c>
+      <c r="S1893">
+        <v>0</v>
+      </c>
+      <c r="T1893">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1894" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1894" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1894">
+        <v>1</v>
+      </c>
+      <c r="D1894">
+        <v>0</v>
+      </c>
+      <c r="E1894">
+        <v>0</v>
+      </c>
+      <c r="F1894">
+        <v>0</v>
+      </c>
+      <c r="I1894">
+        <v>0</v>
+      </c>
+      <c r="J1894">
+        <v>0</v>
+      </c>
+      <c r="L1894">
+        <v>0</v>
+      </c>
+      <c r="M1894">
+        <v>0</v>
+      </c>
+      <c r="N1894">
+        <v>0</v>
+      </c>
+      <c r="O1894">
+        <v>0</v>
+      </c>
+      <c r="P1894">
+        <v>0</v>
+      </c>
+      <c r="Q1894">
+        <v>1</v>
+      </c>
+      <c r="R1894">
+        <v>0</v>
+      </c>
+      <c r="S1894">
+        <v>0</v>
+      </c>
+      <c r="T1894">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1895" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1895" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1895">
+        <v>1</v>
+      </c>
+      <c r="D1895">
+        <v>0</v>
+      </c>
+      <c r="E1895">
+        <v>0</v>
+      </c>
+      <c r="F1895">
+        <v>0</v>
+      </c>
+      <c r="I1895">
+        <v>0</v>
+      </c>
+      <c r="J1895">
+        <v>0</v>
+      </c>
+      <c r="L1895">
+        <v>0</v>
+      </c>
+      <c r="M1895">
+        <v>0</v>
+      </c>
+      <c r="N1895">
+        <v>0</v>
+      </c>
+      <c r="O1895">
+        <v>0</v>
+      </c>
+      <c r="P1895">
+        <v>0</v>
+      </c>
+      <c r="Q1895">
+        <v>0</v>
+      </c>
+      <c r="R1895">
+        <v>0</v>
+      </c>
+      <c r="S1895">
+        <v>0</v>
+      </c>
+      <c r="T1895">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1896" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1896" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1896">
+        <v>1</v>
+      </c>
+      <c r="D1896">
+        <v>1</v>
+      </c>
+      <c r="E1896">
+        <v>1</v>
+      </c>
+      <c r="F1896">
+        <v>0</v>
+      </c>
+      <c r="H1896" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1896">
+        <v>0</v>
+      </c>
+      <c r="J1896">
+        <v>0</v>
+      </c>
+      <c r="L1896">
+        <v>0</v>
+      </c>
+      <c r="M1896">
+        <v>0</v>
+      </c>
+      <c r="N1896">
+        <v>0</v>
+      </c>
+      <c r="O1896">
+        <v>0</v>
+      </c>
+      <c r="P1896">
+        <v>0</v>
+      </c>
+      <c r="Q1896">
+        <v>0</v>
+      </c>
+      <c r="R1896">
+        <v>0</v>
+      </c>
+      <c r="S1896">
+        <v>0</v>
+      </c>
+      <c r="T1896">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1897" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1897" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1897">
+        <v>1</v>
+      </c>
+      <c r="D1897">
+        <v>0</v>
+      </c>
+      <c r="E1897">
+        <v>0</v>
+      </c>
+      <c r="F1897">
+        <v>0</v>
+      </c>
+      <c r="I1897">
+        <v>0</v>
+      </c>
+      <c r="J1897">
+        <v>0</v>
+      </c>
+      <c r="L1897">
+        <v>0</v>
+      </c>
+      <c r="M1897">
+        <v>0</v>
+      </c>
+      <c r="N1897">
+        <v>0</v>
+      </c>
+      <c r="O1897">
+        <v>0</v>
+      </c>
+      <c r="P1897">
+        <v>0</v>
+      </c>
+      <c r="Q1897">
+        <v>0</v>
+      </c>
+      <c r="R1897">
+        <v>0</v>
+      </c>
+      <c r="S1897">
+        <v>0</v>
+      </c>
+      <c r="T1897">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1898" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1898" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1898">
+        <v>1</v>
+      </c>
+      <c r="D1898">
+        <v>0</v>
+      </c>
+      <c r="E1898">
+        <v>0</v>
+      </c>
+      <c r="F1898">
+        <v>0</v>
+      </c>
+      <c r="I1898">
+        <v>0</v>
+      </c>
+      <c r="J1898">
+        <v>0</v>
+      </c>
+      <c r="L1898">
+        <v>0</v>
+      </c>
+      <c r="M1898">
+        <v>0</v>
+      </c>
+      <c r="N1898">
+        <v>0</v>
+      </c>
+      <c r="O1898">
+        <v>0</v>
+      </c>
+      <c r="P1898">
+        <v>0</v>
+      </c>
+      <c r="Q1898">
+        <v>0</v>
+      </c>
+      <c r="R1898">
+        <v>0</v>
+      </c>
+      <c r="S1898">
+        <v>0</v>
+      </c>
+      <c r="T1898">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1899" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1899" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1899">
+        <v>1</v>
+      </c>
+      <c r="D1899">
+        <v>1</v>
+      </c>
+      <c r="E1899">
+        <v>1</v>
+      </c>
+      <c r="F1899">
+        <v>29</v>
+      </c>
+      <c r="H1899" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1899">
+        <v>0</v>
+      </c>
+      <c r="J1899">
+        <v>0</v>
+      </c>
+      <c r="K1899">
+        <v>193.33</v>
+      </c>
+      <c r="L1899">
+        <v>15</v>
+      </c>
+      <c r="M1899">
+        <v>3</v>
+      </c>
+      <c r="N1899">
+        <v>5</v>
+      </c>
+      <c r="O1899">
+        <v>0</v>
+      </c>
+      <c r="P1899">
+        <v>70.73</v>
+      </c>
+      <c r="Q1899">
+        <v>0</v>
+      </c>
+      <c r="R1899">
+        <v>0</v>
+      </c>
+      <c r="S1899">
+        <v>0</v>
+      </c>
+      <c r="T1899">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1900" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1900" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1900">
+        <v>1</v>
+      </c>
+      <c r="D1900">
+        <v>0</v>
+      </c>
+      <c r="E1900">
+        <v>0</v>
+      </c>
+      <c r="F1900">
+        <v>0</v>
+      </c>
+      <c r="I1900">
+        <v>0</v>
+      </c>
+      <c r="J1900">
+        <v>0</v>
+      </c>
+      <c r="L1900">
+        <v>0</v>
+      </c>
+      <c r="M1900">
+        <v>0</v>
+      </c>
+      <c r="N1900">
+        <v>0</v>
+      </c>
+      <c r="O1900">
+        <v>0</v>
+      </c>
+      <c r="P1900">
+        <v>0</v>
+      </c>
+      <c r="Q1900">
+        <v>0</v>
+      </c>
+      <c r="R1900">
+        <v>0</v>
+      </c>
+      <c r="S1900">
+        <v>0</v>
+      </c>
+      <c r="T1900">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1901" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1901" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1901">
+        <v>1</v>
+      </c>
+      <c r="D1901">
+        <v>1</v>
+      </c>
+      <c r="E1901">
+        <v>0</v>
+      </c>
+      <c r="F1901">
+        <v>26</v>
+      </c>
+      <c r="G1901">
+        <v>26</v>
+      </c>
+      <c r="H1901">
+        <v>26</v>
+      </c>
+      <c r="I1901">
+        <v>0</v>
+      </c>
+      <c r="J1901">
+        <v>0</v>
+      </c>
+      <c r="K1901">
+        <v>144.44</v>
+      </c>
+      <c r="L1901">
+        <v>18</v>
+      </c>
+      <c r="M1901">
+        <v>5</v>
+      </c>
+      <c r="N1901">
+        <v>3</v>
+      </c>
+      <c r="O1901">
+        <v>0</v>
+      </c>
+      <c r="P1901">
+        <v>65</v>
+      </c>
+      <c r="Q1901">
+        <v>0</v>
+      </c>
+      <c r="R1901">
+        <v>0</v>
+      </c>
+      <c r="S1901">
+        <v>0</v>
+      </c>
+      <c r="T1901">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1902" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1902" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1902">
+        <v>1</v>
+      </c>
+      <c r="D1902">
+        <v>0</v>
+      </c>
+      <c r="E1902">
+        <v>0</v>
+      </c>
+      <c r="F1902">
+        <v>0</v>
+      </c>
+      <c r="I1902">
+        <v>0</v>
+      </c>
+      <c r="J1902">
+        <v>0</v>
+      </c>
+      <c r="L1902">
+        <v>0</v>
+      </c>
+      <c r="M1902">
+        <v>0</v>
+      </c>
+      <c r="N1902">
+        <v>0</v>
+      </c>
+      <c r="O1902">
+        <v>0</v>
+      </c>
+      <c r="P1902">
+        <v>0</v>
+      </c>
+      <c r="Q1902">
+        <v>0</v>
+      </c>
+      <c r="R1902">
+        <v>0</v>
+      </c>
+      <c r="S1902">
+        <v>0</v>
+      </c>
+      <c r="T1902">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1903" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1903" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1903">
+        <v>1</v>
+      </c>
+      <c r="D1903">
+        <v>0</v>
+      </c>
+      <c r="E1903">
+        <v>0</v>
+      </c>
+      <c r="F1903">
+        <v>0</v>
+      </c>
+      <c r="I1903">
+        <v>0</v>
+      </c>
+      <c r="J1903">
+        <v>0</v>
+      </c>
+      <c r="L1903">
+        <v>0</v>
+      </c>
+      <c r="M1903">
+        <v>0</v>
+      </c>
+      <c r="N1903">
+        <v>0</v>
+      </c>
+      <c r="O1903">
+        <v>0</v>
+      </c>
+      <c r="P1903">
+        <v>0</v>
+      </c>
+      <c r="Q1903">
+        <v>0</v>
+      </c>
+      <c r="R1903">
+        <v>0</v>
+      </c>
+      <c r="S1903">
+        <v>0</v>
+      </c>
+      <c r="T1903">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1904" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1904" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1904">
+        <v>1</v>
+      </c>
+      <c r="D1904">
+        <v>0</v>
+      </c>
+      <c r="E1904">
+        <v>0</v>
+      </c>
+      <c r="F1904">
+        <v>0</v>
+      </c>
+      <c r="I1904">
+        <v>0</v>
+      </c>
+      <c r="J1904">
+        <v>0</v>
+      </c>
+      <c r="L1904">
+        <v>0</v>
+      </c>
+      <c r="M1904">
+        <v>0</v>
+      </c>
+      <c r="N1904">
+        <v>0</v>
+      </c>
+      <c r="O1904">
+        <v>0</v>
+      </c>
+      <c r="P1904">
+        <v>0</v>
+      </c>
+      <c r="Q1904">
+        <v>0</v>
+      </c>
+      <c r="R1904">
+        <v>0</v>
+      </c>
+      <c r="S1904">
+        <v>0</v>
+      </c>
+      <c r="T1904">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1905" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1905" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1905">
+        <v>1</v>
+      </c>
+      <c r="D1905">
+        <v>1</v>
+      </c>
+      <c r="E1905">
+        <v>1</v>
+      </c>
+      <c r="F1905">
+        <v>11</v>
+      </c>
+      <c r="H1905" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1905">
+        <v>0</v>
+      </c>
+      <c r="J1905">
+        <v>0</v>
+      </c>
+      <c r="K1905">
+        <v>220</v>
+      </c>
+      <c r="L1905">
+        <v>5</v>
+      </c>
+      <c r="M1905">
+        <v>1</v>
+      </c>
+      <c r="N1905">
+        <v>2</v>
+      </c>
+      <c r="O1905">
+        <v>0</v>
+      </c>
+      <c r="P1905">
+        <v>26.83</v>
+      </c>
+      <c r="Q1905">
+        <v>0</v>
+      </c>
+      <c r="R1905">
+        <v>0</v>
+      </c>
+      <c r="S1905">
+        <v>0</v>
+      </c>
+      <c r="T1905">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1906" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1906" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1906">
+        <v>1</v>
+      </c>
+      <c r="D1906">
+        <v>0</v>
+      </c>
+      <c r="E1906">
+        <v>0</v>
+      </c>
+      <c r="F1906">
+        <v>0</v>
+      </c>
+      <c r="I1906">
+        <v>0</v>
+      </c>
+      <c r="J1906">
+        <v>0</v>
+      </c>
+      <c r="L1906">
+        <v>0</v>
+      </c>
+      <c r="M1906">
+        <v>0</v>
+      </c>
+      <c r="N1906">
+        <v>0</v>
+      </c>
+      <c r="O1906">
+        <v>0</v>
+      </c>
+      <c r="P1906">
+        <v>0</v>
+      </c>
+      <c r="Q1906">
+        <v>0</v>
+      </c>
+      <c r="R1906">
+        <v>0</v>
+      </c>
+      <c r="S1906">
+        <v>0</v>
+      </c>
+      <c r="T1906">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1907" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1907" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1907">
+        <v>1</v>
+      </c>
+      <c r="D1907">
+        <v>0</v>
+      </c>
+      <c r="E1907">
+        <v>0</v>
+      </c>
+      <c r="F1907">
+        <v>0</v>
+      </c>
+      <c r="I1907">
+        <v>0</v>
+      </c>
+      <c r="J1907">
+        <v>0</v>
+      </c>
+      <c r="L1907">
+        <v>0</v>
+      </c>
+      <c r="M1907">
+        <v>0</v>
+      </c>
+      <c r="N1907">
+        <v>0</v>
+      </c>
+      <c r="O1907">
+        <v>0</v>
+      </c>
+      <c r="P1907">
+        <v>0</v>
+      </c>
+      <c r="Q1907">
+        <v>0</v>
+      </c>
+      <c r="R1907">
+        <v>0</v>
+      </c>
+      <c r="S1907">
+        <v>0</v>
+      </c>
+      <c r="T1907">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1908" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1908" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1908">
+        <v>1</v>
+      </c>
+      <c r="D1908">
+        <v>0</v>
+      </c>
+      <c r="E1908">
+        <v>0</v>
+      </c>
+      <c r="F1908">
+        <v>0</v>
+      </c>
+      <c r="I1908">
+        <v>0</v>
+      </c>
+      <c r="J1908">
+        <v>0</v>
+      </c>
+      <c r="L1908">
+        <v>0</v>
+      </c>
+      <c r="M1908">
+        <v>0</v>
+      </c>
+      <c r="N1908">
+        <v>0</v>
+      </c>
+      <c r="O1908">
+        <v>0</v>
+      </c>
+      <c r="P1908">
+        <v>0</v>
+      </c>
+      <c r="Q1908">
+        <v>0</v>
+      </c>
+      <c r="R1908">
+        <v>0</v>
+      </c>
+      <c r="S1908">
+        <v>0</v>
+      </c>
+      <c r="T1908">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1909" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1909" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1909">
+        <v>1</v>
+      </c>
+      <c r="D1909">
+        <v>0</v>
+      </c>
+      <c r="E1909">
+        <v>0</v>
+      </c>
+      <c r="F1909">
+        <v>0</v>
+      </c>
+      <c r="I1909">
+        <v>0</v>
+      </c>
+      <c r="J1909">
+        <v>0</v>
+      </c>
+      <c r="L1909">
+        <v>0</v>
+      </c>
+      <c r="M1909">
+        <v>0</v>
+      </c>
+      <c r="N1909">
+        <v>0</v>
+      </c>
+      <c r="O1909">
+        <v>0</v>
+      </c>
+      <c r="P1909">
+        <v>0</v>
+      </c>
+      <c r="Q1909">
+        <v>0</v>
+      </c>
+      <c r="R1909">
+        <v>0</v>
+      </c>
+      <c r="S1909">
+        <v>0</v>
+      </c>
+      <c r="T1909">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1910" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1910" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1910">
+        <v>1</v>
+      </c>
+      <c r="D1910">
+        <v>0</v>
+      </c>
+      <c r="E1910">
+        <v>0</v>
+      </c>
+      <c r="F1910">
+        <v>0</v>
+      </c>
+      <c r="I1910">
+        <v>0</v>
+      </c>
+      <c r="J1910">
+        <v>0</v>
+      </c>
+      <c r="L1910">
+        <v>0</v>
+      </c>
+      <c r="M1910">
+        <v>0</v>
+      </c>
+      <c r="N1910">
+        <v>0</v>
+      </c>
+      <c r="O1910">
+        <v>0</v>
+      </c>
+      <c r="P1910">
+        <v>0</v>
+      </c>
+      <c r="Q1910">
+        <v>0</v>
+      </c>
+      <c r="R1910">
+        <v>0</v>
+      </c>
+      <c r="S1910">
+        <v>0</v>
+      </c>
+      <c r="T1910">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1911" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1911" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1911">
+        <v>1</v>
+      </c>
+      <c r="D1911">
+        <v>0</v>
+      </c>
+      <c r="E1911">
+        <v>0</v>
+      </c>
+      <c r="F1911">
+        <v>0</v>
+      </c>
+      <c r="I1911">
+        <v>0</v>
+      </c>
+      <c r="J1911">
+        <v>0</v>
+      </c>
+      <c r="L1911">
+        <v>0</v>
+      </c>
+      <c r="M1911">
+        <v>0</v>
+      </c>
+      <c r="N1911">
+        <v>0</v>
+      </c>
+      <c r="O1911">
+        <v>0</v>
+      </c>
+      <c r="P1911">
+        <v>0</v>
+      </c>
+      <c r="Q1911">
+        <v>0</v>
+      </c>
+      <c r="R1911">
+        <v>0</v>
+      </c>
+      <c r="S1911">
+        <v>0</v>
+      </c>
+      <c r="T1911">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1912" t="s">
+        <v>500</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1912">
+        <v>1</v>
+      </c>
+      <c r="D1912">
+        <v>1</v>
+      </c>
+      <c r="E1912">
+        <v>0</v>
+      </c>
+      <c r="F1912">
+        <v>11</v>
+      </c>
+      <c r="G1912">
+        <v>11</v>
+      </c>
+      <c r="H1912">
+        <v>11</v>
+      </c>
+      <c r="I1912">
+        <v>0</v>
+      </c>
+      <c r="J1912">
+        <v>0</v>
+      </c>
+      <c r="K1912">
+        <v>84.62</v>
+      </c>
+      <c r="L1912">
+        <v>13</v>
+      </c>
+      <c r="M1912">
+        <v>5</v>
+      </c>
+      <c r="N1912">
+        <v>1</v>
+      </c>
+      <c r="O1912">
+        <v>0</v>
+      </c>
+      <c r="P1912">
+        <v>27.5</v>
+      </c>
+      <c r="Q1912">
+        <v>0</v>
+      </c>
+      <c r="R1912">
+        <v>0</v>
+      </c>
+      <c r="S1912">
+        <v>0</v>
+      </c>
+      <c r="T1912">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4203" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4249" uniqueCount="504">
   <si>
     <t>Group</t>
   </si>
@@ -1529,6 +1529,9 @@
   <si>
     <t>Cara Murray</t>
   </si>
+  <si>
+    <t>North Down Women 2nd XI v Muckamore Women 2nd XI, The Green - 10 August 2026</t>
+  </si>
 </sst>
 </file>
 
@@ -2335,7 +2338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1912"/>
+  <dimension ref="A1:T1933"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -114259,6 +114262,1230 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1913" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1913" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1913">
+        <v>1</v>
+      </c>
+      <c r="D1913">
+        <v>1</v>
+      </c>
+      <c r="E1913">
+        <v>1</v>
+      </c>
+      <c r="F1913">
+        <v>15</v>
+      </c>
+      <c r="H1913" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1913">
+        <v>0</v>
+      </c>
+      <c r="J1913">
+        <v>0</v>
+      </c>
+      <c r="K1913">
+        <v>78.95</v>
+      </c>
+      <c r="L1913">
+        <v>19</v>
+      </c>
+      <c r="M1913">
+        <v>7</v>
+      </c>
+      <c r="N1913">
+        <v>0</v>
+      </c>
+      <c r="O1913">
+        <v>0</v>
+      </c>
+      <c r="P1913">
+        <v>10.87</v>
+      </c>
+      <c r="Q1913">
+        <v>0</v>
+      </c>
+      <c r="R1913">
+        <v>0</v>
+      </c>
+      <c r="S1913">
+        <v>0</v>
+      </c>
+      <c r="T1913">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1914" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1914">
+        <v>1</v>
+      </c>
+      <c r="D1914">
+        <v>1</v>
+      </c>
+      <c r="E1914">
+        <v>0</v>
+      </c>
+      <c r="F1914">
+        <v>2</v>
+      </c>
+      <c r="G1914">
+        <v>2</v>
+      </c>
+      <c r="H1914">
+        <v>2</v>
+      </c>
+      <c r="I1914">
+        <v>0</v>
+      </c>
+      <c r="J1914">
+        <v>0</v>
+      </c>
+      <c r="K1914">
+        <v>66.67</v>
+      </c>
+      <c r="L1914">
+        <v>3</v>
+      </c>
+      <c r="M1914">
+        <v>1</v>
+      </c>
+      <c r="N1914">
+        <v>0</v>
+      </c>
+      <c r="O1914">
+        <v>0</v>
+      </c>
+      <c r="P1914">
+        <v>1.45</v>
+      </c>
+      <c r="Q1914">
+        <v>2</v>
+      </c>
+      <c r="R1914">
+        <v>0</v>
+      </c>
+      <c r="S1914">
+        <v>0</v>
+      </c>
+      <c r="T1914">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1915" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1915">
+        <v>1</v>
+      </c>
+      <c r="D1915">
+        <v>0</v>
+      </c>
+      <c r="E1915">
+        <v>0</v>
+      </c>
+      <c r="F1915">
+        <v>0</v>
+      </c>
+      <c r="I1915">
+        <v>0</v>
+      </c>
+      <c r="J1915">
+        <v>0</v>
+      </c>
+      <c r="L1915">
+        <v>0</v>
+      </c>
+      <c r="M1915">
+        <v>0</v>
+      </c>
+      <c r="N1915">
+        <v>0</v>
+      </c>
+      <c r="O1915">
+        <v>0</v>
+      </c>
+      <c r="P1915">
+        <v>0</v>
+      </c>
+      <c r="Q1915">
+        <v>0</v>
+      </c>
+      <c r="R1915">
+        <v>0</v>
+      </c>
+      <c r="S1915">
+        <v>0</v>
+      </c>
+      <c r="T1915">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1916" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1916">
+        <v>1</v>
+      </c>
+      <c r="D1916">
+        <v>1</v>
+      </c>
+      <c r="E1916">
+        <v>1</v>
+      </c>
+      <c r="F1916">
+        <v>50</v>
+      </c>
+      <c r="H1916" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1916">
+        <v>1</v>
+      </c>
+      <c r="J1916">
+        <v>0</v>
+      </c>
+      <c r="K1916">
+        <v>128.21</v>
+      </c>
+      <c r="L1916">
+        <v>39</v>
+      </c>
+      <c r="M1916">
+        <v>8</v>
+      </c>
+      <c r="N1916">
+        <v>6</v>
+      </c>
+      <c r="O1916">
+        <v>0</v>
+      </c>
+      <c r="P1916">
+        <v>36.229999999999997</v>
+      </c>
+      <c r="Q1916">
+        <v>0</v>
+      </c>
+      <c r="R1916">
+        <v>1</v>
+      </c>
+      <c r="S1916">
+        <v>0</v>
+      </c>
+      <c r="T1916">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1917" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>116</v>
+      </c>
+      <c r="C1917">
+        <v>1</v>
+      </c>
+      <c r="D1917">
+        <v>1</v>
+      </c>
+      <c r="E1917">
+        <v>0</v>
+      </c>
+      <c r="F1917">
+        <v>4</v>
+      </c>
+      <c r="G1917">
+        <v>4</v>
+      </c>
+      <c r="H1917">
+        <v>4</v>
+      </c>
+      <c r="I1917">
+        <v>0</v>
+      </c>
+      <c r="J1917">
+        <v>0</v>
+      </c>
+      <c r="K1917">
+        <v>28.57</v>
+      </c>
+      <c r="L1917">
+        <v>14</v>
+      </c>
+      <c r="M1917">
+        <v>11</v>
+      </c>
+      <c r="N1917">
+        <v>0</v>
+      </c>
+      <c r="O1917">
+        <v>0</v>
+      </c>
+      <c r="P1917">
+        <v>3.85</v>
+      </c>
+      <c r="Q1917">
+        <v>0</v>
+      </c>
+      <c r="R1917">
+        <v>0</v>
+      </c>
+      <c r="S1917">
+        <v>0</v>
+      </c>
+      <c r="T1917">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1918" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1918">
+        <v>1</v>
+      </c>
+      <c r="D1918">
+        <v>0</v>
+      </c>
+      <c r="E1918">
+        <v>0</v>
+      </c>
+      <c r="F1918">
+        <v>0</v>
+      </c>
+      <c r="I1918">
+        <v>0</v>
+      </c>
+      <c r="J1918">
+        <v>0</v>
+      </c>
+      <c r="L1918">
+        <v>0</v>
+      </c>
+      <c r="M1918">
+        <v>0</v>
+      </c>
+      <c r="N1918">
+        <v>0</v>
+      </c>
+      <c r="O1918">
+        <v>0</v>
+      </c>
+      <c r="P1918">
+        <v>0</v>
+      </c>
+      <c r="Q1918">
+        <v>1</v>
+      </c>
+      <c r="R1918">
+        <v>0</v>
+      </c>
+      <c r="S1918">
+        <v>0</v>
+      </c>
+      <c r="T1918">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1919" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1919">
+        <v>1</v>
+      </c>
+      <c r="D1919">
+        <v>1</v>
+      </c>
+      <c r="E1919">
+        <v>0</v>
+      </c>
+      <c r="F1919">
+        <v>38</v>
+      </c>
+      <c r="G1919">
+        <v>38</v>
+      </c>
+      <c r="H1919">
+        <v>38</v>
+      </c>
+      <c r="I1919">
+        <v>0</v>
+      </c>
+      <c r="J1919">
+        <v>0</v>
+      </c>
+      <c r="K1919">
+        <v>71.7</v>
+      </c>
+      <c r="L1919">
+        <v>53</v>
+      </c>
+      <c r="M1919">
+        <v>23</v>
+      </c>
+      <c r="N1919">
+        <v>2</v>
+      </c>
+      <c r="O1919">
+        <v>0</v>
+      </c>
+      <c r="P1919">
+        <v>27.54</v>
+      </c>
+      <c r="Q1919">
+        <v>0</v>
+      </c>
+      <c r="R1919">
+        <v>0</v>
+      </c>
+      <c r="S1919">
+        <v>0</v>
+      </c>
+      <c r="T1919">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1920" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1920">
+        <v>1</v>
+      </c>
+      <c r="D1920">
+        <v>1</v>
+      </c>
+      <c r="E1920">
+        <v>1</v>
+      </c>
+      <c r="F1920">
+        <v>0</v>
+      </c>
+      <c r="H1920" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1920">
+        <v>0</v>
+      </c>
+      <c r="J1920">
+        <v>0</v>
+      </c>
+      <c r="L1920">
+        <v>0</v>
+      </c>
+      <c r="M1920">
+        <v>0</v>
+      </c>
+      <c r="N1920">
+        <v>0</v>
+      </c>
+      <c r="O1920">
+        <v>0</v>
+      </c>
+      <c r="P1920">
+        <v>0</v>
+      </c>
+      <c r="Q1920">
+        <v>0</v>
+      </c>
+      <c r="R1920">
+        <v>0</v>
+      </c>
+      <c r="S1920">
+        <v>0</v>
+      </c>
+      <c r="T1920">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1921" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1921">
+        <v>1</v>
+      </c>
+      <c r="D1921">
+        <v>1</v>
+      </c>
+      <c r="E1921">
+        <v>0</v>
+      </c>
+      <c r="F1921">
+        <v>8</v>
+      </c>
+      <c r="G1921">
+        <v>8</v>
+      </c>
+      <c r="H1921">
+        <v>8</v>
+      </c>
+      <c r="I1921">
+        <v>0</v>
+      </c>
+      <c r="J1921">
+        <v>0</v>
+      </c>
+      <c r="K1921">
+        <v>100</v>
+      </c>
+      <c r="L1921">
+        <v>8</v>
+      </c>
+      <c r="M1921">
+        <v>5</v>
+      </c>
+      <c r="N1921">
+        <v>1</v>
+      </c>
+      <c r="O1921">
+        <v>0</v>
+      </c>
+      <c r="P1921">
+        <v>7.69</v>
+      </c>
+      <c r="Q1921">
+        <v>0</v>
+      </c>
+      <c r="R1921">
+        <v>0</v>
+      </c>
+      <c r="S1921">
+        <v>0</v>
+      </c>
+      <c r="T1921">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1922" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1922">
+        <v>1</v>
+      </c>
+      <c r="D1922">
+        <v>1</v>
+      </c>
+      <c r="E1922">
+        <v>0</v>
+      </c>
+      <c r="F1922">
+        <v>6</v>
+      </c>
+      <c r="G1922">
+        <v>6</v>
+      </c>
+      <c r="H1922">
+        <v>6</v>
+      </c>
+      <c r="I1922">
+        <v>0</v>
+      </c>
+      <c r="J1922">
+        <v>0</v>
+      </c>
+      <c r="K1922">
+        <v>66.67</v>
+      </c>
+      <c r="L1922">
+        <v>9</v>
+      </c>
+      <c r="M1922">
+        <v>5</v>
+      </c>
+      <c r="N1922">
+        <v>0</v>
+      </c>
+      <c r="O1922">
+        <v>0</v>
+      </c>
+      <c r="P1922">
+        <v>5.77</v>
+      </c>
+      <c r="Q1922">
+        <v>0</v>
+      </c>
+      <c r="R1922">
+        <v>0</v>
+      </c>
+      <c r="S1922">
+        <v>1</v>
+      </c>
+      <c r="T1922">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1923" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1923">
+        <v>1</v>
+      </c>
+      <c r="D1923">
+        <v>1</v>
+      </c>
+      <c r="E1923">
+        <v>0</v>
+      </c>
+      <c r="F1923">
+        <v>2</v>
+      </c>
+      <c r="G1923">
+        <v>2</v>
+      </c>
+      <c r="H1923">
+        <v>2</v>
+      </c>
+      <c r="I1923">
+        <v>0</v>
+      </c>
+      <c r="J1923">
+        <v>0</v>
+      </c>
+      <c r="K1923">
+        <v>33.33</v>
+      </c>
+      <c r="L1923">
+        <v>6</v>
+      </c>
+      <c r="M1923">
+        <v>4</v>
+      </c>
+      <c r="N1923">
+        <v>0</v>
+      </c>
+      <c r="O1923">
+        <v>0</v>
+      </c>
+      <c r="P1923">
+        <v>1.92</v>
+      </c>
+      <c r="Q1923">
+        <v>1</v>
+      </c>
+      <c r="R1923">
+        <v>0</v>
+      </c>
+      <c r="S1923">
+        <v>0</v>
+      </c>
+      <c r="T1923">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1924" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>310</v>
+      </c>
+      <c r="C1924">
+        <v>1</v>
+      </c>
+      <c r="D1924">
+        <v>1</v>
+      </c>
+      <c r="E1924">
+        <v>0</v>
+      </c>
+      <c r="F1924">
+        <v>0</v>
+      </c>
+      <c r="G1924">
+        <v>0</v>
+      </c>
+      <c r="H1924">
+        <v>0</v>
+      </c>
+      <c r="I1924">
+        <v>0</v>
+      </c>
+      <c r="J1924">
+        <v>0</v>
+      </c>
+      <c r="K1924">
+        <v>0</v>
+      </c>
+      <c r="L1924">
+        <v>3</v>
+      </c>
+      <c r="M1924">
+        <v>3</v>
+      </c>
+      <c r="N1924">
+        <v>0</v>
+      </c>
+      <c r="O1924">
+        <v>0</v>
+      </c>
+      <c r="P1924">
+        <v>0</v>
+      </c>
+      <c r="Q1924">
+        <v>0</v>
+      </c>
+      <c r="R1924">
+        <v>0</v>
+      </c>
+      <c r="S1924">
+        <v>0</v>
+      </c>
+      <c r="T1924">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1925" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1925">
+        <v>1</v>
+      </c>
+      <c r="D1925">
+        <v>1</v>
+      </c>
+      <c r="E1925">
+        <v>0</v>
+      </c>
+      <c r="F1925">
+        <v>18</v>
+      </c>
+      <c r="G1925">
+        <v>18</v>
+      </c>
+      <c r="H1925">
+        <v>18</v>
+      </c>
+      <c r="I1925">
+        <v>0</v>
+      </c>
+      <c r="J1925">
+        <v>0</v>
+      </c>
+      <c r="K1925">
+        <v>42.86</v>
+      </c>
+      <c r="L1925">
+        <v>42</v>
+      </c>
+      <c r="M1925">
+        <v>27</v>
+      </c>
+      <c r="N1925">
+        <v>0</v>
+      </c>
+      <c r="O1925">
+        <v>0</v>
+      </c>
+      <c r="P1925">
+        <v>17.309999999999999</v>
+      </c>
+      <c r="Q1925">
+        <v>1</v>
+      </c>
+      <c r="R1925">
+        <v>0</v>
+      </c>
+      <c r="S1925">
+        <v>0</v>
+      </c>
+      <c r="T1925">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1926" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1926">
+        <v>1</v>
+      </c>
+      <c r="D1926">
+        <v>0</v>
+      </c>
+      <c r="E1926">
+        <v>0</v>
+      </c>
+      <c r="F1926">
+        <v>0</v>
+      </c>
+      <c r="I1926">
+        <v>0</v>
+      </c>
+      <c r="J1926">
+        <v>0</v>
+      </c>
+      <c r="L1926">
+        <v>0</v>
+      </c>
+      <c r="M1926">
+        <v>0</v>
+      </c>
+      <c r="N1926">
+        <v>0</v>
+      </c>
+      <c r="O1926">
+        <v>0</v>
+      </c>
+      <c r="P1926">
+        <v>0</v>
+      </c>
+      <c r="Q1926">
+        <v>0</v>
+      </c>
+      <c r="R1926">
+        <v>0</v>
+      </c>
+      <c r="S1926">
+        <v>0</v>
+      </c>
+      <c r="T1926">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1927" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1927">
+        <v>1</v>
+      </c>
+      <c r="D1927">
+        <v>0</v>
+      </c>
+      <c r="E1927">
+        <v>0</v>
+      </c>
+      <c r="F1927">
+        <v>0</v>
+      </c>
+      <c r="I1927">
+        <v>0</v>
+      </c>
+      <c r="J1927">
+        <v>0</v>
+      </c>
+      <c r="L1927">
+        <v>0</v>
+      </c>
+      <c r="M1927">
+        <v>0</v>
+      </c>
+      <c r="N1927">
+        <v>0</v>
+      </c>
+      <c r="O1927">
+        <v>0</v>
+      </c>
+      <c r="P1927">
+        <v>0</v>
+      </c>
+      <c r="Q1927">
+        <v>0</v>
+      </c>
+      <c r="R1927">
+        <v>0</v>
+      </c>
+      <c r="S1927">
+        <v>0</v>
+      </c>
+      <c r="T1927">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1928" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1928">
+        <v>1</v>
+      </c>
+      <c r="D1928">
+        <v>1</v>
+      </c>
+      <c r="E1928">
+        <v>1</v>
+      </c>
+      <c r="F1928">
+        <v>4</v>
+      </c>
+      <c r="H1928" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1928">
+        <v>0</v>
+      </c>
+      <c r="J1928">
+        <v>0</v>
+      </c>
+      <c r="K1928">
+        <v>44.44</v>
+      </c>
+      <c r="L1928">
+        <v>9</v>
+      </c>
+      <c r="M1928">
+        <v>6</v>
+      </c>
+      <c r="N1928">
+        <v>0</v>
+      </c>
+      <c r="O1928">
+        <v>0</v>
+      </c>
+      <c r="P1928">
+        <v>3.85</v>
+      </c>
+      <c r="Q1928">
+        <v>0</v>
+      </c>
+      <c r="R1928">
+        <v>0</v>
+      </c>
+      <c r="S1928">
+        <v>0</v>
+      </c>
+      <c r="T1928">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1929" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1929">
+        <v>1</v>
+      </c>
+      <c r="D1929">
+        <v>0</v>
+      </c>
+      <c r="E1929">
+        <v>0</v>
+      </c>
+      <c r="F1929">
+        <v>0</v>
+      </c>
+      <c r="I1929">
+        <v>0</v>
+      </c>
+      <c r="J1929">
+        <v>0</v>
+      </c>
+      <c r="L1929">
+        <v>0</v>
+      </c>
+      <c r="M1929">
+        <v>0</v>
+      </c>
+      <c r="N1929">
+        <v>0</v>
+      </c>
+      <c r="O1929">
+        <v>0</v>
+      </c>
+      <c r="P1929">
+        <v>0</v>
+      </c>
+      <c r="Q1929">
+        <v>0</v>
+      </c>
+      <c r="R1929">
+        <v>0</v>
+      </c>
+      <c r="S1929">
+        <v>0</v>
+      </c>
+      <c r="T1929">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1930" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1930">
+        <v>1</v>
+      </c>
+      <c r="D1930">
+        <v>1</v>
+      </c>
+      <c r="E1930">
+        <v>0</v>
+      </c>
+      <c r="F1930">
+        <v>34</v>
+      </c>
+      <c r="G1930">
+        <v>34</v>
+      </c>
+      <c r="H1930">
+        <v>34</v>
+      </c>
+      <c r="I1930">
+        <v>0</v>
+      </c>
+      <c r="J1930">
+        <v>0</v>
+      </c>
+      <c r="K1930">
+        <v>103.03</v>
+      </c>
+      <c r="L1930">
+        <v>33</v>
+      </c>
+      <c r="M1930">
+        <v>13</v>
+      </c>
+      <c r="N1930">
+        <v>3</v>
+      </c>
+      <c r="O1930">
+        <v>0</v>
+      </c>
+      <c r="P1930">
+        <v>32.69</v>
+      </c>
+      <c r="Q1930">
+        <v>0</v>
+      </c>
+      <c r="R1930">
+        <v>0</v>
+      </c>
+      <c r="S1930">
+        <v>0</v>
+      </c>
+      <c r="T1930">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1931" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1931">
+        <v>1</v>
+      </c>
+      <c r="D1931">
+        <v>1</v>
+      </c>
+      <c r="E1931">
+        <v>0</v>
+      </c>
+      <c r="F1931">
+        <v>5</v>
+      </c>
+      <c r="G1931">
+        <v>5</v>
+      </c>
+      <c r="H1931">
+        <v>5</v>
+      </c>
+      <c r="I1931">
+        <v>0</v>
+      </c>
+      <c r="J1931">
+        <v>0</v>
+      </c>
+      <c r="K1931">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1931">
+        <v>7</v>
+      </c>
+      <c r="M1931">
+        <v>5</v>
+      </c>
+      <c r="N1931">
+        <v>1</v>
+      </c>
+      <c r="O1931">
+        <v>0</v>
+      </c>
+      <c r="P1931">
+        <v>3.62</v>
+      </c>
+      <c r="Q1931">
+        <v>0</v>
+      </c>
+      <c r="R1931">
+        <v>0</v>
+      </c>
+      <c r="S1931">
+        <v>0</v>
+      </c>
+      <c r="T1931">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1932" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1932">
+        <v>1</v>
+      </c>
+      <c r="D1932">
+        <v>0</v>
+      </c>
+      <c r="E1932">
+        <v>0</v>
+      </c>
+      <c r="F1932">
+        <v>0</v>
+      </c>
+      <c r="I1932">
+        <v>0</v>
+      </c>
+      <c r="J1932">
+        <v>0</v>
+      </c>
+      <c r="L1932">
+        <v>0</v>
+      </c>
+      <c r="M1932">
+        <v>0</v>
+      </c>
+      <c r="N1932">
+        <v>0</v>
+      </c>
+      <c r="O1932">
+        <v>0</v>
+      </c>
+      <c r="P1932">
+        <v>0</v>
+      </c>
+      <c r="Q1932">
+        <v>0</v>
+      </c>
+      <c r="R1932">
+        <v>0</v>
+      </c>
+      <c r="S1932">
+        <v>0</v>
+      </c>
+      <c r="T1932">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1933" t="s">
+        <v>503</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1933">
+        <v>1</v>
+      </c>
+      <c r="D1933">
+        <v>0</v>
+      </c>
+      <c r="E1933">
+        <v>0</v>
+      </c>
+      <c r="F1933">
+        <v>0</v>
+      </c>
+      <c r="I1933">
+        <v>0</v>
+      </c>
+      <c r="J1933">
+        <v>0</v>
+      </c>
+      <c r="L1933">
+        <v>0</v>
+      </c>
+      <c r="M1933">
+        <v>0</v>
+      </c>
+      <c r="N1933">
+        <v>0</v>
+      </c>
+      <c r="O1933">
+        <v>0</v>
+      </c>
+      <c r="P1933">
+        <v>0</v>
+      </c>
+      <c r="Q1933">
+        <v>0</v>
+      </c>
+      <c r="R1933">
+        <v>0</v>
+      </c>
+      <c r="S1933">
+        <v>0</v>
+      </c>
+      <c r="T1933">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4249" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4297" uniqueCount="506">
   <si>
     <t>Group</t>
   </si>
@@ -1532,6 +1532,12 @@
   <si>
     <t>North Down Women 2nd XI v Muckamore Women 2nd XI, The Green - 10 August 2026</t>
   </si>
+  <si>
+    <t>North Down Women 1st XI v Waringstown Women 1st XI, The Green - 11 August 2026</t>
+  </si>
+  <si>
+    <t>A Megarell</t>
+  </si>
 </sst>
 </file>
 
@@ -2338,7 +2344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1933"/>
+  <dimension ref="A1:T1954"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -115486,6 +115492,1224 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1934" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1934" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1934">
+        <v>1</v>
+      </c>
+      <c r="D1934">
+        <v>0</v>
+      </c>
+      <c r="E1934">
+        <v>0</v>
+      </c>
+      <c r="F1934">
+        <v>0</v>
+      </c>
+      <c r="I1934">
+        <v>0</v>
+      </c>
+      <c r="J1934">
+        <v>0</v>
+      </c>
+      <c r="L1934">
+        <v>0</v>
+      </c>
+      <c r="M1934">
+        <v>0</v>
+      </c>
+      <c r="N1934">
+        <v>0</v>
+      </c>
+      <c r="O1934">
+        <v>0</v>
+      </c>
+      <c r="P1934">
+        <v>0</v>
+      </c>
+      <c r="Q1934">
+        <v>0</v>
+      </c>
+      <c r="R1934">
+        <v>0</v>
+      </c>
+      <c r="S1934">
+        <v>0</v>
+      </c>
+      <c r="T1934">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1935" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1935">
+        <v>1</v>
+      </c>
+      <c r="D1935">
+        <v>1</v>
+      </c>
+      <c r="E1935">
+        <v>0</v>
+      </c>
+      <c r="F1935">
+        <v>7</v>
+      </c>
+      <c r="G1935">
+        <v>7</v>
+      </c>
+      <c r="H1935">
+        <v>7</v>
+      </c>
+      <c r="I1935">
+        <v>0</v>
+      </c>
+      <c r="J1935">
+        <v>0</v>
+      </c>
+      <c r="K1935">
+        <v>46.67</v>
+      </c>
+      <c r="L1935">
+        <v>15</v>
+      </c>
+      <c r="M1935">
+        <v>10</v>
+      </c>
+      <c r="N1935">
+        <v>0</v>
+      </c>
+      <c r="O1935">
+        <v>0</v>
+      </c>
+      <c r="P1935">
+        <v>8.75</v>
+      </c>
+      <c r="Q1935">
+        <v>0</v>
+      </c>
+      <c r="R1935">
+        <v>0</v>
+      </c>
+      <c r="S1935">
+        <v>0</v>
+      </c>
+      <c r="T1935">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1936" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>501</v>
+      </c>
+      <c r="C1936">
+        <v>1</v>
+      </c>
+      <c r="D1936">
+        <v>1</v>
+      </c>
+      <c r="E1936">
+        <v>1</v>
+      </c>
+      <c r="F1936">
+        <v>6</v>
+      </c>
+      <c r="H1936" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1936">
+        <v>0</v>
+      </c>
+      <c r="J1936">
+        <v>0</v>
+      </c>
+      <c r="K1936">
+        <v>40</v>
+      </c>
+      <c r="L1936">
+        <v>15</v>
+      </c>
+      <c r="M1936">
+        <v>10</v>
+      </c>
+      <c r="N1936">
+        <v>0</v>
+      </c>
+      <c r="O1936">
+        <v>0</v>
+      </c>
+      <c r="P1936">
+        <v>7.5</v>
+      </c>
+      <c r="Q1936">
+        <v>0</v>
+      </c>
+      <c r="R1936">
+        <v>0</v>
+      </c>
+      <c r="S1936">
+        <v>0</v>
+      </c>
+      <c r="T1936">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1937" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1937">
+        <v>1</v>
+      </c>
+      <c r="D1937">
+        <v>1</v>
+      </c>
+      <c r="E1937">
+        <v>0</v>
+      </c>
+      <c r="F1937">
+        <v>2</v>
+      </c>
+      <c r="G1937">
+        <v>2</v>
+      </c>
+      <c r="H1937">
+        <v>2</v>
+      </c>
+      <c r="I1937">
+        <v>0</v>
+      </c>
+      <c r="J1937">
+        <v>0</v>
+      </c>
+      <c r="K1937">
+        <v>33.33</v>
+      </c>
+      <c r="L1937">
+        <v>6</v>
+      </c>
+      <c r="M1937">
+        <v>4</v>
+      </c>
+      <c r="N1937">
+        <v>0</v>
+      </c>
+      <c r="O1937">
+        <v>0</v>
+      </c>
+      <c r="P1937">
+        <v>2.5</v>
+      </c>
+      <c r="Q1937">
+        <v>0</v>
+      </c>
+      <c r="R1937">
+        <v>0</v>
+      </c>
+      <c r="S1937">
+        <v>0</v>
+      </c>
+      <c r="T1937">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1938" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1938">
+        <v>1</v>
+      </c>
+      <c r="D1938">
+        <v>1</v>
+      </c>
+      <c r="E1938">
+        <v>0</v>
+      </c>
+      <c r="F1938">
+        <v>2</v>
+      </c>
+      <c r="G1938">
+        <v>2</v>
+      </c>
+      <c r="H1938">
+        <v>2</v>
+      </c>
+      <c r="I1938">
+        <v>0</v>
+      </c>
+      <c r="J1938">
+        <v>0</v>
+      </c>
+      <c r="K1938">
+        <v>33.33</v>
+      </c>
+      <c r="L1938">
+        <v>6</v>
+      </c>
+      <c r="M1938">
+        <v>4</v>
+      </c>
+      <c r="N1938">
+        <v>0</v>
+      </c>
+      <c r="O1938">
+        <v>0</v>
+      </c>
+      <c r="P1938">
+        <v>2.5</v>
+      </c>
+      <c r="Q1938">
+        <v>0</v>
+      </c>
+      <c r="R1938">
+        <v>0</v>
+      </c>
+      <c r="S1938">
+        <v>0</v>
+      </c>
+      <c r="T1938">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1939" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>483</v>
+      </c>
+      <c r="C1939">
+        <v>1</v>
+      </c>
+      <c r="D1939">
+        <v>1</v>
+      </c>
+      <c r="E1939">
+        <v>1</v>
+      </c>
+      <c r="F1939">
+        <v>50</v>
+      </c>
+      <c r="H1939" t="s">
+        <v>169</v>
+      </c>
+      <c r="I1939">
+        <v>1</v>
+      </c>
+      <c r="J1939">
+        <v>0</v>
+      </c>
+      <c r="K1939">
+        <v>125</v>
+      </c>
+      <c r="L1939">
+        <v>40</v>
+      </c>
+      <c r="M1939">
+        <v>13</v>
+      </c>
+      <c r="N1939">
+        <v>5</v>
+      </c>
+      <c r="O1939">
+        <v>0</v>
+      </c>
+      <c r="P1939">
+        <v>32.26</v>
+      </c>
+      <c r="Q1939">
+        <v>0</v>
+      </c>
+      <c r="R1939">
+        <v>0</v>
+      </c>
+      <c r="S1939">
+        <v>0</v>
+      </c>
+      <c r="T1939">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1940" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1940">
+        <v>1</v>
+      </c>
+      <c r="D1940">
+        <v>0</v>
+      </c>
+      <c r="E1940">
+        <v>0</v>
+      </c>
+      <c r="F1940">
+        <v>0</v>
+      </c>
+      <c r="I1940">
+        <v>0</v>
+      </c>
+      <c r="J1940">
+        <v>0</v>
+      </c>
+      <c r="L1940">
+        <v>0</v>
+      </c>
+      <c r="M1940">
+        <v>0</v>
+      </c>
+      <c r="N1940">
+        <v>0</v>
+      </c>
+      <c r="O1940">
+        <v>0</v>
+      </c>
+      <c r="P1940">
+        <v>0</v>
+      </c>
+      <c r="Q1940">
+        <v>0</v>
+      </c>
+      <c r="R1940">
+        <v>0</v>
+      </c>
+      <c r="S1940">
+        <v>0</v>
+      </c>
+      <c r="T1940">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1941" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1941">
+        <v>1</v>
+      </c>
+      <c r="D1941">
+        <v>0</v>
+      </c>
+      <c r="E1941">
+        <v>0</v>
+      </c>
+      <c r="F1941">
+        <v>0</v>
+      </c>
+      <c r="I1941">
+        <v>0</v>
+      </c>
+      <c r="J1941">
+        <v>0</v>
+      </c>
+      <c r="L1941">
+        <v>0</v>
+      </c>
+      <c r="M1941">
+        <v>0</v>
+      </c>
+      <c r="N1941">
+        <v>0</v>
+      </c>
+      <c r="O1941">
+        <v>0</v>
+      </c>
+      <c r="P1941">
+        <v>0</v>
+      </c>
+      <c r="Q1941">
+        <v>1</v>
+      </c>
+      <c r="R1941">
+        <v>0</v>
+      </c>
+      <c r="S1941">
+        <v>0</v>
+      </c>
+      <c r="T1941">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1942" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1942">
+        <v>1</v>
+      </c>
+      <c r="D1942">
+        <v>1</v>
+      </c>
+      <c r="E1942">
+        <v>1</v>
+      </c>
+      <c r="F1942">
+        <v>55</v>
+      </c>
+      <c r="H1942" t="s">
+        <v>406</v>
+      </c>
+      <c r="I1942">
+        <v>1</v>
+      </c>
+      <c r="J1942">
+        <v>0</v>
+      </c>
+      <c r="K1942">
+        <v>166.67</v>
+      </c>
+      <c r="L1942">
+        <v>33</v>
+      </c>
+      <c r="M1942">
+        <v>10</v>
+      </c>
+      <c r="N1942">
+        <v>8</v>
+      </c>
+      <c r="O1942">
+        <v>1</v>
+      </c>
+      <c r="P1942">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="Q1942">
+        <v>0</v>
+      </c>
+      <c r="R1942">
+        <v>0</v>
+      </c>
+      <c r="S1942">
+        <v>0</v>
+      </c>
+      <c r="T1942">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1943" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1943">
+        <v>1</v>
+      </c>
+      <c r="D1943">
+        <v>1</v>
+      </c>
+      <c r="E1943">
+        <v>0</v>
+      </c>
+      <c r="F1943">
+        <v>20</v>
+      </c>
+      <c r="G1943">
+        <v>20</v>
+      </c>
+      <c r="H1943">
+        <v>20</v>
+      </c>
+      <c r="I1943">
+        <v>0</v>
+      </c>
+      <c r="J1943">
+        <v>0</v>
+      </c>
+      <c r="K1943">
+        <v>80</v>
+      </c>
+      <c r="L1943">
+        <v>25</v>
+      </c>
+      <c r="M1943">
+        <v>12</v>
+      </c>
+      <c r="N1943">
+        <v>2</v>
+      </c>
+      <c r="O1943">
+        <v>0</v>
+      </c>
+      <c r="P1943">
+        <v>25</v>
+      </c>
+      <c r="Q1943">
+        <v>0</v>
+      </c>
+      <c r="R1943">
+        <v>0</v>
+      </c>
+      <c r="S1943">
+        <v>0</v>
+      </c>
+      <c r="T1943">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1944" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1944">
+        <v>1</v>
+      </c>
+      <c r="D1944">
+        <v>1</v>
+      </c>
+      <c r="E1944">
+        <v>0</v>
+      </c>
+      <c r="F1944">
+        <v>29</v>
+      </c>
+      <c r="G1944">
+        <v>29</v>
+      </c>
+      <c r="H1944">
+        <v>29</v>
+      </c>
+      <c r="I1944">
+        <v>0</v>
+      </c>
+      <c r="J1944">
+        <v>0</v>
+      </c>
+      <c r="K1944">
+        <v>116</v>
+      </c>
+      <c r="L1944">
+        <v>25</v>
+      </c>
+      <c r="M1944">
+        <v>8</v>
+      </c>
+      <c r="N1944">
+        <v>3</v>
+      </c>
+      <c r="O1944">
+        <v>0</v>
+      </c>
+      <c r="P1944">
+        <v>36.25</v>
+      </c>
+      <c r="Q1944">
+        <v>0</v>
+      </c>
+      <c r="R1944">
+        <v>0</v>
+      </c>
+      <c r="S1944">
+        <v>0</v>
+      </c>
+      <c r="T1944">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1945" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1945">
+        <v>1</v>
+      </c>
+      <c r="D1945">
+        <v>1</v>
+      </c>
+      <c r="E1945">
+        <v>0</v>
+      </c>
+      <c r="F1945">
+        <v>8</v>
+      </c>
+      <c r="G1945">
+        <v>8</v>
+      </c>
+      <c r="H1945">
+        <v>8</v>
+      </c>
+      <c r="I1945">
+        <v>0</v>
+      </c>
+      <c r="J1945">
+        <v>0</v>
+      </c>
+      <c r="K1945">
+        <v>80</v>
+      </c>
+      <c r="L1945">
+        <v>10</v>
+      </c>
+      <c r="M1945">
+        <v>5</v>
+      </c>
+      <c r="N1945">
+        <v>1</v>
+      </c>
+      <c r="O1945">
+        <v>0</v>
+      </c>
+      <c r="P1945">
+        <v>5.16</v>
+      </c>
+      <c r="Q1945">
+        <v>0</v>
+      </c>
+      <c r="R1945">
+        <v>0</v>
+      </c>
+      <c r="S1945">
+        <v>0</v>
+      </c>
+      <c r="T1945">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1946" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1946">
+        <v>1</v>
+      </c>
+      <c r="D1946">
+        <v>1</v>
+      </c>
+      <c r="E1946">
+        <v>1</v>
+      </c>
+      <c r="F1946">
+        <v>22</v>
+      </c>
+      <c r="H1946" t="s">
+        <v>276</v>
+      </c>
+      <c r="I1946">
+        <v>0</v>
+      </c>
+      <c r="J1946">
+        <v>0</v>
+      </c>
+      <c r="K1946">
+        <v>115.79</v>
+      </c>
+      <c r="L1946">
+        <v>19</v>
+      </c>
+      <c r="M1946">
+        <v>7</v>
+      </c>
+      <c r="N1946">
+        <v>1</v>
+      </c>
+      <c r="O1946">
+        <v>0</v>
+      </c>
+      <c r="P1946">
+        <v>14.19</v>
+      </c>
+      <c r="Q1946">
+        <v>0</v>
+      </c>
+      <c r="R1946">
+        <v>0</v>
+      </c>
+      <c r="S1946">
+        <v>0</v>
+      </c>
+      <c r="T1946">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1947" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1947">
+        <v>1</v>
+      </c>
+      <c r="D1947">
+        <v>1</v>
+      </c>
+      <c r="E1947">
+        <v>0</v>
+      </c>
+      <c r="F1947">
+        <v>0</v>
+      </c>
+      <c r="G1947">
+        <v>0</v>
+      </c>
+      <c r="H1947">
+        <v>0</v>
+      </c>
+      <c r="I1947">
+        <v>0</v>
+      </c>
+      <c r="J1947">
+        <v>0</v>
+      </c>
+      <c r="K1947">
+        <v>0</v>
+      </c>
+      <c r="L1947">
+        <v>4</v>
+      </c>
+      <c r="M1947">
+        <v>4</v>
+      </c>
+      <c r="N1947">
+        <v>0</v>
+      </c>
+      <c r="O1947">
+        <v>0</v>
+      </c>
+      <c r="P1947">
+        <v>0</v>
+      </c>
+      <c r="Q1947">
+        <v>0</v>
+      </c>
+      <c r="R1947">
+        <v>0</v>
+      </c>
+      <c r="S1947">
+        <v>0</v>
+      </c>
+      <c r="T1947">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1948" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1948">
+        <v>1</v>
+      </c>
+      <c r="D1948">
+        <v>0</v>
+      </c>
+      <c r="E1948">
+        <v>0</v>
+      </c>
+      <c r="F1948">
+        <v>0</v>
+      </c>
+      <c r="I1948">
+        <v>0</v>
+      </c>
+      <c r="J1948">
+        <v>0</v>
+      </c>
+      <c r="L1948">
+        <v>0</v>
+      </c>
+      <c r="M1948">
+        <v>0</v>
+      </c>
+      <c r="N1948">
+        <v>0</v>
+      </c>
+      <c r="O1948">
+        <v>0</v>
+      </c>
+      <c r="P1948">
+        <v>0</v>
+      </c>
+      <c r="Q1948">
+        <v>0</v>
+      </c>
+      <c r="R1948">
+        <v>0</v>
+      </c>
+      <c r="S1948">
+        <v>0</v>
+      </c>
+      <c r="T1948">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1949" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>505</v>
+      </c>
+      <c r="C1949">
+        <v>1</v>
+      </c>
+      <c r="D1949">
+        <v>0</v>
+      </c>
+      <c r="E1949">
+        <v>0</v>
+      </c>
+      <c r="F1949">
+        <v>0</v>
+      </c>
+      <c r="I1949">
+        <v>0</v>
+      </c>
+      <c r="J1949">
+        <v>0</v>
+      </c>
+      <c r="L1949">
+        <v>0</v>
+      </c>
+      <c r="M1949">
+        <v>0</v>
+      </c>
+      <c r="N1949">
+        <v>0</v>
+      </c>
+      <c r="O1949">
+        <v>0</v>
+      </c>
+      <c r="P1949">
+        <v>0</v>
+      </c>
+      <c r="Q1949">
+        <v>0</v>
+      </c>
+      <c r="R1949">
+        <v>0</v>
+      </c>
+      <c r="S1949">
+        <v>0</v>
+      </c>
+      <c r="T1949">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1950" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1950" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1950">
+        <v>1</v>
+      </c>
+      <c r="D1950">
+        <v>0</v>
+      </c>
+      <c r="E1950">
+        <v>0</v>
+      </c>
+      <c r="F1950">
+        <v>0</v>
+      </c>
+      <c r="I1950">
+        <v>0</v>
+      </c>
+      <c r="J1950">
+        <v>0</v>
+      </c>
+      <c r="L1950">
+        <v>0</v>
+      </c>
+      <c r="M1950">
+        <v>0</v>
+      </c>
+      <c r="N1950">
+        <v>0</v>
+      </c>
+      <c r="O1950">
+        <v>0</v>
+      </c>
+      <c r="P1950">
+        <v>0</v>
+      </c>
+      <c r="Q1950">
+        <v>0</v>
+      </c>
+      <c r="R1950">
+        <v>0</v>
+      </c>
+      <c r="S1950">
+        <v>0</v>
+      </c>
+      <c r="T1950">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1951" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1951" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1951">
+        <v>1</v>
+      </c>
+      <c r="D1951">
+        <v>0</v>
+      </c>
+      <c r="E1951">
+        <v>0</v>
+      </c>
+      <c r="F1951">
+        <v>0</v>
+      </c>
+      <c r="I1951">
+        <v>0</v>
+      </c>
+      <c r="J1951">
+        <v>0</v>
+      </c>
+      <c r="L1951">
+        <v>0</v>
+      </c>
+      <c r="M1951">
+        <v>0</v>
+      </c>
+      <c r="N1951">
+        <v>0</v>
+      </c>
+      <c r="O1951">
+        <v>0</v>
+      </c>
+      <c r="P1951">
+        <v>0</v>
+      </c>
+      <c r="Q1951">
+        <v>0</v>
+      </c>
+      <c r="R1951">
+        <v>0</v>
+      </c>
+      <c r="S1951">
+        <v>0</v>
+      </c>
+      <c r="T1951">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1952" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>488</v>
+      </c>
+      <c r="C1952">
+        <v>1</v>
+      </c>
+      <c r="D1952">
+        <v>1</v>
+      </c>
+      <c r="E1952">
+        <v>1</v>
+      </c>
+      <c r="F1952">
+        <v>1</v>
+      </c>
+      <c r="H1952" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1952">
+        <v>0</v>
+      </c>
+      <c r="J1952">
+        <v>0</v>
+      </c>
+      <c r="K1952">
+        <v>50</v>
+      </c>
+      <c r="L1952">
+        <v>2</v>
+      </c>
+      <c r="M1952">
+        <v>1</v>
+      </c>
+      <c r="N1952">
+        <v>0</v>
+      </c>
+      <c r="O1952">
+        <v>0</v>
+      </c>
+      <c r="P1952">
+        <v>1.25</v>
+      </c>
+      <c r="Q1952">
+        <v>0</v>
+      </c>
+      <c r="R1952">
+        <v>0</v>
+      </c>
+      <c r="S1952">
+        <v>0</v>
+      </c>
+      <c r="T1952">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1953" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1953">
+        <v>1</v>
+      </c>
+      <c r="D1953">
+        <v>1</v>
+      </c>
+      <c r="E1953">
+        <v>1</v>
+      </c>
+      <c r="F1953">
+        <v>0</v>
+      </c>
+      <c r="H1953" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1953">
+        <v>0</v>
+      </c>
+      <c r="J1953">
+        <v>0</v>
+      </c>
+      <c r="L1953">
+        <v>0</v>
+      </c>
+      <c r="M1953">
+        <v>0</v>
+      </c>
+      <c r="N1953">
+        <v>0</v>
+      </c>
+      <c r="O1953">
+        <v>0</v>
+      </c>
+      <c r="P1953">
+        <v>0</v>
+      </c>
+      <c r="Q1953">
+        <v>0</v>
+      </c>
+      <c r="R1953">
+        <v>0</v>
+      </c>
+      <c r="S1953">
+        <v>0</v>
+      </c>
+      <c r="T1953">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1954" t="s">
+        <v>504</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>387</v>
+      </c>
+      <c r="C1954">
+        <v>1</v>
+      </c>
+      <c r="D1954">
+        <v>1</v>
+      </c>
+      <c r="E1954">
+        <v>0</v>
+      </c>
+      <c r="F1954">
+        <v>1</v>
+      </c>
+      <c r="G1954">
+        <v>1</v>
+      </c>
+      <c r="H1954">
+        <v>1</v>
+      </c>
+      <c r="I1954">
+        <v>0</v>
+      </c>
+      <c r="J1954">
+        <v>0</v>
+      </c>
+      <c r="K1954">
+        <v>20</v>
+      </c>
+      <c r="L1954">
+        <v>5</v>
+      </c>
+      <c r="M1954">
+        <v>4</v>
+      </c>
+      <c r="N1954">
+        <v>0</v>
+      </c>
+      <c r="O1954">
+        <v>0</v>
+      </c>
+      <c r="P1954">
+        <v>1.25</v>
+      </c>
+      <c r="Q1954">
+        <v>0</v>
+      </c>
+      <c r="R1954">
+        <v>0</v>
+      </c>
+      <c r="S1954">
+        <v>0</v>
+      </c>
+      <c r="T1954">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/NV Play Women's Fixtures batting stats for season.xlsx
+++ b/NV Play Women's Fixtures batting stats for season.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\-Womens-\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49355D23-995D-49B3-BAEB-69CB10FC1EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NV Play Women's Fixtures battin" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4297" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4393" uniqueCount="508">
   <si>
     <t>Group</t>
   </si>
@@ -1538,11 +1539,17 @@
   <si>
     <t>A Megarell</t>
   </si>
+  <si>
+    <t>Holywood Women 1st XI v Waringstown Women 1st XI, Seapark Oval - 16 August 2026</t>
+  </si>
+  <si>
+    <t>Instonians Women 1st XI v Muckamore Women 1st XI, Shaw's Bridge - 16 August 2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2020,9 +2027,8 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2343,8 +2349,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1954"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T1998"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84" customWidth="1"/>
@@ -87411,7 +87417,7 @@
       <c r="A1456" t="s">
         <v>442</v>
       </c>
-      <c r="B1456" s="1" t="s">
+      <c r="B1456" t="s">
         <v>306</v>
       </c>
       <c r="C1456">
@@ -87473,7 +87479,7 @@
       <c r="A1457" t="s">
         <v>442</v>
       </c>
-      <c r="B1457" s="1" t="s">
+      <c r="B1457" t="s">
         <v>438</v>
       </c>
       <c r="C1457">
@@ -87535,7 +87541,7 @@
       <c r="A1458" t="s">
         <v>442</v>
       </c>
-      <c r="B1458" s="1" t="s">
+      <c r="B1458" t="s">
         <v>417</v>
       </c>
       <c r="C1458">
@@ -87597,7 +87603,7 @@
       <c r="A1459" t="s">
         <v>442</v>
       </c>
-      <c r="B1459" s="1" t="s">
+      <c r="B1459" t="s">
         <v>205</v>
       </c>
       <c r="C1459">
@@ -87656,7 +87662,7 @@
       <c r="A1460" t="s">
         <v>442</v>
       </c>
-      <c r="B1460" s="1" t="s">
+      <c r="B1460" t="s">
         <v>200</v>
       </c>
       <c r="C1460">
@@ -87715,7 +87721,7 @@
       <c r="A1461" t="s">
         <v>442</v>
       </c>
-      <c r="B1461" s="1" t="s">
+      <c r="B1461" t="s">
         <v>110</v>
       </c>
       <c r="C1461">
@@ -87777,7 +87783,7 @@
       <c r="A1462" t="s">
         <v>442</v>
       </c>
-      <c r="B1462" s="1" t="s">
+      <c r="B1462" t="s">
         <v>112</v>
       </c>
       <c r="C1462">
@@ -87839,7 +87845,7 @@
       <c r="A1463" t="s">
         <v>442</v>
       </c>
-      <c r="B1463" s="1" t="s">
+      <c r="B1463" t="s">
         <v>203</v>
       </c>
       <c r="C1463">
@@ -87901,7 +87907,7 @@
       <c r="A1464" t="s">
         <v>442</v>
       </c>
-      <c r="B1464" s="1" t="s">
+      <c r="B1464" t="s">
         <v>307</v>
       </c>
       <c r="C1464">
@@ -87960,7 +87966,7 @@
       <c r="A1465" t="s">
         <v>442</v>
       </c>
-      <c r="B1465" s="1" t="s">
+      <c r="B1465" t="s">
         <v>114</v>
       </c>
       <c r="C1465">
@@ -88022,7 +88028,7 @@
       <c r="A1466" t="s">
         <v>442</v>
       </c>
-      <c r="B1466" s="1" t="s">
+      <c r="B1466" t="s">
         <v>90</v>
       </c>
       <c r="C1466">
@@ -88084,7 +88090,7 @@
       <c r="A1467" t="s">
         <v>442</v>
       </c>
-      <c r="B1467" s="1" t="s">
+      <c r="B1467" t="s">
         <v>106</v>
       </c>
       <c r="C1467">
@@ -88146,7 +88152,7 @@
       <c r="A1468" t="s">
         <v>442</v>
       </c>
-      <c r="B1468" s="1" t="s">
+      <c r="B1468" t="s">
         <v>233</v>
       </c>
       <c r="C1468">
@@ -88199,7 +88205,7 @@
       <c r="A1469" t="s">
         <v>442</v>
       </c>
-      <c r="B1469" s="1" t="s">
+      <c r="B1469" t="s">
         <v>88</v>
       </c>
       <c r="C1469">
@@ -88252,7 +88258,7 @@
       <c r="A1470" t="s">
         <v>442</v>
       </c>
-      <c r="B1470" s="1" t="s">
+      <c r="B1470" t="s">
         <v>104</v>
       </c>
       <c r="C1470">
@@ -88314,7 +88320,7 @@
       <c r="A1471" t="s">
         <v>442</v>
       </c>
-      <c r="B1471" s="1" t="s">
+      <c r="B1471" t="s">
         <v>305</v>
       </c>
       <c r="C1471">
@@ -88373,7 +88379,7 @@
       <c r="A1472" t="s">
         <v>442</v>
       </c>
-      <c r="B1472" s="1" t="s">
+      <c r="B1472" t="s">
         <v>141</v>
       </c>
       <c r="C1472">
@@ -88435,7 +88441,7 @@
       <c r="A1473" t="s">
         <v>442</v>
       </c>
-      <c r="B1473" s="1" t="s">
+      <c r="B1473" t="s">
         <v>111</v>
       </c>
       <c r="C1473">
@@ -88497,7 +88503,7 @@
       <c r="A1474" t="s">
         <v>442</v>
       </c>
-      <c r="B1474" s="1" t="s">
+      <c r="B1474" t="s">
         <v>198</v>
       </c>
       <c r="C1474">
@@ -88550,7 +88556,7 @@
       <c r="A1475" t="s">
         <v>442</v>
       </c>
-      <c r="B1475" s="1" t="s">
+      <c r="B1475" t="s">
         <v>194</v>
       </c>
       <c r="C1475">
@@ -88612,7 +88618,7 @@
       <c r="A1476" t="s">
         <v>442</v>
       </c>
-      <c r="B1476" s="1" t="s">
+      <c r="B1476" t="s">
         <v>89</v>
       </c>
       <c r="C1476">
@@ -88674,7 +88680,7 @@
       <c r="A1477" t="s">
         <v>442</v>
       </c>
-      <c r="B1477" s="1" t="s">
+      <c r="B1477" t="s">
         <v>199</v>
       </c>
       <c r="C1477">
@@ -90013,7 +90019,7 @@
       <c r="A1500" t="s">
         <v>446</v>
       </c>
-      <c r="B1500" s="1" t="s">
+      <c r="B1500" t="s">
         <v>315</v>
       </c>
       <c r="C1500">
@@ -90075,7 +90081,7 @@
       <c r="A1501" t="s">
         <v>446</v>
       </c>
-      <c r="B1501" s="1" t="s">
+      <c r="B1501" t="s">
         <v>215</v>
       </c>
       <c r="C1501">
@@ -90137,7 +90143,7 @@
       <c r="A1502" t="s">
         <v>446</v>
       </c>
-      <c r="B1502" s="1" t="s">
+      <c r="B1502" t="s">
         <v>57</v>
       </c>
       <c r="C1502">
@@ -90196,7 +90202,7 @@
       <c r="A1503" t="s">
         <v>446</v>
       </c>
-      <c r="B1503" s="1" t="s">
+      <c r="B1503" t="s">
         <v>316</v>
       </c>
       <c r="C1503">
@@ -90249,7 +90255,7 @@
       <c r="A1504" t="s">
         <v>446</v>
       </c>
-      <c r="B1504" s="1" t="s">
+      <c r="B1504" t="s">
         <v>401</v>
       </c>
       <c r="C1504">
@@ -90311,7 +90317,7 @@
       <c r="A1505" t="s">
         <v>446</v>
       </c>
-      <c r="B1505" s="1" t="s">
+      <c r="B1505" t="s">
         <v>64</v>
       </c>
       <c r="C1505">
@@ -90364,7 +90370,7 @@
       <c r="A1506" t="s">
         <v>446</v>
       </c>
-      <c r="B1506" s="1" t="s">
+      <c r="B1506" t="s">
         <v>55</v>
       </c>
       <c r="C1506">
@@ -90423,7 +90429,7 @@
       <c r="A1507" t="s">
         <v>446</v>
       </c>
-      <c r="B1507" s="1" t="s">
+      <c r="B1507" t="s">
         <v>175</v>
       </c>
       <c r="C1507">
@@ -90485,7 +90491,7 @@
       <c r="A1508" t="s">
         <v>446</v>
       </c>
-      <c r="B1508" s="1" t="s">
+      <c r="B1508" t="s">
         <v>270</v>
       </c>
       <c r="C1508">
@@ -90538,7 +90544,7 @@
       <c r="A1509" t="s">
         <v>446</v>
       </c>
-      <c r="B1509" s="1" t="s">
+      <c r="B1509" t="s">
         <v>52</v>
       </c>
       <c r="C1509">
@@ -90600,7 +90606,7 @@
       <c r="A1510" t="s">
         <v>446</v>
       </c>
-      <c r="B1510" s="1" t="s">
+      <c r="B1510" t="s">
         <v>51</v>
       </c>
       <c r="C1510">
@@ -90662,7 +90668,7 @@
       <c r="A1511" t="s">
         <v>446</v>
       </c>
-      <c r="B1511" s="1" t="s">
+      <c r="B1511" t="s">
         <v>133</v>
       </c>
       <c r="C1511">
@@ -90715,7 +90721,7 @@
       <c r="A1512" t="s">
         <v>446</v>
       </c>
-      <c r="B1512" s="1" t="s">
+      <c r="B1512" t="s">
         <v>447</v>
       </c>
       <c r="C1512">
@@ -90768,7 +90774,7 @@
       <c r="A1513" t="s">
         <v>446</v>
       </c>
-      <c r="B1513" s="1" t="s">
+      <c r="B1513" t="s">
         <v>138</v>
       </c>
       <c r="C1513">
@@ -90821,7 +90827,7 @@
       <c r="A1514" t="s">
         <v>446</v>
       </c>
-      <c r="B1514" s="1" t="s">
+      <c r="B1514" t="s">
         <v>69</v>
       </c>
       <c r="C1514">
@@ -90880,7 +90886,7 @@
       <c r="A1515" t="s">
         <v>446</v>
       </c>
-      <c r="B1515" s="1" t="s">
+      <c r="B1515" t="s">
         <v>146</v>
       </c>
       <c r="C1515">
@@ -90933,7 +90939,7 @@
       <c r="A1516" t="s">
         <v>446</v>
       </c>
-      <c r="B1516" s="1" t="s">
+      <c r="B1516" t="s">
         <v>209</v>
       </c>
       <c r="C1516">
@@ -90992,7 +90998,7 @@
       <c r="A1517" t="s">
         <v>446</v>
       </c>
-      <c r="B1517" s="1" t="s">
+      <c r="B1517" t="s">
         <v>167</v>
       </c>
       <c r="C1517">
@@ -91051,7 +91057,7 @@
       <c r="A1518" t="s">
         <v>446</v>
       </c>
-      <c r="B1518" s="1" t="s">
+      <c r="B1518" t="s">
         <v>172</v>
       </c>
       <c r="C1518">
@@ -91113,7 +91119,7 @@
       <c r="A1519" t="s">
         <v>446</v>
       </c>
-      <c r="B1519" s="1" t="s">
+      <c r="B1519" t="s">
         <v>432</v>
       </c>
       <c r="C1519">
@@ -91166,7 +91172,7 @@
       <c r="A1520" t="s">
         <v>446</v>
       </c>
-      <c r="B1520" s="1" t="s">
+      <c r="B1520" t="s">
         <v>159</v>
       </c>
       <c r="C1520">
@@ -91228,7 +91234,7 @@
       <c r="A1521" t="s">
         <v>446</v>
       </c>
-      <c r="B1521" s="1" t="s">
+      <c r="B1521" t="s">
         <v>67</v>
       </c>
       <c r="C1521">
@@ -91290,7 +91296,7 @@
       <c r="A1522" t="s">
         <v>448</v>
       </c>
-      <c r="B1522" s="1" t="s">
+      <c r="B1522" t="s">
         <v>244</v>
       </c>
       <c r="C1522">
@@ -91352,7 +91358,7 @@
       <c r="A1523" t="s">
         <v>448</v>
       </c>
-      <c r="B1523" s="1" t="s">
+      <c r="B1523" t="s">
         <v>449</v>
       </c>
       <c r="C1523">
@@ -91405,7 +91411,7 @@
       <c r="A1524" t="s">
         <v>448</v>
       </c>
-      <c r="B1524" s="1" t="s">
+      <c r="B1524" t="s">
         <v>450</v>
       </c>
       <c r="C1524">
@@ -91458,7 +91464,7 @@
       <c r="A1525" t="s">
         <v>448</v>
       </c>
-      <c r="B1525" s="1" t="s">
+      <c r="B1525" t="s">
         <v>342</v>
       </c>
       <c r="C1525">
@@ -91520,7 +91526,7 @@
       <c r="A1526" t="s">
         <v>448</v>
       </c>
-      <c r="B1526" s="1" t="s">
+      <c r="B1526" t="s">
         <v>451</v>
       </c>
       <c r="C1526">
@@ -91582,7 +91588,7 @@
       <c r="A1527" t="s">
         <v>448</v>
       </c>
-      <c r="B1527" s="1" t="s">
+      <c r="B1527" t="s">
         <v>250</v>
       </c>
       <c r="C1527">
@@ -91644,7 +91650,7 @@
       <c r="A1528" t="s">
         <v>448</v>
       </c>
-      <c r="B1528" s="1" t="s">
+      <c r="B1528" t="s">
         <v>452</v>
       </c>
       <c r="C1528">
@@ -91706,7 +91712,7 @@
       <c r="A1529" t="s">
         <v>448</v>
       </c>
-      <c r="B1529" s="1" t="s">
+      <c r="B1529" t="s">
         <v>239</v>
       </c>
       <c r="C1529">
@@ -91768,7 +91774,7 @@
       <c r="A1530" t="s">
         <v>448</v>
       </c>
-      <c r="B1530" s="1" t="s">
+      <c r="B1530" t="s">
         <v>240</v>
       </c>
       <c r="C1530">
@@ -91830,7 +91836,7 @@
       <c r="A1531" t="s">
         <v>448</v>
       </c>
-      <c r="B1531" s="1" t="s">
+      <c r="B1531" t="s">
         <v>245</v>
       </c>
       <c r="C1531">
@@ -91889,7 +91895,7 @@
       <c r="A1532" t="s">
         <v>448</v>
       </c>
-      <c r="B1532" s="1" t="s">
+      <c r="B1532" t="s">
         <v>453</v>
       </c>
       <c r="C1532">
@@ -91948,7 +91954,7 @@
       <c r="A1533" t="s">
         <v>448</v>
       </c>
-      <c r="B1533" s="1" t="s">
+      <c r="B1533" t="s">
         <v>313</v>
       </c>
       <c r="C1533">
@@ -92010,7 +92016,7 @@
       <c r="A1534" t="s">
         <v>448</v>
       </c>
-      <c r="B1534" s="1" t="s">
+      <c r="B1534" t="s">
         <v>375</v>
       </c>
       <c r="C1534">
@@ -92069,7 +92075,7 @@
       <c r="A1535" t="s">
         <v>448</v>
       </c>
-      <c r="B1535" s="1" t="s">
+      <c r="B1535" t="s">
         <v>321</v>
       </c>
       <c r="C1535">
@@ -92131,7 +92137,7 @@
       <c r="A1536" t="s">
         <v>448</v>
       </c>
-      <c r="B1536" s="1" t="s">
+      <c r="B1536" t="s">
         <v>454</v>
       </c>
       <c r="C1536">
@@ -92184,7 +92190,7 @@
       <c r="A1537" t="s">
         <v>448</v>
       </c>
-      <c r="B1537" s="1" t="s">
+      <c r="B1537" t="s">
         <v>252</v>
       </c>
       <c r="C1537">
@@ -92237,7 +92243,7 @@
       <c r="A1538" t="s">
         <v>448</v>
       </c>
-      <c r="B1538" s="1" t="s">
+      <c r="B1538" t="s">
         <v>344</v>
       </c>
       <c r="C1538">
@@ -92296,7 +92302,7 @@
       <c r="A1539" t="s">
         <v>448</v>
       </c>
-      <c r="B1539" s="1" t="s">
+      <c r="B1539" t="s">
         <v>455</v>
       </c>
       <c r="C1539">
@@ -92358,7 +92364,7 @@
       <c r="A1540" t="s">
         <v>448</v>
       </c>
-      <c r="B1540" s="1" t="s">
+      <c r="B1540" t="s">
         <v>456</v>
       </c>
       <c r="C1540">
@@ -92411,7 +92417,7 @@
       <c r="A1541" t="s">
         <v>448</v>
       </c>
-      <c r="B1541" s="1" t="s">
+      <c r="B1541" t="s">
         <v>336</v>
       </c>
       <c r="C1541">
@@ -92470,7 +92476,7 @@
       <c r="A1542" t="s">
         <v>448</v>
       </c>
-      <c r="B1542" s="1" t="s">
+      <c r="B1542" t="s">
         <v>358</v>
       </c>
       <c r="C1542">
@@ -92523,7 +92529,7 @@
       <c r="A1543" t="s">
         <v>448</v>
       </c>
-      <c r="B1543" s="1" t="s">
+      <c r="B1543" t="s">
         <v>155</v>
       </c>
       <c r="C1543">
@@ -116707,6 +116713,2530 @@
         <v>0</v>
       </c>
       <c r="T1954">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1955" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1955">
+        <v>1</v>
+      </c>
+      <c r="D1955">
+        <v>0</v>
+      </c>
+      <c r="E1955">
+        <v>0</v>
+      </c>
+      <c r="F1955">
+        <v>0</v>
+      </c>
+      <c r="I1955">
+        <v>0</v>
+      </c>
+      <c r="J1955">
+        <v>0</v>
+      </c>
+      <c r="L1955">
+        <v>0</v>
+      </c>
+      <c r="M1955">
+        <v>0</v>
+      </c>
+      <c r="N1955">
+        <v>0</v>
+      </c>
+      <c r="O1955">
+        <v>0</v>
+      </c>
+      <c r="P1955">
+        <v>0</v>
+      </c>
+      <c r="Q1955">
+        <v>0</v>
+      </c>
+      <c r="R1955">
+        <v>0</v>
+      </c>
+      <c r="S1955">
+        <v>0</v>
+      </c>
+      <c r="T1955">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1956" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1956">
+        <v>1</v>
+      </c>
+      <c r="D1956">
+        <v>0</v>
+      </c>
+      <c r="E1956">
+        <v>0</v>
+      </c>
+      <c r="F1956">
+        <v>0</v>
+      </c>
+      <c r="I1956">
+        <v>0</v>
+      </c>
+      <c r="J1956">
+        <v>0</v>
+      </c>
+      <c r="L1956">
+        <v>0</v>
+      </c>
+      <c r="M1956">
+        <v>0</v>
+      </c>
+      <c r="N1956">
+        <v>0</v>
+      </c>
+      <c r="O1956">
+        <v>0</v>
+      </c>
+      <c r="P1956">
+        <v>0</v>
+      </c>
+      <c r="Q1956">
+        <v>0</v>
+      </c>
+      <c r="R1956">
+        <v>0</v>
+      </c>
+      <c r="S1956">
+        <v>0</v>
+      </c>
+      <c r="T1956">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1957" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1957">
+        <v>1</v>
+      </c>
+      <c r="D1957">
+        <v>1</v>
+      </c>
+      <c r="E1957">
+        <v>1</v>
+      </c>
+      <c r="F1957">
+        <v>47</v>
+      </c>
+      <c r="H1957" t="s">
+        <v>207</v>
+      </c>
+      <c r="I1957">
+        <v>0</v>
+      </c>
+      <c r="J1957">
+        <v>0</v>
+      </c>
+      <c r="K1957">
+        <v>109.3</v>
+      </c>
+      <c r="L1957">
+        <v>43</v>
+      </c>
+      <c r="M1957">
+        <v>15</v>
+      </c>
+      <c r="N1957">
+        <v>5</v>
+      </c>
+      <c r="O1957">
+        <v>0</v>
+      </c>
+      <c r="P1957">
+        <v>35.880000000000003</v>
+      </c>
+      <c r="Q1957">
+        <v>0</v>
+      </c>
+      <c r="R1957">
+        <v>0</v>
+      </c>
+      <c r="S1957">
+        <v>0</v>
+      </c>
+      <c r="T1957">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1958" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1958">
+        <v>1</v>
+      </c>
+      <c r="D1958">
+        <v>0</v>
+      </c>
+      <c r="E1958">
+        <v>0</v>
+      </c>
+      <c r="F1958">
+        <v>0</v>
+      </c>
+      <c r="I1958">
+        <v>0</v>
+      </c>
+      <c r="J1958">
+        <v>0</v>
+      </c>
+      <c r="L1958">
+        <v>0</v>
+      </c>
+      <c r="M1958">
+        <v>0</v>
+      </c>
+      <c r="N1958">
+        <v>0</v>
+      </c>
+      <c r="O1958">
+        <v>0</v>
+      </c>
+      <c r="P1958">
+        <v>0</v>
+      </c>
+      <c r="Q1958">
+        <v>0</v>
+      </c>
+      <c r="R1958">
+        <v>0</v>
+      </c>
+      <c r="S1958">
+        <v>0</v>
+      </c>
+      <c r="T1958">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1959" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1959">
+        <v>1</v>
+      </c>
+      <c r="D1959">
+        <v>0</v>
+      </c>
+      <c r="E1959">
+        <v>0</v>
+      </c>
+      <c r="F1959">
+        <v>0</v>
+      </c>
+      <c r="I1959">
+        <v>0</v>
+      </c>
+      <c r="J1959">
+        <v>0</v>
+      </c>
+      <c r="L1959">
+        <v>0</v>
+      </c>
+      <c r="M1959">
+        <v>0</v>
+      </c>
+      <c r="N1959">
+        <v>0</v>
+      </c>
+      <c r="O1959">
+        <v>0</v>
+      </c>
+      <c r="P1959">
+        <v>0</v>
+      </c>
+      <c r="Q1959">
+        <v>0</v>
+      </c>
+      <c r="R1959">
+        <v>0</v>
+      </c>
+      <c r="S1959">
+        <v>0</v>
+      </c>
+      <c r="T1959">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1960" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1960">
+        <v>1</v>
+      </c>
+      <c r="D1960">
+        <v>0</v>
+      </c>
+      <c r="E1960">
+        <v>0</v>
+      </c>
+      <c r="F1960">
+        <v>0</v>
+      </c>
+      <c r="I1960">
+        <v>0</v>
+      </c>
+      <c r="J1960">
+        <v>0</v>
+      </c>
+      <c r="L1960">
+        <v>0</v>
+      </c>
+      <c r="M1960">
+        <v>0</v>
+      </c>
+      <c r="N1960">
+        <v>0</v>
+      </c>
+      <c r="O1960">
+        <v>0</v>
+      </c>
+      <c r="P1960">
+        <v>0</v>
+      </c>
+      <c r="Q1960">
+        <v>0</v>
+      </c>
+      <c r="R1960">
+        <v>0</v>
+      </c>
+      <c r="S1960">
+        <v>1</v>
+      </c>
+      <c r="T1960">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1961" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1961">
+        <v>1</v>
+      </c>
+      <c r="D1961">
+        <v>0</v>
+      </c>
+      <c r="E1961">
+        <v>0</v>
+      </c>
+      <c r="F1961">
+        <v>0</v>
+      </c>
+      <c r="I1961">
+        <v>0</v>
+      </c>
+      <c r="J1961">
+        <v>0</v>
+      </c>
+      <c r="L1961">
+        <v>0</v>
+      </c>
+      <c r="M1961">
+        <v>0</v>
+      </c>
+      <c r="N1961">
+        <v>0</v>
+      </c>
+      <c r="O1961">
+        <v>0</v>
+      </c>
+      <c r="P1961">
+        <v>0</v>
+      </c>
+      <c r="Q1961">
+        <v>0</v>
+      </c>
+      <c r="R1961">
+        <v>0</v>
+      </c>
+      <c r="S1961">
+        <v>0</v>
+      </c>
+      <c r="T1961">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1962" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1962">
+        <v>1</v>
+      </c>
+      <c r="D1962">
+        <v>1</v>
+      </c>
+      <c r="E1962">
+        <v>0</v>
+      </c>
+      <c r="F1962">
+        <v>34</v>
+      </c>
+      <c r="G1962">
+        <v>34</v>
+      </c>
+      <c r="H1962">
+        <v>34</v>
+      </c>
+      <c r="I1962">
+        <v>0</v>
+      </c>
+      <c r="J1962">
+        <v>0</v>
+      </c>
+      <c r="K1962">
+        <v>130.77000000000001</v>
+      </c>
+      <c r="L1962">
+        <v>26</v>
+      </c>
+      <c r="M1962">
+        <v>15</v>
+      </c>
+      <c r="N1962">
+        <v>7</v>
+      </c>
+      <c r="O1962">
+        <v>0</v>
+      </c>
+      <c r="P1962">
+        <v>26.15</v>
+      </c>
+      <c r="Q1962">
+        <v>0</v>
+      </c>
+      <c r="R1962">
+        <v>0</v>
+      </c>
+      <c r="S1962">
+        <v>0</v>
+      </c>
+      <c r="T1962">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1963" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1963">
+        <v>1</v>
+      </c>
+      <c r="D1963">
+        <v>0</v>
+      </c>
+      <c r="E1963">
+        <v>0</v>
+      </c>
+      <c r="F1963">
+        <v>0</v>
+      </c>
+      <c r="I1963">
+        <v>0</v>
+      </c>
+      <c r="J1963">
+        <v>0</v>
+      </c>
+      <c r="L1963">
+        <v>0</v>
+      </c>
+      <c r="M1963">
+        <v>0</v>
+      </c>
+      <c r="N1963">
+        <v>0</v>
+      </c>
+      <c r="O1963">
+        <v>0</v>
+      </c>
+      <c r="P1963">
+        <v>0</v>
+      </c>
+      <c r="Q1963">
+        <v>0</v>
+      </c>
+      <c r="R1963">
+        <v>0</v>
+      </c>
+      <c r="S1963">
+        <v>0</v>
+      </c>
+      <c r="T1963">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1964" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1964">
+        <v>1</v>
+      </c>
+      <c r="D1964">
+        <v>1</v>
+      </c>
+      <c r="E1964">
+        <v>1</v>
+      </c>
+      <c r="F1964">
+        <v>28</v>
+      </c>
+      <c r="H1964" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1964">
+        <v>0</v>
+      </c>
+      <c r="J1964">
+        <v>0</v>
+      </c>
+      <c r="K1964">
+        <v>100</v>
+      </c>
+      <c r="L1964">
+        <v>28</v>
+      </c>
+      <c r="M1964">
+        <v>11</v>
+      </c>
+      <c r="N1964">
+        <v>3</v>
+      </c>
+      <c r="O1964">
+        <v>0</v>
+      </c>
+      <c r="P1964">
+        <v>21.37</v>
+      </c>
+      <c r="Q1964">
+        <v>0</v>
+      </c>
+      <c r="R1964">
+        <v>0</v>
+      </c>
+      <c r="S1964">
+        <v>0</v>
+      </c>
+      <c r="T1964">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1965" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1965">
+        <v>1</v>
+      </c>
+      <c r="D1965">
+        <v>0</v>
+      </c>
+      <c r="E1965">
+        <v>0</v>
+      </c>
+      <c r="F1965">
+        <v>0</v>
+      </c>
+      <c r="I1965">
+        <v>0</v>
+      </c>
+      <c r="J1965">
+        <v>0</v>
+      </c>
+      <c r="L1965">
+        <v>0</v>
+      </c>
+      <c r="M1965">
+        <v>0</v>
+      </c>
+      <c r="N1965">
+        <v>0</v>
+      </c>
+      <c r="O1965">
+        <v>0</v>
+      </c>
+      <c r="P1965">
+        <v>0</v>
+      </c>
+      <c r="Q1965">
+        <v>0</v>
+      </c>
+      <c r="R1965">
+        <v>0</v>
+      </c>
+      <c r="S1965">
+        <v>0</v>
+      </c>
+      <c r="T1965">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1966" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1966">
+        <v>1</v>
+      </c>
+      <c r="D1966">
+        <v>1</v>
+      </c>
+      <c r="E1966">
+        <v>0</v>
+      </c>
+      <c r="F1966">
+        <v>36</v>
+      </c>
+      <c r="G1966">
+        <v>36</v>
+      </c>
+      <c r="H1966">
+        <v>36</v>
+      </c>
+      <c r="I1966">
+        <v>0</v>
+      </c>
+      <c r="J1966">
+        <v>0</v>
+      </c>
+      <c r="K1966">
+        <v>171.43</v>
+      </c>
+      <c r="L1966">
+        <v>21</v>
+      </c>
+      <c r="M1966">
+        <v>9</v>
+      </c>
+      <c r="N1966">
+        <v>6</v>
+      </c>
+      <c r="O1966">
+        <v>1</v>
+      </c>
+      <c r="P1966">
+        <v>27.48</v>
+      </c>
+      <c r="Q1966">
+        <v>1</v>
+      </c>
+      <c r="R1966">
+        <v>0</v>
+      </c>
+      <c r="S1966">
+        <v>0</v>
+      </c>
+      <c r="T1966">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1967" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1967">
+        <v>1</v>
+      </c>
+      <c r="D1967">
+        <v>1</v>
+      </c>
+      <c r="E1967">
+        <v>0</v>
+      </c>
+      <c r="F1967">
+        <v>30</v>
+      </c>
+      <c r="G1967">
+        <v>30</v>
+      </c>
+      <c r="H1967">
+        <v>30</v>
+      </c>
+      <c r="I1967">
+        <v>0</v>
+      </c>
+      <c r="J1967">
+        <v>0</v>
+      </c>
+      <c r="K1967">
+        <v>75</v>
+      </c>
+      <c r="L1967">
+        <v>40</v>
+      </c>
+      <c r="M1967">
+        <v>19</v>
+      </c>
+      <c r="N1967">
+        <v>2</v>
+      </c>
+      <c r="O1967">
+        <v>0</v>
+      </c>
+      <c r="P1967">
+        <v>23.08</v>
+      </c>
+      <c r="Q1967">
+        <v>0</v>
+      </c>
+      <c r="R1967">
+        <v>0</v>
+      </c>
+      <c r="S1967">
+        <v>0</v>
+      </c>
+      <c r="T1967">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1968" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1968">
+        <v>1</v>
+      </c>
+      <c r="D1968">
+        <v>0</v>
+      </c>
+      <c r="E1968">
+        <v>0</v>
+      </c>
+      <c r="F1968">
+        <v>0</v>
+      </c>
+      <c r="I1968">
+        <v>0</v>
+      </c>
+      <c r="J1968">
+        <v>0</v>
+      </c>
+      <c r="L1968">
+        <v>0</v>
+      </c>
+      <c r="M1968">
+        <v>0</v>
+      </c>
+      <c r="N1968">
+        <v>0</v>
+      </c>
+      <c r="O1968">
+        <v>0</v>
+      </c>
+      <c r="P1968">
+        <v>0</v>
+      </c>
+      <c r="Q1968">
+        <v>0</v>
+      </c>
+      <c r="R1968">
+        <v>0</v>
+      </c>
+      <c r="S1968">
+        <v>0</v>
+      </c>
+      <c r="T1968">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1969" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1969">
+        <v>1</v>
+      </c>
+      <c r="D1969">
+        <v>1</v>
+      </c>
+      <c r="E1969">
+        <v>0</v>
+      </c>
+      <c r="F1969">
+        <v>5</v>
+      </c>
+      <c r="G1969">
+        <v>5</v>
+      </c>
+      <c r="H1969">
+        <v>5</v>
+      </c>
+      <c r="I1969">
+        <v>0</v>
+      </c>
+      <c r="J1969">
+        <v>0</v>
+      </c>
+      <c r="K1969">
+        <v>45.45</v>
+      </c>
+      <c r="L1969">
+        <v>11</v>
+      </c>
+      <c r="M1969">
+        <v>7</v>
+      </c>
+      <c r="N1969">
+        <v>0</v>
+      </c>
+      <c r="O1969">
+        <v>0</v>
+      </c>
+      <c r="P1969">
+        <v>3.82</v>
+      </c>
+      <c r="Q1969">
+        <v>0</v>
+      </c>
+      <c r="R1969">
+        <v>0</v>
+      </c>
+      <c r="S1969">
+        <v>0</v>
+      </c>
+      <c r="T1969">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1970" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1970">
+        <v>1</v>
+      </c>
+      <c r="D1970">
+        <v>1</v>
+      </c>
+      <c r="E1970">
+        <v>1</v>
+      </c>
+      <c r="F1970">
+        <v>32</v>
+      </c>
+      <c r="H1970" t="s">
+        <v>440</v>
+      </c>
+      <c r="I1970">
+        <v>0</v>
+      </c>
+      <c r="J1970">
+        <v>0</v>
+      </c>
+      <c r="K1970">
+        <v>103.23</v>
+      </c>
+      <c r="L1970">
+        <v>31</v>
+      </c>
+      <c r="M1970">
+        <v>14</v>
+      </c>
+      <c r="N1970">
+        <v>4</v>
+      </c>
+      <c r="O1970">
+        <v>0</v>
+      </c>
+      <c r="P1970">
+        <v>24.62</v>
+      </c>
+      <c r="Q1970">
+        <v>0</v>
+      </c>
+      <c r="R1970">
+        <v>0</v>
+      </c>
+      <c r="S1970">
+        <v>0</v>
+      </c>
+      <c r="T1970">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1971" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1971">
+        <v>1</v>
+      </c>
+      <c r="D1971">
+        <v>1</v>
+      </c>
+      <c r="E1971">
+        <v>0</v>
+      </c>
+      <c r="F1971">
+        <v>0</v>
+      </c>
+      <c r="G1971">
+        <v>0</v>
+      </c>
+      <c r="H1971">
+        <v>0</v>
+      </c>
+      <c r="I1971">
+        <v>0</v>
+      </c>
+      <c r="J1971">
+        <v>0</v>
+      </c>
+      <c r="K1971">
+        <v>0</v>
+      </c>
+      <c r="L1971">
+        <v>1</v>
+      </c>
+      <c r="M1971">
+        <v>1</v>
+      </c>
+      <c r="N1971">
+        <v>0</v>
+      </c>
+      <c r="O1971">
+        <v>0</v>
+      </c>
+      <c r="P1971">
+        <v>0</v>
+      </c>
+      <c r="Q1971">
+        <v>0</v>
+      </c>
+      <c r="R1971">
+        <v>0</v>
+      </c>
+      <c r="S1971">
+        <v>0</v>
+      </c>
+      <c r="T1971">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1972" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1972">
+        <v>1</v>
+      </c>
+      <c r="D1972">
+        <v>0</v>
+      </c>
+      <c r="E1972">
+        <v>0</v>
+      </c>
+      <c r="F1972">
+        <v>0</v>
+      </c>
+      <c r="I1972">
+        <v>0</v>
+      </c>
+      <c r="J1972">
+        <v>0</v>
+      </c>
+      <c r="L1972">
+        <v>0</v>
+      </c>
+      <c r="M1972">
+        <v>0</v>
+      </c>
+      <c r="N1972">
+        <v>0</v>
+      </c>
+      <c r="O1972">
+        <v>0</v>
+      </c>
+      <c r="P1972">
+        <v>0</v>
+      </c>
+      <c r="Q1972">
+        <v>0</v>
+      </c>
+      <c r="R1972">
+        <v>0</v>
+      </c>
+      <c r="S1972">
+        <v>0</v>
+      </c>
+      <c r="T1972">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1973" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>502</v>
+      </c>
+      <c r="C1973">
+        <v>1</v>
+      </c>
+      <c r="D1973">
+        <v>1</v>
+      </c>
+      <c r="E1973">
+        <v>0</v>
+      </c>
+      <c r="F1973">
+        <v>17</v>
+      </c>
+      <c r="G1973">
+        <v>17</v>
+      </c>
+      <c r="H1973">
+        <v>17</v>
+      </c>
+      <c r="I1973">
+        <v>0</v>
+      </c>
+      <c r="J1973">
+        <v>0</v>
+      </c>
+      <c r="K1973">
+        <v>100</v>
+      </c>
+      <c r="L1973">
+        <v>17</v>
+      </c>
+      <c r="M1973">
+        <v>12</v>
+      </c>
+      <c r="N1973">
+        <v>4</v>
+      </c>
+      <c r="O1973">
+        <v>0</v>
+      </c>
+      <c r="P1973">
+        <v>13.08</v>
+      </c>
+      <c r="Q1973">
+        <v>0</v>
+      </c>
+      <c r="R1973">
+        <v>0</v>
+      </c>
+      <c r="S1973">
+        <v>0</v>
+      </c>
+      <c r="T1973">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1974" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1974">
+        <v>1</v>
+      </c>
+      <c r="D1974">
+        <v>0</v>
+      </c>
+      <c r="E1974">
+        <v>0</v>
+      </c>
+      <c r="F1974">
+        <v>0</v>
+      </c>
+      <c r="I1974">
+        <v>0</v>
+      </c>
+      <c r="J1974">
+        <v>0</v>
+      </c>
+      <c r="L1974">
+        <v>0</v>
+      </c>
+      <c r="M1974">
+        <v>0</v>
+      </c>
+      <c r="N1974">
+        <v>0</v>
+      </c>
+      <c r="O1974">
+        <v>0</v>
+      </c>
+      <c r="P1974">
+        <v>0</v>
+      </c>
+      <c r="Q1974">
+        <v>0</v>
+      </c>
+      <c r="R1974">
+        <v>0</v>
+      </c>
+      <c r="S1974">
+        <v>0</v>
+      </c>
+      <c r="T1974">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1975" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1975">
+        <v>1</v>
+      </c>
+      <c r="D1975">
+        <v>0</v>
+      </c>
+      <c r="E1975">
+        <v>0</v>
+      </c>
+      <c r="F1975">
+        <v>0</v>
+      </c>
+      <c r="I1975">
+        <v>0</v>
+      </c>
+      <c r="J1975">
+        <v>0</v>
+      </c>
+      <c r="L1975">
+        <v>0</v>
+      </c>
+      <c r="M1975">
+        <v>0</v>
+      </c>
+      <c r="N1975">
+        <v>0</v>
+      </c>
+      <c r="O1975">
+        <v>0</v>
+      </c>
+      <c r="P1975">
+        <v>0</v>
+      </c>
+      <c r="Q1975">
+        <v>0</v>
+      </c>
+      <c r="R1975">
+        <v>0</v>
+      </c>
+      <c r="S1975">
+        <v>0</v>
+      </c>
+      <c r="T1975">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1976" t="s">
+        <v>506</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1976">
+        <v>1</v>
+      </c>
+      <c r="D1976">
+        <v>1</v>
+      </c>
+      <c r="E1976">
+        <v>1</v>
+      </c>
+      <c r="F1976">
+        <v>4</v>
+      </c>
+      <c r="H1976" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1976">
+        <v>0</v>
+      </c>
+      <c r="J1976">
+        <v>0</v>
+      </c>
+      <c r="K1976">
+        <v>57.14</v>
+      </c>
+      <c r="L1976">
+        <v>7</v>
+      </c>
+      <c r="M1976">
+        <v>3</v>
+      </c>
+      <c r="N1976">
+        <v>0</v>
+      </c>
+      <c r="O1976">
+        <v>0</v>
+      </c>
+      <c r="P1976">
+        <v>3.08</v>
+      </c>
+      <c r="Q1976">
+        <v>0</v>
+      </c>
+      <c r="R1976">
+        <v>0</v>
+      </c>
+      <c r="S1976">
+        <v>0</v>
+      </c>
+      <c r="T1976">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1977" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>292</v>
+      </c>
+      <c r="C1977">
+        <v>1</v>
+      </c>
+      <c r="D1977">
+        <v>1</v>
+      </c>
+      <c r="E1977">
+        <v>0</v>
+      </c>
+      <c r="F1977">
+        <v>29</v>
+      </c>
+      <c r="G1977">
+        <v>29</v>
+      </c>
+      <c r="H1977">
+        <v>29</v>
+      </c>
+      <c r="I1977">
+        <v>0</v>
+      </c>
+      <c r="J1977">
+        <v>0</v>
+      </c>
+      <c r="K1977">
+        <v>80.56</v>
+      </c>
+      <c r="L1977">
+        <v>36</v>
+      </c>
+      <c r="M1977">
+        <v>14</v>
+      </c>
+      <c r="N1977">
+        <v>1</v>
+      </c>
+      <c r="O1977">
+        <v>0</v>
+      </c>
+      <c r="P1977">
+        <v>24.37</v>
+      </c>
+      <c r="Q1977">
+        <v>0</v>
+      </c>
+      <c r="R1977">
+        <v>0</v>
+      </c>
+      <c r="S1977">
+        <v>0</v>
+      </c>
+      <c r="T1977">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1978" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>119</v>
+      </c>
+      <c r="C1978">
+        <v>1</v>
+      </c>
+      <c r="D1978">
+        <v>0</v>
+      </c>
+      <c r="E1978">
+        <v>0</v>
+      </c>
+      <c r="F1978">
+        <v>0</v>
+      </c>
+      <c r="I1978">
+        <v>0</v>
+      </c>
+      <c r="J1978">
+        <v>0</v>
+      </c>
+      <c r="L1978">
+        <v>0</v>
+      </c>
+      <c r="M1978">
+        <v>0</v>
+      </c>
+      <c r="N1978">
+        <v>0</v>
+      </c>
+      <c r="O1978">
+        <v>0</v>
+      </c>
+      <c r="P1978">
+        <v>0</v>
+      </c>
+      <c r="Q1978">
+        <v>0</v>
+      </c>
+      <c r="R1978">
+        <v>0</v>
+      </c>
+      <c r="S1978">
+        <v>0</v>
+      </c>
+      <c r="T1978">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1979" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1979">
+        <v>1</v>
+      </c>
+      <c r="D1979">
+        <v>1</v>
+      </c>
+      <c r="E1979">
+        <v>0</v>
+      </c>
+      <c r="F1979">
+        <v>10</v>
+      </c>
+      <c r="G1979">
+        <v>10</v>
+      </c>
+      <c r="H1979">
+        <v>10</v>
+      </c>
+      <c r="I1979">
+        <v>0</v>
+      </c>
+      <c r="J1979">
+        <v>0</v>
+      </c>
+      <c r="K1979">
+        <v>71.430000000000007</v>
+      </c>
+      <c r="L1979">
+        <v>14</v>
+      </c>
+      <c r="M1979">
+        <v>7</v>
+      </c>
+      <c r="N1979">
+        <v>1</v>
+      </c>
+      <c r="O1979">
+        <v>0</v>
+      </c>
+      <c r="P1979">
+        <v>8.33</v>
+      </c>
+      <c r="Q1979">
+        <v>0</v>
+      </c>
+      <c r="R1979">
+        <v>0</v>
+      </c>
+      <c r="S1979">
+        <v>0</v>
+      </c>
+      <c r="T1979">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1980" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>258</v>
+      </c>
+      <c r="C1980">
+        <v>1</v>
+      </c>
+      <c r="D1980">
+        <v>0</v>
+      </c>
+      <c r="E1980">
+        <v>0</v>
+      </c>
+      <c r="F1980">
+        <v>0</v>
+      </c>
+      <c r="I1980">
+        <v>0</v>
+      </c>
+      <c r="J1980">
+        <v>0</v>
+      </c>
+      <c r="L1980">
+        <v>0</v>
+      </c>
+      <c r="M1980">
+        <v>0</v>
+      </c>
+      <c r="N1980">
+        <v>0</v>
+      </c>
+      <c r="O1980">
+        <v>0</v>
+      </c>
+      <c r="P1980">
+        <v>0</v>
+      </c>
+      <c r="Q1980">
+        <v>0</v>
+      </c>
+      <c r="R1980">
+        <v>0</v>
+      </c>
+      <c r="S1980">
+        <v>0</v>
+      </c>
+      <c r="T1980">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1981" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>120</v>
+      </c>
+      <c r="C1981">
+        <v>1</v>
+      </c>
+      <c r="D1981">
+        <v>1</v>
+      </c>
+      <c r="E1981">
+        <v>0</v>
+      </c>
+      <c r="F1981">
+        <v>30</v>
+      </c>
+      <c r="G1981">
+        <v>30</v>
+      </c>
+      <c r="H1981">
+        <v>30</v>
+      </c>
+      <c r="I1981">
+        <v>0</v>
+      </c>
+      <c r="J1981">
+        <v>0</v>
+      </c>
+      <c r="K1981">
+        <v>85.71</v>
+      </c>
+      <c r="L1981">
+        <v>35</v>
+      </c>
+      <c r="M1981">
+        <v>17</v>
+      </c>
+      <c r="N1981">
+        <v>4</v>
+      </c>
+      <c r="O1981">
+        <v>0</v>
+      </c>
+      <c r="P1981">
+        <v>25</v>
+      </c>
+      <c r="Q1981">
+        <v>0</v>
+      </c>
+      <c r="R1981">
+        <v>1</v>
+      </c>
+      <c r="S1981">
+        <v>0</v>
+      </c>
+      <c r="T1981">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1982" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>309</v>
+      </c>
+      <c r="C1982">
+        <v>1</v>
+      </c>
+      <c r="D1982">
+        <v>1</v>
+      </c>
+      <c r="E1982">
+        <v>1</v>
+      </c>
+      <c r="F1982">
+        <v>11</v>
+      </c>
+      <c r="H1982" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1982">
+        <v>0</v>
+      </c>
+      <c r="J1982">
+        <v>0</v>
+      </c>
+      <c r="K1982">
+        <v>84.62</v>
+      </c>
+      <c r="L1982">
+        <v>13</v>
+      </c>
+      <c r="M1982">
+        <v>6</v>
+      </c>
+      <c r="N1982">
+        <v>1</v>
+      </c>
+      <c r="O1982">
+        <v>0</v>
+      </c>
+      <c r="P1982">
+        <v>9.17</v>
+      </c>
+      <c r="Q1982">
+        <v>0</v>
+      </c>
+      <c r="R1982">
+        <v>0</v>
+      </c>
+      <c r="S1982">
+        <v>0</v>
+      </c>
+      <c r="T1982">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1983" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1983">
+        <v>1</v>
+      </c>
+      <c r="D1983">
+        <v>1</v>
+      </c>
+      <c r="E1983">
+        <v>0</v>
+      </c>
+      <c r="F1983">
+        <v>4</v>
+      </c>
+      <c r="G1983">
+        <v>4</v>
+      </c>
+      <c r="H1983">
+        <v>4</v>
+      </c>
+      <c r="I1983">
+        <v>0</v>
+      </c>
+      <c r="J1983">
+        <v>0</v>
+      </c>
+      <c r="K1983">
+        <v>200</v>
+      </c>
+      <c r="L1983">
+        <v>2</v>
+      </c>
+      <c r="M1983">
+        <v>1</v>
+      </c>
+      <c r="N1983">
+        <v>1</v>
+      </c>
+      <c r="O1983">
+        <v>0</v>
+      </c>
+      <c r="P1983">
+        <v>3.33</v>
+      </c>
+      <c r="Q1983">
+        <v>0</v>
+      </c>
+      <c r="R1983">
+        <v>0</v>
+      </c>
+      <c r="S1983">
+        <v>0</v>
+      </c>
+      <c r="T1983">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1984" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1984">
+        <v>1</v>
+      </c>
+      <c r="D1984">
+        <v>0</v>
+      </c>
+      <c r="E1984">
+        <v>0</v>
+      </c>
+      <c r="F1984">
+        <v>0</v>
+      </c>
+      <c r="I1984">
+        <v>0</v>
+      </c>
+      <c r="J1984">
+        <v>0</v>
+      </c>
+      <c r="L1984">
+        <v>0</v>
+      </c>
+      <c r="M1984">
+        <v>0</v>
+      </c>
+      <c r="N1984">
+        <v>0</v>
+      </c>
+      <c r="O1984">
+        <v>0</v>
+      </c>
+      <c r="P1984">
+        <v>0</v>
+      </c>
+      <c r="Q1984">
+        <v>0</v>
+      </c>
+      <c r="R1984">
+        <v>0</v>
+      </c>
+      <c r="S1984">
+        <v>0</v>
+      </c>
+      <c r="T1984">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1985" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1985">
+        <v>1</v>
+      </c>
+      <c r="D1985">
+        <v>0</v>
+      </c>
+      <c r="E1985">
+        <v>0</v>
+      </c>
+      <c r="F1985">
+        <v>0</v>
+      </c>
+      <c r="I1985">
+        <v>0</v>
+      </c>
+      <c r="J1985">
+        <v>0</v>
+      </c>
+      <c r="L1985">
+        <v>0</v>
+      </c>
+      <c r="M1985">
+        <v>0</v>
+      </c>
+      <c r="N1985">
+        <v>0</v>
+      </c>
+      <c r="O1985">
+        <v>0</v>
+      </c>
+      <c r="P1985">
+        <v>0</v>
+      </c>
+      <c r="Q1985">
+        <v>0</v>
+      </c>
+      <c r="R1985">
+        <v>0</v>
+      </c>
+      <c r="S1985">
+        <v>0</v>
+      </c>
+      <c r="T1985">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1986" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1986">
+        <v>1</v>
+      </c>
+      <c r="D1986">
+        <v>1</v>
+      </c>
+      <c r="E1986">
+        <v>0</v>
+      </c>
+      <c r="F1986">
+        <v>3</v>
+      </c>
+      <c r="G1986">
+        <v>3</v>
+      </c>
+      <c r="H1986">
+        <v>3</v>
+      </c>
+      <c r="I1986">
+        <v>0</v>
+      </c>
+      <c r="J1986">
+        <v>0</v>
+      </c>
+      <c r="K1986">
+        <v>42.86</v>
+      </c>
+      <c r="L1986">
+        <v>7</v>
+      </c>
+      <c r="M1986">
+        <v>4</v>
+      </c>
+      <c r="N1986">
+        <v>0</v>
+      </c>
+      <c r="O1986">
+        <v>0</v>
+      </c>
+      <c r="P1986">
+        <v>2.52</v>
+      </c>
+      <c r="Q1986">
+        <v>0</v>
+      </c>
+      <c r="R1986">
+        <v>0</v>
+      </c>
+      <c r="S1986">
+        <v>0</v>
+      </c>
+      <c r="T1986">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1987" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>145</v>
+      </c>
+      <c r="C1987">
+        <v>1</v>
+      </c>
+      <c r="D1987">
+        <v>1</v>
+      </c>
+      <c r="E1987">
+        <v>1</v>
+      </c>
+      <c r="F1987">
+        <v>5</v>
+      </c>
+      <c r="H1987" t="s">
+        <v>197</v>
+      </c>
+      <c r="I1987">
+        <v>0</v>
+      </c>
+      <c r="J1987">
+        <v>0</v>
+      </c>
+      <c r="K1987">
+        <v>55.56</v>
+      </c>
+      <c r="L1987">
+        <v>9</v>
+      </c>
+      <c r="M1987">
+        <v>5</v>
+      </c>
+      <c r="N1987">
+        <v>0</v>
+      </c>
+      <c r="O1987">
+        <v>0</v>
+      </c>
+      <c r="P1987">
+        <v>4.2</v>
+      </c>
+      <c r="Q1987">
+        <v>0</v>
+      </c>
+      <c r="R1987">
+        <v>0</v>
+      </c>
+      <c r="S1987">
+        <v>0</v>
+      </c>
+      <c r="T1987">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1988" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1988">
+        <v>1</v>
+      </c>
+      <c r="D1988">
+        <v>1</v>
+      </c>
+      <c r="E1988">
+        <v>0</v>
+      </c>
+      <c r="F1988">
+        <v>8</v>
+      </c>
+      <c r="G1988">
+        <v>8</v>
+      </c>
+      <c r="H1988">
+        <v>8</v>
+      </c>
+      <c r="I1988">
+        <v>0</v>
+      </c>
+      <c r="J1988">
+        <v>0</v>
+      </c>
+      <c r="K1988">
+        <v>72.73</v>
+      </c>
+      <c r="L1988">
+        <v>11</v>
+      </c>
+      <c r="M1988">
+        <v>6</v>
+      </c>
+      <c r="N1988">
+        <v>1</v>
+      </c>
+      <c r="O1988">
+        <v>0</v>
+      </c>
+      <c r="P1988">
+        <v>6.67</v>
+      </c>
+      <c r="Q1988">
+        <v>1</v>
+      </c>
+      <c r="R1988">
+        <v>0</v>
+      </c>
+      <c r="S1988">
+        <v>0</v>
+      </c>
+      <c r="T1988">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1989" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1989">
+        <v>1</v>
+      </c>
+      <c r="D1989">
+        <v>1</v>
+      </c>
+      <c r="E1989">
+        <v>1</v>
+      </c>
+      <c r="F1989">
+        <v>4</v>
+      </c>
+      <c r="H1989" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1989">
+        <v>0</v>
+      </c>
+      <c r="J1989">
+        <v>0</v>
+      </c>
+      <c r="K1989">
+        <v>80</v>
+      </c>
+      <c r="L1989">
+        <v>5</v>
+      </c>
+      <c r="M1989">
+        <v>2</v>
+      </c>
+      <c r="N1989">
+        <v>0</v>
+      </c>
+      <c r="O1989">
+        <v>0</v>
+      </c>
+      <c r="P1989">
+        <v>3.33</v>
+      </c>
+      <c r="Q1989">
+        <v>0</v>
+      </c>
+      <c r="R1989">
+        <v>0</v>
+      </c>
+      <c r="S1989">
+        <v>0</v>
+      </c>
+      <c r="T1989">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1990" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1990">
+        <v>1</v>
+      </c>
+      <c r="D1990">
+        <v>1</v>
+      </c>
+      <c r="E1990">
+        <v>0</v>
+      </c>
+      <c r="F1990">
+        <v>18</v>
+      </c>
+      <c r="G1990">
+        <v>18</v>
+      </c>
+      <c r="H1990">
+        <v>18</v>
+      </c>
+      <c r="I1990">
+        <v>0</v>
+      </c>
+      <c r="J1990">
+        <v>0</v>
+      </c>
+      <c r="K1990">
+        <v>105.88</v>
+      </c>
+      <c r="L1990">
+        <v>17</v>
+      </c>
+      <c r="M1990">
+        <v>8</v>
+      </c>
+      <c r="N1990">
+        <v>1</v>
+      </c>
+      <c r="O1990">
+        <v>1</v>
+      </c>
+      <c r="P1990">
+        <v>15</v>
+      </c>
+      <c r="Q1990">
+        <v>0</v>
+      </c>
+      <c r="R1990">
+        <v>0</v>
+      </c>
+      <c r="S1990">
+        <v>0</v>
+      </c>
+      <c r="T1990">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1991" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1991">
+        <v>1</v>
+      </c>
+      <c r="D1991">
+        <v>0</v>
+      </c>
+      <c r="E1991">
+        <v>0</v>
+      </c>
+      <c r="F1991">
+        <v>0</v>
+      </c>
+      <c r="I1991">
+        <v>0</v>
+      </c>
+      <c r="J1991">
+        <v>0</v>
+      </c>
+      <c r="L1991">
+        <v>0</v>
+      </c>
+      <c r="M1991">
+        <v>0</v>
+      </c>
+      <c r="N1991">
+        <v>0</v>
+      </c>
+      <c r="O1991">
+        <v>0</v>
+      </c>
+      <c r="P1991">
+        <v>0</v>
+      </c>
+      <c r="Q1991">
+        <v>0</v>
+      </c>
+      <c r="R1991">
+        <v>0</v>
+      </c>
+      <c r="S1991">
+        <v>0</v>
+      </c>
+      <c r="T1991">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1992" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>402</v>
+      </c>
+      <c r="C1992">
+        <v>1</v>
+      </c>
+      <c r="D1992">
+        <v>1</v>
+      </c>
+      <c r="E1992">
+        <v>0</v>
+      </c>
+      <c r="F1992">
+        <v>20</v>
+      </c>
+      <c r="G1992">
+        <v>20</v>
+      </c>
+      <c r="H1992">
+        <v>20</v>
+      </c>
+      <c r="I1992">
+        <v>0</v>
+      </c>
+      <c r="J1992">
+        <v>0</v>
+      </c>
+      <c r="K1992">
+        <v>76.92</v>
+      </c>
+      <c r="L1992">
+        <v>26</v>
+      </c>
+      <c r="M1992">
+        <v>14</v>
+      </c>
+      <c r="N1992">
+        <v>1</v>
+      </c>
+      <c r="O1992">
+        <v>0</v>
+      </c>
+      <c r="P1992">
+        <v>16.809999999999999</v>
+      </c>
+      <c r="Q1992">
+        <v>0</v>
+      </c>
+      <c r="R1992">
+        <v>0</v>
+      </c>
+      <c r="S1992">
+        <v>0</v>
+      </c>
+      <c r="T1992">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1993" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1993">
+        <v>1</v>
+      </c>
+      <c r="D1993">
+        <v>0</v>
+      </c>
+      <c r="E1993">
+        <v>0</v>
+      </c>
+      <c r="F1993">
+        <v>0</v>
+      </c>
+      <c r="I1993">
+        <v>0</v>
+      </c>
+      <c r="J1993">
+        <v>0</v>
+      </c>
+      <c r="L1993">
+        <v>0</v>
+      </c>
+      <c r="M1993">
+        <v>0</v>
+      </c>
+      <c r="N1993">
+        <v>0</v>
+      </c>
+      <c r="O1993">
+        <v>0</v>
+      </c>
+      <c r="P1993">
+        <v>0</v>
+      </c>
+      <c r="Q1993">
+        <v>0</v>
+      </c>
+      <c r="R1993">
+        <v>0</v>
+      </c>
+      <c r="S1993">
+        <v>0</v>
+      </c>
+      <c r="T1993">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1994" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1994">
+        <v>1</v>
+      </c>
+      <c r="D1994">
+        <v>0</v>
+      </c>
+      <c r="E1994">
+        <v>0</v>
+      </c>
+      <c r="F1994">
+        <v>0</v>
+      </c>
+      <c r="I1994">
+        <v>0</v>
+      </c>
+      <c r="J1994">
+        <v>0</v>
+      </c>
+      <c r="L1994">
+        <v>0</v>
+      </c>
+      <c r="M1994">
+        <v>0</v>
+      </c>
+      <c r="N1994">
+        <v>0</v>
+      </c>
+      <c r="O1994">
+        <v>0</v>
+      </c>
+      <c r="P1994">
+        <v>0</v>
+      </c>
+      <c r="Q1994">
+        <v>0</v>
+      </c>
+      <c r="R1994">
+        <v>0</v>
+      </c>
+      <c r="S1994">
+        <v>0</v>
+      </c>
+      <c r="T1994">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1995" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1995">
+        <v>1</v>
+      </c>
+      <c r="D1995">
+        <v>0</v>
+      </c>
+      <c r="E1995">
+        <v>0</v>
+      </c>
+      <c r="F1995">
+        <v>0</v>
+      </c>
+      <c r="I1995">
+        <v>0</v>
+      </c>
+      <c r="J1995">
+        <v>0</v>
+      </c>
+      <c r="L1995">
+        <v>0</v>
+      </c>
+      <c r="M1995">
+        <v>0</v>
+      </c>
+      <c r="N1995">
+        <v>0</v>
+      </c>
+      <c r="O1995">
+        <v>0</v>
+      </c>
+      <c r="P1995">
+        <v>0</v>
+      </c>
+      <c r="Q1995">
+        <v>0</v>
+      </c>
+      <c r="R1995">
+        <v>0</v>
+      </c>
+      <c r="S1995">
+        <v>0</v>
+      </c>
+      <c r="T1995">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1996" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1996">
+        <v>1</v>
+      </c>
+      <c r="D1996">
+        <v>1</v>
+      </c>
+      <c r="E1996">
+        <v>0</v>
+      </c>
+      <c r="F1996">
+        <v>0</v>
+      </c>
+      <c r="G1996">
+        <v>0</v>
+      </c>
+      <c r="H1996">
+        <v>0</v>
+      </c>
+      <c r="I1996">
+        <v>0</v>
+      </c>
+      <c r="J1996">
+        <v>0</v>
+      </c>
+      <c r="K1996">
+        <v>0</v>
+      </c>
+      <c r="L1996">
+        <v>1</v>
+      </c>
+      <c r="M1996">
+        <v>1</v>
+      </c>
+      <c r="N1996">
+        <v>0</v>
+      </c>
+      <c r="O1996">
+        <v>0</v>
+      </c>
+      <c r="P1996">
+        <v>0</v>
+      </c>
+      <c r="Q1996">
+        <v>0</v>
+      </c>
+      <c r="R1996">
+        <v>0</v>
+      </c>
+      <c r="S1996">
+        <v>0</v>
+      </c>
+      <c r="T1996">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1997" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1997">
+        <v>1</v>
+      </c>
+      <c r="D1997">
+        <v>1</v>
+      </c>
+      <c r="E1997">
+        <v>0</v>
+      </c>
+      <c r="F1997">
+        <v>2</v>
+      </c>
+      <c r="G1997">
+        <v>2</v>
+      </c>
+      <c r="H1997">
+        <v>2</v>
+      </c>
+      <c r="I1997">
+        <v>0</v>
+      </c>
+      <c r="J1997">
+        <v>0</v>
+      </c>
+      <c r="K1997">
+        <v>28.57</v>
+      </c>
+      <c r="L1997">
+        <v>7</v>
+      </c>
+      <c r="M1997">
+        <v>6</v>
+      </c>
+      <c r="N1997">
+        <v>0</v>
+      </c>
+      <c r="O1997">
+        <v>0</v>
+      </c>
+      <c r="P1997">
+        <v>1.68</v>
+      </c>
+      <c r="Q1997">
+        <v>1</v>
+      </c>
+      <c r="R1997">
+        <v>0</v>
+      </c>
+      <c r="S1997">
+        <v>0</v>
+      </c>
+      <c r="T1997">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1998" t="s">
+        <v>507</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1998">
+        <v>1</v>
+      </c>
+      <c r="D1998">
+        <v>1</v>
+      </c>
+      <c r="E1998">
+        <v>1</v>
+      </c>
+      <c r="F1998">
+        <v>44</v>
+      </c>
+      <c r="H1998" t="s">
+        <v>367</v>
+      </c>
+      <c r="I1998">
+        <v>0</v>
+      </c>
+      <c r="J1998">
+        <v>0</v>
+      </c>
+      <c r="K1998">
+        <v>122.22</v>
+      </c>
+      <c r="L1998">
+        <v>36</v>
+      </c>
+      <c r="M1998">
+        <v>15</v>
+      </c>
+      <c r="N1998">
+        <v>7</v>
+      </c>
+      <c r="O1998">
+        <v>0</v>
+      </c>
+      <c r="P1998">
+        <v>36.97</v>
+      </c>
+      <c r="Q1998">
+        <v>0</v>
+      </c>
+      <c r="R1998">
+        <v>0</v>
+      </c>
+      <c r="S1998">
+        <v>0</v>
+      </c>
+      <c r="T1998">
         <v>0</v>
       </c>
     </row>
